--- a/docs/Eschool_Functional_Test_Plan.xlsx
+++ b/docs/Eschool_Functional_Test_Plan.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
-  <fileVersion appName="Calc" lowestEdited="4"/>
+  <fileVersion appName="Calc"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
@@ -16,7 +16,7 @@
   </sheets>
   <definedNames>
     <definedName function="false" hidden="true" localSheetId="4" name="_xlnm._FilterDatabase" vbProcedure="false">'Defect Log'!$A$4:$L$204</definedName>
-    <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">'Test Cases'!$A$1:$O$307</definedName>
+    <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">'Test Cases'!$A$1:$O$336</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3047" uniqueCount="1251">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3379" uniqueCount="1386">
   <si>
     <t xml:space="preserve">Eschool - Functional Test Plan</t>
   </si>
@@ -1137,12 +1137,15 @@
     <t xml:space="preserve">PAR-04</t>
   </si>
   <si>
-    <t xml:space="preserve">Fill all sections (contact preferences, notification checkboxes, work info, address)</t>
+    <t xml:space="preserve">Fill all sections (contact preferences, notification checkboxes, address)</t>
   </si>
   <si>
     <t xml:space="preserve">Saved; Edit shows the same values</t>
   </si>
   <si>
+    <t xml:space="preserve">Reworded Oct 15</t>
+  </si>
+  <si>
     <t xml:space="preserve">PAR-05</t>
   </si>
   <si>
@@ -1224,10 +1227,13 @@
     <t xml:space="preserve">PAR-13</t>
   </si>
   <si>
-    <t xml:space="preserve">Delete a parent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confirm, removed; the student's Linked Parents no longer shows them</t>
+    <t xml:space="preserve">Parent with NO linked children</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Delete the parent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confirm, removed (a parent with children is refused: see PAR-17)</t>
   </si>
   <si>
     <t xml:space="preserve">PAR-14</t>
@@ -1404,10 +1410,13 @@
     <t xml:space="preserve">ADM-19</t>
   </si>
   <si>
-    <t xml:space="preserve">Upload a document while registering (pending documents) and Save</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Application saved together with the document(s); documents appear on the application</t>
+    <t xml:space="preserve">In Documents choose the Document type FIRST, then add a file; Save</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The file picker stays disabled until a type is chosen; each file gets that type (changeable per file); application saved together with the document(s)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reworded Oct 16</t>
   </si>
   <si>
     <t xml:space="preserve">ADM-20</t>
@@ -1428,10 +1437,10 @@
     <t xml:space="preserve">Confirm</t>
   </si>
   <si>
-    <t xml:space="preserve">Confirm Admission: fee 500, reference, blood group, religion, category, notes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Moves to Admitted; fee visible in details</t>
+    <t xml:space="preserve">Confirm Admission: fee 500, payment reference, blood group, religion, category, notes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fee amount and Payment reference both show a red star; moves to Admitted; fee visible in details</t>
   </si>
   <si>
     <t xml:space="preserve">ADM-22</t>
@@ -1737,27 +1746,33 @@
     <t xml:space="preserve">ADM-36</t>
   </si>
   <si>
-    <t xml:space="preserve">Fill roll number, admission number, date, class (Active classes only), optional fields</t>
+    <t xml:space="preserve">Leave roll number and admission number BLANK; set date and class (Active classes only)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Accepted; the student gets a roll number like 5A001 and an admission number like ADM-2026-0001</t>
   </si>
   <si>
     <t xml:space="preserve">ADM-37</t>
   </si>
   <si>
-    <t xml:space="preserve">Roll number used in that class</t>
+    <t xml:space="preserve">Roll number typed by hand that is already used in that class</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Type that roll number and submit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Error 'already taken'</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADM-38</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Class at capacity</t>
   </si>
   <si>
     <t xml:space="preserve">Submit</t>
   </si>
   <si>
-    <t xml:space="preserve">Error 'already taken'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ADM-38</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Class at capacity</t>
-  </si>
-  <si>
     <t xml:space="preserve">Error 'is full (n/n)'</t>
   </si>
   <si>
@@ -1800,10 +1815,10 @@
     <t xml:space="preserve">STU-02</t>
   </si>
   <si>
-    <t xml:space="preserve">Filters: Class, Gender, Curriculum, English Level, House, has allergies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Work and combine; allergy filter uses health data</t>
+    <t xml:space="preserve">Filters: Class, Gender, Curriculum, House, has allergies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Work and combine; allergy filter uses health data (no English-level filter any more)</t>
   </si>
   <si>
     <t xml:space="preserve">STU-03</t>
@@ -1821,7 +1836,7 @@
     <t xml:space="preserve">Hover the row actions</t>
   </si>
   <si>
-    <t xml:space="preserve">View, Fee Summary, Attendance Report, Report Card, Linked Parents, Academic History, Edit, Delete</t>
+    <t xml:space="preserve">View, Fee Summary, Attendance Report, Report Card, Linked Parents, Academic History, Edit, Mark as left (no Delete)</t>
   </si>
   <si>
     <t xml:space="preserve">STU-05</t>
@@ -1974,13 +1989,13 @@
     <t xml:space="preserve">An application in status Admitted; a class with free seats</t>
   </si>
   <si>
-    <t xml:space="preserve">Open the application, choose Enrol; enter an admission number, roll number, class and admission date; add the guardians; confirm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Student created as Active in the chosen class; application becomes Enrolled; Student &gt; History tab shows one Active period; parents linked</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reworded: there is no Add Student screen; students are created only by enrolling an admission.</t>
+    <t xml:space="preserve">Open the application, choose Enrol; leave roll and admission number blank; choose class and date; add the guardians; confirm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Student created as Active; roll number (class + section + 3 digits) and admission number (ADM-year-serial) generated; application becomes Enrolled; History tab shows one Active period; parents linked</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reworded: there is no Add Student screen; students are created only by enrolling an admission.; Reworded Oct 16</t>
   </si>
   <si>
     <t xml:space="preserve">STU-23</t>
@@ -2073,10 +2088,13 @@
     <t xml:space="preserve">STU-31</t>
   </si>
   <si>
-    <t xml:space="preserve">Delete a student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confirm, removed; parent links disappear</t>
+    <t xml:space="preserve">Left</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Look for a Delete button on the Students list and on a student's page</t>
+  </si>
+  <si>
+    <t xml:space="preserve">There is none: a student who has gone is closed with Mark as left (see STU-49)</t>
   </si>
   <si>
     <t xml:space="preserve">STU-40</t>
@@ -2331,13 +2349,13 @@
     <t xml:space="preserve">ATT-17</t>
   </si>
   <si>
-    <t xml:space="preserve">Date 8+ days ago</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open that date as Clerk, then as Admin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clerk: locked ('Only an Admin can change attendance older than 7 days'); Admin can edit</t>
+    <t xml:space="preserve">Date 2 or more days ago (older than yesterday)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open that date as Clerk or Teacher, then as Admin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Non-admin: locked ('Only an Admin can change attendance older than 1 day'); Admin can edit</t>
   </si>
   <si>
     <t xml:space="preserve">ATT-18</t>
@@ -3270,10 +3288,10 @@
     <t xml:space="preserve">Supervisor</t>
   </si>
   <si>
-    <t xml:space="preserve">View a student's identity; try to edit it</t>
-  </si>
-  <si>
-    <t xml:space="preserve">View as allowed by the role; editing needs Students.Manage (expect 403 if the role lacks it)</t>
+    <t xml:space="preserve">View a student's identity numbers; try to edit them</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Supervisor can view as the role allows, but cannot edit identity: that needs both Students.Edit and Students.ViewSensitive (expect the edit to be hidden or refused with 403)</t>
   </si>
   <si>
     <t xml:space="preserve">RBAC-04</t>
@@ -3288,10 +3306,10 @@
     <t xml:space="preserve">RBAC-05</t>
   </si>
   <si>
-    <t xml:space="preserve">Open Admissions and click Enrol</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Refused gracefully (403 message), nothing created</t>
+    <t xml:space="preserve">Look for Admissions in the menu; type /admissions in the address bar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Admissions is not in the Teacher menu; the URL redirects away (Teacher has no Admissions.View); nothing created</t>
   </si>
   <si>
     <t xml:space="preserve">RBAC-06</t>
@@ -3568,6 +3586,393 @@
   </si>
   <si>
     <t xml:space="preserve">Consistent and unambiguous; invalid dates refused</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LOG-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Login page</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open the login page</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heading 'Sign in to Escoule'; brand name Escoule on the left; under the Sign in button: 'Forgot your password? Ask your administrator to reset it.'</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New Oct 15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LAY-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Branding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Look at the sidebar header, the footer and the browser tab title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shows 'Escoule' only: no 'Synergein School' and no 'Demo School'</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CMP-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Searchable dropdown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A dropdown with 6 or more options (Nationality, Class on Attendance, a list filter)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open it, type part of an option, use Arrow keys and Enter; press Esc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A search box sits at the top; the list narrows as you type; Enter picks the highlighted option; Esc closes without changing; 'No matches' when nothing fits; dropdowns with fewer than 6 options stay a plain list</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CMP-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fixed tabs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open an Add/Edit full-page form (e.g. Edit Student); click each section tab; clear a required field and Save</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Only the clicked section shows and its tab is highlighted; no sideways scrolling; after a failed save the first tab with an error opens and shows a red count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADM-42</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open Admissions and an application's page</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Column and header read 'Reg No' (not 'REG #')</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADM-43</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Register - class choice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Classes 'Class 1 A' and 'Class 1 B' exist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New Registration &gt; open the Class list</t>
+  </si>
+  <si>
+    <t xml:space="preserve">One entry per class with its academic year (e.g. 'Class 1 (2026-2027)'), no section; hint says the section is chosen at enrolment; list and details show the class without a section after saving</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADM-44</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enrol - section</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Application registered for 'Class 1'</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Click Enrol; the Class list shows every section; pick Class 1 B; enrol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sections are listed (Class 1 A, 1 B); the student is placed in the section you chose</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADM-45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Register - guardian mobile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Add a guardian with a name but no mobile; Save</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mobile has a red star; error 'Mobile is required.'; saves once the mobile is filled (not needed when an existing parent is picked)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADM-46</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Register - hints</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Read the Remarks and Documents sections of New Registration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Remarks says it is an internal note for the office; Documents says no document is needed to register and that the Type of each file is picked from the list</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STU-47</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Citizenship</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Existing student with an old free-text nationality</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Edit &gt; Citizenship</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nationality is a searchable dropdown (Indian and Emirati first); the old value is still shown and kept; there is no 'Second nationality' field</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STU-48</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Removed fields</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open a student's Edit and View pages and the list filters/export</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No EAL code, no Second nationality, no Insurance provider/expiry, no English-level filter or EAL column in the CSV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STU-49</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active student with a class period and attendance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Click 'Mark as left' (list row icon or the student's page) and confirm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Status becomes Left; the class history period closes as Left; the seat is freed; the student leaves the attendance roster; record and history remain; the button disappears</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STU-50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Left - permission</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open Students and a student page</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No 'Mark as left' action (needs Students.Edit); no Delete anywhere</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STU-51</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Left - twice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Student already Left</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Swagger: POST /api/students/{id}/leave again</t>
+  </si>
+  <si>
+    <t xml:space="preserve">422 'This student has already left.'; nothing changes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAR-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Delete - linked children</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parent linked to a student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Refused: 'This parent is linked to N student(s). Unlink them first, then delete the parent.'; the parent still exists</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAR-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Delete - after unlink</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Same parent as PAR-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unlink every child (Linked children), then delete the parent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Delete now works</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAR-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dropdowns and sections</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Add a parent; look at Country of residence, Preferred language and the sections</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Country of residence offers India and United Arab Emirates; Preferred language includes Tamil; there is no 'Work &amp; billing' section in the form, the details page or the header badges</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATT-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rules - 24 hours</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Class teacher; attendance saved for yesterday</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open yesterday and edit it; then open the day before yesterday</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yesterday and today are editable; the day before is locked ('Only an Admin can change attendance older than 1 day'); Admin can still edit it</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADM-47</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confirm - required payment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open Confirm Admission, leave Fee amount and Payment reference empty; click Confirm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Both fields show a red star and the errors 'Fee amount is required.' / 'Payment reference is required.'; nothing is saved; with both filled it moves to Admitted</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New Oct 16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADM-48</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enrol - generated numbers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Two Admitted applications for the same section</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enrol the first with blank numbers, then the second</t>
+  </si>
+  <si>
+    <t xml:space="preserve">First gets ADM-&lt;year&gt;-0001-style and &lt;class&gt;&lt;section&gt;001; second gets 0002 and 002; no gaps or duplicates; section A and B count separately</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADM-49</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enrol - typed number kept</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Admitted application</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Type your own roll and admission numbers and enrol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Your numbers are used as typed; the next blank enrolment continues after the highest serial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADM-50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Register - document type first</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New Registration &gt; Documents: look before choosing a type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A 'What are you uploading?' dropdown (searchable) is above the file picker, which says 'Choose a document type first' and is disabled until a type is chosen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STU-52</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Labels</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check the Students list header, student pages, class page and parent page</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The label is 'Adm No' everywhere (no 'Adm #')</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STU-53</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Photo upload</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Edit student &gt; Basic: Upload photo, choose a JPG under 2 MB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The photo shows at once in the form and in the header of the student page; no Save needed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STU-54</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Photo - wrong file</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Choose a PDF, a renamed .exe, and a JPG over 2 MB, one by one</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Each is refused with a clear message (JPG or PNG only; size shown); the old photo stays</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STU-55</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Photo remove / replace</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A student with a photo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Change photo to another picture; then Remove</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The new picture replaces the old; after Remove the initials show again</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USR-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Employee number generated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Create a teacher and then a clerk, leaving Employee no. blank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">They get EMP-0001 and EMP-0002; a typed number is kept; a duplicate is refused</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LAY-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No link underlines</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parents and Students lists</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Look at names and mobile numbers, and hover over them</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No underline anywhere, hovering included; links are still coloured and clickable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLS-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Demo class set</t>
+  </si>
+  <si>
+    <t xml:space="preserve">After demo-reset and demo-seed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open Classes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LKG, UKG and Class 1 to 5 each have sections A and B, every one with capacity 30</t>
   </si>
   <si>
     <t xml:space="preserve">Test data to set up first</t>
@@ -4597,28 +5002,28 @@
         <v>40</v>
       </c>
       <c r="B5" s="13" t="n">
-        <f aca="false">COUNTIF('Test Cases'!$B$2:$B$307,$A5)</f>
-        <v>23</v>
+        <f aca="false">COUNTIF('Test Cases'!$B$2:$B$336,$A5)</f>
+        <v>26</v>
       </c>
       <c r="C5" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$307,$A5,'Test Cases'!$K$2:$K$307,"Pass")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A5,'Test Cases'!$K$2:$K$336,"Pass")</f>
         <v>0</v>
       </c>
       <c r="D5" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$307,$A5,'Test Cases'!$K$2:$K$307,"Fail")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A5,'Test Cases'!$K$2:$K$336,"Fail")</f>
         <v>0</v>
       </c>
       <c r="E5" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$307,$A5,'Test Cases'!$K$2:$K$307,"Blocked")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A5,'Test Cases'!$K$2:$K$336,"Blocked")</f>
         <v>0</v>
       </c>
       <c r="F5" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$307,$A5,'Test Cases'!$K$2:$K$307,"N/A")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A5,'Test Cases'!$K$2:$K$336,"N/A")</f>
         <v>0</v>
       </c>
       <c r="G5" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$307,$A5,'Test Cases'!$K$2:$K$307,"Not Run")</f>
-        <v>23</v>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A5,'Test Cases'!$K$2:$K$336,"Not Run")</f>
+        <v>26</v>
       </c>
       <c r="H5" s="14" t="n">
         <f aca="false">IFERROR((B5-G5-F5)/(B5-F5),0)</f>
@@ -4634,28 +5039,28 @@
         <v>41</v>
       </c>
       <c r="B6" s="13" t="n">
-        <f aca="false">COUNTIF('Test Cases'!$B$2:$B$307,$A6)</f>
-        <v>10</v>
+        <f aca="false">COUNTIF('Test Cases'!$B$2:$B$336,$A6)</f>
+        <v>12</v>
       </c>
       <c r="C6" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$307,$A6,'Test Cases'!$K$2:$K$307,"Pass")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A6,'Test Cases'!$K$2:$K$336,"Pass")</f>
         <v>0</v>
       </c>
       <c r="D6" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$307,$A6,'Test Cases'!$K$2:$K$307,"Fail")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A6,'Test Cases'!$K$2:$K$336,"Fail")</f>
         <v>0</v>
       </c>
       <c r="E6" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$307,$A6,'Test Cases'!$K$2:$K$307,"Blocked")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A6,'Test Cases'!$K$2:$K$336,"Blocked")</f>
         <v>0</v>
       </c>
       <c r="F6" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$307,$A6,'Test Cases'!$K$2:$K$307,"N/A")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A6,'Test Cases'!$K$2:$K$336,"N/A")</f>
         <v>0</v>
       </c>
       <c r="G6" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$307,$A6,'Test Cases'!$K$2:$K$307,"Not Run")</f>
-        <v>10</v>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A6,'Test Cases'!$K$2:$K$336,"Not Run")</f>
+        <v>12</v>
       </c>
       <c r="H6" s="14" t="n">
         <f aca="false">IFERROR((B6-G6-F6)/(B6-F6),0)</f>
@@ -4671,28 +5076,28 @@
         <v>42</v>
       </c>
       <c r="B7" s="13" t="n">
-        <f aca="false">COUNTIF('Test Cases'!$B$2:$B$307,$A7)</f>
-        <v>14</v>
+        <f aca="false">COUNTIF('Test Cases'!$B$2:$B$336,$A7)</f>
+        <v>15</v>
       </c>
       <c r="C7" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$307,$A7,'Test Cases'!$K$2:$K$307,"Pass")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A7,'Test Cases'!$K$2:$K$336,"Pass")</f>
         <v>0</v>
       </c>
       <c r="D7" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$307,$A7,'Test Cases'!$K$2:$K$307,"Fail")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A7,'Test Cases'!$K$2:$K$336,"Fail")</f>
         <v>0</v>
       </c>
       <c r="E7" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$307,$A7,'Test Cases'!$K$2:$K$307,"Blocked")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A7,'Test Cases'!$K$2:$K$336,"Blocked")</f>
         <v>0</v>
       </c>
       <c r="F7" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$307,$A7,'Test Cases'!$K$2:$K$307,"N/A")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A7,'Test Cases'!$K$2:$K$336,"N/A")</f>
         <v>0</v>
       </c>
       <c r="G7" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$307,$A7,'Test Cases'!$K$2:$K$307,"Not Run")</f>
-        <v>14</v>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A7,'Test Cases'!$K$2:$K$336,"Not Run")</f>
+        <v>15</v>
       </c>
       <c r="H7" s="14" t="n">
         <f aca="false">IFERROR((B7-G7-F7)/(B7-F7),0)</f>
@@ -4708,27 +5113,27 @@
         <v>43</v>
       </c>
       <c r="B8" s="13" t="n">
-        <f aca="false">COUNTIF('Test Cases'!$B$2:$B$307,$A8)</f>
+        <f aca="false">COUNTIF('Test Cases'!$B$2:$B$336,$A8)</f>
         <v>11</v>
       </c>
       <c r="C8" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$307,$A8,'Test Cases'!$K$2:$K$307,"Pass")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A8,'Test Cases'!$K$2:$K$336,"Pass")</f>
         <v>0</v>
       </c>
       <c r="D8" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$307,$A8,'Test Cases'!$K$2:$K$307,"Fail")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A8,'Test Cases'!$K$2:$K$336,"Fail")</f>
         <v>0</v>
       </c>
       <c r="E8" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$307,$A8,'Test Cases'!$K$2:$K$307,"Blocked")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A8,'Test Cases'!$K$2:$K$336,"Blocked")</f>
         <v>0</v>
       </c>
       <c r="F8" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$307,$A8,'Test Cases'!$K$2:$K$307,"N/A")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A8,'Test Cases'!$K$2:$K$336,"N/A")</f>
         <v>0</v>
       </c>
       <c r="G8" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$307,$A8,'Test Cases'!$K$2:$K$307,"Not Run")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A8,'Test Cases'!$K$2:$K$336,"Not Run")</f>
         <v>11</v>
       </c>
       <c r="H8" s="14" t="n">
@@ -4745,27 +5150,27 @@
         <v>44</v>
       </c>
       <c r="B9" s="13" t="n">
-        <f aca="false">COUNTIF('Test Cases'!$B$2:$B$307,$A9)</f>
+        <f aca="false">COUNTIF('Test Cases'!$B$2:$B$336,$A9)</f>
         <v>18</v>
       </c>
       <c r="C9" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$307,$A9,'Test Cases'!$K$2:$K$307,"Pass")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A9,'Test Cases'!$K$2:$K$336,"Pass")</f>
         <v>0</v>
       </c>
       <c r="D9" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$307,$A9,'Test Cases'!$K$2:$K$307,"Fail")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A9,'Test Cases'!$K$2:$K$336,"Fail")</f>
         <v>0</v>
       </c>
       <c r="E9" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$307,$A9,'Test Cases'!$K$2:$K$307,"Blocked")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A9,'Test Cases'!$K$2:$K$336,"Blocked")</f>
         <v>0</v>
       </c>
       <c r="F9" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$307,$A9,'Test Cases'!$K$2:$K$307,"N/A")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A9,'Test Cases'!$K$2:$K$336,"N/A")</f>
         <v>0</v>
       </c>
       <c r="G9" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$307,$A9,'Test Cases'!$K$2:$K$307,"Not Run")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A9,'Test Cases'!$K$2:$K$336,"Not Run")</f>
         <v>18</v>
       </c>
       <c r="H9" s="14" t="n">
@@ -4782,28 +5187,28 @@
         <v>45</v>
       </c>
       <c r="B10" s="13" t="n">
-        <f aca="false">COUNTIF('Test Cases'!$B$2:$B$307,$A10)</f>
-        <v>16</v>
+        <f aca="false">COUNTIF('Test Cases'!$B$2:$B$336,$A10)</f>
+        <v>19</v>
       </c>
       <c r="C10" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$307,$A10,'Test Cases'!$K$2:$K$307,"Pass")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A10,'Test Cases'!$K$2:$K$336,"Pass")</f>
         <v>0</v>
       </c>
       <c r="D10" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$307,$A10,'Test Cases'!$K$2:$K$307,"Fail")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A10,'Test Cases'!$K$2:$K$336,"Fail")</f>
         <v>0</v>
       </c>
       <c r="E10" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$307,$A10,'Test Cases'!$K$2:$K$307,"Blocked")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A10,'Test Cases'!$K$2:$K$336,"Blocked")</f>
         <v>0</v>
       </c>
       <c r="F10" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$307,$A10,'Test Cases'!$K$2:$K$307,"N/A")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A10,'Test Cases'!$K$2:$K$336,"N/A")</f>
         <v>0</v>
       </c>
       <c r="G10" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$307,$A10,'Test Cases'!$K$2:$K$307,"Not Run")</f>
-        <v>16</v>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A10,'Test Cases'!$K$2:$K$336,"Not Run")</f>
+        <v>19</v>
       </c>
       <c r="H10" s="14" t="n">
         <f aca="false">IFERROR((B10-G10-F10)/(B10-F10),0)</f>
@@ -4819,28 +5224,28 @@
         <v>46</v>
       </c>
       <c r="B11" s="13" t="n">
-        <f aca="false">COUNTIF('Test Cases'!$B$2:$B$307,$A11)</f>
-        <v>51</v>
+        <f aca="false">COUNTIF('Test Cases'!$B$2:$B$336,$A11)</f>
+        <v>60</v>
       </c>
       <c r="C11" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$307,$A11,'Test Cases'!$K$2:$K$307,"Pass")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A11,'Test Cases'!$K$2:$K$336,"Pass")</f>
         <v>0</v>
       </c>
       <c r="D11" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$307,$A11,'Test Cases'!$K$2:$K$307,"Fail")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A11,'Test Cases'!$K$2:$K$336,"Fail")</f>
         <v>0</v>
       </c>
       <c r="E11" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$307,$A11,'Test Cases'!$K$2:$K$307,"Blocked")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A11,'Test Cases'!$K$2:$K$336,"Blocked")</f>
         <v>0</v>
       </c>
       <c r="F11" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$307,$A11,'Test Cases'!$K$2:$K$307,"N/A")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A11,'Test Cases'!$K$2:$K$336,"N/A")</f>
         <v>0</v>
       </c>
       <c r="G11" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$307,$A11,'Test Cases'!$K$2:$K$307,"Not Run")</f>
-        <v>51</v>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A11,'Test Cases'!$K$2:$K$336,"Not Run")</f>
+        <v>60</v>
       </c>
       <c r="H11" s="14" t="n">
         <f aca="false">IFERROR((B11-G11-F11)/(B11-F11),0)</f>
@@ -4856,28 +5261,28 @@
         <v>47</v>
       </c>
       <c r="B12" s="13" t="n">
-        <f aca="false">COUNTIF('Test Cases'!$B$2:$B$307,$A12)</f>
-        <v>36</v>
+        <f aca="false">COUNTIF('Test Cases'!$B$2:$B$336,$A12)</f>
+        <v>45</v>
       </c>
       <c r="C12" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$307,$A12,'Test Cases'!$K$2:$K$307,"Pass")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A12,'Test Cases'!$K$2:$K$336,"Pass")</f>
         <v>0</v>
       </c>
       <c r="D12" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$307,$A12,'Test Cases'!$K$2:$K$307,"Fail")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A12,'Test Cases'!$K$2:$K$336,"Fail")</f>
         <v>0</v>
       </c>
       <c r="E12" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$307,$A12,'Test Cases'!$K$2:$K$307,"Blocked")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A12,'Test Cases'!$K$2:$K$336,"Blocked")</f>
         <v>0</v>
       </c>
       <c r="F12" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$307,$A12,'Test Cases'!$K$2:$K$307,"N/A")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A12,'Test Cases'!$K$2:$K$336,"N/A")</f>
         <v>0</v>
       </c>
       <c r="G12" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$307,$A12,'Test Cases'!$K$2:$K$307,"Not Run")</f>
-        <v>36</v>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A12,'Test Cases'!$K$2:$K$336,"Not Run")</f>
+        <v>45</v>
       </c>
       <c r="H12" s="14" t="n">
         <f aca="false">IFERROR((B12-G12-F12)/(B12-F12),0)</f>
@@ -4893,28 +5298,28 @@
         <v>48</v>
       </c>
       <c r="B13" s="13" t="n">
-        <f aca="false">COUNTIF('Test Cases'!$B$2:$B$307,$A13)</f>
-        <v>25</v>
+        <f aca="false">COUNTIF('Test Cases'!$B$2:$B$336,$A13)</f>
+        <v>26</v>
       </c>
       <c r="C13" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$307,$A13,'Test Cases'!$K$2:$K$307,"Pass")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A13,'Test Cases'!$K$2:$K$336,"Pass")</f>
         <v>0</v>
       </c>
       <c r="D13" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$307,$A13,'Test Cases'!$K$2:$K$307,"Fail")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A13,'Test Cases'!$K$2:$K$336,"Fail")</f>
         <v>0</v>
       </c>
       <c r="E13" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$307,$A13,'Test Cases'!$K$2:$K$307,"Blocked")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A13,'Test Cases'!$K$2:$K$336,"Blocked")</f>
         <v>0</v>
       </c>
       <c r="F13" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$307,$A13,'Test Cases'!$K$2:$K$307,"N/A")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A13,'Test Cases'!$K$2:$K$336,"N/A")</f>
         <v>0</v>
       </c>
       <c r="G13" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$307,$A13,'Test Cases'!$K$2:$K$307,"Not Run")</f>
-        <v>25</v>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A13,'Test Cases'!$K$2:$K$336,"Not Run")</f>
+        <v>26</v>
       </c>
       <c r="H13" s="14" t="n">
         <f aca="false">IFERROR((B13-G13-F13)/(B13-F13),0)</f>
@@ -4930,27 +5335,27 @@
         <v>49</v>
       </c>
       <c r="B14" s="13" t="n">
-        <f aca="false">COUNTIF('Test Cases'!$B$2:$B$307,$A14)</f>
+        <f aca="false">COUNTIF('Test Cases'!$B$2:$B$336,$A14)</f>
         <v>23</v>
       </c>
       <c r="C14" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$307,$A14,'Test Cases'!$K$2:$K$307,"Pass")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A14,'Test Cases'!$K$2:$K$336,"Pass")</f>
         <v>0</v>
       </c>
       <c r="D14" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$307,$A14,'Test Cases'!$K$2:$K$307,"Fail")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A14,'Test Cases'!$K$2:$K$336,"Fail")</f>
         <v>0</v>
       </c>
       <c r="E14" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$307,$A14,'Test Cases'!$K$2:$K$307,"Blocked")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A14,'Test Cases'!$K$2:$K$336,"Blocked")</f>
         <v>0</v>
       </c>
       <c r="F14" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$307,$A14,'Test Cases'!$K$2:$K$307,"N/A")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A14,'Test Cases'!$K$2:$K$336,"N/A")</f>
         <v>0</v>
       </c>
       <c r="G14" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$307,$A14,'Test Cases'!$K$2:$K$307,"Not Run")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A14,'Test Cases'!$K$2:$K$336,"Not Run")</f>
         <v>23</v>
       </c>
       <c r="H14" s="14" t="n">
@@ -4967,28 +5372,28 @@
         <v>50</v>
       </c>
       <c r="B15" s="13" t="n">
-        <f aca="false">COUNTIF('Test Cases'!$B$2:$B$307,$A15)</f>
-        <v>22</v>
+        <f aca="false">COUNTIF('Test Cases'!$B$2:$B$336,$A15)</f>
+        <v>23</v>
       </c>
       <c r="C15" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$307,$A15,'Test Cases'!$K$2:$K$307,"Pass")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A15,'Test Cases'!$K$2:$K$336,"Pass")</f>
         <v>0</v>
       </c>
       <c r="D15" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$307,$A15,'Test Cases'!$K$2:$K$307,"Fail")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A15,'Test Cases'!$K$2:$K$336,"Fail")</f>
         <v>0</v>
       </c>
       <c r="E15" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$307,$A15,'Test Cases'!$K$2:$K$307,"Blocked")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A15,'Test Cases'!$K$2:$K$336,"Blocked")</f>
         <v>0</v>
       </c>
       <c r="F15" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$307,$A15,'Test Cases'!$K$2:$K$307,"N/A")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A15,'Test Cases'!$K$2:$K$336,"N/A")</f>
         <v>0</v>
       </c>
       <c r="G15" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$307,$A15,'Test Cases'!$K$2:$K$307,"Not Run")</f>
-        <v>22</v>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A15,'Test Cases'!$K$2:$K$336,"Not Run")</f>
+        <v>23</v>
       </c>
       <c r="H15" s="14" t="n">
         <f aca="false">IFERROR((B15-G15-F15)/(B15-F15),0)</f>
@@ -5004,27 +5409,27 @@
         <v>51</v>
       </c>
       <c r="B16" s="13" t="n">
-        <f aca="false">COUNTIF('Test Cases'!$B$2:$B$307,$A16)</f>
+        <f aca="false">COUNTIF('Test Cases'!$B$2:$B$336,$A16)</f>
         <v>11</v>
       </c>
       <c r="C16" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$307,$A16,'Test Cases'!$K$2:$K$307,"Pass")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A16,'Test Cases'!$K$2:$K$336,"Pass")</f>
         <v>0</v>
       </c>
       <c r="D16" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$307,$A16,'Test Cases'!$K$2:$K$307,"Fail")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A16,'Test Cases'!$K$2:$K$336,"Fail")</f>
         <v>0</v>
       </c>
       <c r="E16" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$307,$A16,'Test Cases'!$K$2:$K$307,"Blocked")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A16,'Test Cases'!$K$2:$K$336,"Blocked")</f>
         <v>0</v>
       </c>
       <c r="F16" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$307,$A16,'Test Cases'!$K$2:$K$307,"N/A")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A16,'Test Cases'!$K$2:$K$336,"N/A")</f>
         <v>0</v>
       </c>
       <c r="G16" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$307,$A16,'Test Cases'!$K$2:$K$307,"Not Run")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A16,'Test Cases'!$K$2:$K$336,"Not Run")</f>
         <v>11</v>
       </c>
       <c r="H16" s="14" t="n">
@@ -5041,27 +5446,27 @@
         <v>52</v>
       </c>
       <c r="B17" s="13" t="n">
-        <f aca="false">COUNTIF('Test Cases'!$B$2:$B$307,$A17)</f>
+        <f aca="false">COUNTIF('Test Cases'!$B$2:$B$336,$A17)</f>
         <v>9</v>
       </c>
       <c r="C17" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$307,$A17,'Test Cases'!$K$2:$K$307,"Pass")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A17,'Test Cases'!$K$2:$K$336,"Pass")</f>
         <v>0</v>
       </c>
       <c r="D17" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$307,$A17,'Test Cases'!$K$2:$K$307,"Fail")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A17,'Test Cases'!$K$2:$K$336,"Fail")</f>
         <v>0</v>
       </c>
       <c r="E17" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$307,$A17,'Test Cases'!$K$2:$K$307,"Blocked")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A17,'Test Cases'!$K$2:$K$336,"Blocked")</f>
         <v>0</v>
       </c>
       <c r="F17" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$307,$A17,'Test Cases'!$K$2:$K$307,"N/A")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A17,'Test Cases'!$K$2:$K$336,"N/A")</f>
         <v>0</v>
       </c>
       <c r="G17" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$307,$A17,'Test Cases'!$K$2:$K$307,"Not Run")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A17,'Test Cases'!$K$2:$K$336,"Not Run")</f>
         <v>9</v>
       </c>
       <c r="H17" s="14" t="n">
@@ -5078,27 +5483,27 @@
         <v>53</v>
       </c>
       <c r="B18" s="13" t="n">
-        <f aca="false">COUNTIF('Test Cases'!$B$2:$B$307,$A18)</f>
+        <f aca="false">COUNTIF('Test Cases'!$B$2:$B$336,$A18)</f>
         <v>9</v>
       </c>
       <c r="C18" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$307,$A18,'Test Cases'!$K$2:$K$307,"Pass")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A18,'Test Cases'!$K$2:$K$336,"Pass")</f>
         <v>0</v>
       </c>
       <c r="D18" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$307,$A18,'Test Cases'!$K$2:$K$307,"Fail")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A18,'Test Cases'!$K$2:$K$336,"Fail")</f>
         <v>0</v>
       </c>
       <c r="E18" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$307,$A18,'Test Cases'!$K$2:$K$307,"Blocked")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A18,'Test Cases'!$K$2:$K$336,"Blocked")</f>
         <v>0</v>
       </c>
       <c r="F18" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$307,$A18,'Test Cases'!$K$2:$K$307,"N/A")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A18,'Test Cases'!$K$2:$K$336,"N/A")</f>
         <v>0</v>
       </c>
       <c r="G18" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$307,$A18,'Test Cases'!$K$2:$K$307,"Not Run")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A18,'Test Cases'!$K$2:$K$336,"Not Run")</f>
         <v>9</v>
       </c>
       <c r="H18" s="14" t="n">
@@ -5115,27 +5520,27 @@
         <v>54</v>
       </c>
       <c r="B19" s="13" t="n">
-        <f aca="false">COUNTIF('Test Cases'!$B$2:$B$307,$A19)</f>
+        <f aca="false">COUNTIF('Test Cases'!$B$2:$B$336,$A19)</f>
         <v>1</v>
       </c>
       <c r="C19" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$307,$A19,'Test Cases'!$K$2:$K$307,"Pass")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A19,'Test Cases'!$K$2:$K$336,"Pass")</f>
         <v>0</v>
       </c>
       <c r="D19" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$307,$A19,'Test Cases'!$K$2:$K$307,"Fail")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A19,'Test Cases'!$K$2:$K$336,"Fail")</f>
         <v>0</v>
       </c>
       <c r="E19" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$307,$A19,'Test Cases'!$K$2:$K$307,"Blocked")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A19,'Test Cases'!$K$2:$K$336,"Blocked")</f>
         <v>0</v>
       </c>
       <c r="F19" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$307,$A19,'Test Cases'!$K$2:$K$307,"N/A")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A19,'Test Cases'!$K$2:$K$336,"N/A")</f>
         <v>0</v>
       </c>
       <c r="G19" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$307,$A19,'Test Cases'!$K$2:$K$307,"Not Run")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A19,'Test Cases'!$K$2:$K$336,"Not Run")</f>
         <v>1</v>
       </c>
       <c r="H19" s="14" t="n">
@@ -5152,27 +5557,27 @@
         <v>55</v>
       </c>
       <c r="B20" s="13" t="n">
-        <f aca="false">COUNTIF('Test Cases'!$B$2:$B$307,$A20)</f>
+        <f aca="false">COUNTIF('Test Cases'!$B$2:$B$336,$A20)</f>
         <v>8</v>
       </c>
       <c r="C20" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$307,$A20,'Test Cases'!$K$2:$K$307,"Pass")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A20,'Test Cases'!$K$2:$K$336,"Pass")</f>
         <v>0</v>
       </c>
       <c r="D20" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$307,$A20,'Test Cases'!$K$2:$K$307,"Fail")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A20,'Test Cases'!$K$2:$K$336,"Fail")</f>
         <v>0</v>
       </c>
       <c r="E20" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$307,$A20,'Test Cases'!$K$2:$K$307,"Blocked")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A20,'Test Cases'!$K$2:$K$336,"Blocked")</f>
         <v>0</v>
       </c>
       <c r="F20" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$307,$A20,'Test Cases'!$K$2:$K$307,"N/A")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A20,'Test Cases'!$K$2:$K$336,"N/A")</f>
         <v>0</v>
       </c>
       <c r="G20" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$307,$A20,'Test Cases'!$K$2:$K$307,"Not Run")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A20,'Test Cases'!$K$2:$K$336,"Not Run")</f>
         <v>8</v>
       </c>
       <c r="H20" s="14" t="n">
@@ -5189,27 +5594,27 @@
         <v>56</v>
       </c>
       <c r="B21" s="13" t="n">
-        <f aca="false">COUNTIF('Test Cases'!$B$2:$B$307,$A21)</f>
+        <f aca="false">COUNTIF('Test Cases'!$B$2:$B$336,$A21)</f>
         <v>11</v>
       </c>
       <c r="C21" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$307,$A21,'Test Cases'!$K$2:$K$307,"Pass")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A21,'Test Cases'!$K$2:$K$336,"Pass")</f>
         <v>0</v>
       </c>
       <c r="D21" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$307,$A21,'Test Cases'!$K$2:$K$307,"Fail")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A21,'Test Cases'!$K$2:$K$336,"Fail")</f>
         <v>0</v>
       </c>
       <c r="E21" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$307,$A21,'Test Cases'!$K$2:$K$307,"Blocked")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A21,'Test Cases'!$K$2:$K$336,"Blocked")</f>
         <v>0</v>
       </c>
       <c r="F21" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$307,$A21,'Test Cases'!$K$2:$K$307,"N/A")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A21,'Test Cases'!$K$2:$K$336,"N/A")</f>
         <v>0</v>
       </c>
       <c r="G21" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$307,$A21,'Test Cases'!$K$2:$K$307,"Not Run")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A21,'Test Cases'!$K$2:$K$336,"Not Run")</f>
         <v>11</v>
       </c>
       <c r="H21" s="14" t="n">
@@ -5226,27 +5631,27 @@
         <v>57</v>
       </c>
       <c r="B22" s="13" t="n">
-        <f aca="false">COUNTIF('Test Cases'!$B$2:$B$307,$A22)</f>
+        <f aca="false">COUNTIF('Test Cases'!$B$2:$B$336,$A22)</f>
         <v>8</v>
       </c>
       <c r="C22" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$307,$A22,'Test Cases'!$K$2:$K$307,"Pass")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A22,'Test Cases'!$K$2:$K$336,"Pass")</f>
         <v>0</v>
       </c>
       <c r="D22" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$307,$A22,'Test Cases'!$K$2:$K$307,"Fail")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A22,'Test Cases'!$K$2:$K$336,"Fail")</f>
         <v>0</v>
       </c>
       <c r="E22" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$307,$A22,'Test Cases'!$K$2:$K$307,"Blocked")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A22,'Test Cases'!$K$2:$K$336,"Blocked")</f>
         <v>0</v>
       </c>
       <c r="F22" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$307,$A22,'Test Cases'!$K$2:$K$307,"N/A")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A22,'Test Cases'!$K$2:$K$336,"N/A")</f>
         <v>0</v>
       </c>
       <c r="G22" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$307,$A22,'Test Cases'!$K$2:$K$307,"Not Run")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A22,'Test Cases'!$K$2:$K$336,"Not Run")</f>
         <v>8</v>
       </c>
       <c r="H22" s="14" t="n">
@@ -5264,7 +5669,7 @@
       </c>
       <c r="B23" s="16" t="n">
         <f aca="false">SUM(B5:B22)</f>
-        <v>306</v>
+        <v>335</v>
       </c>
       <c r="C23" s="16" t="n">
         <f aca="false">SUM(C5:C22)</f>
@@ -5284,7 +5689,7 @@
       </c>
       <c r="G23" s="16" t="n">
         <f aca="false">SUM(G5:G22)</f>
-        <v>306</v>
+        <v>335</v>
       </c>
       <c r="H23" s="17" t="n">
         <f aca="false">IFERROR((B23-G23-F23)/(B23-F23),0)</f>
@@ -5305,8 +5710,8 @@
         <v>60</v>
       </c>
       <c r="B27" s="8" t="n">
-        <f aca="false">COUNTIF('Test Cases'!$E$2:$E$307,"High")</f>
-        <v>168</v>
+        <f aca="false">COUNTIF('Test Cases'!$E$2:$E$336,"High")</f>
+        <v>177</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5314,7 +5719,7 @@
         <v>61</v>
       </c>
       <c r="B28" s="8" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$E$2:$E$307,"High",'Test Cases'!$K$2:$K$307,"Fail")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$E$2:$E$336,"High",'Test Cases'!$K$2:$K$336,"Fail")</f>
         <v>0</v>
       </c>
     </row>
@@ -5323,8 +5728,8 @@
         <v>62</v>
       </c>
       <c r="B29" s="8" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$E$2:$E$307,"High",'Test Cases'!$K$2:$K$307,"Not Run")</f>
-        <v>168</v>
+        <f aca="false">COUNTIFS('Test Cases'!$E$2:$E$336,"High",'Test Cases'!$K$2:$K$336,"Not Run")</f>
+        <v>177</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5366,7 +5771,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:O307"/>
+  <dimension ref="A1:O336"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10"/>
@@ -8296,11 +8701,13 @@
       <c r="L81" s="19"/>
       <c r="M81" s="20"/>
       <c r="N81" s="19"/>
-      <c r="O81" s="19"/>
+      <c r="O81" s="19" t="s">
+        <v>371</v>
+      </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="18" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B82" s="18" t="s">
         <v>45</v>
@@ -8319,10 +8726,10 @@
       </c>
       <c r="G82" s="18"/>
       <c r="H82" s="18" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="I82" s="18" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="J82" s="19"/>
       <c r="K82" s="19" t="s">
@@ -8335,7 +8742,7 @@
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="18" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B83" s="18" t="s">
         <v>45</v>
@@ -8357,7 +8764,7 @@
         <v>247</v>
       </c>
       <c r="I83" s="18" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="J83" s="19"/>
       <c r="K83" s="19" t="s">
@@ -8370,13 +8777,13 @@
     </row>
     <row r="84" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A84" s="18" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B84" s="18" t="s">
         <v>45</v>
       </c>
       <c r="C84" s="18" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="D84" s="18" t="s">
         <v>93</v>
@@ -8388,13 +8795,13 @@
         <v>94</v>
       </c>
       <c r="G84" s="18" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="H84" s="18" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="I84" s="18" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="J84" s="19"/>
       <c r="K84" s="19" t="s">
@@ -8407,13 +8814,13 @@
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A85" s="18" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B85" s="18" t="s">
         <v>45</v>
       </c>
       <c r="C85" s="18" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="D85" s="18" t="s">
         <v>93</v>
@@ -8426,10 +8833,10 @@
       </c>
       <c r="G85" s="18"/>
       <c r="H85" s="18" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="I85" s="18" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="J85" s="19"/>
       <c r="K85" s="19" t="s">
@@ -8442,13 +8849,13 @@
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A86" s="18" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B86" s="18" t="s">
         <v>45</v>
       </c>
       <c r="C86" s="18" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="D86" s="18" t="s">
         <v>82</v>
@@ -8461,10 +8868,10 @@
       </c>
       <c r="G86" s="18"/>
       <c r="H86" s="18" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="I86" s="18" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="J86" s="19"/>
       <c r="K86" s="19" t="s">
@@ -8477,13 +8884,13 @@
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A87" s="18" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B87" s="18" t="s">
         <v>45</v>
       </c>
       <c r="C87" s="18" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="D87" s="18" t="s">
         <v>93</v>
@@ -8495,13 +8902,13 @@
         <v>94</v>
       </c>
       <c r="G87" s="18" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H87" s="18" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="I87" s="18" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="J87" s="19"/>
       <c r="K87" s="19" t="s">
@@ -8514,13 +8921,13 @@
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="18" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B88" s="18" t="s">
         <v>45</v>
       </c>
       <c r="C88" s="18" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="D88" s="18" t="s">
         <v>93</v>
@@ -8533,7 +8940,7 @@
       </c>
       <c r="G88" s="18"/>
       <c r="H88" s="18" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="I88" s="18" t="s">
         <v>295</v>
@@ -8549,13 +8956,13 @@
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="18" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B89" s="18" t="s">
         <v>45</v>
       </c>
       <c r="C89" s="18" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="D89" s="18" t="s">
         <v>110</v>
@@ -8568,10 +8975,10 @@
       </c>
       <c r="G89" s="18"/>
       <c r="H89" s="18" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="I89" s="18" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="J89" s="19"/>
       <c r="K89" s="19" t="s">
@@ -8584,7 +8991,7 @@
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="18" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B90" s="18" t="s">
         <v>45</v>
@@ -8601,12 +9008,14 @@
       <c r="F90" s="18" t="s">
         <v>94</v>
       </c>
-      <c r="G90" s="18"/>
+      <c r="G90" s="18" t="s">
+        <v>399</v>
+      </c>
       <c r="H90" s="18" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="I90" s="18" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="J90" s="19"/>
       <c r="K90" s="19" t="s">
@@ -8615,11 +9024,13 @@
       <c r="L90" s="19"/>
       <c r="M90" s="20"/>
       <c r="N90" s="19"/>
-      <c r="O90" s="19"/>
+      <c r="O90" s="19" t="s">
+        <v>371</v>
+      </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="18" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="B91" s="18" t="s">
         <v>45</v>
@@ -8628,7 +9039,7 @@
         <v>106</v>
       </c>
       <c r="D91" s="18" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="E91" s="18" t="s">
         <v>111</v>
@@ -8637,13 +9048,13 @@
         <v>94</v>
       </c>
       <c r="G91" s="18" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="H91" s="18" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="I91" s="18" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="J91" s="19"/>
       <c r="K91" s="19" t="s">
@@ -8656,7 +9067,7 @@
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="18" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="B92" s="18" t="s">
         <v>45</v>
@@ -8675,10 +9086,10 @@
       </c>
       <c r="G92" s="18"/>
       <c r="H92" s="18" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="I92" s="18" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="J92" s="19"/>
       <c r="K92" s="19" t="s">
@@ -8691,13 +9102,13 @@
     </row>
     <row r="93" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A93" s="18" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="B93" s="18" t="s">
         <v>45</v>
       </c>
       <c r="C93" s="18" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="D93" s="18" t="s">
         <v>132</v>
@@ -8706,16 +9117,16 @@
         <v>83</v>
       </c>
       <c r="F93" s="18" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="G93" s="18" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="H93" s="18" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="I93" s="18" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="J93" s="19"/>
       <c r="K93" s="19" t="s">
@@ -8728,13 +9139,13 @@
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A94" s="18" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="B94" s="18" t="s">
         <v>46</v>
       </c>
       <c r="C94" s="18" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="D94" s="18" t="s">
         <v>93</v>
@@ -8747,10 +9158,10 @@
       </c>
       <c r="G94" s="18"/>
       <c r="H94" s="18" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="I94" s="18" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="J94" s="19"/>
       <c r="K94" s="19" t="s">
@@ -8763,13 +9174,13 @@
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A95" s="18" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="B95" s="18" t="s">
         <v>46</v>
       </c>
       <c r="C95" s="18" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="D95" s="18" t="s">
         <v>93</v>
@@ -8782,10 +9193,10 @@
       </c>
       <c r="G95" s="18"/>
       <c r="H95" s="18" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="I95" s="18" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="J95" s="19"/>
       <c r="K95" s="19" t="s">
@@ -8798,13 +9209,13 @@
     </row>
     <row r="96" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A96" s="18" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="B96" s="18" t="s">
         <v>46</v>
       </c>
       <c r="C96" s="18" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="D96" s="18" t="s">
         <v>93</v>
@@ -8817,7 +9228,7 @@
       </c>
       <c r="G96" s="18"/>
       <c r="H96" s="18" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="I96" s="18" t="s">
         <v>292</v>
@@ -8833,13 +9244,13 @@
     </row>
     <row r="97" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A97" s="18" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="B97" s="18" t="s">
         <v>46</v>
       </c>
       <c r="C97" s="18" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="D97" s="18" t="s">
         <v>93</v>
@@ -8851,13 +9262,13 @@
         <v>94</v>
       </c>
       <c r="G97" s="18" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="H97" s="18" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="I97" s="18" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="J97" s="19"/>
       <c r="K97" s="19" t="s">
@@ -8870,13 +9281,13 @@
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A98" s="18" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="B98" s="18" t="s">
         <v>46</v>
       </c>
       <c r="C98" s="18" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="D98" s="18" t="s">
         <v>93</v>
@@ -8892,7 +9303,7 @@
         <v>197</v>
       </c>
       <c r="I98" s="18" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="J98" s="19"/>
       <c r="K98" s="19" t="s">
@@ -8905,13 +9316,13 @@
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A99" s="18" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="B99" s="18" t="s">
         <v>46</v>
       </c>
       <c r="C99" s="18" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="D99" s="18" t="s">
         <v>106</v>
@@ -8924,10 +9335,10 @@
       </c>
       <c r="G99" s="18"/>
       <c r="H99" s="18" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="I99" s="18" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="J99" s="19"/>
       <c r="K99" s="19" t="s">
@@ -8940,13 +9351,13 @@
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A100" s="18" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="B100" s="18" t="s">
         <v>46</v>
       </c>
       <c r="C100" s="18" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="D100" s="18" t="s">
         <v>93</v>
@@ -8959,10 +9370,10 @@
       </c>
       <c r="G100" s="18"/>
       <c r="H100" s="18" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="I100" s="18" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="J100" s="19"/>
       <c r="K100" s="19" t="s">
@@ -8975,13 +9386,13 @@
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A101" s="18" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="B101" s="18" t="s">
         <v>46</v>
       </c>
       <c r="C101" s="18" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="D101" s="18" t="s">
         <v>93</v>
@@ -8994,10 +9405,10 @@
       </c>
       <c r="G101" s="18"/>
       <c r="H101" s="18" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="I101" s="18" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="J101" s="19"/>
       <c r="K101" s="19" t="s">
@@ -9010,13 +9421,13 @@
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A102" s="18" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="B102" s="18" t="s">
         <v>46</v>
       </c>
       <c r="C102" s="18" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="D102" s="18" t="s">
         <v>106</v>
@@ -9029,10 +9440,10 @@
       </c>
       <c r="G102" s="18"/>
       <c r="H102" s="18" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="I102" s="18" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="J102" s="19"/>
       <c r="K102" s="19" t="s">
@@ -9045,13 +9456,13 @@
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A103" s="18" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="B103" s="18" t="s">
         <v>46</v>
       </c>
       <c r="C103" s="18" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="D103" s="18" t="s">
         <v>106</v>
@@ -9064,10 +9475,10 @@
       </c>
       <c r="G103" s="18"/>
       <c r="H103" s="18" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="I103" s="18" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="J103" s="19"/>
       <c r="K103" s="19" t="s">
@@ -9080,13 +9491,13 @@
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A104" s="18" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="B104" s="18" t="s">
         <v>46</v>
       </c>
       <c r="C104" s="18" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="D104" s="18" t="s">
         <v>93</v>
@@ -9099,10 +9510,10 @@
       </c>
       <c r="G104" s="18"/>
       <c r="H104" s="18" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="I104" s="18" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="J104" s="19"/>
       <c r="K104" s="19" t="s">
@@ -9115,13 +9526,13 @@
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A105" s="18" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="B105" s="18" t="s">
         <v>46</v>
       </c>
       <c r="C105" s="18" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="D105" s="18" t="s">
         <v>93</v>
@@ -9134,10 +9545,10 @@
       </c>
       <c r="G105" s="18"/>
       <c r="H105" s="18" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="I105" s="18" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="J105" s="19"/>
       <c r="K105" s="19" t="s">
@@ -9150,13 +9561,13 @@
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A106" s="18" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="B106" s="18" t="s">
         <v>46</v>
       </c>
       <c r="C106" s="18" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="D106" s="18" t="s">
         <v>106</v>
@@ -9169,10 +9580,10 @@
       </c>
       <c r="G106" s="18"/>
       <c r="H106" s="18" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="I106" s="18" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="J106" s="19"/>
       <c r="K106" s="19" t="s">
@@ -9185,13 +9596,13 @@
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A107" s="18" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="B107" s="18" t="s">
         <v>46</v>
       </c>
       <c r="C107" s="18" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="D107" s="18" t="s">
         <v>93</v>
@@ -9204,10 +9615,10 @@
       </c>
       <c r="G107" s="18"/>
       <c r="H107" s="18" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="I107" s="18" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="J107" s="19"/>
       <c r="K107" s="19" t="s">
@@ -9220,13 +9631,13 @@
     </row>
     <row r="108" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A108" s="18" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="B108" s="18" t="s">
         <v>46</v>
       </c>
       <c r="C108" s="18" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="D108" s="18" t="s">
         <v>93</v>
@@ -9239,10 +9650,10 @@
       </c>
       <c r="G108" s="18"/>
       <c r="H108" s="18" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="I108" s="18" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="J108" s="19"/>
       <c r="K108" s="19" t="s">
@@ -9251,11 +9662,13 @@
       <c r="L108" s="19"/>
       <c r="M108" s="20"/>
       <c r="N108" s="19"/>
-      <c r="O108" s="19"/>
+      <c r="O108" s="19" t="s">
+        <v>462</v>
+      </c>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A109" s="18" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="B109" s="18" t="s">
         <v>46</v>
@@ -9273,13 +9686,13 @@
         <v>94</v>
       </c>
       <c r="G109" s="18" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="H109" s="18" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="I109" s="18" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="J109" s="19"/>
       <c r="K109" s="19" t="s">
@@ -9292,13 +9705,13 @@
     </row>
     <row r="110" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A110" s="18" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="B110" s="18" t="s">
         <v>46</v>
       </c>
       <c r="C110" s="18" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="D110" s="18" t="s">
         <v>93</v>
@@ -9310,13 +9723,13 @@
         <v>94</v>
       </c>
       <c r="G110" s="18" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="H110" s="18" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="I110" s="18" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="J110" s="19"/>
       <c r="K110" s="19" t="s">
@@ -9325,17 +9738,19 @@
       <c r="L110" s="19"/>
       <c r="M110" s="20"/>
       <c r="N110" s="19"/>
-      <c r="O110" s="19"/>
+      <c r="O110" s="19" t="s">
+        <v>462</v>
+      </c>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A111" s="18" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="B111" s="18" t="s">
         <v>46</v>
       </c>
       <c r="C111" s="18" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="D111" s="18" t="s">
         <v>106</v>
@@ -9348,10 +9763,10 @@
       </c>
       <c r="G111" s="18"/>
       <c r="H111" s="18" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="I111" s="18" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="J111" s="19"/>
       <c r="K111" s="19" t="s">
@@ -9364,13 +9779,13 @@
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A112" s="18" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="B112" s="18" t="s">
         <v>46</v>
       </c>
       <c r="C112" s="18" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="D112" s="18" t="s">
         <v>110</v>
@@ -9383,10 +9798,10 @@
       </c>
       <c r="G112" s="18"/>
       <c r="H112" s="18" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="I112" s="18" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="J112" s="19"/>
       <c r="K112" s="19" t="s">
@@ -9399,13 +9814,13 @@
     </row>
     <row r="113" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A113" s="18" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="B113" s="18" t="s">
         <v>46</v>
       </c>
       <c r="C113" s="18" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="D113" s="18" t="s">
         <v>93</v>
@@ -9418,10 +9833,10 @@
       </c>
       <c r="G113" s="18"/>
       <c r="H113" s="18" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="I113" s="18" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="J113" s="19"/>
       <c r="K113" s="19" t="s">
@@ -9434,13 +9849,13 @@
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A114" s="18" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="B114" s="18" t="s">
         <v>46</v>
       </c>
       <c r="C114" s="18" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="D114" s="18" t="s">
         <v>82</v>
@@ -9452,13 +9867,13 @@
         <v>94</v>
       </c>
       <c r="G114" s="18" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="H114" s="18" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="I114" s="18" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="J114" s="19"/>
       <c r="K114" s="19" t="s">
@@ -9471,7 +9886,7 @@
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A115" s="18" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="B115" s="18" t="s">
         <v>46</v>
@@ -9490,10 +9905,10 @@
       </c>
       <c r="G115" s="18"/>
       <c r="H115" s="18" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="I115" s="18" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="J115" s="19"/>
       <c r="K115" s="19" t="s">
@@ -9506,13 +9921,13 @@
     </row>
     <row r="116" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A116" s="18" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="B116" s="18" t="s">
         <v>46</v>
       </c>
       <c r="C116" s="18" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="D116" s="18" t="s">
         <v>93</v>
@@ -9524,13 +9939,13 @@
         <v>94</v>
       </c>
       <c r="G116" s="18" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="H116" s="18" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="I116" s="18" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="J116" s="19"/>
       <c r="K116" s="19" t="s">
@@ -9543,13 +9958,13 @@
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A117" s="18" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="B117" s="18" t="s">
         <v>46</v>
       </c>
       <c r="C117" s="18" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="D117" s="18" t="s">
         <v>93</v>
@@ -9562,10 +9977,10 @@
       </c>
       <c r="G117" s="18"/>
       <c r="H117" s="18" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="I117" s="18" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="J117" s="19"/>
       <c r="K117" s="19" t="s">
@@ -9578,13 +9993,13 @@
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A118" s="18" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="B118" s="18" t="s">
         <v>46</v>
       </c>
       <c r="C118" s="18" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="D118" s="18" t="s">
         <v>106</v>
@@ -9597,10 +10012,10 @@
       </c>
       <c r="G118" s="18"/>
       <c r="H118" s="18" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="I118" s="18" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="J118" s="19"/>
       <c r="K118" s="19" t="s">
@@ -9613,13 +10028,13 @@
     </row>
     <row r="119" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A119" s="18" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="B119" s="18" t="s">
         <v>46</v>
       </c>
       <c r="C119" s="18" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="D119" s="18" t="s">
         <v>93</v>
@@ -9632,10 +10047,10 @@
       </c>
       <c r="G119" s="18"/>
       <c r="H119" s="18" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="I119" s="18" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="J119" s="19"/>
       <c r="K119" s="19" t="s">
@@ -9648,13 +10063,13 @@
     </row>
     <row r="120" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A120" s="18" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="B120" s="18" t="s">
         <v>46</v>
       </c>
       <c r="C120" s="18" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="D120" s="18" t="s">
         <v>93</v>
@@ -9666,13 +10081,13 @@
         <v>94</v>
       </c>
       <c r="G120" s="18" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="H120" s="18" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="I120" s="18" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="J120" s="19"/>
       <c r="K120" s="19" t="s">
@@ -9685,13 +10100,13 @@
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A121" s="18" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="B121" s="18" t="s">
         <v>46</v>
       </c>
       <c r="C121" s="18" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="D121" s="18" t="s">
         <v>93</v>
@@ -9703,13 +10118,13 @@
         <v>94</v>
       </c>
       <c r="G121" s="18" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="H121" s="18" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="I121" s="18" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="J121" s="19"/>
       <c r="K121" s="19" t="s">
@@ -9722,13 +10137,13 @@
     </row>
     <row r="122" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A122" s="18" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="B122" s="18" t="s">
         <v>46</v>
       </c>
       <c r="C122" s="18" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="D122" s="18" t="s">
         <v>82</v>
@@ -9741,10 +10156,10 @@
       </c>
       <c r="G122" s="18"/>
       <c r="H122" s="18" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="I122" s="18" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="J122" s="19"/>
       <c r="K122" s="19" t="s">
@@ -9757,13 +10172,13 @@
     </row>
     <row r="123" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A123" s="18" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="B123" s="18" t="s">
         <v>46</v>
       </c>
       <c r="C123" s="18" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="D123" s="18" t="s">
         <v>93</v>
@@ -9775,13 +10190,13 @@
         <v>94</v>
       </c>
       <c r="G123" s="18" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="H123" s="18" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="I123" s="18" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="J123" s="19"/>
       <c r="K123" s="19" t="s">
@@ -9794,13 +10209,13 @@
     </row>
     <row r="124" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A124" s="18" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="B124" s="18" t="s">
         <v>46</v>
       </c>
       <c r="C124" s="18" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="D124" s="18" t="s">
         <v>132</v>
@@ -9809,16 +10224,16 @@
         <v>83</v>
       </c>
       <c r="F124" s="18" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="G124" s="18" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="H124" s="18" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="I124" s="18" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="J124" s="19"/>
       <c r="K124" s="19" t="s">
@@ -9831,13 +10246,13 @@
     </row>
     <row r="125" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A125" s="18" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="B125" s="18" t="s">
         <v>46</v>
       </c>
       <c r="C125" s="18" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="D125" s="18" t="s">
         <v>132</v>
@@ -9846,16 +10261,16 @@
         <v>83</v>
       </c>
       <c r="F125" s="18" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="G125" s="18" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="H125" s="18" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="I125" s="18" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="J125" s="19"/>
       <c r="K125" s="19" t="s">
@@ -9868,13 +10283,13 @@
     </row>
     <row r="126" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A126" s="18" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="B126" s="18" t="s">
         <v>46</v>
       </c>
       <c r="C126" s="18" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="D126" s="18" t="s">
         <v>132</v>
@@ -9883,16 +10298,16 @@
         <v>83</v>
       </c>
       <c r="F126" s="18" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="G126" s="18" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="H126" s="18" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="I126" s="18" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="J126" s="19"/>
       <c r="K126" s="19" t="s">
@@ -9905,13 +10320,13 @@
     </row>
     <row r="127" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A127" s="18" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="B127" s="18" t="s">
         <v>46</v>
       </c>
       <c r="C127" s="18" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="D127" s="18" t="s">
         <v>93</v>
@@ -9923,13 +10338,13 @@
         <v>94</v>
       </c>
       <c r="G127" s="18" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="H127" s="18" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="I127" s="18" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="J127" s="19"/>
       <c r="K127" s="19" t="s">
@@ -9942,13 +10357,13 @@
     </row>
     <row r="128" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A128" s="18" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="B128" s="18" t="s">
         <v>46</v>
       </c>
       <c r="C128" s="18" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="D128" s="18" t="s">
         <v>93</v>
@@ -9961,10 +10376,10 @@
       </c>
       <c r="G128" s="18"/>
       <c r="H128" s="18" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="I128" s="18" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="J128" s="19"/>
       <c r="K128" s="19" t="s">
@@ -9977,13 +10392,13 @@
     </row>
     <row r="129" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A129" s="18" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="B129" s="18" t="s">
         <v>46</v>
       </c>
       <c r="C129" s="18" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="D129" s="18" t="s">
         <v>93</v>
@@ -9995,13 +10410,13 @@
         <v>94</v>
       </c>
       <c r="G129" s="18" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="H129" s="18" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="I129" s="18" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="J129" s="19"/>
       <c r="K129" s="19" t="s">
@@ -10014,13 +10429,13 @@
     </row>
     <row r="130" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A130" s="18" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="B130" s="18" t="s">
         <v>46</v>
       </c>
       <c r="C130" s="18" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="D130" s="18" t="s">
         <v>82</v>
@@ -10032,13 +10447,13 @@
         <v>94</v>
       </c>
       <c r="G130" s="18" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="H130" s="18" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="I130" s="18" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="J130" s="19"/>
       <c r="K130" s="19" t="s">
@@ -10051,13 +10466,13 @@
     </row>
     <row r="131" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A131" s="18" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="B131" s="18" t="s">
         <v>46</v>
       </c>
       <c r="C131" s="18" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="D131" s="18" t="s">
         <v>93</v>
@@ -10069,13 +10484,13 @@
         <v>94</v>
       </c>
       <c r="G131" s="18" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="H131" s="18" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="I131" s="18" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="J131" s="19"/>
       <c r="K131" s="19" t="s">
@@ -10088,13 +10503,13 @@
     </row>
     <row r="132" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A132" s="18" t="s">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="B132" s="18" t="s">
         <v>46</v>
       </c>
       <c r="C132" s="18" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="D132" s="18" t="s">
         <v>93</v>
@@ -10106,13 +10521,13 @@
         <v>94</v>
       </c>
       <c r="G132" s="18" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="H132" s="18" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="I132" s="18" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="J132" s="19"/>
       <c r="K132" s="19" t="s">
@@ -10125,13 +10540,13 @@
     </row>
     <row r="133" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A133" s="18" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="B133" s="18" t="s">
         <v>46</v>
       </c>
       <c r="C133" s="18" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="D133" s="18" t="s">
         <v>93</v>
@@ -10143,13 +10558,13 @@
         <v>94</v>
       </c>
       <c r="G133" s="18" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="H133" s="18" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="I133" s="18" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="J133" s="19"/>
       <c r="K133" s="19" t="s">
@@ -10162,13 +10577,13 @@
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A134" s="18" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="B134" s="18" t="s">
         <v>46</v>
       </c>
       <c r="C134" s="18" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="D134" s="18" t="s">
         <v>93</v>
@@ -10181,10 +10596,10 @@
       </c>
       <c r="G134" s="18"/>
       <c r="H134" s="18" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="I134" s="18" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="J134" s="19"/>
       <c r="K134" s="19" t="s">
@@ -10197,13 +10612,13 @@
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A135" s="18" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="B135" s="18" t="s">
         <v>46</v>
       </c>
       <c r="C135" s="18" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="D135" s="18" t="s">
         <v>93</v>
@@ -10215,13 +10630,13 @@
         <v>94</v>
       </c>
       <c r="G135" s="18" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="H135" s="18" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="I135" s="18" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="J135" s="19"/>
       <c r="K135" s="19" t="s">
@@ -10234,13 +10649,13 @@
     </row>
     <row r="136" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A136" s="18" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="B136" s="18" t="s">
         <v>46</v>
       </c>
       <c r="C136" s="18" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="D136" s="18" t="s">
         <v>106</v>
@@ -10252,13 +10667,13 @@
         <v>94</v>
       </c>
       <c r="G136" s="18" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="H136" s="18" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="I136" s="18" t="s">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="J136" s="19"/>
       <c r="K136" s="19" t="s">
@@ -10271,13 +10686,13 @@
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A137" s="18" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="B137" s="18" t="s">
         <v>46</v>
       </c>
       <c r="C137" s="18" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="D137" s="18" t="s">
         <v>106</v>
@@ -10290,10 +10705,10 @@
       </c>
       <c r="G137" s="18"/>
       <c r="H137" s="18" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="I137" s="18" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="J137" s="19"/>
       <c r="K137" s="19" t="s">
@@ -10306,13 +10721,13 @@
     </row>
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A138" s="18" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="B138" s="18" t="s">
         <v>46</v>
       </c>
       <c r="C138" s="18" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="D138" s="18" t="s">
         <v>93</v>
@@ -10325,10 +10740,10 @@
       </c>
       <c r="G138" s="18"/>
       <c r="H138" s="18" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="I138" s="18" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="J138" s="19"/>
       <c r="K138" s="19" t="s">
@@ -10341,13 +10756,13 @@
     </row>
     <row r="139" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A139" s="18" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="B139" s="18" t="s">
         <v>46</v>
       </c>
       <c r="C139" s="18" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="D139" s="18" t="s">
         <v>93</v>
@@ -10360,10 +10775,10 @@
       </c>
       <c r="G139" s="18"/>
       <c r="H139" s="18" t="s">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="I139" s="18" t="s">
-        <v>233</v>
+        <v>573</v>
       </c>
       <c r="J139" s="19"/>
       <c r="K139" s="19" t="s">
@@ -10372,17 +10787,19 @@
       <c r="L139" s="19"/>
       <c r="M139" s="20"/>
       <c r="N139" s="19"/>
-      <c r="O139" s="19"/>
+      <c r="O139" s="19" t="s">
+        <v>462</v>
+      </c>
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A140" s="18" t="s">
-        <v>570</v>
+        <v>574</v>
       </c>
       <c r="B140" s="18" t="s">
         <v>46</v>
       </c>
       <c r="C140" s="18" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="D140" s="18" t="s">
         <v>82</v>
@@ -10394,13 +10811,13 @@
         <v>94</v>
       </c>
       <c r="G140" s="18" t="s">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="H140" s="18" t="s">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="I140" s="18" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="J140" s="19"/>
       <c r="K140" s="19" t="s">
@@ -10409,17 +10826,19 @@
       <c r="L140" s="19"/>
       <c r="M140" s="20"/>
       <c r="N140" s="19"/>
-      <c r="O140" s="19"/>
+      <c r="O140" s="19" t="s">
+        <v>462</v>
+      </c>
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A141" s="18" t="s">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="B141" s="18" t="s">
         <v>46</v>
       </c>
       <c r="C141" s="18" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="D141" s="18" t="s">
         <v>82</v>
@@ -10431,13 +10850,13 @@
         <v>94</v>
       </c>
       <c r="G141" s="18" t="s">
-        <v>575</v>
+        <v>579</v>
       </c>
       <c r="H141" s="18" t="s">
-        <v>572</v>
+        <v>580</v>
       </c>
       <c r="I141" s="18" t="s">
-        <v>576</v>
+        <v>581</v>
       </c>
       <c r="J141" s="19"/>
       <c r="K141" s="19" t="s">
@@ -10450,13 +10869,13 @@
     </row>
     <row r="142" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A142" s="18" t="s">
-        <v>577</v>
+        <v>582</v>
       </c>
       <c r="B142" s="18" t="s">
         <v>46</v>
       </c>
       <c r="C142" s="18" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="D142" s="18" t="s">
         <v>93</v>
@@ -10469,10 +10888,10 @@
       </c>
       <c r="G142" s="18"/>
       <c r="H142" s="18" t="s">
-        <v>578</v>
+        <v>583</v>
       </c>
       <c r="I142" s="18" t="s">
-        <v>579</v>
+        <v>584</v>
       </c>
       <c r="J142" s="19"/>
       <c r="K142" s="19" t="s">
@@ -10485,13 +10904,13 @@
     </row>
     <row r="143" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A143" s="18" t="s">
-        <v>580</v>
+        <v>585</v>
       </c>
       <c r="B143" s="18" t="s">
         <v>46</v>
       </c>
       <c r="C143" s="18" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="D143" s="18" t="s">
         <v>82</v>
@@ -10504,10 +10923,10 @@
       </c>
       <c r="G143" s="18"/>
       <c r="H143" s="18" t="s">
-        <v>581</v>
+        <v>586</v>
       </c>
       <c r="I143" s="18" t="s">
-        <v>582</v>
+        <v>587</v>
       </c>
       <c r="J143" s="19"/>
       <c r="K143" s="19" t="s">
@@ -10520,13 +10939,13 @@
     </row>
     <row r="144" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A144" s="18" t="s">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="B144" s="18" t="s">
         <v>46</v>
       </c>
       <c r="C144" s="18" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="D144" s="18" t="s">
         <v>82</v>
@@ -10539,10 +10958,10 @@
       </c>
       <c r="G144" s="18"/>
       <c r="H144" s="18" t="s">
-        <v>584</v>
+        <v>589</v>
       </c>
       <c r="I144" s="18" t="s">
-        <v>585</v>
+        <v>590</v>
       </c>
       <c r="J144" s="19"/>
       <c r="K144" s="19" t="s">
@@ -10555,7 +10974,7 @@
     </row>
     <row r="145" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A145" s="18" t="s">
-        <v>586</v>
+        <v>591</v>
       </c>
       <c r="B145" s="18" t="s">
         <v>47</v>
@@ -10574,10 +10993,10 @@
       </c>
       <c r="G145" s="18"/>
       <c r="H145" s="18" t="s">
-        <v>587</v>
+        <v>592</v>
       </c>
       <c r="I145" s="18" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="J145" s="19"/>
       <c r="K145" s="19" t="s">
@@ -10590,7 +11009,7 @@
     </row>
     <row r="146" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A146" s="18" t="s">
-        <v>589</v>
+        <v>594</v>
       </c>
       <c r="B146" s="18" t="s">
         <v>47</v>
@@ -10609,10 +11028,10 @@
       </c>
       <c r="G146" s="18"/>
       <c r="H146" s="18" t="s">
-        <v>590</v>
+        <v>595</v>
       </c>
       <c r="I146" s="18" t="s">
-        <v>591</v>
+        <v>596</v>
       </c>
       <c r="J146" s="19"/>
       <c r="K146" s="19" t="s">
@@ -10621,11 +11040,13 @@
       <c r="L146" s="19"/>
       <c r="M146" s="20"/>
       <c r="N146" s="19"/>
-      <c r="O146" s="19"/>
+      <c r="O146" s="19" t="s">
+        <v>371</v>
+      </c>
     </row>
     <row r="147" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A147" s="18" t="s">
-        <v>592</v>
+        <v>597</v>
       </c>
       <c r="B147" s="18" t="s">
         <v>47</v>
@@ -10644,10 +11065,10 @@
       </c>
       <c r="G147" s="18"/>
       <c r="H147" s="18" t="s">
-        <v>593</v>
+        <v>598</v>
       </c>
       <c r="I147" s="18" t="s">
-        <v>594</v>
+        <v>599</v>
       </c>
       <c r="J147" s="19"/>
       <c r="K147" s="19" t="s">
@@ -10660,7 +11081,7 @@
     </row>
     <row r="148" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A148" s="18" t="s">
-        <v>595</v>
+        <v>600</v>
       </c>
       <c r="B148" s="18" t="s">
         <v>47</v>
@@ -10679,10 +11100,10 @@
       </c>
       <c r="G148" s="18"/>
       <c r="H148" s="18" t="s">
-        <v>596</v>
+        <v>601</v>
       </c>
       <c r="I148" s="18" t="s">
-        <v>597</v>
+        <v>602</v>
       </c>
       <c r="J148" s="19"/>
       <c r="K148" s="19" t="s">
@@ -10691,11 +11112,13 @@
       <c r="L148" s="19"/>
       <c r="M148" s="20"/>
       <c r="N148" s="19"/>
-      <c r="O148" s="19"/>
+      <c r="O148" s="19" t="s">
+        <v>371</v>
+      </c>
     </row>
     <row r="149" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A149" s="18" t="s">
-        <v>598</v>
+        <v>603</v>
       </c>
       <c r="B149" s="18" t="s">
         <v>47</v>
@@ -10714,10 +11137,10 @@
       </c>
       <c r="G149" s="18"/>
       <c r="H149" s="18" t="s">
-        <v>599</v>
+        <v>604</v>
       </c>
       <c r="I149" s="18" t="s">
-        <v>600</v>
+        <v>605</v>
       </c>
       <c r="J149" s="19"/>
       <c r="K149" s="19" t="s">
@@ -10730,7 +11153,7 @@
     </row>
     <row r="150" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A150" s="18" t="s">
-        <v>601</v>
+        <v>606</v>
       </c>
       <c r="B150" s="18" t="s">
         <v>47</v>
@@ -10752,7 +11175,7 @@
         <v>197</v>
       </c>
       <c r="I150" s="18" t="s">
-        <v>602</v>
+        <v>607</v>
       </c>
       <c r="J150" s="19"/>
       <c r="K150" s="19" t="s">
@@ -10765,7 +11188,7 @@
     </row>
     <row r="151" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A151" s="18" t="s">
-        <v>603</v>
+        <v>608</v>
       </c>
       <c r="B151" s="18" t="s">
         <v>47</v>
@@ -10783,13 +11206,13 @@
         <v>94</v>
       </c>
       <c r="G151" s="18" t="s">
-        <v>604</v>
+        <v>609</v>
       </c>
       <c r="H151" s="18" t="s">
-        <v>605</v>
+        <v>610</v>
       </c>
       <c r="I151" s="18" t="s">
-        <v>606</v>
+        <v>611</v>
       </c>
       <c r="J151" s="19"/>
       <c r="K151" s="19" t="s">
@@ -10802,7 +11225,7 @@
     </row>
     <row r="152" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A152" s="18" t="s">
-        <v>607</v>
+        <v>612</v>
       </c>
       <c r="B152" s="18" t="s">
         <v>47</v>
@@ -10820,13 +11243,13 @@
         <v>94</v>
       </c>
       <c r="G152" s="18" t="s">
-        <v>608</v>
+        <v>613</v>
       </c>
       <c r="H152" s="18" t="s">
-        <v>609</v>
+        <v>614</v>
       </c>
       <c r="I152" s="18" t="s">
-        <v>610</v>
+        <v>615</v>
       </c>
       <c r="J152" s="19"/>
       <c r="K152" s="19" t="s">
@@ -10839,7 +11262,7 @@
     </row>
     <row r="153" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A153" s="18" t="s">
-        <v>611</v>
+        <v>616</v>
       </c>
       <c r="B153" s="18" t="s">
         <v>47</v>
@@ -10858,10 +11281,10 @@
       </c>
       <c r="G153" s="18"/>
       <c r="H153" s="18" t="s">
-        <v>612</v>
+        <v>617</v>
       </c>
       <c r="I153" s="18" t="s">
-        <v>613</v>
+        <v>618</v>
       </c>
       <c r="J153" s="19"/>
       <c r="K153" s="19" t="s">
@@ -10874,7 +11297,7 @@
     </row>
     <row r="154" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A154" s="18" t="s">
-        <v>614</v>
+        <v>619</v>
       </c>
       <c r="B154" s="18" t="s">
         <v>47</v>
@@ -10893,10 +11316,10 @@
       </c>
       <c r="G154" s="18"/>
       <c r="H154" s="18" t="s">
-        <v>615</v>
+        <v>620</v>
       </c>
       <c r="I154" s="18" t="s">
-        <v>616</v>
+        <v>621</v>
       </c>
       <c r="J154" s="19"/>
       <c r="K154" s="19" t="s">
@@ -10909,7 +11332,7 @@
     </row>
     <row r="155" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A155" s="18" t="s">
-        <v>617</v>
+        <v>622</v>
       </c>
       <c r="B155" s="18" t="s">
         <v>47</v>
@@ -10928,10 +11351,10 @@
       </c>
       <c r="G155" s="18"/>
       <c r="H155" s="18" t="s">
-        <v>618</v>
+        <v>623</v>
       </c>
       <c r="I155" s="18" t="s">
-        <v>619</v>
+        <v>624</v>
       </c>
       <c r="J155" s="19"/>
       <c r="K155" s="19" t="s">
@@ -10944,7 +11367,7 @@
     </row>
     <row r="156" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A156" s="18" t="s">
-        <v>620</v>
+        <v>625</v>
       </c>
       <c r="B156" s="18" t="s">
         <v>47</v>
@@ -10963,10 +11386,10 @@
       </c>
       <c r="G156" s="18"/>
       <c r="H156" s="18" t="s">
-        <v>621</v>
+        <v>626</v>
       </c>
       <c r="I156" s="18" t="s">
-        <v>622</v>
+        <v>627</v>
       </c>
       <c r="J156" s="19"/>
       <c r="K156" s="19" t="s">
@@ -10979,7 +11402,7 @@
     </row>
     <row r="157" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A157" s="18" t="s">
-        <v>623</v>
+        <v>628</v>
       </c>
       <c r="B157" s="18" t="s">
         <v>47</v>
@@ -10998,7 +11421,7 @@
       </c>
       <c r="G157" s="18"/>
       <c r="H157" s="18" t="s">
-        <v>624</v>
+        <v>629</v>
       </c>
       <c r="I157" s="18" t="s">
         <v>280</v>
@@ -11014,7 +11437,7 @@
     </row>
     <row r="158" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A158" s="18" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="B158" s="18" t="s">
         <v>47</v>
@@ -11033,10 +11456,10 @@
       </c>
       <c r="G158" s="18"/>
       <c r="H158" s="18" t="s">
-        <v>626</v>
+        <v>631</v>
       </c>
       <c r="I158" s="18" t="s">
-        <v>627</v>
+        <v>632</v>
       </c>
       <c r="J158" s="19"/>
       <c r="K158" s="19" t="s">
@@ -11049,7 +11472,7 @@
     </row>
     <row r="159" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A159" s="18" t="s">
-        <v>628</v>
+        <v>633</v>
       </c>
       <c r="B159" s="18" t="s">
         <v>47</v>
@@ -11068,10 +11491,10 @@
       </c>
       <c r="G159" s="18"/>
       <c r="H159" s="18" t="s">
-        <v>629</v>
+        <v>634</v>
       </c>
       <c r="I159" s="18" t="s">
-        <v>630</v>
+        <v>635</v>
       </c>
       <c r="J159" s="19"/>
       <c r="K159" s="19" t="s">
@@ -11084,13 +11507,13 @@
     </row>
     <row r="160" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A160" s="18" t="s">
-        <v>631</v>
+        <v>636</v>
       </c>
       <c r="B160" s="18" t="s">
         <v>47</v>
       </c>
       <c r="C160" s="18" t="s">
-        <v>632</v>
+        <v>637</v>
       </c>
       <c r="D160" s="18" t="s">
         <v>132</v>
@@ -11103,10 +11526,10 @@
       </c>
       <c r="G160" s="18"/>
       <c r="H160" s="18" t="s">
-        <v>633</v>
+        <v>638</v>
       </c>
       <c r="I160" s="18" t="s">
-        <v>634</v>
+        <v>639</v>
       </c>
       <c r="J160" s="19"/>
       <c r="K160" s="19" t="s">
@@ -11119,13 +11542,13 @@
     </row>
     <row r="161" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A161" s="18" t="s">
-        <v>635</v>
+        <v>640</v>
       </c>
       <c r="B161" s="18" t="s">
         <v>47</v>
       </c>
       <c r="C161" s="18" t="s">
-        <v>632</v>
+        <v>637</v>
       </c>
       <c r="D161" s="18" t="s">
         <v>132</v>
@@ -11138,10 +11561,10 @@
       </c>
       <c r="G161" s="18"/>
       <c r="H161" s="18" t="s">
-        <v>636</v>
+        <v>641</v>
       </c>
       <c r="I161" s="18" t="s">
-        <v>637</v>
+        <v>642</v>
       </c>
       <c r="J161" s="19"/>
       <c r="K161" s="19" t="s">
@@ -11154,13 +11577,13 @@
     </row>
     <row r="162" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A162" s="18" t="s">
-        <v>638</v>
+        <v>643</v>
       </c>
       <c r="B162" s="18" t="s">
         <v>47</v>
       </c>
       <c r="C162" s="18" t="s">
-        <v>632</v>
+        <v>637</v>
       </c>
       <c r="D162" s="18" t="s">
         <v>106</v>
@@ -11173,10 +11596,10 @@
       </c>
       <c r="G162" s="18"/>
       <c r="H162" s="18" t="s">
-        <v>639</v>
+        <v>644</v>
       </c>
       <c r="I162" s="18" t="s">
-        <v>640</v>
+        <v>645</v>
       </c>
       <c r="J162" s="19"/>
       <c r="K162" s="19" t="s">
@@ -11189,13 +11612,13 @@
     </row>
     <row r="163" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A163" s="18" t="s">
-        <v>641</v>
+        <v>646</v>
       </c>
       <c r="B163" s="18" t="s">
         <v>47</v>
       </c>
       <c r="C163" s="18" t="s">
-        <v>632</v>
+        <v>637</v>
       </c>
       <c r="D163" s="18" t="s">
         <v>82</v>
@@ -11207,13 +11630,13 @@
         <v>94</v>
       </c>
       <c r="G163" s="18" t="s">
-        <v>642</v>
+        <v>647</v>
       </c>
       <c r="H163" s="18" t="s">
-        <v>643</v>
+        <v>648</v>
       </c>
       <c r="I163" s="18" t="s">
-        <v>644</v>
+        <v>649</v>
       </c>
       <c r="J163" s="19"/>
       <c r="K163" s="19" t="s">
@@ -11226,13 +11649,13 @@
     </row>
     <row r="164" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A164" s="18" t="s">
-        <v>645</v>
+        <v>650</v>
       </c>
       <c r="B164" s="18" t="s">
         <v>47</v>
       </c>
       <c r="C164" s="18" t="s">
-        <v>646</v>
+        <v>651</v>
       </c>
       <c r="D164" s="18" t="s">
         <v>93</v>
@@ -11244,13 +11667,13 @@
         <v>94</v>
       </c>
       <c r="G164" s="18" t="s">
-        <v>647</v>
+        <v>652</v>
       </c>
       <c r="H164" s="18" t="s">
-        <v>648</v>
+        <v>653</v>
       </c>
       <c r="I164" s="18" t="s">
-        <v>649</v>
+        <v>654</v>
       </c>
       <c r="J164" s="19"/>
       <c r="K164" s="19" t="s">
@@ -11260,18 +11683,18 @@
       <c r="M164" s="20"/>
       <c r="N164" s="19"/>
       <c r="O164" s="19" t="s">
-        <v>650</v>
+        <v>655</v>
       </c>
     </row>
     <row r="165" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A165" s="18" t="s">
-        <v>651</v>
+        <v>656</v>
       </c>
       <c r="B165" s="18" t="s">
         <v>47</v>
       </c>
       <c r="C165" s="18" t="s">
-        <v>646</v>
+        <v>651</v>
       </c>
       <c r="D165" s="18" t="s">
         <v>82</v>
@@ -11283,13 +11706,13 @@
         <v>94</v>
       </c>
       <c r="G165" s="18" t="s">
-        <v>652</v>
+        <v>657</v>
       </c>
       <c r="H165" s="18" t="s">
-        <v>653</v>
+        <v>658</v>
       </c>
       <c r="I165" s="18" t="s">
-        <v>654</v>
+        <v>659</v>
       </c>
       <c r="J165" s="19"/>
       <c r="K165" s="19" t="s">
@@ -11299,12 +11722,12 @@
       <c r="M165" s="20"/>
       <c r="N165" s="19"/>
       <c r="O165" s="19" t="s">
-        <v>655</v>
+        <v>660</v>
       </c>
     </row>
     <row r="166" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A166" s="18" t="s">
-        <v>656</v>
+        <v>661</v>
       </c>
       <c r="B166" s="18" t="s">
         <v>47</v>
@@ -11323,10 +11746,10 @@
       </c>
       <c r="G166" s="18"/>
       <c r="H166" s="18" t="s">
-        <v>657</v>
+        <v>662</v>
       </c>
       <c r="I166" s="18" t="s">
-        <v>658</v>
+        <v>663</v>
       </c>
       <c r="J166" s="19"/>
       <c r="K166" s="19" t="s">
@@ -11339,13 +11762,13 @@
     </row>
     <row r="167" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A167" s="18" t="s">
-        <v>659</v>
+        <v>664</v>
       </c>
       <c r="B167" s="18" t="s">
         <v>47</v>
       </c>
       <c r="C167" s="18" t="s">
-        <v>660</v>
+        <v>665</v>
       </c>
       <c r="D167" s="18" t="s">
         <v>93</v>
@@ -11357,13 +11780,13 @@
         <v>94</v>
       </c>
       <c r="G167" s="18" t="s">
-        <v>661</v>
+        <v>666</v>
       </c>
       <c r="H167" s="18" t="s">
-        <v>662</v>
+        <v>667</v>
       </c>
       <c r="I167" s="18" t="s">
-        <v>663</v>
+        <v>668</v>
       </c>
       <c r="J167" s="19"/>
       <c r="K167" s="19" t="s">
@@ -11376,13 +11799,13 @@
     </row>
     <row r="168" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A168" s="18" t="s">
-        <v>664</v>
+        <v>669</v>
       </c>
       <c r="B168" s="18" t="s">
         <v>47</v>
       </c>
       <c r="C168" s="18" t="s">
-        <v>660</v>
+        <v>665</v>
       </c>
       <c r="D168" s="18" t="s">
         <v>82</v>
@@ -11395,10 +11818,10 @@
       </c>
       <c r="G168" s="18"/>
       <c r="H168" s="18" t="s">
-        <v>665</v>
+        <v>670</v>
       </c>
       <c r="I168" s="18" t="s">
-        <v>666</v>
+        <v>671</v>
       </c>
       <c r="J168" s="19"/>
       <c r="K168" s="19" t="s">
@@ -11411,13 +11834,13 @@
     </row>
     <row r="169" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A169" s="18" t="s">
-        <v>667</v>
+        <v>672</v>
       </c>
       <c r="B169" s="18" t="s">
         <v>47</v>
       </c>
       <c r="C169" s="18" t="s">
-        <v>660</v>
+        <v>665</v>
       </c>
       <c r="D169" s="18" t="s">
         <v>82</v>
@@ -11429,13 +11852,13 @@
         <v>94</v>
       </c>
       <c r="G169" s="18" t="s">
-        <v>668</v>
+        <v>673</v>
       </c>
       <c r="H169" s="18" t="s">
-        <v>669</v>
+        <v>674</v>
       </c>
       <c r="I169" s="18" t="s">
-        <v>670</v>
+        <v>675</v>
       </c>
       <c r="J169" s="19"/>
       <c r="K169" s="19" t="s">
@@ -11448,7 +11871,7 @@
     </row>
     <row r="170" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A170" s="18" t="s">
-        <v>671</v>
+        <v>676</v>
       </c>
       <c r="B170" s="18" t="s">
         <v>47</v>
@@ -11467,10 +11890,10 @@
       </c>
       <c r="G170" s="18"/>
       <c r="H170" s="18" t="s">
-        <v>672</v>
+        <v>677</v>
       </c>
       <c r="I170" s="18" t="s">
-        <v>673</v>
+        <v>678</v>
       </c>
       <c r="J170" s="19"/>
       <c r="K170" s="19" t="s">
@@ -11483,7 +11906,7 @@
     </row>
     <row r="171" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A171" s="18" t="s">
-        <v>674</v>
+        <v>679</v>
       </c>
       <c r="B171" s="18" t="s">
         <v>47</v>
@@ -11502,10 +11925,10 @@
       </c>
       <c r="G171" s="18"/>
       <c r="H171" s="18" t="s">
-        <v>675</v>
+        <v>680</v>
       </c>
       <c r="I171" s="18" t="s">
-        <v>676</v>
+        <v>681</v>
       </c>
       <c r="J171" s="19"/>
       <c r="K171" s="19" t="s">
@@ -11518,7 +11941,7 @@
     </row>
     <row r="172" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A172" s="18" t="s">
-        <v>677</v>
+        <v>682</v>
       </c>
       <c r="B172" s="18" t="s">
         <v>47</v>
@@ -11536,13 +11959,13 @@
         <v>94</v>
       </c>
       <c r="G172" s="18" t="s">
-        <v>604</v>
+        <v>609</v>
       </c>
       <c r="H172" s="18" t="s">
-        <v>678</v>
+        <v>683</v>
       </c>
       <c r="I172" s="18" t="s">
-        <v>679</v>
+        <v>684</v>
       </c>
       <c r="J172" s="19"/>
       <c r="K172" s="19" t="s">
@@ -11555,13 +11978,13 @@
     </row>
     <row r="173" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A173" s="18" t="s">
-        <v>680</v>
+        <v>685</v>
       </c>
       <c r="B173" s="18" t="s">
         <v>47</v>
       </c>
       <c r="C173" s="18" t="s">
-        <v>254</v>
+        <v>686</v>
       </c>
       <c r="D173" s="18" t="s">
         <v>93</v>
@@ -11574,10 +11997,10 @@
       </c>
       <c r="G173" s="18"/>
       <c r="H173" s="18" t="s">
-        <v>681</v>
+        <v>687</v>
       </c>
       <c r="I173" s="18" t="s">
-        <v>682</v>
+        <v>688</v>
       </c>
       <c r="J173" s="19"/>
       <c r="K173" s="19" t="s">
@@ -11586,17 +12009,19 @@
       <c r="L173" s="19"/>
       <c r="M173" s="20"/>
       <c r="N173" s="19"/>
-      <c r="O173" s="19"/>
+      <c r="O173" s="19" t="s">
+        <v>371</v>
+      </c>
     </row>
     <row r="174" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A174" s="18" t="s">
-        <v>683</v>
+        <v>689</v>
       </c>
       <c r="B174" s="18" t="s">
         <v>47</v>
       </c>
       <c r="C174" s="18" t="s">
-        <v>684</v>
+        <v>690</v>
       </c>
       <c r="D174" s="18" t="s">
         <v>93</v>
@@ -11609,10 +12034,10 @@
       </c>
       <c r="G174" s="18"/>
       <c r="H174" s="18" t="s">
-        <v>685</v>
+        <v>691</v>
       </c>
       <c r="I174" s="18" t="s">
-        <v>686</v>
+        <v>692</v>
       </c>
       <c r="J174" s="19"/>
       <c r="K174" s="19" t="s">
@@ -11625,13 +12050,13 @@
     </row>
     <row r="175" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A175" s="18" t="s">
-        <v>687</v>
+        <v>693</v>
       </c>
       <c r="B175" s="18" t="s">
         <v>47</v>
       </c>
       <c r="C175" s="18" t="s">
-        <v>684</v>
+        <v>690</v>
       </c>
       <c r="D175" s="18" t="s">
         <v>93</v>
@@ -11643,13 +12068,13 @@
         <v>94</v>
       </c>
       <c r="G175" s="18" t="s">
-        <v>688</v>
+        <v>694</v>
       </c>
       <c r="H175" s="18" t="s">
-        <v>689</v>
+        <v>695</v>
       </c>
       <c r="I175" s="18" t="s">
-        <v>690</v>
+        <v>696</v>
       </c>
       <c r="J175" s="19"/>
       <c r="K175" s="19" t="s">
@@ -11662,13 +12087,13 @@
     </row>
     <row r="176" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A176" s="18" t="s">
-        <v>691</v>
+        <v>697</v>
       </c>
       <c r="B176" s="18" t="s">
         <v>47</v>
       </c>
       <c r="C176" s="18" t="s">
-        <v>684</v>
+        <v>690</v>
       </c>
       <c r="D176" s="18" t="s">
         <v>110</v>
@@ -11681,10 +12106,10 @@
       </c>
       <c r="G176" s="18"/>
       <c r="H176" s="18" t="s">
-        <v>692</v>
+        <v>698</v>
       </c>
       <c r="I176" s="18" t="s">
-        <v>693</v>
+        <v>699</v>
       </c>
       <c r="J176" s="19"/>
       <c r="K176" s="19" t="s">
@@ -11697,13 +12122,13 @@
     </row>
     <row r="177" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A177" s="18" t="s">
-        <v>694</v>
+        <v>700</v>
       </c>
       <c r="B177" s="18" t="s">
         <v>47</v>
       </c>
       <c r="C177" s="18" t="s">
-        <v>684</v>
+        <v>690</v>
       </c>
       <c r="D177" s="18" t="s">
         <v>82</v>
@@ -11716,10 +12141,10 @@
       </c>
       <c r="G177" s="18"/>
       <c r="H177" s="18" t="s">
-        <v>695</v>
+        <v>701</v>
       </c>
       <c r="I177" s="18" t="s">
-        <v>696</v>
+        <v>702</v>
       </c>
       <c r="J177" s="19"/>
       <c r="K177" s="19" t="s">
@@ -11732,13 +12157,13 @@
     </row>
     <row r="178" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A178" s="18" t="s">
-        <v>697</v>
+        <v>703</v>
       </c>
       <c r="B178" s="18" t="s">
         <v>47</v>
       </c>
       <c r="C178" s="18" t="s">
-        <v>698</v>
+        <v>704</v>
       </c>
       <c r="D178" s="18" t="s">
         <v>93</v>
@@ -11751,10 +12176,10 @@
       </c>
       <c r="G178" s="18"/>
       <c r="H178" s="18" t="s">
-        <v>699</v>
+        <v>705</v>
       </c>
       <c r="I178" s="18" t="s">
-        <v>700</v>
+        <v>706</v>
       </c>
       <c r="J178" s="19"/>
       <c r="K178" s="19" t="s">
@@ -11767,13 +12192,13 @@
     </row>
     <row r="179" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A179" s="18" t="s">
-        <v>701</v>
+        <v>707</v>
       </c>
       <c r="B179" s="18" t="s">
         <v>47</v>
       </c>
       <c r="C179" s="18" t="s">
-        <v>702</v>
+        <v>708</v>
       </c>
       <c r="D179" s="18" t="s">
         <v>93</v>
@@ -11786,10 +12211,10 @@
       </c>
       <c r="G179" s="18"/>
       <c r="H179" s="18" t="s">
-        <v>703</v>
+        <v>709</v>
       </c>
       <c r="I179" s="18" t="s">
-        <v>704</v>
+        <v>710</v>
       </c>
       <c r="J179" s="19"/>
       <c r="K179" s="19" t="s">
@@ -11802,13 +12227,13 @@
     </row>
     <row r="180" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A180" s="18" t="s">
-        <v>705</v>
+        <v>711</v>
       </c>
       <c r="B180" s="18" t="s">
         <v>47</v>
       </c>
       <c r="C180" s="18" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="D180" s="18" t="s">
         <v>132</v>
@@ -11817,16 +12242,16 @@
         <v>83</v>
       </c>
       <c r="F180" s="18" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="G180" s="18" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="H180" s="18" t="s">
-        <v>706</v>
+        <v>712</v>
       </c>
       <c r="I180" s="18" t="s">
-        <v>707</v>
+        <v>713</v>
       </c>
       <c r="J180" s="19"/>
       <c r="K180" s="19" t="s">
@@ -11839,13 +12264,13 @@
     </row>
     <row r="181" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A181" s="18" t="s">
-        <v>708</v>
+        <v>714</v>
       </c>
       <c r="B181" s="18" t="s">
         <v>48</v>
       </c>
       <c r="C181" s="18" t="s">
-        <v>709</v>
+        <v>715</v>
       </c>
       <c r="D181" s="18" t="s">
         <v>93</v>
@@ -11858,10 +12283,10 @@
       </c>
       <c r="G181" s="18"/>
       <c r="H181" s="18" t="s">
-        <v>710</v>
+        <v>716</v>
       </c>
       <c r="I181" s="18" t="s">
-        <v>711</v>
+        <v>717</v>
       </c>
       <c r="J181" s="19"/>
       <c r="K181" s="19" t="s">
@@ -11874,13 +12299,13 @@
     </row>
     <row r="182" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A182" s="18" t="s">
-        <v>712</v>
+        <v>718</v>
       </c>
       <c r="B182" s="18" t="s">
         <v>48</v>
       </c>
       <c r="C182" s="18" t="s">
-        <v>713</v>
+        <v>719</v>
       </c>
       <c r="D182" s="18" t="s">
         <v>93</v>
@@ -11895,10 +12320,10 @@
         <v>239</v>
       </c>
       <c r="H182" s="18" t="s">
-        <v>714</v>
+        <v>720</v>
       </c>
       <c r="I182" s="18" t="s">
-        <v>715</v>
+        <v>721</v>
       </c>
       <c r="J182" s="19"/>
       <c r="K182" s="19" t="s">
@@ -11911,13 +12336,13 @@
     </row>
     <row r="183" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A183" s="18" t="s">
-        <v>716</v>
+        <v>722</v>
       </c>
       <c r="B183" s="18" t="s">
         <v>48</v>
       </c>
       <c r="C183" s="18" t="s">
-        <v>717</v>
+        <v>723</v>
       </c>
       <c r="D183" s="18" t="s">
         <v>93</v>
@@ -11929,13 +12354,13 @@
         <v>94</v>
       </c>
       <c r="G183" s="18" t="s">
-        <v>718</v>
+        <v>724</v>
       </c>
       <c r="H183" s="18" t="s">
-        <v>719</v>
+        <v>725</v>
       </c>
       <c r="I183" s="18" t="s">
-        <v>720</v>
+        <v>726</v>
       </c>
       <c r="J183" s="19"/>
       <c r="K183" s="19" t="s">
@@ -11948,13 +12373,13 @@
     </row>
     <row r="184" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A184" s="18" t="s">
-        <v>721</v>
+        <v>727</v>
       </c>
       <c r="B184" s="18" t="s">
         <v>48</v>
       </c>
       <c r="C184" s="18" t="s">
-        <v>717</v>
+        <v>723</v>
       </c>
       <c r="D184" s="18" t="s">
         <v>93</v>
@@ -11967,10 +12392,10 @@
       </c>
       <c r="G184" s="18"/>
       <c r="H184" s="18" t="s">
-        <v>722</v>
+        <v>728</v>
       </c>
       <c r="I184" s="18" t="s">
-        <v>723</v>
+        <v>729</v>
       </c>
       <c r="J184" s="19"/>
       <c r="K184" s="19" t="s">
@@ -11983,13 +12408,13 @@
     </row>
     <row r="185" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A185" s="18" t="s">
-        <v>724</v>
+        <v>730</v>
       </c>
       <c r="B185" s="18" t="s">
         <v>48</v>
       </c>
       <c r="C185" s="18" t="s">
-        <v>725</v>
+        <v>731</v>
       </c>
       <c r="D185" s="18" t="s">
         <v>93</v>
@@ -12002,10 +12427,10 @@
       </c>
       <c r="G185" s="18"/>
       <c r="H185" s="18" t="s">
-        <v>726</v>
+        <v>732</v>
       </c>
       <c r="I185" s="18" t="s">
-        <v>727</v>
+        <v>733</v>
       </c>
       <c r="J185" s="19"/>
       <c r="K185" s="19" t="s">
@@ -12018,13 +12443,13 @@
     </row>
     <row r="186" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A186" s="18" t="s">
-        <v>728</v>
+        <v>734</v>
       </c>
       <c r="B186" s="18" t="s">
         <v>48</v>
       </c>
       <c r="C186" s="18" t="s">
-        <v>725</v>
+        <v>731</v>
       </c>
       <c r="D186" s="18" t="s">
         <v>93</v>
@@ -12037,10 +12462,10 @@
       </c>
       <c r="G186" s="18"/>
       <c r="H186" s="18" t="s">
-        <v>729</v>
+        <v>735</v>
       </c>
       <c r="I186" s="18" t="s">
-        <v>730</v>
+        <v>736</v>
       </c>
       <c r="J186" s="19"/>
       <c r="K186" s="19" t="s">
@@ -12053,13 +12478,13 @@
     </row>
     <row r="187" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A187" s="18" t="s">
-        <v>731</v>
+        <v>737</v>
       </c>
       <c r="B187" s="18" t="s">
         <v>48</v>
       </c>
       <c r="C187" s="18" t="s">
-        <v>725</v>
+        <v>731</v>
       </c>
       <c r="D187" s="18" t="s">
         <v>93</v>
@@ -12072,10 +12497,10 @@
       </c>
       <c r="G187" s="18"/>
       <c r="H187" s="18" t="s">
-        <v>732</v>
+        <v>738</v>
       </c>
       <c r="I187" s="18" t="s">
-        <v>733</v>
+        <v>739</v>
       </c>
       <c r="J187" s="19"/>
       <c r="K187" s="19" t="s">
@@ -12088,13 +12513,13 @@
     </row>
     <row r="188" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A188" s="18" t="s">
-        <v>734</v>
+        <v>740</v>
       </c>
       <c r="B188" s="18" t="s">
         <v>48</v>
       </c>
       <c r="C188" s="18" t="s">
-        <v>735</v>
+        <v>741</v>
       </c>
       <c r="D188" s="18" t="s">
         <v>106</v>
@@ -12107,10 +12532,10 @@
       </c>
       <c r="G188" s="18"/>
       <c r="H188" s="18" t="s">
-        <v>736</v>
+        <v>742</v>
       </c>
       <c r="I188" s="18" t="s">
-        <v>737</v>
+        <v>743</v>
       </c>
       <c r="J188" s="19"/>
       <c r="K188" s="19" t="s">
@@ -12123,13 +12548,13 @@
     </row>
     <row r="189" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A189" s="18" t="s">
-        <v>738</v>
+        <v>744</v>
       </c>
       <c r="B189" s="18" t="s">
         <v>48</v>
       </c>
       <c r="C189" s="18" t="s">
-        <v>735</v>
+        <v>741</v>
       </c>
       <c r="D189" s="18" t="s">
         <v>93</v>
@@ -12142,10 +12567,10 @@
       </c>
       <c r="G189" s="18"/>
       <c r="H189" s="18" t="s">
-        <v>735</v>
+        <v>741</v>
       </c>
       <c r="I189" s="18" t="s">
-        <v>739</v>
+        <v>745</v>
       </c>
       <c r="J189" s="19"/>
       <c r="K189" s="19" t="s">
@@ -12158,13 +12583,13 @@
     </row>
     <row r="190" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A190" s="18" t="s">
-        <v>740</v>
+        <v>746</v>
       </c>
       <c r="B190" s="18" t="s">
         <v>48</v>
       </c>
       <c r="C190" s="18" t="s">
-        <v>735</v>
+        <v>741</v>
       </c>
       <c r="D190" s="18" t="s">
         <v>93</v>
@@ -12176,13 +12601,13 @@
         <v>94</v>
       </c>
       <c r="G190" s="18" t="s">
-        <v>741</v>
+        <v>747</v>
       </c>
       <c r="H190" s="18" t="s">
-        <v>742</v>
+        <v>748</v>
       </c>
       <c r="I190" s="18" t="s">
-        <v>743</v>
+        <v>749</v>
       </c>
       <c r="J190" s="19"/>
       <c r="K190" s="19" t="s">
@@ -12195,13 +12620,13 @@
     </row>
     <row r="191" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A191" s="18" t="s">
-        <v>744</v>
+        <v>750</v>
       </c>
       <c r="B191" s="18" t="s">
         <v>48</v>
       </c>
       <c r="C191" s="18" t="s">
-        <v>735</v>
+        <v>741</v>
       </c>
       <c r="D191" s="18" t="s">
         <v>93</v>
@@ -12214,10 +12639,10 @@
       </c>
       <c r="G191" s="18"/>
       <c r="H191" s="18" t="s">
-        <v>745</v>
+        <v>751</v>
       </c>
       <c r="I191" s="18" t="s">
-        <v>746</v>
+        <v>752</v>
       </c>
       <c r="J191" s="19"/>
       <c r="K191" s="19" t="s">
@@ -12230,13 +12655,13 @@
     </row>
     <row r="192" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A192" s="18" t="s">
-        <v>747</v>
+        <v>753</v>
       </c>
       <c r="B192" s="18" t="s">
         <v>48</v>
       </c>
       <c r="C192" s="18" t="s">
-        <v>748</v>
+        <v>754</v>
       </c>
       <c r="D192" s="18" t="s">
         <v>93</v>
@@ -12248,13 +12673,13 @@
         <v>94</v>
       </c>
       <c r="G192" s="18" t="s">
-        <v>749</v>
+        <v>755</v>
       </c>
       <c r="H192" s="18" t="s">
-        <v>750</v>
+        <v>756</v>
       </c>
       <c r="I192" s="18" t="s">
-        <v>751</v>
+        <v>757</v>
       </c>
       <c r="J192" s="19"/>
       <c r="K192" s="19" t="s">
@@ -12267,7 +12692,7 @@
     </row>
     <row r="193" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A193" s="18" t="s">
-        <v>752</v>
+        <v>758</v>
       </c>
       <c r="B193" s="18" t="s">
         <v>48</v>
@@ -12286,10 +12711,10 @@
       </c>
       <c r="G193" s="18"/>
       <c r="H193" s="18" t="s">
-        <v>753</v>
+        <v>759</v>
       </c>
       <c r="I193" s="18" t="s">
-        <v>754</v>
+        <v>760</v>
       </c>
       <c r="J193" s="19"/>
       <c r="K193" s="19" t="s">
@@ -12302,13 +12727,13 @@
     </row>
     <row r="194" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A194" s="18" t="s">
-        <v>755</v>
+        <v>761</v>
       </c>
       <c r="B194" s="18" t="s">
         <v>48</v>
       </c>
       <c r="C194" s="18" t="s">
-        <v>756</v>
+        <v>762</v>
       </c>
       <c r="D194" s="18" t="s">
         <v>93</v>
@@ -12320,13 +12745,13 @@
         <v>94</v>
       </c>
       <c r="G194" s="18" t="s">
-        <v>756</v>
+        <v>762</v>
       </c>
       <c r="H194" s="18" t="s">
-        <v>757</v>
+        <v>763</v>
       </c>
       <c r="I194" s="18" t="s">
-        <v>758</v>
+        <v>764</v>
       </c>
       <c r="J194" s="19"/>
       <c r="K194" s="19" t="s">
@@ -12339,13 +12764,13 @@
     </row>
     <row r="195" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A195" s="18" t="s">
-        <v>759</v>
+        <v>765</v>
       </c>
       <c r="B195" s="18" t="s">
         <v>48</v>
       </c>
       <c r="C195" s="18" t="s">
-        <v>756</v>
+        <v>762</v>
       </c>
       <c r="D195" s="18" t="s">
         <v>93</v>
@@ -12357,13 +12782,13 @@
         <v>94</v>
       </c>
       <c r="G195" s="18" t="s">
-        <v>756</v>
+        <v>762</v>
       </c>
       <c r="H195" s="18" t="s">
-        <v>760</v>
+        <v>766</v>
       </c>
       <c r="I195" s="18" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="J195" s="19"/>
       <c r="K195" s="19" t="s">
@@ -12376,13 +12801,13 @@
     </row>
     <row r="196" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A196" s="18" t="s">
-        <v>762</v>
+        <v>768</v>
       </c>
       <c r="B196" s="18" t="s">
         <v>48</v>
       </c>
       <c r="C196" s="18" t="s">
-        <v>763</v>
+        <v>769</v>
       </c>
       <c r="D196" s="18" t="s">
         <v>82</v>
@@ -12395,10 +12820,10 @@
       </c>
       <c r="G196" s="18"/>
       <c r="H196" s="18" t="s">
-        <v>764</v>
+        <v>770</v>
       </c>
       <c r="I196" s="18" t="s">
-        <v>765</v>
+        <v>771</v>
       </c>
       <c r="J196" s="19"/>
       <c r="K196" s="19" t="s">
@@ -12411,13 +12836,13 @@
     </row>
     <row r="197" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A197" s="18" t="s">
-        <v>766</v>
+        <v>772</v>
       </c>
       <c r="B197" s="18" t="s">
         <v>48</v>
       </c>
       <c r="C197" s="18" t="s">
-        <v>763</v>
+        <v>769</v>
       </c>
       <c r="D197" s="18" t="s">
         <v>132</v>
@@ -12429,13 +12854,13 @@
         <v>168</v>
       </c>
       <c r="G197" s="18" t="s">
-        <v>767</v>
+        <v>773</v>
       </c>
       <c r="H197" s="18" t="s">
-        <v>768</v>
+        <v>774</v>
       </c>
       <c r="I197" s="18" t="s">
-        <v>769</v>
+        <v>775</v>
       </c>
       <c r="J197" s="19"/>
       <c r="K197" s="19" t="s">
@@ -12444,17 +12869,19 @@
       <c r="L197" s="19"/>
       <c r="M197" s="20"/>
       <c r="N197" s="19"/>
-      <c r="O197" s="19"/>
+      <c r="O197" s="19" t="s">
+        <v>371</v>
+      </c>
     </row>
     <row r="198" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A198" s="18" t="s">
-        <v>770</v>
+        <v>776</v>
       </c>
       <c r="B198" s="18" t="s">
         <v>48</v>
       </c>
       <c r="C198" s="18" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="D198" s="18" t="s">
         <v>93</v>
@@ -12463,16 +12890,16 @@
         <v>83</v>
       </c>
       <c r="F198" s="18" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="G198" s="18" t="s">
-        <v>771</v>
+        <v>777</v>
       </c>
       <c r="H198" s="18" t="s">
-        <v>772</v>
+        <v>778</v>
       </c>
       <c r="I198" s="18" t="s">
-        <v>773</v>
+        <v>779</v>
       </c>
       <c r="J198" s="19"/>
       <c r="K198" s="19" t="s">
@@ -12485,13 +12912,13 @@
     </row>
     <row r="199" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A199" s="18" t="s">
-        <v>774</v>
+        <v>780</v>
       </c>
       <c r="B199" s="18" t="s">
         <v>48</v>
       </c>
       <c r="C199" s="18" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="D199" s="18" t="s">
         <v>132</v>
@@ -12500,14 +12927,14 @@
         <v>83</v>
       </c>
       <c r="F199" s="18" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="G199" s="18"/>
       <c r="H199" s="18" t="s">
-        <v>775</v>
+        <v>781</v>
       </c>
       <c r="I199" s="18" t="s">
-        <v>776</v>
+        <v>782</v>
       </c>
       <c r="J199" s="19"/>
       <c r="K199" s="19" t="s">
@@ -12520,13 +12947,13 @@
     </row>
     <row r="200" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A200" s="18" t="s">
-        <v>777</v>
+        <v>783</v>
       </c>
       <c r="B200" s="18" t="s">
         <v>48</v>
       </c>
       <c r="C200" s="18" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="D200" s="18" t="s">
         <v>132</v>
@@ -12535,14 +12962,14 @@
         <v>99</v>
       </c>
       <c r="F200" s="18" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="G200" s="18"/>
       <c r="H200" s="18" t="s">
-        <v>778</v>
+        <v>784</v>
       </c>
       <c r="I200" s="18" t="s">
-        <v>779</v>
+        <v>785</v>
       </c>
       <c r="J200" s="19"/>
       <c r="K200" s="19" t="s">
@@ -12555,13 +12982,13 @@
     </row>
     <row r="201" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A201" s="18" t="s">
-        <v>780</v>
+        <v>786</v>
       </c>
       <c r="B201" s="18" t="s">
         <v>48</v>
       </c>
       <c r="C201" s="18" t="s">
-        <v>684</v>
+        <v>690</v>
       </c>
       <c r="D201" s="18" t="s">
         <v>93</v>
@@ -12573,13 +13000,13 @@
         <v>94</v>
       </c>
       <c r="G201" s="18" t="s">
-        <v>781</v>
+        <v>787</v>
       </c>
       <c r="H201" s="18" t="s">
-        <v>782</v>
+        <v>788</v>
       </c>
       <c r="I201" s="18" t="s">
-        <v>783</v>
+        <v>789</v>
       </c>
       <c r="J201" s="19"/>
       <c r="K201" s="19" t="s">
@@ -12592,13 +13019,13 @@
     </row>
     <row r="202" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A202" s="18" t="s">
-        <v>784</v>
+        <v>790</v>
       </c>
       <c r="B202" s="18" t="s">
         <v>48</v>
       </c>
       <c r="C202" s="18" t="s">
-        <v>684</v>
+        <v>690</v>
       </c>
       <c r="D202" s="18" t="s">
         <v>93</v>
@@ -12610,13 +13037,13 @@
         <v>94</v>
       </c>
       <c r="G202" s="18" t="s">
-        <v>785</v>
+        <v>791</v>
       </c>
       <c r="H202" s="18" t="s">
-        <v>786</v>
+        <v>792</v>
       </c>
       <c r="I202" s="18" t="s">
-        <v>787</v>
+        <v>793</v>
       </c>
       <c r="J202" s="19"/>
       <c r="K202" s="19" t="s">
@@ -12629,13 +13056,13 @@
     </row>
     <row r="203" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A203" s="18" t="s">
-        <v>788</v>
+        <v>794</v>
       </c>
       <c r="B203" s="18" t="s">
         <v>48</v>
       </c>
       <c r="C203" s="18" t="s">
-        <v>789</v>
+        <v>795</v>
       </c>
       <c r="D203" s="18" t="s">
         <v>93</v>
@@ -12648,10 +13075,10 @@
       </c>
       <c r="G203" s="18"/>
       <c r="H203" s="18" t="s">
-        <v>790</v>
+        <v>796</v>
       </c>
       <c r="I203" s="18" t="s">
-        <v>791</v>
+        <v>797</v>
       </c>
       <c r="J203" s="19"/>
       <c r="K203" s="19" t="s">
@@ -12664,13 +13091,13 @@
     </row>
     <row r="204" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A204" s="18" t="s">
-        <v>792</v>
+        <v>798</v>
       </c>
       <c r="B204" s="18" t="s">
         <v>48</v>
       </c>
       <c r="C204" s="18" t="s">
-        <v>793</v>
+        <v>799</v>
       </c>
       <c r="D204" s="18" t="s">
         <v>110</v>
@@ -12682,13 +13109,13 @@
         <v>94</v>
       </c>
       <c r="G204" s="18" t="s">
-        <v>794</v>
+        <v>800</v>
       </c>
       <c r="H204" s="18" t="s">
-        <v>795</v>
+        <v>801</v>
       </c>
       <c r="I204" s="18" t="s">
-        <v>796</v>
+        <v>802</v>
       </c>
       <c r="J204" s="19"/>
       <c r="K204" s="19" t="s">
@@ -12701,16 +13128,16 @@
     </row>
     <row r="205" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A205" s="18" t="s">
-        <v>797</v>
+        <v>803</v>
       </c>
       <c r="B205" s="18" t="s">
         <v>48</v>
       </c>
       <c r="C205" s="18" t="s">
-        <v>798</v>
+        <v>804</v>
       </c>
       <c r="D205" s="18" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="E205" s="18" t="s">
         <v>99</v>
@@ -12719,13 +13146,13 @@
         <v>94</v>
       </c>
       <c r="G205" s="18" t="s">
-        <v>799</v>
+        <v>805</v>
       </c>
       <c r="H205" s="18" t="s">
-        <v>800</v>
+        <v>806</v>
       </c>
       <c r="I205" s="18" t="s">
-        <v>801</v>
+        <v>807</v>
       </c>
       <c r="J205" s="19"/>
       <c r="K205" s="19" t="s">
@@ -12738,13 +13165,13 @@
     </row>
     <row r="206" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A206" s="18" t="s">
-        <v>802</v>
+        <v>808</v>
       </c>
       <c r="B206" s="18" t="s">
         <v>49</v>
       </c>
       <c r="C206" s="18" t="s">
-        <v>803</v>
+        <v>809</v>
       </c>
       <c r="D206" s="18" t="s">
         <v>93</v>
@@ -12756,13 +13183,13 @@
         <v>94</v>
       </c>
       <c r="G206" s="18" t="s">
-        <v>804</v>
+        <v>810</v>
       </c>
       <c r="H206" s="18" t="s">
-        <v>805</v>
+        <v>811</v>
       </c>
       <c r="I206" s="18" t="s">
-        <v>806</v>
+        <v>812</v>
       </c>
       <c r="J206" s="19"/>
       <c r="K206" s="19" t="s">
@@ -12775,13 +13202,13 @@
     </row>
     <row r="207" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A207" s="18" t="s">
-        <v>807</v>
+        <v>813</v>
       </c>
       <c r="B207" s="18" t="s">
         <v>49</v>
       </c>
       <c r="C207" s="18" t="s">
-        <v>808</v>
+        <v>814</v>
       </c>
       <c r="D207" s="18" t="s">
         <v>93</v>
@@ -12793,13 +13220,13 @@
         <v>94</v>
       </c>
       <c r="G207" s="18" t="s">
-        <v>809</v>
+        <v>815</v>
       </c>
       <c r="H207" s="18" t="s">
-        <v>810</v>
+        <v>816</v>
       </c>
       <c r="I207" s="18" t="s">
-        <v>811</v>
+        <v>817</v>
       </c>
       <c r="J207" s="19"/>
       <c r="K207" s="19" t="s">
@@ -12812,13 +13239,13 @@
     </row>
     <row r="208" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A208" s="18" t="s">
-        <v>812</v>
+        <v>818</v>
       </c>
       <c r="B208" s="18" t="s">
         <v>49</v>
       </c>
       <c r="C208" s="18" t="s">
-        <v>808</v>
+        <v>814</v>
       </c>
       <c r="D208" s="18" t="s">
         <v>93</v>
@@ -12831,10 +13258,10 @@
       </c>
       <c r="G208" s="18"/>
       <c r="H208" s="18" t="s">
-        <v>813</v>
+        <v>819</v>
       </c>
       <c r="I208" s="18" t="s">
-        <v>814</v>
+        <v>820</v>
       </c>
       <c r="J208" s="19"/>
       <c r="K208" s="19" t="s">
@@ -12847,13 +13274,13 @@
     </row>
     <row r="209" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A209" s="18" t="s">
-        <v>815</v>
+        <v>821</v>
       </c>
       <c r="B209" s="18" t="s">
         <v>49</v>
       </c>
       <c r="C209" s="18" t="s">
-        <v>808</v>
+        <v>814</v>
       </c>
       <c r="D209" s="18" t="s">
         <v>82</v>
@@ -12865,13 +13292,13 @@
         <v>94</v>
       </c>
       <c r="G209" s="18" t="s">
-        <v>816</v>
+        <v>822</v>
       </c>
       <c r="H209" s="18" t="s">
-        <v>817</v>
+        <v>823</v>
       </c>
       <c r="I209" s="18" t="s">
-        <v>818</v>
+        <v>824</v>
       </c>
       <c r="J209" s="19"/>
       <c r="K209" s="19" t="s">
@@ -12884,13 +13311,13 @@
     </row>
     <row r="210" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A210" s="18" t="s">
-        <v>819</v>
+        <v>825</v>
       </c>
       <c r="B210" s="18" t="s">
         <v>49</v>
       </c>
       <c r="C210" s="18" t="s">
-        <v>808</v>
+        <v>814</v>
       </c>
       <c r="D210" s="18" t="s">
         <v>93</v>
@@ -12902,13 +13329,13 @@
         <v>94</v>
       </c>
       <c r="G210" s="18" t="s">
-        <v>820</v>
+        <v>826</v>
       </c>
       <c r="H210" s="18" t="s">
-        <v>817</v>
+        <v>823</v>
       </c>
       <c r="I210" s="18" t="s">
-        <v>821</v>
+        <v>827</v>
       </c>
       <c r="J210" s="19"/>
       <c r="K210" s="19" t="s">
@@ -12921,13 +13348,13 @@
     </row>
     <row r="211" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A211" s="18" t="s">
-        <v>822</v>
+        <v>828</v>
       </c>
       <c r="B211" s="18" t="s">
         <v>49</v>
       </c>
       <c r="C211" s="18" t="s">
-        <v>808</v>
+        <v>814</v>
       </c>
       <c r="D211" s="18" t="s">
         <v>82</v>
@@ -12939,13 +13366,13 @@
         <v>94</v>
       </c>
       <c r="G211" s="18" t="s">
+        <v>829</v>
+      </c>
+      <c r="H211" s="18" t="s">
         <v>823</v>
       </c>
-      <c r="H211" s="18" t="s">
-        <v>817</v>
-      </c>
       <c r="I211" s="18" t="s">
-        <v>824</v>
+        <v>830</v>
       </c>
       <c r="J211" s="19"/>
       <c r="K211" s="19" t="s">
@@ -12958,13 +13385,13 @@
     </row>
     <row r="212" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A212" s="18" t="s">
-        <v>825</v>
+        <v>831</v>
       </c>
       <c r="B212" s="18" t="s">
         <v>49</v>
       </c>
       <c r="C212" s="18" t="s">
-        <v>808</v>
+        <v>814</v>
       </c>
       <c r="D212" s="18" t="s">
         <v>106</v>
@@ -12977,10 +13404,10 @@
       </c>
       <c r="G212" s="18"/>
       <c r="H212" s="18" t="s">
-        <v>826</v>
+        <v>832</v>
       </c>
       <c r="I212" s="18" t="s">
-        <v>827</v>
+        <v>833</v>
       </c>
       <c r="J212" s="19"/>
       <c r="K212" s="19" t="s">
@@ -12993,13 +13420,13 @@
     </row>
     <row r="213" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A213" s="18" t="s">
-        <v>828</v>
+        <v>834</v>
       </c>
       <c r="B213" s="18" t="s">
         <v>49</v>
       </c>
       <c r="C213" s="18" t="s">
-        <v>808</v>
+        <v>814</v>
       </c>
       <c r="D213" s="18" t="s">
         <v>106</v>
@@ -13012,10 +13439,10 @@
       </c>
       <c r="G213" s="18"/>
       <c r="H213" s="18" t="s">
-        <v>829</v>
+        <v>835</v>
       </c>
       <c r="I213" s="18" t="s">
-        <v>830</v>
+        <v>836</v>
       </c>
       <c r="J213" s="19"/>
       <c r="K213" s="19" t="s">
@@ -13028,13 +13455,13 @@
     </row>
     <row r="214" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A214" s="18" t="s">
-        <v>831</v>
+        <v>837</v>
       </c>
       <c r="B214" s="18" t="s">
         <v>49</v>
       </c>
       <c r="C214" s="18" t="s">
-        <v>808</v>
+        <v>814</v>
       </c>
       <c r="D214" s="18" t="s">
         <v>82</v>
@@ -13047,10 +13474,10 @@
       </c>
       <c r="G214" s="18"/>
       <c r="H214" s="18" t="s">
-        <v>832</v>
+        <v>838</v>
       </c>
       <c r="I214" s="18" t="s">
-        <v>833</v>
+        <v>839</v>
       </c>
       <c r="J214" s="19"/>
       <c r="K214" s="19" t="s">
@@ -13063,13 +13490,13 @@
     </row>
     <row r="215" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A215" s="18" t="s">
-        <v>834</v>
+        <v>840</v>
       </c>
       <c r="B215" s="18" t="s">
         <v>49</v>
       </c>
       <c r="C215" s="18" t="s">
-        <v>808</v>
+        <v>814</v>
       </c>
       <c r="D215" s="18" t="s">
         <v>93</v>
@@ -13082,10 +13509,10 @@
       </c>
       <c r="G215" s="18"/>
       <c r="H215" s="18" t="s">
-        <v>835</v>
+        <v>841</v>
       </c>
       <c r="I215" s="18" t="s">
-        <v>836</v>
+        <v>842</v>
       </c>
       <c r="J215" s="19"/>
       <c r="K215" s="19" t="s">
@@ -13098,13 +13525,13 @@
     </row>
     <row r="216" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A216" s="18" t="s">
-        <v>837</v>
+        <v>843</v>
       </c>
       <c r="B216" s="18" t="s">
         <v>49</v>
       </c>
       <c r="C216" s="18" t="s">
-        <v>838</v>
+        <v>844</v>
       </c>
       <c r="D216" s="18" t="s">
         <v>93</v>
@@ -13113,16 +13540,16 @@
         <v>83</v>
       </c>
       <c r="F216" s="18" t="s">
-        <v>839</v>
+        <v>845</v>
       </c>
       <c r="G216" s="18" t="s">
-        <v>840</v>
+        <v>846</v>
       </c>
       <c r="H216" s="18" t="s">
-        <v>841</v>
+        <v>847</v>
       </c>
       <c r="I216" s="18" t="s">
-        <v>842</v>
+        <v>848</v>
       </c>
       <c r="J216" s="19"/>
       <c r="K216" s="19" t="s">
@@ -13135,13 +13562,13 @@
     </row>
     <row r="217" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A217" s="18" t="s">
-        <v>843</v>
+        <v>849</v>
       </c>
       <c r="B217" s="18" t="s">
         <v>49</v>
       </c>
       <c r="C217" s="18" t="s">
-        <v>838</v>
+        <v>844</v>
       </c>
       <c r="D217" s="18" t="s">
         <v>93</v>
@@ -13150,14 +13577,14 @@
         <v>83</v>
       </c>
       <c r="F217" s="18" t="s">
-        <v>839</v>
+        <v>845</v>
       </c>
       <c r="G217" s="18"/>
       <c r="H217" s="18" t="s">
-        <v>844</v>
+        <v>850</v>
       </c>
       <c r="I217" s="18" t="s">
-        <v>845</v>
+        <v>851</v>
       </c>
       <c r="J217" s="19"/>
       <c r="K217" s="19" t="s">
@@ -13170,13 +13597,13 @@
     </row>
     <row r="218" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A218" s="18" t="s">
-        <v>846</v>
+        <v>852</v>
       </c>
       <c r="B218" s="18" t="s">
         <v>49</v>
       </c>
       <c r="C218" s="18" t="s">
-        <v>838</v>
+        <v>844</v>
       </c>
       <c r="D218" s="18" t="s">
         <v>82</v>
@@ -13188,13 +13615,13 @@
         <v>94</v>
       </c>
       <c r="G218" s="18" t="s">
-        <v>847</v>
+        <v>853</v>
       </c>
       <c r="H218" s="18" t="s">
-        <v>848</v>
+        <v>854</v>
       </c>
       <c r="I218" s="18" t="s">
-        <v>849</v>
+        <v>855</v>
       </c>
       <c r="J218" s="19"/>
       <c r="K218" s="19" t="s">
@@ -13207,13 +13634,13 @@
     </row>
     <row r="219" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A219" s="18" t="s">
-        <v>850</v>
+        <v>856</v>
       </c>
       <c r="B219" s="18" t="s">
         <v>49</v>
       </c>
       <c r="C219" s="18" t="s">
-        <v>838</v>
+        <v>844</v>
       </c>
       <c r="D219" s="18" t="s">
         <v>93</v>
@@ -13222,16 +13649,16 @@
         <v>99</v>
       </c>
       <c r="F219" s="18" t="s">
-        <v>839</v>
+        <v>845</v>
       </c>
       <c r="G219" s="18" t="s">
-        <v>851</v>
+        <v>857</v>
       </c>
       <c r="H219" s="18" t="s">
-        <v>852</v>
+        <v>858</v>
       </c>
       <c r="I219" s="18" t="s">
-        <v>853</v>
+        <v>859</v>
       </c>
       <c r="J219" s="19"/>
       <c r="K219" s="19" t="s">
@@ -13244,13 +13671,13 @@
     </row>
     <row r="220" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A220" s="18" t="s">
-        <v>854</v>
+        <v>860</v>
       </c>
       <c r="B220" s="18" t="s">
         <v>49</v>
       </c>
       <c r="C220" s="18" t="s">
-        <v>838</v>
+        <v>844</v>
       </c>
       <c r="D220" s="18" t="s">
         <v>82</v>
@@ -13259,16 +13686,16 @@
         <v>99</v>
       </c>
       <c r="F220" s="18" t="s">
-        <v>839</v>
+        <v>845</v>
       </c>
       <c r="G220" s="18" t="s">
-        <v>855</v>
+        <v>861</v>
       </c>
       <c r="H220" s="18" t="s">
-        <v>856</v>
+        <v>862</v>
       </c>
       <c r="I220" s="18" t="s">
-        <v>857</v>
+        <v>863</v>
       </c>
       <c r="J220" s="19"/>
       <c r="K220" s="19" t="s">
@@ -13281,7 +13708,7 @@
     </row>
     <row r="221" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A221" s="18" t="s">
-        <v>858</v>
+        <v>864</v>
       </c>
       <c r="B221" s="18" t="s">
         <v>49</v>
@@ -13299,13 +13726,13 @@
         <v>94</v>
       </c>
       <c r="G221" s="18" t="s">
-        <v>851</v>
+        <v>857</v>
       </c>
       <c r="H221" s="18" t="s">
-        <v>859</v>
+        <v>865</v>
       </c>
       <c r="I221" s="18" t="s">
-        <v>860</v>
+        <v>866</v>
       </c>
       <c r="J221" s="19"/>
       <c r="K221" s="19" t="s">
@@ -13318,7 +13745,7 @@
     </row>
     <row r="222" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A222" s="18" t="s">
-        <v>861</v>
+        <v>867</v>
       </c>
       <c r="B222" s="18" t="s">
         <v>49</v>
@@ -13336,13 +13763,13 @@
         <v>94</v>
       </c>
       <c r="G222" s="18" t="s">
-        <v>862</v>
+        <v>868</v>
       </c>
       <c r="H222" s="18" t="s">
-        <v>859</v>
+        <v>865</v>
       </c>
       <c r="I222" s="18" t="s">
-        <v>863</v>
+        <v>869</v>
       </c>
       <c r="J222" s="19"/>
       <c r="K222" s="19" t="s">
@@ -13355,13 +13782,13 @@
     </row>
     <row r="223" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A223" s="18" t="s">
-        <v>864</v>
+        <v>870</v>
       </c>
       <c r="B223" s="18" t="s">
         <v>49</v>
       </c>
       <c r="C223" s="18" t="s">
-        <v>865</v>
+        <v>871</v>
       </c>
       <c r="D223" s="18" t="s">
         <v>93</v>
@@ -13374,10 +13801,10 @@
       </c>
       <c r="G223" s="18"/>
       <c r="H223" s="18" t="s">
-        <v>866</v>
+        <v>872</v>
       </c>
       <c r="I223" s="18" t="s">
-        <v>867</v>
+        <v>873</v>
       </c>
       <c r="J223" s="19"/>
       <c r="K223" s="19" t="s">
@@ -13390,13 +13817,13 @@
     </row>
     <row r="224" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A224" s="18" t="s">
-        <v>868</v>
+        <v>874</v>
       </c>
       <c r="B224" s="18" t="s">
         <v>49</v>
       </c>
       <c r="C224" s="18" t="s">
-        <v>865</v>
+        <v>871</v>
       </c>
       <c r="D224" s="18" t="s">
         <v>132</v>
@@ -13405,16 +13832,16 @@
         <v>83</v>
       </c>
       <c r="F224" s="18" t="s">
-        <v>869</v>
+        <v>875</v>
       </c>
       <c r="G224" s="18" t="s">
-        <v>870</v>
+        <v>876</v>
       </c>
       <c r="H224" s="18" t="s">
-        <v>871</v>
+        <v>877</v>
       </c>
       <c r="I224" s="18" t="s">
-        <v>872</v>
+        <v>878</v>
       </c>
       <c r="J224" s="19"/>
       <c r="K224" s="19" t="s">
@@ -13427,13 +13854,13 @@
     </row>
     <row r="225" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A225" s="18" t="s">
-        <v>873</v>
+        <v>879</v>
       </c>
       <c r="B225" s="18" t="s">
         <v>49</v>
       </c>
       <c r="C225" s="18" t="s">
-        <v>874</v>
+        <v>880</v>
       </c>
       <c r="D225" s="18" t="s">
         <v>93</v>
@@ -13445,13 +13872,13 @@
         <v>94</v>
       </c>
       <c r="G225" s="18" t="s">
-        <v>875</v>
+        <v>881</v>
       </c>
       <c r="H225" s="18" t="s">
-        <v>876</v>
+        <v>882</v>
       </c>
       <c r="I225" s="18" t="s">
-        <v>877</v>
+        <v>883</v>
       </c>
       <c r="J225" s="19"/>
       <c r="K225" s="19" t="s">
@@ -13464,7 +13891,7 @@
     </row>
     <row r="226" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A226" s="18" t="s">
-        <v>878</v>
+        <v>884</v>
       </c>
       <c r="B226" s="18" t="s">
         <v>49</v>
@@ -13479,16 +13906,16 @@
         <v>83</v>
       </c>
       <c r="F226" s="18" t="s">
-        <v>879</v>
+        <v>885</v>
       </c>
       <c r="G226" s="18" t="s">
-        <v>880</v>
+        <v>886</v>
       </c>
       <c r="H226" s="18" t="s">
-        <v>881</v>
+        <v>887</v>
       </c>
       <c r="I226" s="18" t="s">
-        <v>882</v>
+        <v>888</v>
       </c>
       <c r="J226" s="19"/>
       <c r="K226" s="19" t="s">
@@ -13501,13 +13928,13 @@
     </row>
     <row r="227" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A227" s="18" t="s">
-        <v>883</v>
+        <v>889</v>
       </c>
       <c r="B227" s="18" t="s">
         <v>49</v>
       </c>
       <c r="C227" s="18" t="s">
-        <v>884</v>
+        <v>890</v>
       </c>
       <c r="D227" s="18" t="s">
         <v>93</v>
@@ -13519,13 +13946,13 @@
         <v>94</v>
       </c>
       <c r="G227" s="18" t="s">
-        <v>885</v>
+        <v>891</v>
       </c>
       <c r="H227" s="18" t="s">
-        <v>886</v>
+        <v>892</v>
       </c>
       <c r="I227" s="18" t="s">
-        <v>887</v>
+        <v>893</v>
       </c>
       <c r="J227" s="19"/>
       <c r="K227" s="19" t="s">
@@ -13538,13 +13965,13 @@
     </row>
     <row r="228" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A228" s="18" t="s">
-        <v>888</v>
+        <v>894</v>
       </c>
       <c r="B228" s="18" t="s">
         <v>49</v>
       </c>
       <c r="C228" s="18" t="s">
-        <v>884</v>
+        <v>890</v>
       </c>
       <c r="D228" s="18" t="s">
         <v>82</v>
@@ -13556,13 +13983,13 @@
         <v>94</v>
       </c>
       <c r="G228" s="18" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="H228" s="18" t="s">
-        <v>889</v>
+        <v>895</v>
       </c>
       <c r="I228" s="18" t="s">
-        <v>890</v>
+        <v>896</v>
       </c>
       <c r="J228" s="19"/>
       <c r="K228" s="19" t="s">
@@ -13575,7 +14002,7 @@
     </row>
     <row r="229" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A229" s="18" t="s">
-        <v>891</v>
+        <v>897</v>
       </c>
       <c r="B229" s="18" t="s">
         <v>50</v>
@@ -13594,10 +14021,10 @@
       </c>
       <c r="G229" s="18"/>
       <c r="H229" s="18" t="s">
-        <v>892</v>
+        <v>898</v>
       </c>
       <c r="I229" s="18" t="s">
-        <v>893</v>
+        <v>899</v>
       </c>
       <c r="J229" s="19"/>
       <c r="K229" s="19" t="s">
@@ -13610,7 +14037,7 @@
     </row>
     <row r="230" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A230" s="18" t="s">
-        <v>894</v>
+        <v>900</v>
       </c>
       <c r="B230" s="18" t="s">
         <v>50</v>
@@ -13629,10 +14056,10 @@
       </c>
       <c r="G230" s="18"/>
       <c r="H230" s="18" t="s">
-        <v>895</v>
+        <v>901</v>
       </c>
       <c r="I230" s="18" t="s">
-        <v>896</v>
+        <v>902</v>
       </c>
       <c r="J230" s="19"/>
       <c r="K230" s="19" t="s">
@@ -13645,7 +14072,7 @@
     </row>
     <row r="231" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A231" s="18" t="s">
-        <v>897</v>
+        <v>903</v>
       </c>
       <c r="B231" s="18" t="s">
         <v>50</v>
@@ -13664,10 +14091,10 @@
       </c>
       <c r="G231" s="18"/>
       <c r="H231" s="18" t="s">
-        <v>898</v>
+        <v>904</v>
       </c>
       <c r="I231" s="18" t="s">
-        <v>899</v>
+        <v>905</v>
       </c>
       <c r="J231" s="19"/>
       <c r="K231" s="19" t="s">
@@ -13680,7 +14107,7 @@
     </row>
     <row r="232" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A232" s="18" t="s">
-        <v>900</v>
+        <v>906</v>
       </c>
       <c r="B232" s="18" t="s">
         <v>50</v>
@@ -13699,10 +14126,10 @@
       </c>
       <c r="G232" s="18"/>
       <c r="H232" s="18" t="s">
-        <v>901</v>
+        <v>907</v>
       </c>
       <c r="I232" s="18" t="s">
-        <v>902</v>
+        <v>908</v>
       </c>
       <c r="J232" s="19"/>
       <c r="K232" s="19" t="s">
@@ -13715,7 +14142,7 @@
     </row>
     <row r="233" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A233" s="18" t="s">
-        <v>903</v>
+        <v>909</v>
       </c>
       <c r="B233" s="18" t="s">
         <v>50</v>
@@ -13734,7 +14161,7 @@
       </c>
       <c r="G233" s="18"/>
       <c r="H233" s="18" t="s">
-        <v>904</v>
+        <v>910</v>
       </c>
       <c r="I233" s="18" t="s">
         <v>318</v>
@@ -13750,7 +14177,7 @@
     </row>
     <row r="234" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A234" s="18" t="s">
-        <v>905</v>
+        <v>911</v>
       </c>
       <c r="B234" s="18" t="s">
         <v>50</v>
@@ -13769,10 +14196,10 @@
       </c>
       <c r="G234" s="18"/>
       <c r="H234" s="18" t="s">
-        <v>906</v>
+        <v>912</v>
       </c>
       <c r="I234" s="18" t="s">
-        <v>907</v>
+        <v>913</v>
       </c>
       <c r="J234" s="19"/>
       <c r="K234" s="19" t="s">
@@ -13785,7 +14212,7 @@
     </row>
     <row r="235" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A235" s="18" t="s">
-        <v>908</v>
+        <v>914</v>
       </c>
       <c r="B235" s="18" t="s">
         <v>50</v>
@@ -13804,10 +14231,10 @@
       </c>
       <c r="G235" s="18"/>
       <c r="H235" s="18" t="s">
-        <v>909</v>
+        <v>915</v>
       </c>
       <c r="I235" s="18" t="s">
-        <v>910</v>
+        <v>916</v>
       </c>
       <c r="J235" s="19"/>
       <c r="K235" s="19" t="s">
@@ -13820,7 +14247,7 @@
     </row>
     <row r="236" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A236" s="18" t="s">
-        <v>911</v>
+        <v>917</v>
       </c>
       <c r="B236" s="18" t="s">
         <v>50</v>
@@ -13839,10 +14266,10 @@
       </c>
       <c r="G236" s="18"/>
       <c r="H236" s="18" t="s">
-        <v>912</v>
+        <v>918</v>
       </c>
       <c r="I236" s="18" t="s">
-        <v>913</v>
+        <v>919</v>
       </c>
       <c r="J236" s="19"/>
       <c r="K236" s="19" t="s">
@@ -13855,7 +14282,7 @@
     </row>
     <row r="237" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A237" s="18" t="s">
-        <v>914</v>
+        <v>920</v>
       </c>
       <c r="B237" s="18" t="s">
         <v>50</v>
@@ -13873,13 +14300,13 @@
         <v>94</v>
       </c>
       <c r="G237" s="18" t="s">
-        <v>915</v>
+        <v>921</v>
       </c>
       <c r="H237" s="18" t="s">
-        <v>916</v>
+        <v>922</v>
       </c>
       <c r="I237" s="18" t="s">
-        <v>917</v>
+        <v>923</v>
       </c>
       <c r="J237" s="19"/>
       <c r="K237" s="19" t="s">
@@ -13892,7 +14319,7 @@
     </row>
     <row r="238" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A238" s="18" t="s">
-        <v>918</v>
+        <v>924</v>
       </c>
       <c r="B238" s="18" t="s">
         <v>50</v>
@@ -13911,10 +14338,10 @@
       </c>
       <c r="G238" s="18"/>
       <c r="H238" s="18" t="s">
-        <v>919</v>
+        <v>925</v>
       </c>
       <c r="I238" s="18" t="s">
-        <v>920</v>
+        <v>926</v>
       </c>
       <c r="J238" s="19"/>
       <c r="K238" s="19" t="s">
@@ -13927,7 +14354,7 @@
     </row>
     <row r="239" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A239" s="18" t="s">
-        <v>921</v>
+        <v>927</v>
       </c>
       <c r="B239" s="18" t="s">
         <v>50</v>
@@ -13945,13 +14372,13 @@
         <v>94</v>
       </c>
       <c r="G239" s="18" t="s">
-        <v>922</v>
+        <v>928</v>
       </c>
       <c r="H239" s="18" t="s">
-        <v>923</v>
+        <v>929</v>
       </c>
       <c r="I239" s="18" t="s">
-        <v>924</v>
+        <v>930</v>
       </c>
       <c r="J239" s="19"/>
       <c r="K239" s="19" t="s">
@@ -13964,7 +14391,7 @@
     </row>
     <row r="240" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A240" s="18" t="s">
-        <v>925</v>
+        <v>931</v>
       </c>
       <c r="B240" s="18" t="s">
         <v>50</v>
@@ -13982,13 +14409,13 @@
         <v>94</v>
       </c>
       <c r="G240" s="18" t="s">
-        <v>926</v>
+        <v>932</v>
       </c>
       <c r="H240" s="18" t="s">
-        <v>927</v>
+        <v>933</v>
       </c>
       <c r="I240" s="18" t="s">
-        <v>928</v>
+        <v>934</v>
       </c>
       <c r="J240" s="19"/>
       <c r="K240" s="19" t="s">
@@ -14001,7 +14428,7 @@
     </row>
     <row r="241" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A241" s="18" t="s">
-        <v>929</v>
+        <v>935</v>
       </c>
       <c r="B241" s="18" t="s">
         <v>50</v>
@@ -14019,13 +14446,13 @@
         <v>94</v>
       </c>
       <c r="G241" s="18" t="s">
-        <v>930</v>
+        <v>936</v>
       </c>
       <c r="H241" s="18" t="s">
-        <v>931</v>
+        <v>937</v>
       </c>
       <c r="I241" s="18" t="s">
-        <v>932</v>
+        <v>938</v>
       </c>
       <c r="J241" s="19"/>
       <c r="K241" s="19" t="s">
@@ -14038,13 +14465,13 @@
     </row>
     <row r="242" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A242" s="18" t="s">
-        <v>933</v>
+        <v>939</v>
       </c>
       <c r="B242" s="18" t="s">
         <v>50</v>
       </c>
       <c r="C242" s="18" t="s">
-        <v>934</v>
+        <v>940</v>
       </c>
       <c r="D242" s="18" t="s">
         <v>93</v>
@@ -14057,10 +14484,10 @@
       </c>
       <c r="G242" s="18"/>
       <c r="H242" s="18" t="s">
-        <v>935</v>
+        <v>941</v>
       </c>
       <c r="I242" s="18" t="s">
-        <v>936</v>
+        <v>942</v>
       </c>
       <c r="J242" s="19"/>
       <c r="K242" s="19" t="s">
@@ -14073,13 +14500,13 @@
     </row>
     <row r="243" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A243" s="18" t="s">
-        <v>937</v>
+        <v>943</v>
       </c>
       <c r="B243" s="18" t="s">
         <v>50</v>
       </c>
       <c r="C243" s="18" t="s">
-        <v>938</v>
+        <v>944</v>
       </c>
       <c r="D243" s="18" t="s">
         <v>93</v>
@@ -14091,13 +14518,13 @@
         <v>94</v>
       </c>
       <c r="G243" s="18" t="s">
-        <v>939</v>
+        <v>945</v>
       </c>
       <c r="H243" s="18" t="s">
-        <v>940</v>
+        <v>946</v>
       </c>
       <c r="I243" s="18" t="s">
-        <v>941</v>
+        <v>947</v>
       </c>
       <c r="J243" s="19"/>
       <c r="K243" s="19" t="s">
@@ -14110,7 +14537,7 @@
     </row>
     <row r="244" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A244" s="18" t="s">
-        <v>942</v>
+        <v>948</v>
       </c>
       <c r="B244" s="18" t="s">
         <v>50</v>
@@ -14129,10 +14556,10 @@
       </c>
       <c r="G244" s="18"/>
       <c r="H244" s="18" t="s">
-        <v>943</v>
+        <v>949</v>
       </c>
       <c r="I244" s="18" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="J244" s="19"/>
       <c r="K244" s="19" t="s">
@@ -14145,7 +14572,7 @@
     </row>
     <row r="245" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A245" s="18" t="s">
-        <v>945</v>
+        <v>951</v>
       </c>
       <c r="B245" s="18" t="s">
         <v>50</v>
@@ -14166,10 +14593,10 @@
         <v>350</v>
       </c>
       <c r="H245" s="18" t="s">
-        <v>946</v>
+        <v>952</v>
       </c>
       <c r="I245" s="18" t="s">
-        <v>947</v>
+        <v>953</v>
       </c>
       <c r="J245" s="19"/>
       <c r="K245" s="19" t="s">
@@ -14182,7 +14609,7 @@
     </row>
     <row r="246" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A246" s="18" t="s">
-        <v>948</v>
+        <v>954</v>
       </c>
       <c r="B246" s="18" t="s">
         <v>50</v>
@@ -14197,16 +14624,16 @@
         <v>83</v>
       </c>
       <c r="F246" s="18" t="s">
-        <v>949</v>
+        <v>955</v>
       </c>
       <c r="G246" s="18" t="s">
-        <v>950</v>
+        <v>956</v>
       </c>
       <c r="H246" s="18" t="s">
-        <v>951</v>
+        <v>957</v>
       </c>
       <c r="I246" s="18" t="s">
-        <v>952</v>
+        <v>958</v>
       </c>
       <c r="J246" s="19"/>
       <c r="K246" s="19" t="s">
@@ -14219,13 +14646,13 @@
     </row>
     <row r="247" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A247" s="18" t="s">
-        <v>953</v>
+        <v>959</v>
       </c>
       <c r="B247" s="18" t="s">
         <v>50</v>
       </c>
       <c r="C247" s="18" t="s">
-        <v>954</v>
+        <v>960</v>
       </c>
       <c r="D247" s="18" t="s">
         <v>110</v>
@@ -14238,10 +14665,10 @@
       </c>
       <c r="G247" s="18"/>
       <c r="H247" s="18" t="s">
-        <v>955</v>
+        <v>961</v>
       </c>
       <c r="I247" s="18" t="s">
-        <v>956</v>
+        <v>962</v>
       </c>
       <c r="J247" s="19"/>
       <c r="K247" s="19" t="s">
@@ -14254,13 +14681,13 @@
     </row>
     <row r="248" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A248" s="18" t="s">
-        <v>957</v>
+        <v>963</v>
       </c>
       <c r="B248" s="18" t="s">
         <v>50</v>
       </c>
       <c r="C248" s="18" t="s">
-        <v>958</v>
+        <v>964</v>
       </c>
       <c r="D248" s="18" t="s">
         <v>93</v>
@@ -14273,10 +14700,10 @@
       </c>
       <c r="G248" s="18"/>
       <c r="H248" s="18" t="s">
-        <v>959</v>
+        <v>965</v>
       </c>
       <c r="I248" s="18" t="s">
-        <v>960</v>
+        <v>966</v>
       </c>
       <c r="J248" s="19"/>
       <c r="K248" s="19" t="s">
@@ -14289,7 +14716,7 @@
     </row>
     <row r="249" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A249" s="18" t="s">
-        <v>961</v>
+        <v>967</v>
       </c>
       <c r="B249" s="18" t="s">
         <v>50</v>
@@ -14307,13 +14734,13 @@
         <v>168</v>
       </c>
       <c r="G249" s="18" t="s">
-        <v>962</v>
+        <v>968</v>
       </c>
       <c r="H249" s="18" t="s">
-        <v>963</v>
+        <v>969</v>
       </c>
       <c r="I249" s="18" t="s">
-        <v>964</v>
+        <v>970</v>
       </c>
       <c r="J249" s="19"/>
       <c r="K249" s="19" t="s">
@@ -14326,13 +14753,13 @@
     </row>
     <row r="250" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A250" s="18" t="s">
-        <v>965</v>
+        <v>971</v>
       </c>
       <c r="B250" s="18" t="s">
         <v>50</v>
       </c>
       <c r="C250" s="18" t="s">
-        <v>966</v>
+        <v>972</v>
       </c>
       <c r="D250" s="18" t="s">
         <v>82</v>
@@ -14344,13 +14771,13 @@
         <v>94</v>
       </c>
       <c r="G250" s="18" t="s">
-        <v>967</v>
+        <v>973</v>
       </c>
       <c r="H250" s="18" t="s">
-        <v>968</v>
+        <v>974</v>
       </c>
       <c r="I250" s="18" t="s">
-        <v>969</v>
+        <v>975</v>
       </c>
       <c r="J250" s="19"/>
       <c r="K250" s="19" t="s">
@@ -14363,7 +14790,7 @@
     </row>
     <row r="251" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A251" s="18" t="s">
-        <v>970</v>
+        <v>976</v>
       </c>
       <c r="B251" s="18" t="s">
         <v>51</v>
@@ -14382,10 +14809,10 @@
       </c>
       <c r="G251" s="18"/>
       <c r="H251" s="18" t="s">
-        <v>971</v>
+        <v>977</v>
       </c>
       <c r="I251" s="18" t="s">
-        <v>972</v>
+        <v>978</v>
       </c>
       <c r="J251" s="19"/>
       <c r="K251" s="19" t="s">
@@ -14398,7 +14825,7 @@
     </row>
     <row r="252" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A252" s="18" t="s">
-        <v>973</v>
+        <v>979</v>
       </c>
       <c r="B252" s="18" t="s">
         <v>51</v>
@@ -14417,10 +14844,10 @@
       </c>
       <c r="G252" s="18"/>
       <c r="H252" s="18" t="s">
-        <v>974</v>
+        <v>980</v>
       </c>
       <c r="I252" s="18" t="s">
-        <v>975</v>
+        <v>981</v>
       </c>
       <c r="J252" s="19"/>
       <c r="K252" s="19" t="s">
@@ -14433,13 +14860,13 @@
     </row>
     <row r="253" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A253" s="18" t="s">
-        <v>976</v>
+        <v>982</v>
       </c>
       <c r="B253" s="18" t="s">
         <v>51</v>
       </c>
       <c r="C253" s="18" t="s">
-        <v>977</v>
+        <v>983</v>
       </c>
       <c r="D253" s="18" t="s">
         <v>110</v>
@@ -14452,10 +14879,10 @@
       </c>
       <c r="G253" s="18"/>
       <c r="H253" s="18" t="s">
-        <v>978</v>
+        <v>984</v>
       </c>
       <c r="I253" s="18" t="s">
-        <v>979</v>
+        <v>985</v>
       </c>
       <c r="J253" s="19"/>
       <c r="K253" s="19" t="s">
@@ -14468,13 +14895,13 @@
     </row>
     <row r="254" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A254" s="18" t="s">
-        <v>980</v>
+        <v>986</v>
       </c>
       <c r="B254" s="18" t="s">
         <v>51</v>
       </c>
       <c r="C254" s="18" t="s">
-        <v>977</v>
+        <v>983</v>
       </c>
       <c r="D254" s="18" t="s">
         <v>93</v>
@@ -14487,10 +14914,10 @@
       </c>
       <c r="G254" s="18"/>
       <c r="H254" s="18" t="s">
-        <v>981</v>
+        <v>987</v>
       </c>
       <c r="I254" s="18" t="s">
-        <v>982</v>
+        <v>988</v>
       </c>
       <c r="J254" s="19"/>
       <c r="K254" s="19" t="s">
@@ -14503,7 +14930,7 @@
     </row>
     <row r="255" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A255" s="18" t="s">
-        <v>983</v>
+        <v>989</v>
       </c>
       <c r="B255" s="18" t="s">
         <v>51</v>
@@ -14522,10 +14949,10 @@
       </c>
       <c r="G255" s="18"/>
       <c r="H255" s="18" t="s">
-        <v>984</v>
+        <v>990</v>
       </c>
       <c r="I255" s="18" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="J255" s="19"/>
       <c r="K255" s="19" t="s">
@@ -14538,7 +14965,7 @@
     </row>
     <row r="256" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A256" s="18" t="s">
-        <v>985</v>
+        <v>991</v>
       </c>
       <c r="B256" s="18" t="s">
         <v>51</v>
@@ -14556,13 +14983,13 @@
         <v>94</v>
       </c>
       <c r="G256" s="18" t="s">
-        <v>986</v>
+        <v>992</v>
       </c>
       <c r="H256" s="18" t="s">
-        <v>987</v>
+        <v>993</v>
       </c>
       <c r="I256" s="18" t="s">
-        <v>988</v>
+        <v>994</v>
       </c>
       <c r="J256" s="19"/>
       <c r="K256" s="19" t="s">
@@ -14575,7 +15002,7 @@
     </row>
     <row r="257" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A257" s="18" t="s">
-        <v>989</v>
+        <v>995</v>
       </c>
       <c r="B257" s="18" t="s">
         <v>51</v>
@@ -14594,10 +15021,10 @@
       </c>
       <c r="G257" s="18"/>
       <c r="H257" s="18" t="s">
-        <v>990</v>
+        <v>996</v>
       </c>
       <c r="I257" s="18" t="s">
-        <v>991</v>
+        <v>997</v>
       </c>
       <c r="J257" s="19"/>
       <c r="K257" s="19" t="s">
@@ -14610,7 +15037,7 @@
     </row>
     <row r="258" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A258" s="18" t="s">
-        <v>992</v>
+        <v>998</v>
       </c>
       <c r="B258" s="18" t="s">
         <v>51</v>
@@ -14628,13 +15055,13 @@
         <v>94</v>
       </c>
       <c r="G258" s="18" t="s">
-        <v>993</v>
+        <v>999</v>
       </c>
       <c r="H258" s="18" t="s">
-        <v>994</v>
+        <v>1000</v>
       </c>
       <c r="I258" s="18" t="s">
-        <v>995</v>
+        <v>1001</v>
       </c>
       <c r="J258" s="19"/>
       <c r="K258" s="19" t="s">
@@ -14647,16 +15074,16 @@
     </row>
     <row r="259" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A259" s="18" t="s">
-        <v>996</v>
+        <v>1002</v>
       </c>
       <c r="B259" s="18" t="s">
         <v>51</v>
       </c>
       <c r="C259" s="18" t="s">
-        <v>997</v>
+        <v>1003</v>
       </c>
       <c r="D259" s="18" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="E259" s="18" t="s">
         <v>99</v>
@@ -14666,10 +15093,10 @@
       </c>
       <c r="G259" s="18"/>
       <c r="H259" s="18" t="s">
-        <v>998</v>
+        <v>1004</v>
       </c>
       <c r="I259" s="18" t="s">
-        <v>999</v>
+        <v>1005</v>
       </c>
       <c r="J259" s="19"/>
       <c r="K259" s="19" t="s">
@@ -14682,7 +15109,7 @@
     </row>
     <row r="260" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A260" s="18" t="s">
-        <v>1000</v>
+        <v>1006</v>
       </c>
       <c r="B260" s="18" t="s">
         <v>51</v>
@@ -14697,16 +15124,16 @@
         <v>83</v>
       </c>
       <c r="F260" s="18" t="s">
-        <v>1001</v>
+        <v>1007</v>
       </c>
       <c r="G260" s="18" t="s">
-        <v>1002</v>
+        <v>1008</v>
       </c>
       <c r="H260" s="18" t="s">
-        <v>1003</v>
+        <v>1009</v>
       </c>
       <c r="I260" s="18" t="s">
-        <v>1004</v>
+        <v>1010</v>
       </c>
       <c r="J260" s="19"/>
       <c r="K260" s="19" t="s">
@@ -14719,7 +15146,7 @@
     </row>
     <row r="261" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A261" s="18" t="s">
-        <v>1005</v>
+        <v>1011</v>
       </c>
       <c r="B261" s="18" t="s">
         <v>51</v>
@@ -14737,13 +15164,13 @@
         <v>168</v>
       </c>
       <c r="G261" s="18" t="s">
-        <v>1006</v>
+        <v>1012</v>
       </c>
       <c r="H261" s="18" t="s">
-        <v>971</v>
+        <v>977</v>
       </c>
       <c r="I261" s="18" t="s">
-        <v>1007</v>
+        <v>1013</v>
       </c>
       <c r="J261" s="19"/>
       <c r="K261" s="19" t="s">
@@ -14756,13 +15183,13 @@
     </row>
     <row r="262" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A262" s="18" t="s">
-        <v>1008</v>
+        <v>1014</v>
       </c>
       <c r="B262" s="18" t="s">
         <v>52</v>
       </c>
       <c r="C262" s="18" t="s">
-        <v>1009</v>
+        <v>1015</v>
       </c>
       <c r="D262" s="18" t="s">
         <v>93</v>
@@ -14771,16 +15198,16 @@
         <v>83</v>
       </c>
       <c r="F262" s="18" t="s">
-        <v>1010</v>
+        <v>1016</v>
       </c>
       <c r="G262" s="18" t="s">
         <v>116</v>
       </c>
       <c r="H262" s="18" t="s">
-        <v>1011</v>
+        <v>1017</v>
       </c>
       <c r="I262" s="18" t="s">
-        <v>1012</v>
+        <v>1018</v>
       </c>
       <c r="J262" s="19"/>
       <c r="K262" s="19" t="s">
@@ -14793,13 +15220,13 @@
     </row>
     <row r="263" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A263" s="18" t="s">
-        <v>1013</v>
+        <v>1019</v>
       </c>
       <c r="B263" s="18" t="s">
         <v>52</v>
       </c>
       <c r="C263" s="18" t="s">
-        <v>1009</v>
+        <v>1015</v>
       </c>
       <c r="D263" s="18" t="s">
         <v>93</v>
@@ -14808,14 +15235,14 @@
         <v>83</v>
       </c>
       <c r="F263" s="18" t="s">
-        <v>1010</v>
+        <v>1016</v>
       </c>
       <c r="G263" s="18"/>
       <c r="H263" s="18" t="s">
-        <v>1014</v>
+        <v>1020</v>
       </c>
       <c r="I263" s="18" t="s">
-        <v>1015</v>
+        <v>1021</v>
       </c>
       <c r="J263" s="19"/>
       <c r="K263" s="19" t="s">
@@ -14828,13 +15255,13 @@
     </row>
     <row r="264" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A264" s="18" t="s">
-        <v>1016</v>
+        <v>1022</v>
       </c>
       <c r="B264" s="18" t="s">
         <v>52</v>
       </c>
       <c r="C264" s="18" t="s">
-        <v>1009</v>
+        <v>1015</v>
       </c>
       <c r="D264" s="18" t="s">
         <v>132</v>
@@ -14843,14 +15270,14 @@
         <v>83</v>
       </c>
       <c r="F264" s="18" t="s">
-        <v>1010</v>
+        <v>1016</v>
       </c>
       <c r="G264" s="18"/>
       <c r="H264" s="18" t="s">
-        <v>1017</v>
+        <v>1023</v>
       </c>
       <c r="I264" s="18" t="s">
-        <v>1018</v>
+        <v>1024</v>
       </c>
       <c r="J264" s="19"/>
       <c r="K264" s="19" t="s">
@@ -14863,13 +15290,13 @@
     </row>
     <row r="265" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A265" s="18" t="s">
-        <v>1019</v>
+        <v>1025</v>
       </c>
       <c r="B265" s="18" t="s">
         <v>52</v>
       </c>
       <c r="C265" s="18" t="s">
-        <v>1009</v>
+        <v>1015</v>
       </c>
       <c r="D265" s="18" t="s">
         <v>106</v>
@@ -14878,14 +15305,14 @@
         <v>99</v>
       </c>
       <c r="F265" s="18" t="s">
-        <v>1010</v>
+        <v>1016</v>
       </c>
       <c r="G265" s="18"/>
       <c r="H265" s="18" t="s">
-        <v>1020</v>
+        <v>1026</v>
       </c>
       <c r="I265" s="18" t="s">
-        <v>1021</v>
+        <v>1027</v>
       </c>
       <c r="J265" s="19"/>
       <c r="K265" s="19" t="s">
@@ -14898,13 +15325,13 @@
     </row>
     <row r="266" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A266" s="18" t="s">
-        <v>1022</v>
+        <v>1028</v>
       </c>
       <c r="B266" s="18" t="s">
         <v>52</v>
       </c>
       <c r="C266" s="18" t="s">
-        <v>958</v>
+        <v>964</v>
       </c>
       <c r="D266" s="18" t="s">
         <v>93</v>
@@ -14913,11 +15340,11 @@
         <v>99</v>
       </c>
       <c r="F266" s="18" t="s">
-        <v>1010</v>
+        <v>1016</v>
       </c>
       <c r="G266" s="18"/>
       <c r="H266" s="18" t="s">
-        <v>1023</v>
+        <v>1029</v>
       </c>
       <c r="I266" s="18" t="s">
         <v>289</v>
@@ -14933,13 +15360,13 @@
     </row>
     <row r="267" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A267" s="18" t="s">
-        <v>1024</v>
+        <v>1030</v>
       </c>
       <c r="B267" s="18" t="s">
         <v>52</v>
       </c>
       <c r="C267" s="18" t="s">
-        <v>1025</v>
+        <v>1031</v>
       </c>
       <c r="D267" s="18" t="s">
         <v>93</v>
@@ -14948,14 +15375,14 @@
         <v>83</v>
       </c>
       <c r="F267" s="18" t="s">
-        <v>1010</v>
+        <v>1016</v>
       </c>
       <c r="G267" s="18"/>
       <c r="H267" s="18" t="s">
-        <v>1026</v>
+        <v>1032</v>
       </c>
       <c r="I267" s="18" t="s">
-        <v>1027</v>
+        <v>1033</v>
       </c>
       <c r="J267" s="19"/>
       <c r="K267" s="19" t="s">
@@ -14968,13 +15395,13 @@
     </row>
     <row r="268" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A268" s="18" t="s">
-        <v>1028</v>
+        <v>1034</v>
       </c>
       <c r="B268" s="18" t="s">
         <v>52</v>
       </c>
       <c r="C268" s="18" t="s">
-        <v>1025</v>
+        <v>1031</v>
       </c>
       <c r="D268" s="18" t="s">
         <v>82</v>
@@ -14983,14 +15410,14 @@
         <v>83</v>
       </c>
       <c r="F268" s="18" t="s">
-        <v>1010</v>
+        <v>1016</v>
       </c>
       <c r="G268" s="18"/>
       <c r="H268" s="18" t="s">
-        <v>1029</v>
+        <v>1035</v>
       </c>
       <c r="I268" s="18" t="s">
-        <v>1030</v>
+        <v>1036</v>
       </c>
       <c r="J268" s="19"/>
       <c r="K268" s="19" t="s">
@@ -15003,13 +15430,13 @@
     </row>
     <row r="269" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A269" s="18" t="s">
-        <v>1031</v>
+        <v>1037</v>
       </c>
       <c r="B269" s="18" t="s">
         <v>52</v>
       </c>
       <c r="C269" s="18" t="s">
-        <v>1032</v>
+        <v>1038</v>
       </c>
       <c r="D269" s="18" t="s">
         <v>110</v>
@@ -15018,14 +15445,14 @@
         <v>111</v>
       </c>
       <c r="F269" s="18" t="s">
-        <v>1010</v>
+        <v>1016</v>
       </c>
       <c r="G269" s="18"/>
       <c r="H269" s="18" t="s">
-        <v>1033</v>
+        <v>1039</v>
       </c>
       <c r="I269" s="18" t="s">
-        <v>1034</v>
+        <v>1040</v>
       </c>
       <c r="J269" s="19"/>
       <c r="K269" s="19" t="s">
@@ -15038,13 +15465,13 @@
     </row>
     <row r="270" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A270" s="18" t="s">
-        <v>1035</v>
+        <v>1041</v>
       </c>
       <c r="B270" s="18" t="s">
         <v>52</v>
       </c>
       <c r="C270" s="18" t="s">
-        <v>1036</v>
+        <v>1042</v>
       </c>
       <c r="D270" s="18" t="s">
         <v>93</v>
@@ -15053,16 +15480,16 @@
         <v>83</v>
       </c>
       <c r="F270" s="18" t="s">
-        <v>1037</v>
+        <v>1043</v>
       </c>
       <c r="G270" s="18" t="s">
-        <v>1038</v>
+        <v>1044</v>
       </c>
       <c r="H270" s="18" t="s">
-        <v>1039</v>
+        <v>1045</v>
       </c>
       <c r="I270" s="18" t="s">
-        <v>1040</v>
+        <v>1046</v>
       </c>
       <c r="J270" s="19"/>
       <c r="K270" s="19" t="s">
@@ -15075,7 +15502,7 @@
     </row>
     <row r="271" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A271" s="18" t="s">
-        <v>1041</v>
+        <v>1047</v>
       </c>
       <c r="B271" s="18" t="s">
         <v>53</v>
@@ -15094,10 +15521,10 @@
       </c>
       <c r="G271" s="18"/>
       <c r="H271" s="18" t="s">
-        <v>1042</v>
+        <v>1048</v>
       </c>
       <c r="I271" s="18" t="s">
-        <v>1043</v>
+        <v>1049</v>
       </c>
       <c r="J271" s="19"/>
       <c r="K271" s="19" t="s">
@@ -15110,7 +15537,7 @@
     </row>
     <row r="272" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A272" s="18" t="s">
-        <v>1044</v>
+        <v>1050</v>
       </c>
       <c r="B272" s="18" t="s">
         <v>53</v>
@@ -15129,10 +15556,10 @@
       </c>
       <c r="G272" s="18"/>
       <c r="H272" s="18" t="s">
-        <v>1045</v>
+        <v>1051</v>
       </c>
       <c r="I272" s="18" t="s">
-        <v>1046</v>
+        <v>1052</v>
       </c>
       <c r="J272" s="19"/>
       <c r="K272" s="19" t="s">
@@ -15145,7 +15572,7 @@
     </row>
     <row r="273" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A273" s="18" t="s">
-        <v>1047</v>
+        <v>1053</v>
       </c>
       <c r="B273" s="18" t="s">
         <v>53</v>
@@ -15164,10 +15591,10 @@
       </c>
       <c r="G273" s="18"/>
       <c r="H273" s="18" t="s">
-        <v>1048</v>
+        <v>1054</v>
       </c>
       <c r="I273" s="18" t="s">
-        <v>1049</v>
+        <v>1055</v>
       </c>
       <c r="J273" s="19"/>
       <c r="K273" s="19" t="s">
@@ -15180,7 +15607,7 @@
     </row>
     <row r="274" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A274" s="18" t="s">
-        <v>1050</v>
+        <v>1056</v>
       </c>
       <c r="B274" s="18" t="s">
         <v>53</v>
@@ -15199,10 +15626,10 @@
       </c>
       <c r="G274" s="18"/>
       <c r="H274" s="18" t="s">
-        <v>1051</v>
+        <v>1057</v>
       </c>
       <c r="I274" s="18" t="s">
-        <v>1052</v>
+        <v>1058</v>
       </c>
       <c r="J274" s="19"/>
       <c r="K274" s="19" t="s">
@@ -15215,7 +15642,7 @@
     </row>
     <row r="275" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A275" s="18" t="s">
-        <v>1053</v>
+        <v>1059</v>
       </c>
       <c r="B275" s="18" t="s">
         <v>53</v>
@@ -15234,10 +15661,10 @@
       </c>
       <c r="G275" s="18"/>
       <c r="H275" s="18" t="s">
-        <v>1054</v>
+        <v>1060</v>
       </c>
       <c r="I275" s="18" t="s">
-        <v>1055</v>
+        <v>1061</v>
       </c>
       <c r="J275" s="19"/>
       <c r="K275" s="19" t="s">
@@ -15250,7 +15677,7 @@
     </row>
     <row r="276" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A276" s="18" t="s">
-        <v>1056</v>
+        <v>1062</v>
       </c>
       <c r="B276" s="18" t="s">
         <v>53</v>
@@ -15269,10 +15696,10 @@
       </c>
       <c r="G276" s="18"/>
       <c r="H276" s="18" t="s">
-        <v>1057</v>
+        <v>1063</v>
       </c>
       <c r="I276" s="18" t="s">
-        <v>1058</v>
+        <v>1064</v>
       </c>
       <c r="J276" s="19"/>
       <c r="K276" s="19" t="s">
@@ -15285,13 +15712,13 @@
     </row>
     <row r="277" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A277" s="18" t="s">
-        <v>1059</v>
+        <v>1065</v>
       </c>
       <c r="B277" s="18" t="s">
         <v>53</v>
       </c>
       <c r="C277" s="18" t="s">
-        <v>966</v>
+        <v>972</v>
       </c>
       <c r="D277" s="18" t="s">
         <v>82</v>
@@ -15303,13 +15730,13 @@
         <v>94</v>
       </c>
       <c r="G277" s="18" t="s">
-        <v>1060</v>
+        <v>1066</v>
       </c>
       <c r="H277" s="18" t="s">
-        <v>1061</v>
+        <v>1067</v>
       </c>
       <c r="I277" s="18" t="s">
-        <v>1062</v>
+        <v>1068</v>
       </c>
       <c r="J277" s="19"/>
       <c r="K277" s="19" t="s">
@@ -15322,7 +15749,7 @@
     </row>
     <row r="278" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A278" s="18" t="s">
-        <v>1063</v>
+        <v>1069</v>
       </c>
       <c r="B278" s="18" t="s">
         <v>53</v>
@@ -15337,16 +15764,16 @@
         <v>83</v>
       </c>
       <c r="F278" s="18" t="s">
-        <v>879</v>
+        <v>885</v>
       </c>
       <c r="G278" s="18" t="s">
-        <v>1064</v>
+        <v>1070</v>
       </c>
       <c r="H278" s="18" t="s">
-        <v>1042</v>
+        <v>1048</v>
       </c>
       <c r="I278" s="18" t="s">
-        <v>1007</v>
+        <v>1013</v>
       </c>
       <c r="J278" s="19"/>
       <c r="K278" s="19" t="s">
@@ -15359,7 +15786,7 @@
     </row>
     <row r="279" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A279" s="18" t="s">
-        <v>1065</v>
+        <v>1071</v>
       </c>
       <c r="B279" s="18" t="s">
         <v>53</v>
@@ -15374,14 +15801,14 @@
         <v>99</v>
       </c>
       <c r="F279" s="18" t="s">
-        <v>1066</v>
+        <v>1072</v>
       </c>
       <c r="G279" s="18"/>
       <c r="H279" s="18" t="s">
-        <v>1042</v>
+        <v>1048</v>
       </c>
       <c r="I279" s="18" t="s">
-        <v>1067</v>
+        <v>1073</v>
       </c>
       <c r="J279" s="19"/>
       <c r="K279" s="19" t="s">
@@ -15394,7 +15821,7 @@
     </row>
     <row r="280" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A280" s="18" t="s">
-        <v>1068</v>
+        <v>1074</v>
       </c>
       <c r="B280" s="18" t="s">
         <v>54</v>
@@ -15413,10 +15840,10 @@
       </c>
       <c r="G280" s="18"/>
       <c r="H280" s="18" t="s">
-        <v>1069</v>
+        <v>1075</v>
       </c>
       <c r="I280" s="18" t="s">
-        <v>1070</v>
+        <v>1076</v>
       </c>
       <c r="J280" s="19"/>
       <c r="K280" s="19" t="s">
@@ -15429,7 +15856,7 @@
     </row>
     <row r="281" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A281" s="18" t="s">
-        <v>1071</v>
+        <v>1077</v>
       </c>
       <c r="B281" s="18" t="s">
         <v>55</v>
@@ -15448,10 +15875,10 @@
       </c>
       <c r="G281" s="18"/>
       <c r="H281" s="18" t="s">
-        <v>1072</v>
+        <v>1078</v>
       </c>
       <c r="I281" s="18" t="s">
-        <v>1073</v>
+        <v>1079</v>
       </c>
       <c r="J281" s="19"/>
       <c r="K281" s="19" t="s">
@@ -15464,7 +15891,7 @@
     </row>
     <row r="282" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A282" s="18" t="s">
-        <v>1074</v>
+        <v>1080</v>
       </c>
       <c r="B282" s="18" t="s">
         <v>55</v>
@@ -15482,13 +15909,13 @@
         <v>168</v>
       </c>
       <c r="G282" s="18" t="s">
-        <v>1075</v>
+        <v>1081</v>
       </c>
       <c r="H282" s="18" t="s">
-        <v>1076</v>
+        <v>1082</v>
       </c>
       <c r="I282" s="18" t="s">
-        <v>1077</v>
+        <v>1083</v>
       </c>
       <c r="J282" s="19"/>
       <c r="K282" s="19" t="s">
@@ -15501,13 +15928,13 @@
     </row>
     <row r="283" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A283" s="18" t="s">
-        <v>1078</v>
+        <v>1084</v>
       </c>
       <c r="B283" s="18" t="s">
         <v>55</v>
       </c>
       <c r="C283" s="18" t="s">
-        <v>1079</v>
+        <v>1085</v>
       </c>
       <c r="D283" s="18" t="s">
         <v>132</v>
@@ -15516,14 +15943,14 @@
         <v>99</v>
       </c>
       <c r="F283" s="18" t="s">
-        <v>1079</v>
+        <v>1085</v>
       </c>
       <c r="G283" s="18"/>
       <c r="H283" s="18" t="s">
-        <v>1080</v>
+        <v>1086</v>
       </c>
       <c r="I283" s="18" t="s">
-        <v>1081</v>
+        <v>1087</v>
       </c>
       <c r="J283" s="19"/>
       <c r="K283" s="19" t="s">
@@ -15532,17 +15959,19 @@
       <c r="L283" s="19"/>
       <c r="M283" s="20"/>
       <c r="N283" s="19"/>
-      <c r="O283" s="19"/>
+      <c r="O283" s="19" t="s">
+        <v>371</v>
+      </c>
     </row>
     <row r="284" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A284" s="18" t="s">
-        <v>1082</v>
+        <v>1088</v>
       </c>
       <c r="B284" s="18" t="s">
         <v>55</v>
       </c>
       <c r="C284" s="18" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="D284" s="18" t="s">
         <v>93</v>
@@ -15551,14 +15980,14 @@
         <v>83</v>
       </c>
       <c r="F284" s="18" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="G284" s="18"/>
       <c r="H284" s="18" t="s">
-        <v>1083</v>
+        <v>1089</v>
       </c>
       <c r="I284" s="18" t="s">
-        <v>1084</v>
+        <v>1090</v>
       </c>
       <c r="J284" s="19"/>
       <c r="K284" s="19" t="s">
@@ -15571,13 +16000,13 @@
     </row>
     <row r="285" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A285" s="18" t="s">
-        <v>1085</v>
+        <v>1091</v>
       </c>
       <c r="B285" s="18" t="s">
         <v>55</v>
       </c>
       <c r="C285" s="18" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="D285" s="18" t="s">
         <v>132</v>
@@ -15586,14 +16015,14 @@
         <v>83</v>
       </c>
       <c r="F285" s="18" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="G285" s="18"/>
       <c r="H285" s="18" t="s">
-        <v>1086</v>
+        <v>1092</v>
       </c>
       <c r="I285" s="18" t="s">
-        <v>1087</v>
+        <v>1093</v>
       </c>
       <c r="J285" s="19"/>
       <c r="K285" s="19" t="s">
@@ -15602,17 +16031,19 @@
       <c r="L285" s="19"/>
       <c r="M285" s="20"/>
       <c r="N285" s="19"/>
-      <c r="O285" s="19"/>
+      <c r="O285" s="19" t="s">
+        <v>371</v>
+      </c>
     </row>
     <row r="286" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A286" s="18" t="s">
-        <v>1088</v>
+        <v>1094</v>
       </c>
       <c r="B286" s="18" t="s">
         <v>55</v>
       </c>
       <c r="C286" s="18" t="s">
-        <v>1089</v>
+        <v>1095</v>
       </c>
       <c r="D286" s="18" t="s">
         <v>93</v>
@@ -15624,13 +16055,13 @@
         <v>94</v>
       </c>
       <c r="G286" s="18" t="s">
-        <v>1090</v>
+        <v>1096</v>
       </c>
       <c r="H286" s="18" t="s">
-        <v>1091</v>
+        <v>1097</v>
       </c>
       <c r="I286" s="18" t="s">
-        <v>1092</v>
+        <v>1098</v>
       </c>
       <c r="J286" s="19"/>
       <c r="K286" s="19" t="s">
@@ -15643,13 +16074,13 @@
     </row>
     <row r="287" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A287" s="18" t="s">
-        <v>1093</v>
+        <v>1099</v>
       </c>
       <c r="B287" s="18" t="s">
         <v>55</v>
       </c>
       <c r="C287" s="18" t="s">
-        <v>1094</v>
+        <v>1100</v>
       </c>
       <c r="D287" s="18" t="s">
         <v>132</v>
@@ -15661,13 +16092,13 @@
         <v>133</v>
       </c>
       <c r="G287" s="18" t="s">
-        <v>1095</v>
+        <v>1101</v>
       </c>
       <c r="H287" s="18" t="s">
-        <v>1096</v>
+        <v>1102</v>
       </c>
       <c r="I287" s="18" t="s">
-        <v>1097</v>
+        <v>1103</v>
       </c>
       <c r="J287" s="19"/>
       <c r="K287" s="19" t="s">
@@ -15680,13 +16111,13 @@
     </row>
     <row r="288" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A288" s="18" t="s">
-        <v>1098</v>
+        <v>1104</v>
       </c>
       <c r="B288" s="18" t="s">
         <v>55</v>
       </c>
       <c r="C288" s="18" t="s">
-        <v>1099</v>
+        <v>1105</v>
       </c>
       <c r="D288" s="18" t="s">
         <v>132</v>
@@ -15699,10 +16130,10 @@
       </c>
       <c r="G288" s="18"/>
       <c r="H288" s="18" t="s">
-        <v>1100</v>
+        <v>1106</v>
       </c>
       <c r="I288" s="18" t="s">
-        <v>1101</v>
+        <v>1107</v>
       </c>
       <c r="J288" s="19"/>
       <c r="K288" s="19" t="s">
@@ -15715,13 +16146,13 @@
     </row>
     <row r="289" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A289" s="18" t="s">
-        <v>1102</v>
+        <v>1108</v>
       </c>
       <c r="B289" s="18" t="s">
         <v>56</v>
       </c>
       <c r="C289" s="18" t="s">
-        <v>1103</v>
+        <v>1109</v>
       </c>
       <c r="D289" s="18" t="s">
         <v>93</v>
@@ -15733,13 +16164,13 @@
         <v>94</v>
       </c>
       <c r="G289" s="18" t="s">
-        <v>1104</v>
+        <v>1110</v>
       </c>
       <c r="H289" s="18" t="s">
-        <v>1105</v>
+        <v>1111</v>
       </c>
       <c r="I289" s="18" t="s">
-        <v>1106</v>
+        <v>1112</v>
       </c>
       <c r="J289" s="19"/>
       <c r="K289" s="19" t="s">
@@ -15752,13 +16183,13 @@
     </row>
     <row r="290" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A290" s="18" t="s">
-        <v>1107</v>
+        <v>1113</v>
       </c>
       <c r="B290" s="18" t="s">
         <v>56</v>
       </c>
       <c r="C290" s="18" t="s">
-        <v>1103</v>
+        <v>1109</v>
       </c>
       <c r="D290" s="18" t="s">
         <v>93</v>
@@ -15770,13 +16201,13 @@
         <v>94</v>
       </c>
       <c r="G290" s="18" t="s">
-        <v>1108</v>
+        <v>1114</v>
       </c>
       <c r="H290" s="18" t="s">
-        <v>1109</v>
+        <v>1115</v>
       </c>
       <c r="I290" s="18" t="s">
-        <v>1110</v>
+        <v>1116</v>
       </c>
       <c r="J290" s="19"/>
       <c r="K290" s="19" t="s">
@@ -15789,13 +16220,13 @@
     </row>
     <row r="291" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A291" s="18" t="s">
-        <v>1111</v>
+        <v>1117</v>
       </c>
       <c r="B291" s="18" t="s">
         <v>56</v>
       </c>
       <c r="C291" s="18" t="s">
-        <v>1103</v>
+        <v>1109</v>
       </c>
       <c r="D291" s="18" t="s">
         <v>93</v>
@@ -15807,13 +16238,13 @@
         <v>94</v>
       </c>
       <c r="G291" s="18" t="s">
-        <v>1112</v>
+        <v>1118</v>
       </c>
       <c r="H291" s="18" t="s">
-        <v>1113</v>
+        <v>1119</v>
       </c>
       <c r="I291" s="18" t="s">
-        <v>1114</v>
+        <v>1120</v>
       </c>
       <c r="J291" s="19"/>
       <c r="K291" s="19" t="s">
@@ -15826,13 +16257,13 @@
     </row>
     <row r="292" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A292" s="18" t="s">
-        <v>1115</v>
+        <v>1121</v>
       </c>
       <c r="B292" s="18" t="s">
         <v>56</v>
       </c>
       <c r="C292" s="18" t="s">
-        <v>1103</v>
+        <v>1109</v>
       </c>
       <c r="D292" s="18" t="s">
         <v>132</v>
@@ -15841,16 +16272,16 @@
         <v>83</v>
       </c>
       <c r="F292" s="18" t="s">
-        <v>1116</v>
+        <v>1122</v>
       </c>
       <c r="G292" s="18" t="s">
-        <v>1117</v>
+        <v>1123</v>
       </c>
       <c r="H292" s="18" t="s">
-        <v>1118</v>
+        <v>1124</v>
       </c>
       <c r="I292" s="18" t="s">
-        <v>1119</v>
+        <v>1125</v>
       </c>
       <c r="J292" s="19"/>
       <c r="K292" s="19" t="s">
@@ -15863,13 +16294,13 @@
     </row>
     <row r="293" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A293" s="18" t="s">
-        <v>1120</v>
+        <v>1126</v>
       </c>
       <c r="B293" s="18" t="s">
         <v>56</v>
       </c>
       <c r="C293" s="18" t="s">
-        <v>1103</v>
+        <v>1109</v>
       </c>
       <c r="D293" s="18" t="s">
         <v>93</v>
@@ -15882,10 +16313,10 @@
       </c>
       <c r="G293" s="18"/>
       <c r="H293" s="18" t="s">
-        <v>1121</v>
+        <v>1127</v>
       </c>
       <c r="I293" s="18" t="s">
-        <v>1122</v>
+        <v>1128</v>
       </c>
       <c r="J293" s="19"/>
       <c r="K293" s="19" t="s">
@@ -15898,13 +16329,13 @@
     </row>
     <row r="294" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A294" s="18" t="s">
-        <v>1123</v>
+        <v>1129</v>
       </c>
       <c r="B294" s="18" t="s">
         <v>56</v>
       </c>
       <c r="C294" s="18" t="s">
-        <v>1124</v>
+        <v>1130</v>
       </c>
       <c r="D294" s="18" t="s">
         <v>93</v>
@@ -15917,10 +16348,10 @@
       </c>
       <c r="G294" s="18"/>
       <c r="H294" s="18" t="s">
-        <v>1125</v>
+        <v>1131</v>
       </c>
       <c r="I294" s="18" t="s">
-        <v>1126</v>
+        <v>1132</v>
       </c>
       <c r="J294" s="19"/>
       <c r="K294" s="19" t="s">
@@ -15933,13 +16364,13 @@
     </row>
     <row r="295" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A295" s="18" t="s">
-        <v>1127</v>
+        <v>1133</v>
       </c>
       <c r="B295" s="18" t="s">
         <v>56</v>
       </c>
       <c r="C295" s="18" t="s">
-        <v>1124</v>
+        <v>1130</v>
       </c>
       <c r="D295" s="18" t="s">
         <v>93</v>
@@ -15952,10 +16383,10 @@
       </c>
       <c r="G295" s="18"/>
       <c r="H295" s="18" t="s">
-        <v>1128</v>
+        <v>1134</v>
       </c>
       <c r="I295" s="18" t="s">
-        <v>1129</v>
+        <v>1135</v>
       </c>
       <c r="J295" s="19"/>
       <c r="K295" s="19" t="s">
@@ -15968,13 +16399,13 @@
     </row>
     <row r="296" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A296" s="18" t="s">
-        <v>1130</v>
+        <v>1136</v>
       </c>
       <c r="B296" s="18" t="s">
         <v>56</v>
       </c>
       <c r="C296" s="18" t="s">
-        <v>1131</v>
+        <v>1137</v>
       </c>
       <c r="D296" s="18" t="s">
         <v>93</v>
@@ -15987,10 +16418,10 @@
       </c>
       <c r="G296" s="18"/>
       <c r="H296" s="18" t="s">
-        <v>1132</v>
+        <v>1138</v>
       </c>
       <c r="I296" s="18" t="s">
-        <v>1133</v>
+        <v>1139</v>
       </c>
       <c r="J296" s="19"/>
       <c r="K296" s="19" t="s">
@@ -16003,13 +16434,13 @@
     </row>
     <row r="297" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A297" s="18" t="s">
-        <v>1134</v>
+        <v>1140</v>
       </c>
       <c r="B297" s="18" t="s">
         <v>56</v>
       </c>
       <c r="C297" s="18" t="s">
-        <v>1135</v>
+        <v>1141</v>
       </c>
       <c r="D297" s="18" t="s">
         <v>93</v>
@@ -16022,10 +16453,10 @@
       </c>
       <c r="G297" s="18"/>
       <c r="H297" s="18" t="s">
-        <v>1136</v>
+        <v>1142</v>
       </c>
       <c r="I297" s="18" t="s">
-        <v>1137</v>
+        <v>1143</v>
       </c>
       <c r="J297" s="19"/>
       <c r="K297" s="19" t="s">
@@ -16038,13 +16469,13 @@
     </row>
     <row r="298" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A298" s="18" t="s">
-        <v>1138</v>
+        <v>1144</v>
       </c>
       <c r="B298" s="18" t="s">
         <v>56</v>
       </c>
       <c r="C298" s="18" t="s">
-        <v>1139</v>
+        <v>1145</v>
       </c>
       <c r="D298" s="18" t="s">
         <v>93</v>
@@ -16057,10 +16488,10 @@
       </c>
       <c r="G298" s="18"/>
       <c r="H298" s="18" t="s">
-        <v>1140</v>
+        <v>1146</v>
       </c>
       <c r="I298" s="18" t="s">
-        <v>1141</v>
+        <v>1147</v>
       </c>
       <c r="J298" s="19"/>
       <c r="K298" s="19" t="s">
@@ -16073,7 +16504,7 @@
     </row>
     <row r="299" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A299" s="18" t="s">
-        <v>1142</v>
+        <v>1148</v>
       </c>
       <c r="B299" s="18" t="s">
         <v>56</v>
@@ -16091,13 +16522,13 @@
         <v>94</v>
       </c>
       <c r="G299" s="18" t="s">
-        <v>1143</v>
+        <v>1149</v>
       </c>
       <c r="H299" s="18" t="s">
-        <v>1144</v>
+        <v>1150</v>
       </c>
       <c r="I299" s="18" t="s">
-        <v>1145</v>
+        <v>1151</v>
       </c>
       <c r="J299" s="19"/>
       <c r="K299" s="19" t="s">
@@ -16110,13 +16541,13 @@
     </row>
     <row r="300" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A300" s="18" t="s">
-        <v>1146</v>
+        <v>1152</v>
       </c>
       <c r="B300" s="18" t="s">
         <v>57</v>
       </c>
       <c r="C300" s="18" t="s">
-        <v>1147</v>
+        <v>1153</v>
       </c>
       <c r="D300" s="18" t="s">
         <v>110</v>
@@ -16129,10 +16560,10 @@
       </c>
       <c r="G300" s="18"/>
       <c r="H300" s="18" t="s">
-        <v>1148</v>
+        <v>1154</v>
       </c>
       <c r="I300" s="18" t="s">
-        <v>1149</v>
+        <v>1155</v>
       </c>
       <c r="J300" s="19"/>
       <c r="K300" s="19" t="s">
@@ -16145,13 +16576,13 @@
     </row>
     <row r="301" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A301" s="18" t="s">
-        <v>1150</v>
+        <v>1156</v>
       </c>
       <c r="B301" s="18" t="s">
         <v>57</v>
       </c>
       <c r="C301" s="18" t="s">
-        <v>1151</v>
+        <v>1157</v>
       </c>
       <c r="D301" s="18" t="s">
         <v>110</v>
@@ -16164,10 +16595,10 @@
       </c>
       <c r="G301" s="18"/>
       <c r="H301" s="18" t="s">
-        <v>1152</v>
+        <v>1158</v>
       </c>
       <c r="I301" s="18" t="s">
-        <v>1153</v>
+        <v>1159</v>
       </c>
       <c r="J301" s="19"/>
       <c r="K301" s="19" t="s">
@@ -16180,13 +16611,13 @@
     </row>
     <row r="302" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A302" s="18" t="s">
-        <v>1154</v>
+        <v>1160</v>
       </c>
       <c r="B302" s="18" t="s">
         <v>57</v>
       </c>
       <c r="C302" s="18" t="s">
-        <v>1155</v>
+        <v>1161</v>
       </c>
       <c r="D302" s="18" t="s">
         <v>110</v>
@@ -16199,10 +16630,10 @@
       </c>
       <c r="G302" s="18"/>
       <c r="H302" s="18" t="s">
-        <v>1156</v>
+        <v>1162</v>
       </c>
       <c r="I302" s="18" t="s">
-        <v>1157</v>
+        <v>1163</v>
       </c>
       <c r="J302" s="19"/>
       <c r="K302" s="19" t="s">
@@ -16215,13 +16646,13 @@
     </row>
     <row r="303" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A303" s="18" t="s">
-        <v>1158</v>
+        <v>1164</v>
       </c>
       <c r="B303" s="18" t="s">
         <v>57</v>
       </c>
       <c r="C303" s="18" t="s">
-        <v>1159</v>
+        <v>1165</v>
       </c>
       <c r="D303" s="18" t="s">
         <v>93</v>
@@ -16233,13 +16664,13 @@
         <v>94</v>
       </c>
       <c r="G303" s="18" t="s">
-        <v>1160</v>
+        <v>1166</v>
       </c>
       <c r="H303" s="18" t="s">
-        <v>1161</v>
+        <v>1167</v>
       </c>
       <c r="I303" s="18" t="s">
-        <v>1162</v>
+        <v>1168</v>
       </c>
       <c r="J303" s="19"/>
       <c r="K303" s="19" t="s">
@@ -16252,13 +16683,13 @@
     </row>
     <row r="304" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A304" s="18" t="s">
-        <v>1163</v>
+        <v>1169</v>
       </c>
       <c r="B304" s="18" t="s">
         <v>57</v>
       </c>
       <c r="C304" s="18" t="s">
-        <v>1164</v>
+        <v>1170</v>
       </c>
       <c r="D304" s="18" t="s">
         <v>82</v>
@@ -16271,10 +16702,10 @@
       </c>
       <c r="G304" s="18"/>
       <c r="H304" s="18" t="s">
-        <v>1165</v>
+        <v>1171</v>
       </c>
       <c r="I304" s="18" t="s">
-        <v>1166</v>
+        <v>1172</v>
       </c>
       <c r="J304" s="19"/>
       <c r="K304" s="19" t="s">
@@ -16287,13 +16718,13 @@
     </row>
     <row r="305" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A305" s="18" t="s">
-        <v>1167</v>
+        <v>1173</v>
       </c>
       <c r="B305" s="18" t="s">
         <v>57</v>
       </c>
       <c r="C305" s="18" t="s">
-        <v>1168</v>
+        <v>1174</v>
       </c>
       <c r="D305" s="18" t="s">
         <v>82</v>
@@ -16306,10 +16737,10 @@
       </c>
       <c r="G305" s="18"/>
       <c r="H305" s="18" t="s">
-        <v>1169</v>
+        <v>1175</v>
       </c>
       <c r="I305" s="18" t="s">
-        <v>1170</v>
+        <v>1176</v>
       </c>
       <c r="J305" s="19"/>
       <c r="K305" s="19" t="s">
@@ -16322,13 +16753,13 @@
     </row>
     <row r="306" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A306" s="18" t="s">
-        <v>1171</v>
+        <v>1177</v>
       </c>
       <c r="B306" s="18" t="s">
         <v>57</v>
       </c>
       <c r="C306" s="18" t="s">
-        <v>1172</v>
+        <v>1178</v>
       </c>
       <c r="D306" s="18" t="s">
         <v>93</v>
@@ -16340,13 +16771,13 @@
         <v>133</v>
       </c>
       <c r="G306" s="18" t="s">
-        <v>1173</v>
+        <v>1179</v>
       </c>
       <c r="H306" s="18" t="s">
-        <v>1174</v>
+        <v>1180</v>
       </c>
       <c r="I306" s="18" t="s">
-        <v>1175</v>
+        <v>1181</v>
       </c>
       <c r="J306" s="19"/>
       <c r="K306" s="19" t="s">
@@ -16359,16 +16790,16 @@
     </row>
     <row r="307" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A307" s="18" t="s">
-        <v>1176</v>
+        <v>1182</v>
       </c>
       <c r="B307" s="18" t="s">
         <v>57</v>
       </c>
       <c r="C307" s="18" t="s">
-        <v>1177</v>
+        <v>1183</v>
       </c>
       <c r="D307" s="18" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="E307" s="18" t="s">
         <v>111</v>
@@ -16378,10 +16809,10 @@
       </c>
       <c r="G307" s="18"/>
       <c r="H307" s="18" t="s">
-        <v>1178</v>
+        <v>1184</v>
       </c>
       <c r="I307" s="18" t="s">
-        <v>1179</v>
+        <v>1185</v>
       </c>
       <c r="J307" s="19"/>
       <c r="K307" s="19" t="s">
@@ -16392,9 +16823,1140 @@
       <c r="N307" s="19"/>
       <c r="O307" s="19"/>
     </row>
+    <row r="308" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A308" s="18" t="s">
+        <v>1186</v>
+      </c>
+      <c r="B308" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="C308" s="18" t="s">
+        <v>1187</v>
+      </c>
+      <c r="D308" s="18" t="s">
+        <v>110</v>
+      </c>
+      <c r="E308" s="18" t="s">
+        <v>99</v>
+      </c>
+      <c r="F308" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="G308" s="18" t="s">
+        <v>85</v>
+      </c>
+      <c r="H308" s="18" t="s">
+        <v>1188</v>
+      </c>
+      <c r="I308" s="18" t="s">
+        <v>1189</v>
+      </c>
+      <c r="J308" s="19"/>
+      <c r="K308" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="L308" s="19"/>
+      <c r="M308" s="20"/>
+      <c r="N308" s="19"/>
+      <c r="O308" s="19" t="s">
+        <v>1190</v>
+      </c>
+    </row>
+    <row r="309" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A309" s="18" t="s">
+        <v>1191</v>
+      </c>
+      <c r="B309" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="C309" s="18" t="s">
+        <v>1192</v>
+      </c>
+      <c r="D309" s="18" t="s">
+        <v>110</v>
+      </c>
+      <c r="E309" s="18" t="s">
+        <v>99</v>
+      </c>
+      <c r="F309" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="G309" s="18" t="s">
+        <v>116</v>
+      </c>
+      <c r="H309" s="18" t="s">
+        <v>1193</v>
+      </c>
+      <c r="I309" s="18" t="s">
+        <v>1194</v>
+      </c>
+      <c r="J309" s="19"/>
+      <c r="K309" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="L309" s="19"/>
+      <c r="M309" s="20"/>
+      <c r="N309" s="19"/>
+      <c r="O309" s="19" t="s">
+        <v>1190</v>
+      </c>
+    </row>
+    <row r="310" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A310" s="18" t="s">
+        <v>1195</v>
+      </c>
+      <c r="B310" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="C310" s="18" t="s">
+        <v>1196</v>
+      </c>
+      <c r="D310" s="18" t="s">
+        <v>93</v>
+      </c>
+      <c r="E310" s="18" t="s">
+        <v>99</v>
+      </c>
+      <c r="F310" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="G310" s="18" t="s">
+        <v>1197</v>
+      </c>
+      <c r="H310" s="18" t="s">
+        <v>1198</v>
+      </c>
+      <c r="I310" s="18" t="s">
+        <v>1199</v>
+      </c>
+      <c r="J310" s="19"/>
+      <c r="K310" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="L310" s="19"/>
+      <c r="M310" s="20"/>
+      <c r="N310" s="19"/>
+      <c r="O310" s="19" t="s">
+        <v>1190</v>
+      </c>
+    </row>
+    <row r="311" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A311" s="18" t="s">
+        <v>1200</v>
+      </c>
+      <c r="B311" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="C311" s="18" t="s">
+        <v>1201</v>
+      </c>
+      <c r="D311" s="18" t="s">
+        <v>110</v>
+      </c>
+      <c r="E311" s="18" t="s">
+        <v>99</v>
+      </c>
+      <c r="F311" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="G311" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="H311" s="18" t="s">
+        <v>1202</v>
+      </c>
+      <c r="I311" s="18" t="s">
+        <v>1203</v>
+      </c>
+      <c r="J311" s="19"/>
+      <c r="K311" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="L311" s="19"/>
+      <c r="M311" s="20"/>
+      <c r="N311" s="19"/>
+      <c r="O311" s="19" t="s">
+        <v>1190</v>
+      </c>
+    </row>
+    <row r="312" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A312" s="18" t="s">
+        <v>1204</v>
+      </c>
+      <c r="B312" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="C312" s="18" t="s">
+        <v>214</v>
+      </c>
+      <c r="D312" s="18" t="s">
+        <v>110</v>
+      </c>
+      <c r="E312" s="18" t="s">
+        <v>111</v>
+      </c>
+      <c r="F312" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="G312" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="H312" s="18" t="s">
+        <v>1205</v>
+      </c>
+      <c r="I312" s="18" t="s">
+        <v>1206</v>
+      </c>
+      <c r="J312" s="19"/>
+      <c r="K312" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="L312" s="19"/>
+      <c r="M312" s="20"/>
+      <c r="N312" s="19"/>
+      <c r="O312" s="19" t="s">
+        <v>1190</v>
+      </c>
+    </row>
+    <row r="313" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A313" s="18" t="s">
+        <v>1207</v>
+      </c>
+      <c r="B313" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="C313" s="18" t="s">
+        <v>1208</v>
+      </c>
+      <c r="D313" s="18" t="s">
+        <v>93</v>
+      </c>
+      <c r="E313" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="F313" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="G313" s="18" t="s">
+        <v>1209</v>
+      </c>
+      <c r="H313" s="18" t="s">
+        <v>1210</v>
+      </c>
+      <c r="I313" s="18" t="s">
+        <v>1211</v>
+      </c>
+      <c r="J313" s="19"/>
+      <c r="K313" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="L313" s="19"/>
+      <c r="M313" s="20"/>
+      <c r="N313" s="19"/>
+      <c r="O313" s="19" t="s">
+        <v>1190</v>
+      </c>
+    </row>
+    <row r="314" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A314" s="18" t="s">
+        <v>1212</v>
+      </c>
+      <c r="B314" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="C314" s="18" t="s">
+        <v>1213</v>
+      </c>
+      <c r="D314" s="18" t="s">
+        <v>93</v>
+      </c>
+      <c r="E314" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="F314" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="G314" s="18" t="s">
+        <v>1214</v>
+      </c>
+      <c r="H314" s="18" t="s">
+        <v>1215</v>
+      </c>
+      <c r="I314" s="18" t="s">
+        <v>1216</v>
+      </c>
+      <c r="J314" s="19"/>
+      <c r="K314" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="L314" s="19"/>
+      <c r="M314" s="20"/>
+      <c r="N314" s="19"/>
+      <c r="O314" s="19" t="s">
+        <v>1190</v>
+      </c>
+    </row>
+    <row r="315" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A315" s="18" t="s">
+        <v>1217</v>
+      </c>
+      <c r="B315" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="C315" s="18" t="s">
+        <v>1218</v>
+      </c>
+      <c r="D315" s="18" t="s">
+        <v>106</v>
+      </c>
+      <c r="E315" s="18" t="s">
+        <v>99</v>
+      </c>
+      <c r="F315" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="G315" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="H315" s="18" t="s">
+        <v>1219</v>
+      </c>
+      <c r="I315" s="18" t="s">
+        <v>1220</v>
+      </c>
+      <c r="J315" s="19"/>
+      <c r="K315" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="L315" s="19"/>
+      <c r="M315" s="20"/>
+      <c r="N315" s="19"/>
+      <c r="O315" s="19" t="s">
+        <v>1190</v>
+      </c>
+    </row>
+    <row r="316" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A316" s="18" t="s">
+        <v>1221</v>
+      </c>
+      <c r="B316" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="C316" s="18" t="s">
+        <v>1222</v>
+      </c>
+      <c r="D316" s="18" t="s">
+        <v>110</v>
+      </c>
+      <c r="E316" s="18" t="s">
+        <v>111</v>
+      </c>
+      <c r="F316" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="G316" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="H316" s="18" t="s">
+        <v>1223</v>
+      </c>
+      <c r="I316" s="18" t="s">
+        <v>1224</v>
+      </c>
+      <c r="J316" s="19"/>
+      <c r="K316" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="L316" s="19"/>
+      <c r="M316" s="20"/>
+      <c r="N316" s="19"/>
+      <c r="O316" s="19" t="s">
+        <v>1190</v>
+      </c>
+    </row>
+    <row r="317" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A317" s="18" t="s">
+        <v>1225</v>
+      </c>
+      <c r="B317" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="C317" s="18" t="s">
+        <v>1226</v>
+      </c>
+      <c r="D317" s="18" t="s">
+        <v>93</v>
+      </c>
+      <c r="E317" s="18" t="s">
+        <v>99</v>
+      </c>
+      <c r="F317" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="G317" s="18" t="s">
+        <v>1227</v>
+      </c>
+      <c r="H317" s="18" t="s">
+        <v>1228</v>
+      </c>
+      <c r="I317" s="18" t="s">
+        <v>1229</v>
+      </c>
+      <c r="J317" s="19"/>
+      <c r="K317" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="L317" s="19"/>
+      <c r="M317" s="20"/>
+      <c r="N317" s="19"/>
+      <c r="O317" s="19" t="s">
+        <v>1190</v>
+      </c>
+    </row>
+    <row r="318" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A318" s="18" t="s">
+        <v>1230</v>
+      </c>
+      <c r="B318" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="C318" s="18" t="s">
+        <v>1231</v>
+      </c>
+      <c r="D318" s="18" t="s">
+        <v>110</v>
+      </c>
+      <c r="E318" s="18" t="s">
+        <v>111</v>
+      </c>
+      <c r="F318" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="G318" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="H318" s="18" t="s">
+        <v>1232</v>
+      </c>
+      <c r="I318" s="18" t="s">
+        <v>1233</v>
+      </c>
+      <c r="J318" s="19"/>
+      <c r="K318" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="L318" s="19"/>
+      <c r="M318" s="20"/>
+      <c r="N318" s="19"/>
+      <c r="O318" s="19" t="s">
+        <v>1190</v>
+      </c>
+    </row>
+    <row r="319" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A319" s="18" t="s">
+        <v>1234</v>
+      </c>
+      <c r="B319" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="C319" s="18" t="s">
+        <v>686</v>
+      </c>
+      <c r="D319" s="18" t="s">
+        <v>93</v>
+      </c>
+      <c r="E319" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="F319" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="G319" s="18" t="s">
+        <v>1235</v>
+      </c>
+      <c r="H319" s="18" t="s">
+        <v>1236</v>
+      </c>
+      <c r="I319" s="18" t="s">
+        <v>1237</v>
+      </c>
+      <c r="J319" s="19"/>
+      <c r="K319" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="L319" s="19"/>
+      <c r="M319" s="20"/>
+      <c r="N319" s="19"/>
+      <c r="O319" s="19" t="s">
+        <v>1190</v>
+      </c>
+    </row>
+    <row r="320" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A320" s="18" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B320" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="C320" s="18" t="s">
+        <v>1239</v>
+      </c>
+      <c r="D320" s="18" t="s">
+        <v>132</v>
+      </c>
+      <c r="E320" s="18" t="s">
+        <v>99</v>
+      </c>
+      <c r="F320" s="18" t="s">
+        <v>168</v>
+      </c>
+      <c r="G320" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="H320" s="18" t="s">
+        <v>1240</v>
+      </c>
+      <c r="I320" s="18" t="s">
+        <v>1241</v>
+      </c>
+      <c r="J320" s="19"/>
+      <c r="K320" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="L320" s="19"/>
+      <c r="M320" s="20"/>
+      <c r="N320" s="19"/>
+      <c r="O320" s="19" t="s">
+        <v>1190</v>
+      </c>
+    </row>
+    <row r="321" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A321" s="18" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B321" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="C321" s="18" t="s">
+        <v>1243</v>
+      </c>
+      <c r="D321" s="18" t="s">
+        <v>82</v>
+      </c>
+      <c r="E321" s="18" t="s">
+        <v>111</v>
+      </c>
+      <c r="F321" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="G321" s="18" t="s">
+        <v>1244</v>
+      </c>
+      <c r="H321" s="18" t="s">
+        <v>1245</v>
+      </c>
+      <c r="I321" s="18" t="s">
+        <v>1246</v>
+      </c>
+      <c r="J321" s="19"/>
+      <c r="K321" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="L321" s="19"/>
+      <c r="M321" s="20"/>
+      <c r="N321" s="19"/>
+      <c r="O321" s="19" t="s">
+        <v>1190</v>
+      </c>
+    </row>
+    <row r="322" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A322" s="18" t="s">
+        <v>1247</v>
+      </c>
+      <c r="B322" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="C322" s="18" t="s">
+        <v>1248</v>
+      </c>
+      <c r="D322" s="18" t="s">
+        <v>82</v>
+      </c>
+      <c r="E322" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="F322" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="G322" s="18" t="s">
+        <v>1249</v>
+      </c>
+      <c r="H322" s="18" t="s">
+        <v>400</v>
+      </c>
+      <c r="I322" s="18" t="s">
+        <v>1250</v>
+      </c>
+      <c r="J322" s="19"/>
+      <c r="K322" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="L322" s="19"/>
+      <c r="M322" s="20"/>
+      <c r="N322" s="19"/>
+      <c r="O322" s="19" t="s">
+        <v>1190</v>
+      </c>
+    </row>
+    <row r="323" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A323" s="18" t="s">
+        <v>1251</v>
+      </c>
+      <c r="B323" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="C323" s="18" t="s">
+        <v>1252</v>
+      </c>
+      <c r="D323" s="18" t="s">
+        <v>93</v>
+      </c>
+      <c r="E323" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="F323" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="G323" s="18" t="s">
+        <v>1253</v>
+      </c>
+      <c r="H323" s="18" t="s">
+        <v>1254</v>
+      </c>
+      <c r="I323" s="18" t="s">
+        <v>1255</v>
+      </c>
+      <c r="J323" s="19"/>
+      <c r="K323" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="L323" s="19"/>
+      <c r="M323" s="20"/>
+      <c r="N323" s="19"/>
+      <c r="O323" s="19" t="s">
+        <v>1190</v>
+      </c>
+    </row>
+    <row r="324" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A324" s="18" t="s">
+        <v>1256</v>
+      </c>
+      <c r="B324" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="C324" s="18" t="s">
+        <v>1257</v>
+      </c>
+      <c r="D324" s="18" t="s">
+        <v>110</v>
+      </c>
+      <c r="E324" s="18" t="s">
+        <v>99</v>
+      </c>
+      <c r="F324" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="G324" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="H324" s="18" t="s">
+        <v>1258</v>
+      </c>
+      <c r="I324" s="18" t="s">
+        <v>1259</v>
+      </c>
+      <c r="J324" s="19"/>
+      <c r="K324" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="L324" s="19"/>
+      <c r="M324" s="20"/>
+      <c r="N324" s="19"/>
+      <c r="O324" s="19" t="s">
+        <v>1190</v>
+      </c>
+    </row>
+    <row r="325" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A325" s="18" t="s">
+        <v>1260</v>
+      </c>
+      <c r="B325" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="C325" s="18" t="s">
+        <v>1261</v>
+      </c>
+      <c r="D325" s="18" t="s">
+        <v>93</v>
+      </c>
+      <c r="E325" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="F325" s="18" t="s">
+        <v>412</v>
+      </c>
+      <c r="G325" s="18" t="s">
+        <v>1262</v>
+      </c>
+      <c r="H325" s="18" t="s">
+        <v>1263</v>
+      </c>
+      <c r="I325" s="18" t="s">
+        <v>1264</v>
+      </c>
+      <c r="J325" s="19"/>
+      <c r="K325" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="L325" s="19"/>
+      <c r="M325" s="20"/>
+      <c r="N325" s="19"/>
+      <c r="O325" s="19" t="s">
+        <v>1190</v>
+      </c>
+    </row>
+    <row r="326" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A326" s="18" t="s">
+        <v>1265</v>
+      </c>
+      <c r="B326" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="C326" s="18" t="s">
+        <v>1266</v>
+      </c>
+      <c r="D326" s="18" t="s">
+        <v>106</v>
+      </c>
+      <c r="E326" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="F326" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="G326" s="18" t="s">
+        <v>464</v>
+      </c>
+      <c r="H326" s="18" t="s">
+        <v>1267</v>
+      </c>
+      <c r="I326" s="18" t="s">
+        <v>1268</v>
+      </c>
+      <c r="J326" s="19"/>
+      <c r="K326" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="L326" s="19"/>
+      <c r="M326" s="20"/>
+      <c r="N326" s="19"/>
+      <c r="O326" s="19" t="s">
+        <v>1269</v>
+      </c>
+    </row>
+    <row r="327" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A327" s="18" t="s">
+        <v>1270</v>
+      </c>
+      <c r="B327" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="C327" s="18" t="s">
+        <v>1271</v>
+      </c>
+      <c r="D327" s="18" t="s">
+        <v>93</v>
+      </c>
+      <c r="E327" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="F327" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="G327" s="18" t="s">
+        <v>1272</v>
+      </c>
+      <c r="H327" s="18" t="s">
+        <v>1273</v>
+      </c>
+      <c r="I327" s="18" t="s">
+        <v>1274</v>
+      </c>
+      <c r="J327" s="19"/>
+      <c r="K327" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="L327" s="19"/>
+      <c r="M327" s="20"/>
+      <c r="N327" s="19"/>
+      <c r="O327" s="19" t="s">
+        <v>1269</v>
+      </c>
+    </row>
+    <row r="328" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A328" s="18" t="s">
+        <v>1275</v>
+      </c>
+      <c r="B328" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="C328" s="18" t="s">
+        <v>1276</v>
+      </c>
+      <c r="D328" s="18" t="s">
+        <v>93</v>
+      </c>
+      <c r="E328" s="18" t="s">
+        <v>99</v>
+      </c>
+      <c r="F328" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="G328" s="18" t="s">
+        <v>1277</v>
+      </c>
+      <c r="H328" s="18" t="s">
+        <v>1278</v>
+      </c>
+      <c r="I328" s="18" t="s">
+        <v>1279</v>
+      </c>
+      <c r="J328" s="19"/>
+      <c r="K328" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="L328" s="19"/>
+      <c r="M328" s="20"/>
+      <c r="N328" s="19"/>
+      <c r="O328" s="19" t="s">
+        <v>1269</v>
+      </c>
+    </row>
+    <row r="329" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A329" s="18" t="s">
+        <v>1280</v>
+      </c>
+      <c r="B329" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="C329" s="18" t="s">
+        <v>1281</v>
+      </c>
+      <c r="D329" s="18" t="s">
+        <v>110</v>
+      </c>
+      <c r="E329" s="18" t="s">
+        <v>99</v>
+      </c>
+      <c r="F329" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="G329" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="H329" s="18" t="s">
+        <v>1282</v>
+      </c>
+      <c r="I329" s="18" t="s">
+        <v>1283</v>
+      </c>
+      <c r="J329" s="19"/>
+      <c r="K329" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="L329" s="19"/>
+      <c r="M329" s="20"/>
+      <c r="N329" s="19"/>
+      <c r="O329" s="19" t="s">
+        <v>1269</v>
+      </c>
+    </row>
+    <row r="330" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A330" s="18" t="s">
+        <v>1284</v>
+      </c>
+      <c r="B330" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="C330" s="18" t="s">
+        <v>1285</v>
+      </c>
+      <c r="D330" s="18" t="s">
+        <v>110</v>
+      </c>
+      <c r="E330" s="18" t="s">
+        <v>111</v>
+      </c>
+      <c r="F330" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="G330" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="H330" s="18" t="s">
+        <v>1286</v>
+      </c>
+      <c r="I330" s="18" t="s">
+        <v>1287</v>
+      </c>
+      <c r="J330" s="19"/>
+      <c r="K330" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="L330" s="19"/>
+      <c r="M330" s="20"/>
+      <c r="N330" s="19"/>
+      <c r="O330" s="19" t="s">
+        <v>1269</v>
+      </c>
+    </row>
+    <row r="331" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A331" s="18" t="s">
+        <v>1288</v>
+      </c>
+      <c r="B331" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="C331" s="18" t="s">
+        <v>1289</v>
+      </c>
+      <c r="D331" s="18" t="s">
+        <v>93</v>
+      </c>
+      <c r="E331" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="F331" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="G331" s="18" t="s">
+        <v>815</v>
+      </c>
+      <c r="H331" s="18" t="s">
+        <v>1290</v>
+      </c>
+      <c r="I331" s="18" t="s">
+        <v>1291</v>
+      </c>
+      <c r="J331" s="19"/>
+      <c r="K331" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="L331" s="19"/>
+      <c r="M331" s="20"/>
+      <c r="N331" s="19"/>
+      <c r="O331" s="19" t="s">
+        <v>1269</v>
+      </c>
+    </row>
+    <row r="332" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A332" s="18" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B332" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="C332" s="18" t="s">
+        <v>1293</v>
+      </c>
+      <c r="D332" s="18" t="s">
+        <v>106</v>
+      </c>
+      <c r="E332" s="18" t="s">
+        <v>99</v>
+      </c>
+      <c r="F332" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="G332" s="18" t="s">
+        <v>815</v>
+      </c>
+      <c r="H332" s="18" t="s">
+        <v>1294</v>
+      </c>
+      <c r="I332" s="18" t="s">
+        <v>1295</v>
+      </c>
+      <c r="J332" s="19"/>
+      <c r="K332" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="L332" s="19"/>
+      <c r="M332" s="20"/>
+      <c r="N332" s="19"/>
+      <c r="O332" s="19" t="s">
+        <v>1269</v>
+      </c>
+    </row>
+    <row r="333" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A333" s="18" t="s">
+        <v>1296</v>
+      </c>
+      <c r="B333" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="C333" s="18" t="s">
+        <v>1297</v>
+      </c>
+      <c r="D333" s="18" t="s">
+        <v>93</v>
+      </c>
+      <c r="E333" s="18" t="s">
+        <v>99</v>
+      </c>
+      <c r="F333" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="G333" s="18" t="s">
+        <v>1298</v>
+      </c>
+      <c r="H333" s="18" t="s">
+        <v>1299</v>
+      </c>
+      <c r="I333" s="18" t="s">
+        <v>1300</v>
+      </c>
+      <c r="J333" s="19"/>
+      <c r="K333" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="L333" s="19"/>
+      <c r="M333" s="20"/>
+      <c r="N333" s="19"/>
+      <c r="O333" s="19" t="s">
+        <v>1269</v>
+      </c>
+    </row>
+    <row r="334" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A334" s="18" t="s">
+        <v>1301</v>
+      </c>
+      <c r="B334" s="18" t="s">
+        <v>50</v>
+      </c>
+      <c r="C334" s="18" t="s">
+        <v>1302</v>
+      </c>
+      <c r="D334" s="18" t="s">
+        <v>93</v>
+      </c>
+      <c r="E334" s="18" t="s">
+        <v>99</v>
+      </c>
+      <c r="F334" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="G334" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="H334" s="18" t="s">
+        <v>1303</v>
+      </c>
+      <c r="I334" s="18" t="s">
+        <v>1304</v>
+      </c>
+      <c r="J334" s="19"/>
+      <c r="K334" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="L334" s="19"/>
+      <c r="M334" s="20"/>
+      <c r="N334" s="19"/>
+      <c r="O334" s="19" t="s">
+        <v>1269</v>
+      </c>
+    </row>
+    <row r="335" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A335" s="18" t="s">
+        <v>1305</v>
+      </c>
+      <c r="B335" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="C335" s="18" t="s">
+        <v>1306</v>
+      </c>
+      <c r="D335" s="18" t="s">
+        <v>110</v>
+      </c>
+      <c r="E335" s="18" t="s">
+        <v>111</v>
+      </c>
+      <c r="F335" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="G335" s="18" t="s">
+        <v>1307</v>
+      </c>
+      <c r="H335" s="18" t="s">
+        <v>1308</v>
+      </c>
+      <c r="I335" s="18" t="s">
+        <v>1309</v>
+      </c>
+      <c r="J335" s="19"/>
+      <c r="K335" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="L335" s="19"/>
+      <c r="M335" s="20"/>
+      <c r="N335" s="19"/>
+      <c r="O335" s="19" t="s">
+        <v>1269</v>
+      </c>
+    </row>
+    <row r="336" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A336" s="18" t="s">
+        <v>1310</v>
+      </c>
+      <c r="B336" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="C336" s="18" t="s">
+        <v>1311</v>
+      </c>
+      <c r="D336" s="18" t="s">
+        <v>93</v>
+      </c>
+      <c r="E336" s="18" t="s">
+        <v>99</v>
+      </c>
+      <c r="F336" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="G336" s="18" t="s">
+        <v>1312</v>
+      </c>
+      <c r="H336" s="18" t="s">
+        <v>1313</v>
+      </c>
+      <c r="I336" s="18" t="s">
+        <v>1314</v>
+      </c>
+      <c r="J336" s="19"/>
+      <c r="K336" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="L336" s="19"/>
+      <c r="M336" s="20"/>
+      <c r="N336" s="19"/>
+      <c r="O336" s="19" t="s">
+        <v>1269</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O307"/>
-  <conditionalFormatting sqref="K2:K307">
+  <autoFilter ref="A1:O336"/>
+  <conditionalFormatting sqref="K2:K336">
     <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
       <formula>"Pass"</formula>
     </cfRule>
@@ -16408,17 +17970,17 @@
       <formula>"Not Run"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2:E307">
+  <conditionalFormatting sqref="A2:E336">
     <cfRule type="expression" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
       <formula>$E2="High"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="K2:K307" type="list">
+    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="K2:K336" type="list">
       <formula1>"Not Run,Pass,Fail,Blocked,N/A"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Enter a date" errorStyle="stop" operator="greaterThan" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="M2:M307" type="date">
+    <dataValidation allowBlank="true" error="Enter a date" errorStyle="stop" operator="greaterThan" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="M2:M336" type="date">
       <formula1>36526</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -16450,195 +18012,195 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>1180</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="10" t="s">
-        <v>1181</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="21" t="s">
-        <v>1182</v>
+        <v>1317</v>
       </c>
       <c r="B4" s="21" t="s">
-        <v>1183</v>
+        <v>1318</v>
       </c>
       <c r="C4" s="21" t="s">
-        <v>1184</v>
+        <v>1319</v>
       </c>
       <c r="D4" s="21" t="s">
-        <v>1185</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="18" t="s">
-        <v>1186</v>
+        <v>1321</v>
       </c>
       <c r="B5" s="18" t="s">
         <v>94</v>
       </c>
       <c r="C5" s="18" t="s">
-        <v>1187</v>
+        <v>1322</v>
       </c>
       <c r="D5" s="18" t="s">
-        <v>1188</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="18" t="s">
-        <v>1189</v>
+        <v>1324</v>
       </c>
       <c r="B6" s="18" t="s">
         <v>94</v>
       </c>
       <c r="C6" s="18" t="s">
-        <v>1190</v>
+        <v>1325</v>
       </c>
       <c r="D6" s="18" t="s">
-        <v>1191</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="18" t="s">
-        <v>1192</v>
+        <v>1327</v>
       </c>
       <c r="B7" s="18" t="s">
         <v>168</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>1193</v>
+        <v>1328</v>
       </c>
       <c r="D7" s="18" t="s">
-        <v>1194</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="18" t="s">
-        <v>1195</v>
+        <v>1330</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>1079</v>
+        <v>1085</v>
       </c>
       <c r="C8" s="18" t="s">
-        <v>1196</v>
+        <v>1331</v>
       </c>
       <c r="D8" s="18" t="s">
-        <v>1197</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="18" t="s">
-        <v>1198</v>
+        <v>1333</v>
       </c>
       <c r="B9" s="18" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C9" s="18" t="s">
-        <v>1199</v>
+        <v>1334</v>
       </c>
       <c r="D9" s="18" t="s">
-        <v>1200</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="18" t="s">
-        <v>1201</v>
+        <v>1336</v>
       </c>
       <c r="B10" s="18" t="s">
-        <v>1202</v>
+        <v>1337</v>
       </c>
       <c r="C10" s="18" t="s">
-        <v>1203</v>
+        <v>1338</v>
       </c>
       <c r="D10" s="18" t="s">
-        <v>1204</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>1205</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="21" t="s">
-        <v>1206</v>
+        <v>1341</v>
       </c>
       <c r="B13" s="21" t="s">
-        <v>1207</v>
+        <v>1342</v>
       </c>
       <c r="C13" s="21" t="s">
-        <v>1208</v>
+        <v>1343</v>
       </c>
       <c r="D13" s="21" t="s">
-        <v>1185</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="18" t="s">
-        <v>1209</v>
+        <v>1344</v>
       </c>
       <c r="B14" s="18" t="s">
         <v>269</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>1210</v>
+        <v>1345</v>
       </c>
       <c r="D14" s="18" t="s">
-        <v>1211</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="18" t="s">
-        <v>1212</v>
+        <v>1347</v>
       </c>
       <c r="B15" s="18" t="s">
-        <v>1213</v>
+        <v>1348</v>
       </c>
       <c r="C15" s="18" t="s">
-        <v>1214</v>
+        <v>1349</v>
       </c>
       <c r="D15" s="18"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="18" t="s">
-        <v>1215</v>
+        <v>1350</v>
       </c>
       <c r="B16" s="18" t="s">
-        <v>1216</v>
+        <v>1351</v>
       </c>
       <c r="C16" s="18" t="s">
-        <v>1217</v>
+        <v>1352</v>
       </c>
       <c r="D16" s="18" t="s">
-        <v>1218</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="18" t="s">
-        <v>1215</v>
+        <v>1350</v>
       </c>
       <c r="B17" s="18" t="s">
-        <v>1219</v>
+        <v>1354</v>
       </c>
       <c r="C17" s="18" t="s">
-        <v>1220</v>
+        <v>1355</v>
       </c>
       <c r="D17" s="18"/>
     </row>
     <row r="18" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="18" t="s">
-        <v>1221</v>
+        <v>1356</v>
       </c>
       <c r="B18" s="18" t="s">
-        <v>1222</v>
+        <v>1357</v>
       </c>
       <c r="C18" s="18" t="s">
-        <v>1223</v>
+        <v>1358</v>
       </c>
       <c r="D18" s="18" t="s">
-        <v>1224</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16646,27 +18208,27 @@
         <v>49</v>
       </c>
       <c r="B19" s="18" t="s">
-        <v>1225</v>
+        <v>1360</v>
       </c>
       <c r="C19" s="18" t="s">
-        <v>1226</v>
+        <v>1361</v>
       </c>
       <c r="D19" s="18" t="s">
-        <v>1227</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="18" t="s">
-        <v>1228</v>
+        <v>1363</v>
       </c>
       <c r="B20" s="18" t="s">
-        <v>1229</v>
+        <v>1364</v>
       </c>
       <c r="C20" s="18" t="s">
-        <v>1230</v>
+        <v>1365</v>
       </c>
       <c r="D20" s="18" t="s">
-        <v>1231</v>
+        <v>1366</v>
       </c>
     </row>
   </sheetData>
@@ -16703,15 +18265,15 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>1232</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="10" t="s">
-        <v>1233</v>
+        <v>1368</v>
       </c>
       <c r="L2" s="10" t="s">
-        <v>1234</v>
+        <v>1369</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16719,7 +18281,7 @@
         <v>78</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>1235</v>
+        <v>1370</v>
       </c>
       <c r="C4" s="11" t="s">
         <v>31</v>
@@ -16728,63 +18290,63 @@
         <v>66</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>1236</v>
+        <v>1371</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>1237</v>
+        <v>1372</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>1238</v>
+        <v>1373</v>
       </c>
       <c r="H4" s="11" t="s">
-        <v>1239</v>
+        <v>1374</v>
       </c>
       <c r="I4" s="11" t="s">
         <v>75</v>
       </c>
       <c r="J4" s="11" t="s">
-        <v>1240</v>
+        <v>1375</v>
       </c>
       <c r="K4" s="11" t="s">
-        <v>1241</v>
+        <v>1376</v>
       </c>
       <c r="L4" s="11" t="s">
-        <v>1242</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="22" t="s">
-        <v>1243</v>
+        <v>1378</v>
       </c>
       <c r="B5" s="22" t="s">
-        <v>1244</v>
+        <v>1379</v>
       </c>
       <c r="C5" s="22" t="s">
         <v>47</v>
       </c>
       <c r="D5" s="22" t="s">
-        <v>659</v>
+        <v>664</v>
       </c>
       <c r="E5" s="22" t="s">
-        <v>1245</v>
+        <v>1380</v>
       </c>
       <c r="F5" s="22" t="s">
-        <v>1246</v>
+        <v>1381</v>
       </c>
       <c r="G5" s="22" t="s">
-        <v>1247</v>
+        <v>1382</v>
       </c>
       <c r="H5" s="22" t="s">
         <v>83</v>
       </c>
       <c r="I5" s="22" t="s">
-        <v>1248</v>
+        <v>1383</v>
       </c>
       <c r="J5" s="22" t="s">
-        <v>1249</v>
+        <v>1384</v>
       </c>
       <c r="K5" s="22" t="s">
-        <v>1250</v>
+        <v>1385</v>
       </c>
       <c r="L5" s="22"/>
     </row>

--- a/docs/Eschool_Functional_Test_Plan.xlsx
+++ b/docs/Eschool_Functional_Test_Plan.xlsx
@@ -16,7 +16,7 @@
   </sheets>
   <definedNames>
     <definedName function="false" hidden="true" localSheetId="4" name="_xlnm._FilterDatabase" vbProcedure="false">'Defect Log'!$A$4:$L$204</definedName>
-    <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">'Test Cases'!$A$1:$O$336</definedName>
+    <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">'Test Cases'!$A$1:$O$371</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3379" uniqueCount="1386">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3745" uniqueCount="1571">
   <si>
     <t xml:space="preserve">Eschool - Functional Test Plan</t>
   </si>
@@ -45,7 +45,7 @@
     <t xml:space="preserve">Modules covered</t>
   </si>
   <si>
-    <t xml:space="preserve">Login &amp; Layout, Reusable Components, Class Sections, Subjects, Teachers, Parents, Admissions (incl. existing-parent picker), Students, Attendance, Documents, Users &amp; Staff, Roles &amp; Permissions, My Account, School Settings, Dashboard, role-based access, end-to-end flows, non-functional checks.</t>
+    <t xml:space="preserve">Login &amp; Layout, Reusable Components, Class Sections, Subjects, Teachers, Parents, Admissions (incl. existing-parent picker), Students, Attendance, Documents, Users &amp; Staff, Roles &amp; Permissions, My Account, School Settings (incl. Masters &gt; Admission fees), Dashboard, role-based access, end-to-end flows, non-functional checks.</t>
   </si>
   <si>
     <t xml:space="preserve">NOT in scope</t>
@@ -93,7 +93,7 @@
     <t xml:space="preserve">Known limitations</t>
   </si>
   <si>
-    <t xml:space="preserve">1) Attendance 'today' currently follows UTC, so between 00:00 and 04:00 Abu Dhabi time it can show yesterday (fix planned: F2). 2) Parent e-mail uniqueness is not enforced (PAR-14). 3) Lists load fully (no server paging yet): expect slowness only at very large volumes. 4) Fee, report-card and attendance-report buttons on students show 'not yet available'.</t>
+    <t xml:space="preserve">1) Attendance 'today' currently follows UTC, so between 00:00 and 04:00 Abu Dhabi time it can show yesterday (fix planned: F2). 2) Parent e-mail uniqueness is not enforced (PAR-14). 3) Lists load fully (no server paging yet): expect slowness only at very large volumes. 4) Fee, report-card and attendance-report buttons on students show 'not yet available'. 5) Students have no 'Deleted students' screen: Restore for students exists only in the API and cannot be reached from the app (a student with a class period cannot be deleted).</t>
   </si>
   <si>
     <t xml:space="preserve">Summary</t>
@@ -2589,13 +2589,16 @@
     <t xml:space="preserve">DOC-13</t>
   </si>
   <si>
+    <t xml:space="preserve">Custom role with Documents.Verify (NOT Admin)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Document uploaded by yourself</t>
   </si>
   <si>
     <t xml:space="preserve">Try to verify or reject your own upload</t>
   </si>
   <si>
-    <t xml:space="preserve">Refused (nobody reviews their own upload)</t>
+    <t xml:space="preserve">Refused: 'You uploaded this document, so someone else must verify or reject it.' (An Admin may review their own upload: see DOC-24.)</t>
   </si>
   <si>
     <t xml:space="preserve">DOC-14</t>
@@ -3822,7 +3825,7 @@
     <t xml:space="preserve">Open yesterday and edit it; then open the day before yesterday</t>
   </si>
   <si>
-    <t xml:space="preserve">Yesterday and today are editable; the day before is locked ('Only an Admin can change attendance older than 1 day'); Admin can still edit it</t>
+    <t xml:space="preserve">Yesterday is editable only while 24 hours have not passed since the register was FIRST saved (see ATT-27, ATT-28); the day before yesterday is locked ('Only an Admin can change attendance older than 1 day'); Admin can still edit both</t>
   </si>
   <si>
     <t xml:space="preserve">ADM-47</t>
@@ -3831,7 +3834,7 @@
     <t xml:space="preserve">Confirm - required payment</t>
   </si>
   <si>
-    <t xml:space="preserve">Open Confirm Admission, leave Fee amount and Payment reference empty; click Confirm</t>
+    <t xml:space="preserve">Open Confirm Admission; clear any pre-filled Fee amount (it is filled from Masters when a fee is set for the class); leave Fee amount and Payment reference empty; click Confirm</t>
   </si>
   <si>
     <t xml:space="preserve">Both fields show a red star and the errors 'Fee amount is required.' / 'Payment reference is required.'; nothing is saved; with both filled it moves to Admitted</t>
@@ -3975,6 +3978,510 @@
     <t xml:space="preserve">LKG, UKG and Class 1 to 5 each have sections A and B, every one with capacity 30</t>
   </si>
   <si>
+    <t xml:space="preserve">ADM-51</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confirm - fee from Masters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Admission fee set for 'ZT Class A' in Masters (500); a Registered application for that class</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open Confirm Admission</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fee amount is already filled with 500; Payment reference is empty and still required; the fee can be changed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADM-52</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confirm - no fee set</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No fee set in Masters for the class of a Registered application</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fee amount is empty (nothing filled in); Confirm with it empty shows 'Fee amount is required.'</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADM-53</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confirm - fee edited</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fee 500 set in Masters for the class; Registered application of that class</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Change the pre-filled fee to 450, enter a payment reference, confirm; then open Masters &gt; Admission fees</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The application keeps 450; the Masters fee for the class is still 500</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADM-54</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deleted list</t>
+  </si>
+  <si>
+    <t xml:space="preserve">One deleted application</t>
+  </si>
+  <si>
+    <t xml:space="preserve">On Admissions open 'Deleted applications' and click Show deleted</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Row shows Reg No, applicant and phone, class applied for, status when deleted, date deleted and who deleted it (username); newest first</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADM-55</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deleted list - permission</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Role without Admissions.Delete</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The 'Deleted applications' panel is not shown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADM-56</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Restore</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A deleted Registered application</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Show deleted; click Restore on the row; confirm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Success message; the row leaves the Deleted list and the application is back in the Admissions list with its old status and details; Edit/View work</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADM-57</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Restore - Admin only</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Custom role 'ZT DeleteNoAdmin' (Admissions.View + Admissions.Delete)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A deleted application</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Show deleted and look at the rows; then try Restore through Swagger (POST /api/admissions/{id}/restore)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The list is visible but there is no Restore button; the API answers 403 'Only an Admin can restore a deleted application.'; the application stays deleted</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADM-58</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Restore - already restored</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A deleted application open in two browser tabs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Restore it in tab 1; then click Restore in tab 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tab 2 shows an error that the application is not deleted (409); nothing changes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADM-59</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Restore - audit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">An application you just restored</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ask a developer to look in AuditLogs for TableName 'Admissions' and this Id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">An 'Update' row shows IsDeleted true -&gt; false with the user and the time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADM-60</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Admission number - year</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Two Admitted applications</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enrol one with admission date in 2026 and one with admission date in 2027 (blank numbers); then enrol a second one in 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADM-2026-000n for 2026 and ADM-2027-0001 for 2027 (the serial restarts each year); the second 2026 number continues the 2026 serial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADM-61</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Registration date and REG year</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test between 00:00 and 04:00 Abu Dhabi time, or on 1 January</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Register an application and read its registration date and REG-year</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Both follow the SCHOOL's date (School settings time zone), not the server's UTC date. Record what you see</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STU-56</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Emirates ID - shown by school country</t>
+  </si>
+  <si>
+    <t xml:space="preserve">School settings country = United Arab Emirates</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Edit a student &gt; Identity section</t>
+  </si>
+  <si>
+    <t xml:space="preserve">An optional Emirates ID field is shown; the student can be saved with it blank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STU-57</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Emirates ID - formats</t>
+  </si>
+  <si>
+    <t xml:space="preserve">School country UAE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enter 784-1990-1234567-1, save; then enter 784199012345671 on another student, save; reopen both</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Both are accepted; stored as 15 digits and shown with dashes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STU-58</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Emirates ID - invalid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Try 14 digits, 16 digits, a number not starting 784, and one with a letter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Each is refused with 'Emirates ID must be 15 digits starting with 784 (for example 784-1990-1234567-1).'</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STU-59</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Emirates ID - duplicate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Student A has an Emirates ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Give the same Emirates ID to student B and save</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Refused with a clear message that the number is used by another student; B is unchanged</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STU-60</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Emirates ID - other countries</t>
+  </si>
+  <si>
+    <t xml:space="preserve">School settings country changed to India (then change it back)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Emirates ID field is not shown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STU-61</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Identity - stale save</t>
+  </si>
+  <si>
+    <t xml:space="preserve">One student open in two browser tabs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tab 1: change the passport number and save. Tab 2 (not refreshed): change the Emirates ID and save</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tab 2 is refused with a conflict message asking to reload; nothing from tab 2 is saved. After reload, editing works</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STU-62</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reactivate into a full class</t>
+  </si>
+  <si>
+    <t xml:space="preserve">An Inactive student in a class that is now full</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Edit the student; set Status to Active; save</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Refused: the class is full; the student stays Inactive</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STU-63</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reactivate with room</t>
+  </si>
+  <si>
+    <t xml:space="preserve">An Inactive student in a class with a free seat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Set Status to Active; save</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Saved; the student is Active and counts in the class seats</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STU-64</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Primary guardian - switch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A student with two linked parents, one primary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Use 'Set as primary' on the other parent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exactly one primary contact remains (the new one); the old one is no longer primary; no error</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STU-65</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Second primary guardian</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A student that already has a primary contact</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Link another parent AS primary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Refused (409) with a message naming the current primary and telling you to link without the flag and then 'Set as primary'; the existing primary is unchanged</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAR-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Field lengths</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Add a parent with a 101-character name, e-mail of 101 characters, then a 21-character mobile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Each field shows its own error naming the field; nothing is saved</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAR-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E-mail and phone formats</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enter email 'abc', mobile 'abc', WhatsApp '12', work e-mail 'x@' and work phone 'zz'</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Each shows a field error (e-mail / phone format); optional fields left blank are accepted</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAR-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Edit with an old mobile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A parent whose mobile has odd characters (older data)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open Edit and save without changing the mobile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Record what you see: the mobile must now match the phone format, so an old odd value may show a field error</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATT-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lock - 24 hours after first save</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A register for yesterday that was first saved more than 24 hours ago (still within the one-day window)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open that date and try to change a status and save</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Refused: 'This register was saved more than 24 hours ago. Only an Admin can change it now.'; nothing changes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATT-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Edit within 24 hours</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Class teacher; a register for today saved a few hours ago</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open today; change two statuses; save; repeat once more</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Both saves succeed; the register stays editable until 24 hours after its FIRST save</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATT-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Admin is not locked</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A register first saved more than 24 hours ago, and one older than yesterday</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open each and change a status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Both can be edited and saved by an Admin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DOC-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Admin verifies own upload</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A document uploaded by the same Admin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify it (and, on another one, reject it)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Allowed: status Verified / Rejected; reviewer is the Admin. (A non-Admin cannot, see DOC-13)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USR-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Employee numbers back-filled</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A copy of the database from before the back-fill migration, with staff that have no employee number and some that do</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Run the update; open Users &amp; Staff</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Every staff member and teacher has an employee number; old numbers are unchanged; new ones continue after the highest EMP-nnnn in order of creation; no duplicates</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USR-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Employee numbers - simultaneous</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Two Admins signed in on two computers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Both create a staff account at the same moment, employee number blank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Both succeed with different numbers (for example EMP-0007 and EMP-0008); no 'just taken' error</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SET-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Masters menu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Look at the sidebar Overview section; open Masters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Masters is listed; the hub shows an Admission fees card; opening it shows the fees page</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SET-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Admission fees - list</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Classes exist in several sections and years</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open Masters &gt; Admission fees</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Each class NAME appears once (not per section or year), with its fee or 'Not set'</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SET-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Admission fees - set</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Set 'ZT Class A' to 500; then 250.456; then -1; then 1000001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">500 saved; 250.456 saved as 250.46; -1 and 1,000,001 refused with a field error</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SET-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Admission fees - clear</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A class with a fee</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clear the fee</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The class shows 'Not set'; Confirm Admission for that class no longer pre-fills a fee</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SET-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Masters - permissions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Role with Settings.View only</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open Masters &gt; Admission fees; try to change a fee (or PUT /api/admission-fees/{class} in Swagger)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fees can be read but not changed: no way to save in the UI and the API answers 403; a user without Settings.View does not see Masters</t>
+  </si>
+  <si>
     <t xml:space="preserve">Test data to set up first</t>
   </si>
   <si>
@@ -4050,6 +4557,30 @@
     <t xml:space="preserve">Create a role with Admissions.Create/Edit but WITHOUT Parents.View (cases ADM-G09, G10). Also create 'ZT ParentsOnly' with Parents.View but no Admissions rights (ADM-G11).</t>
   </si>
   <si>
+    <t xml:space="preserve">zt.deleteonly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Custom role 'ZT DeleteNoAdmin'</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZtDelete#2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Role with Admissions.View + Admissions.Delete only, NOT Admin (cases ADM-57).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">zt.settingsview</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Custom role 'ZT SettingsView'</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZtSettings#2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Role with Settings.View only (case SET-14).</t>
+  </si>
+  <si>
     <t xml:space="preserve">Sample records</t>
   </si>
   <si>
@@ -4129,6 +4660,30 @@
   </si>
   <si>
     <t xml:space="preserve">For case ATT-25 only.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Admission fee</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Class 1 or ZT Class A = 500</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Masters &gt; Admission fees</t>
+  </si>
+  <si>
+    <t xml:space="preserve">For ADM-51 to ADM-53 and SET-10 to SET-14.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Emirates ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">784-1990-1234567-1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15 digits starting 784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Also 784-1985-7654321-3 for a second student (STU-57, STU-59).</t>
   </si>
   <si>
     <t xml:space="preserve">Defect Log</t>
@@ -5002,27 +5557,27 @@
         <v>40</v>
       </c>
       <c r="B5" s="13" t="n">
-        <f aca="false">COUNTIF('Test Cases'!$B$2:$B$336,$A5)</f>
+        <f aca="false">COUNTIF('Test Cases'!$B$2:$B$371,$A5)</f>
         <v>26</v>
       </c>
       <c r="C5" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A5,'Test Cases'!$K$2:$K$336,"Pass")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$371,$A5,'Test Cases'!$K$2:$K$371,"Pass")</f>
         <v>0</v>
       </c>
       <c r="D5" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A5,'Test Cases'!$K$2:$K$336,"Fail")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$371,$A5,'Test Cases'!$K$2:$K$371,"Fail")</f>
         <v>0</v>
       </c>
       <c r="E5" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A5,'Test Cases'!$K$2:$K$336,"Blocked")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$371,$A5,'Test Cases'!$K$2:$K$371,"Blocked")</f>
         <v>0</v>
       </c>
       <c r="F5" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A5,'Test Cases'!$K$2:$K$336,"N/A")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$371,$A5,'Test Cases'!$K$2:$K$371,"N/A")</f>
         <v>0</v>
       </c>
       <c r="G5" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A5,'Test Cases'!$K$2:$K$336,"Not Run")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$371,$A5,'Test Cases'!$K$2:$K$371,"Not Run")</f>
         <v>26</v>
       </c>
       <c r="H5" s="14" t="n">
@@ -5039,27 +5594,27 @@
         <v>41</v>
       </c>
       <c r="B6" s="13" t="n">
-        <f aca="false">COUNTIF('Test Cases'!$B$2:$B$336,$A6)</f>
+        <f aca="false">COUNTIF('Test Cases'!$B$2:$B$371,$A6)</f>
         <v>12</v>
       </c>
       <c r="C6" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A6,'Test Cases'!$K$2:$K$336,"Pass")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$371,$A6,'Test Cases'!$K$2:$K$371,"Pass")</f>
         <v>0</v>
       </c>
       <c r="D6" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A6,'Test Cases'!$K$2:$K$336,"Fail")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$371,$A6,'Test Cases'!$K$2:$K$371,"Fail")</f>
         <v>0</v>
       </c>
       <c r="E6" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A6,'Test Cases'!$K$2:$K$336,"Blocked")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$371,$A6,'Test Cases'!$K$2:$K$371,"Blocked")</f>
         <v>0</v>
       </c>
       <c r="F6" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A6,'Test Cases'!$K$2:$K$336,"N/A")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$371,$A6,'Test Cases'!$K$2:$K$371,"N/A")</f>
         <v>0</v>
       </c>
       <c r="G6" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A6,'Test Cases'!$K$2:$K$336,"Not Run")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$371,$A6,'Test Cases'!$K$2:$K$371,"Not Run")</f>
         <v>12</v>
       </c>
       <c r="H6" s="14" t="n">
@@ -5076,27 +5631,27 @@
         <v>42</v>
       </c>
       <c r="B7" s="13" t="n">
-        <f aca="false">COUNTIF('Test Cases'!$B$2:$B$336,$A7)</f>
+        <f aca="false">COUNTIF('Test Cases'!$B$2:$B$371,$A7)</f>
         <v>15</v>
       </c>
       <c r="C7" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A7,'Test Cases'!$K$2:$K$336,"Pass")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$371,$A7,'Test Cases'!$K$2:$K$371,"Pass")</f>
         <v>0</v>
       </c>
       <c r="D7" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A7,'Test Cases'!$K$2:$K$336,"Fail")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$371,$A7,'Test Cases'!$K$2:$K$371,"Fail")</f>
         <v>0</v>
       </c>
       <c r="E7" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A7,'Test Cases'!$K$2:$K$336,"Blocked")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$371,$A7,'Test Cases'!$K$2:$K$371,"Blocked")</f>
         <v>0</v>
       </c>
       <c r="F7" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A7,'Test Cases'!$K$2:$K$336,"N/A")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$371,$A7,'Test Cases'!$K$2:$K$371,"N/A")</f>
         <v>0</v>
       </c>
       <c r="G7" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A7,'Test Cases'!$K$2:$K$336,"Not Run")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$371,$A7,'Test Cases'!$K$2:$K$371,"Not Run")</f>
         <v>15</v>
       </c>
       <c r="H7" s="14" t="n">
@@ -5113,27 +5668,27 @@
         <v>43</v>
       </c>
       <c r="B8" s="13" t="n">
-        <f aca="false">COUNTIF('Test Cases'!$B$2:$B$336,$A8)</f>
+        <f aca="false">COUNTIF('Test Cases'!$B$2:$B$371,$A8)</f>
         <v>11</v>
       </c>
       <c r="C8" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A8,'Test Cases'!$K$2:$K$336,"Pass")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$371,$A8,'Test Cases'!$K$2:$K$371,"Pass")</f>
         <v>0</v>
       </c>
       <c r="D8" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A8,'Test Cases'!$K$2:$K$336,"Fail")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$371,$A8,'Test Cases'!$K$2:$K$371,"Fail")</f>
         <v>0</v>
       </c>
       <c r="E8" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A8,'Test Cases'!$K$2:$K$336,"Blocked")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$371,$A8,'Test Cases'!$K$2:$K$371,"Blocked")</f>
         <v>0</v>
       </c>
       <c r="F8" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A8,'Test Cases'!$K$2:$K$336,"N/A")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$371,$A8,'Test Cases'!$K$2:$K$371,"N/A")</f>
         <v>0</v>
       </c>
       <c r="G8" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A8,'Test Cases'!$K$2:$K$336,"Not Run")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$371,$A8,'Test Cases'!$K$2:$K$371,"Not Run")</f>
         <v>11</v>
       </c>
       <c r="H8" s="14" t="n">
@@ -5150,27 +5705,27 @@
         <v>44</v>
       </c>
       <c r="B9" s="13" t="n">
-        <f aca="false">COUNTIF('Test Cases'!$B$2:$B$336,$A9)</f>
+        <f aca="false">COUNTIF('Test Cases'!$B$2:$B$371,$A9)</f>
         <v>18</v>
       </c>
       <c r="C9" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A9,'Test Cases'!$K$2:$K$336,"Pass")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$371,$A9,'Test Cases'!$K$2:$K$371,"Pass")</f>
         <v>0</v>
       </c>
       <c r="D9" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A9,'Test Cases'!$K$2:$K$336,"Fail")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$371,$A9,'Test Cases'!$K$2:$K$371,"Fail")</f>
         <v>0</v>
       </c>
       <c r="E9" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A9,'Test Cases'!$K$2:$K$336,"Blocked")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$371,$A9,'Test Cases'!$K$2:$K$371,"Blocked")</f>
         <v>0</v>
       </c>
       <c r="F9" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A9,'Test Cases'!$K$2:$K$336,"N/A")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$371,$A9,'Test Cases'!$K$2:$K$371,"N/A")</f>
         <v>0</v>
       </c>
       <c r="G9" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A9,'Test Cases'!$K$2:$K$336,"Not Run")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$371,$A9,'Test Cases'!$K$2:$K$371,"Not Run")</f>
         <v>18</v>
       </c>
       <c r="H9" s="14" t="n">
@@ -5187,28 +5742,28 @@
         <v>45</v>
       </c>
       <c r="B10" s="13" t="n">
-        <f aca="false">COUNTIF('Test Cases'!$B$2:$B$336,$A10)</f>
-        <v>19</v>
+        <f aca="false">COUNTIF('Test Cases'!$B$2:$B$371,$A10)</f>
+        <v>22</v>
       </c>
       <c r="C10" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A10,'Test Cases'!$K$2:$K$336,"Pass")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$371,$A10,'Test Cases'!$K$2:$K$371,"Pass")</f>
         <v>0</v>
       </c>
       <c r="D10" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A10,'Test Cases'!$K$2:$K$336,"Fail")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$371,$A10,'Test Cases'!$K$2:$K$371,"Fail")</f>
         <v>0</v>
       </c>
       <c r="E10" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A10,'Test Cases'!$K$2:$K$336,"Blocked")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$371,$A10,'Test Cases'!$K$2:$K$371,"Blocked")</f>
         <v>0</v>
       </c>
       <c r="F10" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A10,'Test Cases'!$K$2:$K$336,"N/A")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$371,$A10,'Test Cases'!$K$2:$K$371,"N/A")</f>
         <v>0</v>
       </c>
       <c r="G10" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A10,'Test Cases'!$K$2:$K$336,"Not Run")</f>
-        <v>19</v>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$371,$A10,'Test Cases'!$K$2:$K$371,"Not Run")</f>
+        <v>22</v>
       </c>
       <c r="H10" s="14" t="n">
         <f aca="false">IFERROR((B10-G10-F10)/(B10-F10),0)</f>
@@ -5224,28 +5779,28 @@
         <v>46</v>
       </c>
       <c r="B11" s="13" t="n">
-        <f aca="false">COUNTIF('Test Cases'!$B$2:$B$336,$A11)</f>
-        <v>60</v>
+        <f aca="false">COUNTIF('Test Cases'!$B$2:$B$371,$A11)</f>
+        <v>71</v>
       </c>
       <c r="C11" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A11,'Test Cases'!$K$2:$K$336,"Pass")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$371,$A11,'Test Cases'!$K$2:$K$371,"Pass")</f>
         <v>0</v>
       </c>
       <c r="D11" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A11,'Test Cases'!$K$2:$K$336,"Fail")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$371,$A11,'Test Cases'!$K$2:$K$371,"Fail")</f>
         <v>0</v>
       </c>
       <c r="E11" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A11,'Test Cases'!$K$2:$K$336,"Blocked")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$371,$A11,'Test Cases'!$K$2:$K$371,"Blocked")</f>
         <v>0</v>
       </c>
       <c r="F11" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A11,'Test Cases'!$K$2:$K$336,"N/A")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$371,$A11,'Test Cases'!$K$2:$K$371,"N/A")</f>
         <v>0</v>
       </c>
       <c r="G11" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A11,'Test Cases'!$K$2:$K$336,"Not Run")</f>
-        <v>60</v>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$371,$A11,'Test Cases'!$K$2:$K$371,"Not Run")</f>
+        <v>71</v>
       </c>
       <c r="H11" s="14" t="n">
         <f aca="false">IFERROR((B11-G11-F11)/(B11-F11),0)</f>
@@ -5261,28 +5816,28 @@
         <v>47</v>
       </c>
       <c r="B12" s="13" t="n">
-        <f aca="false">COUNTIF('Test Cases'!$B$2:$B$336,$A12)</f>
-        <v>45</v>
+        <f aca="false">COUNTIF('Test Cases'!$B$2:$B$371,$A12)</f>
+        <v>55</v>
       </c>
       <c r="C12" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A12,'Test Cases'!$K$2:$K$336,"Pass")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$371,$A12,'Test Cases'!$K$2:$K$371,"Pass")</f>
         <v>0</v>
       </c>
       <c r="D12" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A12,'Test Cases'!$K$2:$K$336,"Fail")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$371,$A12,'Test Cases'!$K$2:$K$371,"Fail")</f>
         <v>0</v>
       </c>
       <c r="E12" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A12,'Test Cases'!$K$2:$K$336,"Blocked")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$371,$A12,'Test Cases'!$K$2:$K$371,"Blocked")</f>
         <v>0</v>
       </c>
       <c r="F12" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A12,'Test Cases'!$K$2:$K$336,"N/A")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$371,$A12,'Test Cases'!$K$2:$K$371,"N/A")</f>
         <v>0</v>
       </c>
       <c r="G12" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A12,'Test Cases'!$K$2:$K$336,"Not Run")</f>
-        <v>45</v>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$371,$A12,'Test Cases'!$K$2:$K$371,"Not Run")</f>
+        <v>55</v>
       </c>
       <c r="H12" s="14" t="n">
         <f aca="false">IFERROR((B12-G12-F12)/(B12-F12),0)</f>
@@ -5298,28 +5853,28 @@
         <v>48</v>
       </c>
       <c r="B13" s="13" t="n">
-        <f aca="false">COUNTIF('Test Cases'!$B$2:$B$336,$A13)</f>
-        <v>26</v>
+        <f aca="false">COUNTIF('Test Cases'!$B$2:$B$371,$A13)</f>
+        <v>29</v>
       </c>
       <c r="C13" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A13,'Test Cases'!$K$2:$K$336,"Pass")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$371,$A13,'Test Cases'!$K$2:$K$371,"Pass")</f>
         <v>0</v>
       </c>
       <c r="D13" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A13,'Test Cases'!$K$2:$K$336,"Fail")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$371,$A13,'Test Cases'!$K$2:$K$371,"Fail")</f>
         <v>0</v>
       </c>
       <c r="E13" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A13,'Test Cases'!$K$2:$K$336,"Blocked")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$371,$A13,'Test Cases'!$K$2:$K$371,"Blocked")</f>
         <v>0</v>
       </c>
       <c r="F13" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A13,'Test Cases'!$K$2:$K$336,"N/A")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$371,$A13,'Test Cases'!$K$2:$K$371,"N/A")</f>
         <v>0</v>
       </c>
       <c r="G13" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A13,'Test Cases'!$K$2:$K$336,"Not Run")</f>
-        <v>26</v>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$371,$A13,'Test Cases'!$K$2:$K$371,"Not Run")</f>
+        <v>29</v>
       </c>
       <c r="H13" s="14" t="n">
         <f aca="false">IFERROR((B13-G13-F13)/(B13-F13),0)</f>
@@ -5335,28 +5890,28 @@
         <v>49</v>
       </c>
       <c r="B14" s="13" t="n">
-        <f aca="false">COUNTIF('Test Cases'!$B$2:$B$336,$A14)</f>
-        <v>23</v>
+        <f aca="false">COUNTIF('Test Cases'!$B$2:$B$371,$A14)</f>
+        <v>24</v>
       </c>
       <c r="C14" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A14,'Test Cases'!$K$2:$K$336,"Pass")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$371,$A14,'Test Cases'!$K$2:$K$371,"Pass")</f>
         <v>0</v>
       </c>
       <c r="D14" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A14,'Test Cases'!$K$2:$K$336,"Fail")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$371,$A14,'Test Cases'!$K$2:$K$371,"Fail")</f>
         <v>0</v>
       </c>
       <c r="E14" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A14,'Test Cases'!$K$2:$K$336,"Blocked")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$371,$A14,'Test Cases'!$K$2:$K$371,"Blocked")</f>
         <v>0</v>
       </c>
       <c r="F14" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A14,'Test Cases'!$K$2:$K$336,"N/A")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$371,$A14,'Test Cases'!$K$2:$K$371,"N/A")</f>
         <v>0</v>
       </c>
       <c r="G14" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A14,'Test Cases'!$K$2:$K$336,"Not Run")</f>
-        <v>23</v>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$371,$A14,'Test Cases'!$K$2:$K$371,"Not Run")</f>
+        <v>24</v>
       </c>
       <c r="H14" s="14" t="n">
         <f aca="false">IFERROR((B14-G14-F14)/(B14-F14),0)</f>
@@ -5372,28 +5927,28 @@
         <v>50</v>
       </c>
       <c r="B15" s="13" t="n">
-        <f aca="false">COUNTIF('Test Cases'!$B$2:$B$336,$A15)</f>
-        <v>23</v>
+        <f aca="false">COUNTIF('Test Cases'!$B$2:$B$371,$A15)</f>
+        <v>25</v>
       </c>
       <c r="C15" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A15,'Test Cases'!$K$2:$K$336,"Pass")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$371,$A15,'Test Cases'!$K$2:$K$371,"Pass")</f>
         <v>0</v>
       </c>
       <c r="D15" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A15,'Test Cases'!$K$2:$K$336,"Fail")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$371,$A15,'Test Cases'!$K$2:$K$371,"Fail")</f>
         <v>0</v>
       </c>
       <c r="E15" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A15,'Test Cases'!$K$2:$K$336,"Blocked")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$371,$A15,'Test Cases'!$K$2:$K$371,"Blocked")</f>
         <v>0</v>
       </c>
       <c r="F15" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A15,'Test Cases'!$K$2:$K$336,"N/A")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$371,$A15,'Test Cases'!$K$2:$K$371,"N/A")</f>
         <v>0</v>
       </c>
       <c r="G15" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A15,'Test Cases'!$K$2:$K$336,"Not Run")</f>
-        <v>23</v>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$371,$A15,'Test Cases'!$K$2:$K$371,"Not Run")</f>
+        <v>25</v>
       </c>
       <c r="H15" s="14" t="n">
         <f aca="false">IFERROR((B15-G15-F15)/(B15-F15),0)</f>
@@ -5409,27 +5964,27 @@
         <v>51</v>
       </c>
       <c r="B16" s="13" t="n">
-        <f aca="false">COUNTIF('Test Cases'!$B$2:$B$336,$A16)</f>
+        <f aca="false">COUNTIF('Test Cases'!$B$2:$B$371,$A16)</f>
         <v>11</v>
       </c>
       <c r="C16" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A16,'Test Cases'!$K$2:$K$336,"Pass")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$371,$A16,'Test Cases'!$K$2:$K$371,"Pass")</f>
         <v>0</v>
       </c>
       <c r="D16" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A16,'Test Cases'!$K$2:$K$336,"Fail")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$371,$A16,'Test Cases'!$K$2:$K$371,"Fail")</f>
         <v>0</v>
       </c>
       <c r="E16" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A16,'Test Cases'!$K$2:$K$336,"Blocked")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$371,$A16,'Test Cases'!$K$2:$K$371,"Blocked")</f>
         <v>0</v>
       </c>
       <c r="F16" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A16,'Test Cases'!$K$2:$K$336,"N/A")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$371,$A16,'Test Cases'!$K$2:$K$371,"N/A")</f>
         <v>0</v>
       </c>
       <c r="G16" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A16,'Test Cases'!$K$2:$K$336,"Not Run")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$371,$A16,'Test Cases'!$K$2:$K$371,"Not Run")</f>
         <v>11</v>
       </c>
       <c r="H16" s="14" t="n">
@@ -5446,27 +6001,27 @@
         <v>52</v>
       </c>
       <c r="B17" s="13" t="n">
-        <f aca="false">COUNTIF('Test Cases'!$B$2:$B$336,$A17)</f>
+        <f aca="false">COUNTIF('Test Cases'!$B$2:$B$371,$A17)</f>
         <v>9</v>
       </c>
       <c r="C17" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A17,'Test Cases'!$K$2:$K$336,"Pass")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$371,$A17,'Test Cases'!$K$2:$K$371,"Pass")</f>
         <v>0</v>
       </c>
       <c r="D17" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A17,'Test Cases'!$K$2:$K$336,"Fail")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$371,$A17,'Test Cases'!$K$2:$K$371,"Fail")</f>
         <v>0</v>
       </c>
       <c r="E17" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A17,'Test Cases'!$K$2:$K$336,"Blocked")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$371,$A17,'Test Cases'!$K$2:$K$371,"Blocked")</f>
         <v>0</v>
       </c>
       <c r="F17" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A17,'Test Cases'!$K$2:$K$336,"N/A")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$371,$A17,'Test Cases'!$K$2:$K$371,"N/A")</f>
         <v>0</v>
       </c>
       <c r="G17" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A17,'Test Cases'!$K$2:$K$336,"Not Run")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$371,$A17,'Test Cases'!$K$2:$K$371,"Not Run")</f>
         <v>9</v>
       </c>
       <c r="H17" s="14" t="n">
@@ -5483,28 +6038,28 @@
         <v>53</v>
       </c>
       <c r="B18" s="13" t="n">
-        <f aca="false">COUNTIF('Test Cases'!$B$2:$B$336,$A18)</f>
-        <v>9</v>
+        <f aca="false">COUNTIF('Test Cases'!$B$2:$B$371,$A18)</f>
+        <v>14</v>
       </c>
       <c r="C18" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A18,'Test Cases'!$K$2:$K$336,"Pass")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$371,$A18,'Test Cases'!$K$2:$K$371,"Pass")</f>
         <v>0</v>
       </c>
       <c r="D18" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A18,'Test Cases'!$K$2:$K$336,"Fail")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$371,$A18,'Test Cases'!$K$2:$K$371,"Fail")</f>
         <v>0</v>
       </c>
       <c r="E18" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A18,'Test Cases'!$K$2:$K$336,"Blocked")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$371,$A18,'Test Cases'!$K$2:$K$371,"Blocked")</f>
         <v>0</v>
       </c>
       <c r="F18" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A18,'Test Cases'!$K$2:$K$336,"N/A")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$371,$A18,'Test Cases'!$K$2:$K$371,"N/A")</f>
         <v>0</v>
       </c>
       <c r="G18" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A18,'Test Cases'!$K$2:$K$336,"Not Run")</f>
-        <v>9</v>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$371,$A18,'Test Cases'!$K$2:$K$371,"Not Run")</f>
+        <v>14</v>
       </c>
       <c r="H18" s="14" t="n">
         <f aca="false">IFERROR((B18-G18-F18)/(B18-F18),0)</f>
@@ -5520,27 +6075,27 @@
         <v>54</v>
       </c>
       <c r="B19" s="13" t="n">
-        <f aca="false">COUNTIF('Test Cases'!$B$2:$B$336,$A19)</f>
+        <f aca="false">COUNTIF('Test Cases'!$B$2:$B$371,$A19)</f>
         <v>1</v>
       </c>
       <c r="C19" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A19,'Test Cases'!$K$2:$K$336,"Pass")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$371,$A19,'Test Cases'!$K$2:$K$371,"Pass")</f>
         <v>0</v>
       </c>
       <c r="D19" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A19,'Test Cases'!$K$2:$K$336,"Fail")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$371,$A19,'Test Cases'!$K$2:$K$371,"Fail")</f>
         <v>0</v>
       </c>
       <c r="E19" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A19,'Test Cases'!$K$2:$K$336,"Blocked")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$371,$A19,'Test Cases'!$K$2:$K$371,"Blocked")</f>
         <v>0</v>
       </c>
       <c r="F19" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A19,'Test Cases'!$K$2:$K$336,"N/A")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$371,$A19,'Test Cases'!$K$2:$K$371,"N/A")</f>
         <v>0</v>
       </c>
       <c r="G19" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A19,'Test Cases'!$K$2:$K$336,"Not Run")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$371,$A19,'Test Cases'!$K$2:$K$371,"Not Run")</f>
         <v>1</v>
       </c>
       <c r="H19" s="14" t="n">
@@ -5557,27 +6112,27 @@
         <v>55</v>
       </c>
       <c r="B20" s="13" t="n">
-        <f aca="false">COUNTIF('Test Cases'!$B$2:$B$336,$A20)</f>
+        <f aca="false">COUNTIF('Test Cases'!$B$2:$B$371,$A20)</f>
         <v>8</v>
       </c>
       <c r="C20" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A20,'Test Cases'!$K$2:$K$336,"Pass")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$371,$A20,'Test Cases'!$K$2:$K$371,"Pass")</f>
         <v>0</v>
       </c>
       <c r="D20" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A20,'Test Cases'!$K$2:$K$336,"Fail")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$371,$A20,'Test Cases'!$K$2:$K$371,"Fail")</f>
         <v>0</v>
       </c>
       <c r="E20" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A20,'Test Cases'!$K$2:$K$336,"Blocked")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$371,$A20,'Test Cases'!$K$2:$K$371,"Blocked")</f>
         <v>0</v>
       </c>
       <c r="F20" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A20,'Test Cases'!$K$2:$K$336,"N/A")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$371,$A20,'Test Cases'!$K$2:$K$371,"N/A")</f>
         <v>0</v>
       </c>
       <c r="G20" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A20,'Test Cases'!$K$2:$K$336,"Not Run")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$371,$A20,'Test Cases'!$K$2:$K$371,"Not Run")</f>
         <v>8</v>
       </c>
       <c r="H20" s="14" t="n">
@@ -5594,27 +6149,27 @@
         <v>56</v>
       </c>
       <c r="B21" s="13" t="n">
-        <f aca="false">COUNTIF('Test Cases'!$B$2:$B$336,$A21)</f>
+        <f aca="false">COUNTIF('Test Cases'!$B$2:$B$371,$A21)</f>
         <v>11</v>
       </c>
       <c r="C21" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A21,'Test Cases'!$K$2:$K$336,"Pass")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$371,$A21,'Test Cases'!$K$2:$K$371,"Pass")</f>
         <v>0</v>
       </c>
       <c r="D21" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A21,'Test Cases'!$K$2:$K$336,"Fail")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$371,$A21,'Test Cases'!$K$2:$K$371,"Fail")</f>
         <v>0</v>
       </c>
       <c r="E21" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A21,'Test Cases'!$K$2:$K$336,"Blocked")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$371,$A21,'Test Cases'!$K$2:$K$371,"Blocked")</f>
         <v>0</v>
       </c>
       <c r="F21" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A21,'Test Cases'!$K$2:$K$336,"N/A")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$371,$A21,'Test Cases'!$K$2:$K$371,"N/A")</f>
         <v>0</v>
       </c>
       <c r="G21" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A21,'Test Cases'!$K$2:$K$336,"Not Run")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$371,$A21,'Test Cases'!$K$2:$K$371,"Not Run")</f>
         <v>11</v>
       </c>
       <c r="H21" s="14" t="n">
@@ -5631,27 +6186,27 @@
         <v>57</v>
       </c>
       <c r="B22" s="13" t="n">
-        <f aca="false">COUNTIF('Test Cases'!$B$2:$B$336,$A22)</f>
+        <f aca="false">COUNTIF('Test Cases'!$B$2:$B$371,$A22)</f>
         <v>8</v>
       </c>
       <c r="C22" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A22,'Test Cases'!$K$2:$K$336,"Pass")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$371,$A22,'Test Cases'!$K$2:$K$371,"Pass")</f>
         <v>0</v>
       </c>
       <c r="D22" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A22,'Test Cases'!$K$2:$K$336,"Fail")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$371,$A22,'Test Cases'!$K$2:$K$371,"Fail")</f>
         <v>0</v>
       </c>
       <c r="E22" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A22,'Test Cases'!$K$2:$K$336,"Blocked")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$371,$A22,'Test Cases'!$K$2:$K$371,"Blocked")</f>
         <v>0</v>
       </c>
       <c r="F22" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A22,'Test Cases'!$K$2:$K$336,"N/A")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$371,$A22,'Test Cases'!$K$2:$K$371,"N/A")</f>
         <v>0</v>
       </c>
       <c r="G22" s="13" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$336,$A22,'Test Cases'!$K$2:$K$336,"Not Run")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$B$2:$B$371,$A22,'Test Cases'!$K$2:$K$371,"Not Run")</f>
         <v>8</v>
       </c>
       <c r="H22" s="14" t="n">
@@ -5669,7 +6224,7 @@
       </c>
       <c r="B23" s="16" t="n">
         <f aca="false">SUM(B5:B22)</f>
-        <v>335</v>
+        <v>370</v>
       </c>
       <c r="C23" s="16" t="n">
         <f aca="false">SUM(C5:C22)</f>
@@ -5689,7 +6244,7 @@
       </c>
       <c r="G23" s="16" t="n">
         <f aca="false">SUM(G5:G22)</f>
-        <v>335</v>
+        <v>370</v>
       </c>
       <c r="H23" s="17" t="n">
         <f aca="false">IFERROR((B23-G23-F23)/(B23-F23),0)</f>
@@ -5710,8 +6265,8 @@
         <v>60</v>
       </c>
       <c r="B27" s="8" t="n">
-        <f aca="false">COUNTIF('Test Cases'!$E$2:$E$336,"High")</f>
-        <v>177</v>
+        <f aca="false">COUNTIF('Test Cases'!$E$2:$E$371,"High")</f>
+        <v>198</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5719,7 +6274,7 @@
         <v>61</v>
       </c>
       <c r="B28" s="8" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$E$2:$E$336,"High",'Test Cases'!$K$2:$K$336,"Fail")</f>
+        <f aca="false">COUNTIFS('Test Cases'!$E$2:$E$371,"High",'Test Cases'!$K$2:$K$371,"Fail")</f>
         <v>0</v>
       </c>
     </row>
@@ -5728,8 +6283,8 @@
         <v>62</v>
       </c>
       <c r="B29" s="8" t="n">
-        <f aca="false">COUNTIFS('Test Cases'!$E$2:$E$336,"High",'Test Cases'!$K$2:$K$336,"Not Run")</f>
-        <v>177</v>
+        <f aca="false">COUNTIFS('Test Cases'!$E$2:$E$371,"High",'Test Cases'!$K$2:$K$371,"Not Run")</f>
+        <v>198</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5771,7 +6326,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:O336"/>
+  <dimension ref="A1:O371"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10"/>
@@ -13612,16 +14167,16 @@
         <v>83</v>
       </c>
       <c r="F218" s="18" t="s">
-        <v>94</v>
+        <v>853</v>
       </c>
       <c r="G218" s="18" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="H218" s="18" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="I218" s="18" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="J218" s="19"/>
       <c r="K218" s="19" t="s">
@@ -13634,7 +14189,7 @@
     </row>
     <row r="219" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A219" s="18" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="B219" s="18" t="s">
         <v>49</v>
@@ -13652,13 +14207,13 @@
         <v>845</v>
       </c>
       <c r="G219" s="18" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="H219" s="18" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="I219" s="18" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="J219" s="19"/>
       <c r="K219" s="19" t="s">
@@ -13671,7 +14226,7 @@
     </row>
     <row r="220" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A220" s="18" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="B220" s="18" t="s">
         <v>49</v>
@@ -13689,13 +14244,13 @@
         <v>845</v>
       </c>
       <c r="G220" s="18" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="H220" s="18" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="I220" s="18" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="J220" s="19"/>
       <c r="K220" s="19" t="s">
@@ -13708,7 +14263,7 @@
     </row>
     <row r="221" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A221" s="18" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="B221" s="18" t="s">
         <v>49</v>
@@ -13726,13 +14281,13 @@
         <v>94</v>
       </c>
       <c r="G221" s="18" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="H221" s="18" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="I221" s="18" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="J221" s="19"/>
       <c r="K221" s="19" t="s">
@@ -13745,7 +14300,7 @@
     </row>
     <row r="222" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A222" s="18" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="B222" s="18" t="s">
         <v>49</v>
@@ -13763,13 +14318,13 @@
         <v>94</v>
       </c>
       <c r="G222" s="18" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="H222" s="18" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="I222" s="18" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="J222" s="19"/>
       <c r="K222" s="19" t="s">
@@ -13782,13 +14337,13 @@
     </row>
     <row r="223" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A223" s="18" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="B223" s="18" t="s">
         <v>49</v>
       </c>
       <c r="C223" s="18" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="D223" s="18" t="s">
         <v>93</v>
@@ -13801,10 +14356,10 @@
       </c>
       <c r="G223" s="18"/>
       <c r="H223" s="18" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="I223" s="18" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="J223" s="19"/>
       <c r="K223" s="19" t="s">
@@ -13817,13 +14372,13 @@
     </row>
     <row r="224" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A224" s="18" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="B224" s="18" t="s">
         <v>49</v>
       </c>
       <c r="C224" s="18" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="D224" s="18" t="s">
         <v>132</v>
@@ -13832,16 +14387,16 @@
         <v>83</v>
       </c>
       <c r="F224" s="18" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="G224" s="18" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="H224" s="18" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="I224" s="18" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="J224" s="19"/>
       <c r="K224" s="19" t="s">
@@ -13854,13 +14409,13 @@
     </row>
     <row r="225" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A225" s="18" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="B225" s="18" t="s">
         <v>49</v>
       </c>
       <c r="C225" s="18" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="D225" s="18" t="s">
         <v>93</v>
@@ -13872,13 +14427,13 @@
         <v>94</v>
       </c>
       <c r="G225" s="18" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="H225" s="18" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="I225" s="18" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="J225" s="19"/>
       <c r="K225" s="19" t="s">
@@ -13891,7 +14446,7 @@
     </row>
     <row r="226" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A226" s="18" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="B226" s="18" t="s">
         <v>49</v>
@@ -13906,16 +14461,16 @@
         <v>83</v>
       </c>
       <c r="F226" s="18" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="G226" s="18" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="H226" s="18" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="I226" s="18" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="J226" s="19"/>
       <c r="K226" s="19" t="s">
@@ -13928,13 +14483,13 @@
     </row>
     <row r="227" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A227" s="18" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="B227" s="18" t="s">
         <v>49</v>
       </c>
       <c r="C227" s="18" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="D227" s="18" t="s">
         <v>93</v>
@@ -13946,13 +14501,13 @@
         <v>94</v>
       </c>
       <c r="G227" s="18" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="H227" s="18" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="I227" s="18" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="J227" s="19"/>
       <c r="K227" s="19" t="s">
@@ -13965,13 +14520,13 @@
     </row>
     <row r="228" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A228" s="18" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="B228" s="18" t="s">
         <v>49</v>
       </c>
       <c r="C228" s="18" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="D228" s="18" t="s">
         <v>82</v>
@@ -13986,10 +14541,10 @@
         <v>481</v>
       </c>
       <c r="H228" s="18" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="I228" s="18" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="J228" s="19"/>
       <c r="K228" s="19" t="s">
@@ -14002,7 +14557,7 @@
     </row>
     <row r="229" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A229" s="18" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="B229" s="18" t="s">
         <v>50</v>
@@ -14021,10 +14576,10 @@
       </c>
       <c r="G229" s="18"/>
       <c r="H229" s="18" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="I229" s="18" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="J229" s="19"/>
       <c r="K229" s="19" t="s">
@@ -14037,7 +14592,7 @@
     </row>
     <row r="230" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A230" s="18" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="B230" s="18" t="s">
         <v>50</v>
@@ -14056,10 +14611,10 @@
       </c>
       <c r="G230" s="18"/>
       <c r="H230" s="18" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="I230" s="18" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="J230" s="19"/>
       <c r="K230" s="19" t="s">
@@ -14072,7 +14627,7 @@
     </row>
     <row r="231" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A231" s="18" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="B231" s="18" t="s">
         <v>50</v>
@@ -14091,10 +14646,10 @@
       </c>
       <c r="G231" s="18"/>
       <c r="H231" s="18" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="I231" s="18" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="J231" s="19"/>
       <c r="K231" s="19" t="s">
@@ -14107,7 +14662,7 @@
     </row>
     <row r="232" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A232" s="18" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="B232" s="18" t="s">
         <v>50</v>
@@ -14126,10 +14681,10 @@
       </c>
       <c r="G232" s="18"/>
       <c r="H232" s="18" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="I232" s="18" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="J232" s="19"/>
       <c r="K232" s="19" t="s">
@@ -14142,7 +14697,7 @@
     </row>
     <row r="233" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A233" s="18" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="B233" s="18" t="s">
         <v>50</v>
@@ -14161,7 +14716,7 @@
       </c>
       <c r="G233" s="18"/>
       <c r="H233" s="18" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="I233" s="18" t="s">
         <v>318</v>
@@ -14177,7 +14732,7 @@
     </row>
     <row r="234" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A234" s="18" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="B234" s="18" t="s">
         <v>50</v>
@@ -14196,10 +14751,10 @@
       </c>
       <c r="G234" s="18"/>
       <c r="H234" s="18" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="I234" s="18" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="J234" s="19"/>
       <c r="K234" s="19" t="s">
@@ -14212,7 +14767,7 @@
     </row>
     <row r="235" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A235" s="18" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="B235" s="18" t="s">
         <v>50</v>
@@ -14231,10 +14786,10 @@
       </c>
       <c r="G235" s="18"/>
       <c r="H235" s="18" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="I235" s="18" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="J235" s="19"/>
       <c r="K235" s="19" t="s">
@@ -14247,7 +14802,7 @@
     </row>
     <row r="236" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A236" s="18" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="B236" s="18" t="s">
         <v>50</v>
@@ -14266,10 +14821,10 @@
       </c>
       <c r="G236" s="18"/>
       <c r="H236" s="18" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="I236" s="18" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="J236" s="19"/>
       <c r="K236" s="19" t="s">
@@ -14282,7 +14837,7 @@
     </row>
     <row r="237" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A237" s="18" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="B237" s="18" t="s">
         <v>50</v>
@@ -14300,13 +14855,13 @@
         <v>94</v>
       </c>
       <c r="G237" s="18" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="H237" s="18" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="I237" s="18" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="J237" s="19"/>
       <c r="K237" s="19" t="s">
@@ -14319,7 +14874,7 @@
     </row>
     <row r="238" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A238" s="18" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="B238" s="18" t="s">
         <v>50</v>
@@ -14338,10 +14893,10 @@
       </c>
       <c r="G238" s="18"/>
       <c r="H238" s="18" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="I238" s="18" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="J238" s="19"/>
       <c r="K238" s="19" t="s">
@@ -14354,7 +14909,7 @@
     </row>
     <row r="239" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A239" s="18" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="B239" s="18" t="s">
         <v>50</v>
@@ -14372,13 +14927,13 @@
         <v>94</v>
       </c>
       <c r="G239" s="18" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="H239" s="18" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="I239" s="18" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="J239" s="19"/>
       <c r="K239" s="19" t="s">
@@ -14391,7 +14946,7 @@
     </row>
     <row r="240" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A240" s="18" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="B240" s="18" t="s">
         <v>50</v>
@@ -14409,13 +14964,13 @@
         <v>94</v>
       </c>
       <c r="G240" s="18" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="H240" s="18" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="I240" s="18" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="J240" s="19"/>
       <c r="K240" s="19" t="s">
@@ -14428,7 +14983,7 @@
     </row>
     <row r="241" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A241" s="18" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="B241" s="18" t="s">
         <v>50</v>
@@ -14446,13 +15001,13 @@
         <v>94</v>
       </c>
       <c r="G241" s="18" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="H241" s="18" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="I241" s="18" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="J241" s="19"/>
       <c r="K241" s="19" t="s">
@@ -14465,13 +15020,13 @@
     </row>
     <row r="242" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A242" s="18" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="B242" s="18" t="s">
         <v>50</v>
       </c>
       <c r="C242" s="18" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="D242" s="18" t="s">
         <v>93</v>
@@ -14484,10 +15039,10 @@
       </c>
       <c r="G242" s="18"/>
       <c r="H242" s="18" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="I242" s="18" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="J242" s="19"/>
       <c r="K242" s="19" t="s">
@@ -14500,13 +15055,13 @@
     </row>
     <row r="243" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A243" s="18" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="B243" s="18" t="s">
         <v>50</v>
       </c>
       <c r="C243" s="18" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="D243" s="18" t="s">
         <v>93</v>
@@ -14518,13 +15073,13 @@
         <v>94</v>
       </c>
       <c r="G243" s="18" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="H243" s="18" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="I243" s="18" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="J243" s="19"/>
       <c r="K243" s="19" t="s">
@@ -14537,7 +15092,7 @@
     </row>
     <row r="244" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A244" s="18" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="B244" s="18" t="s">
         <v>50</v>
@@ -14556,10 +15111,10 @@
       </c>
       <c r="G244" s="18"/>
       <c r="H244" s="18" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="I244" s="18" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="J244" s="19"/>
       <c r="K244" s="19" t="s">
@@ -14572,7 +15127,7 @@
     </row>
     <row r="245" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A245" s="18" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="B245" s="18" t="s">
         <v>50</v>
@@ -14593,10 +15148,10 @@
         <v>350</v>
       </c>
       <c r="H245" s="18" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="I245" s="18" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="J245" s="19"/>
       <c r="K245" s="19" t="s">
@@ -14609,7 +15164,7 @@
     </row>
     <row r="246" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A246" s="18" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="B246" s="18" t="s">
         <v>50</v>
@@ -14624,16 +15179,16 @@
         <v>83</v>
       </c>
       <c r="F246" s="18" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="G246" s="18" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="H246" s="18" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="I246" s="18" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="J246" s="19"/>
       <c r="K246" s="19" t="s">
@@ -14646,13 +15201,13 @@
     </row>
     <row r="247" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A247" s="18" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="B247" s="18" t="s">
         <v>50</v>
       </c>
       <c r="C247" s="18" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="D247" s="18" t="s">
         <v>110</v>
@@ -14665,10 +15220,10 @@
       </c>
       <c r="G247" s="18"/>
       <c r="H247" s="18" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="I247" s="18" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="J247" s="19"/>
       <c r="K247" s="19" t="s">
@@ -14681,13 +15236,13 @@
     </row>
     <row r="248" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A248" s="18" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="B248" s="18" t="s">
         <v>50</v>
       </c>
       <c r="C248" s="18" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="D248" s="18" t="s">
         <v>93</v>
@@ -14700,10 +15255,10 @@
       </c>
       <c r="G248" s="18"/>
       <c r="H248" s="18" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="I248" s="18" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="J248" s="19"/>
       <c r="K248" s="19" t="s">
@@ -14716,7 +15271,7 @@
     </row>
     <row r="249" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A249" s="18" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="B249" s="18" t="s">
         <v>50</v>
@@ -14734,13 +15289,13 @@
         <v>168</v>
       </c>
       <c r="G249" s="18" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="H249" s="18" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="I249" s="18" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="J249" s="19"/>
       <c r="K249" s="19" t="s">
@@ -14753,13 +15308,13 @@
     </row>
     <row r="250" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A250" s="18" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="B250" s="18" t="s">
         <v>50</v>
       </c>
       <c r="C250" s="18" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="D250" s="18" t="s">
         <v>82</v>
@@ -14771,13 +15326,13 @@
         <v>94</v>
       </c>
       <c r="G250" s="18" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="H250" s="18" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="I250" s="18" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="J250" s="19"/>
       <c r="K250" s="19" t="s">
@@ -14790,7 +15345,7 @@
     </row>
     <row r="251" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A251" s="18" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="B251" s="18" t="s">
         <v>51</v>
@@ -14809,10 +15364,10 @@
       </c>
       <c r="G251" s="18"/>
       <c r="H251" s="18" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="I251" s="18" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="J251" s="19"/>
       <c r="K251" s="19" t="s">
@@ -14825,7 +15380,7 @@
     </row>
     <row r="252" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A252" s="18" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="B252" s="18" t="s">
         <v>51</v>
@@ -14844,10 +15399,10 @@
       </c>
       <c r="G252" s="18"/>
       <c r="H252" s="18" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="I252" s="18" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="J252" s="19"/>
       <c r="K252" s="19" t="s">
@@ -14860,13 +15415,13 @@
     </row>
     <row r="253" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A253" s="18" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="B253" s="18" t="s">
         <v>51</v>
       </c>
       <c r="C253" s="18" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="D253" s="18" t="s">
         <v>110</v>
@@ -14879,10 +15434,10 @@
       </c>
       <c r="G253" s="18"/>
       <c r="H253" s="18" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="I253" s="18" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="J253" s="19"/>
       <c r="K253" s="19" t="s">
@@ -14895,13 +15450,13 @@
     </row>
     <row r="254" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A254" s="18" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="B254" s="18" t="s">
         <v>51</v>
       </c>
       <c r="C254" s="18" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="D254" s="18" t="s">
         <v>93</v>
@@ -14914,10 +15469,10 @@
       </c>
       <c r="G254" s="18"/>
       <c r="H254" s="18" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="I254" s="18" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="J254" s="19"/>
       <c r="K254" s="19" t="s">
@@ -14930,7 +15485,7 @@
     </row>
     <row r="255" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A255" s="18" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="B255" s="18" t="s">
         <v>51</v>
@@ -14949,7 +15504,7 @@
       </c>
       <c r="G255" s="18"/>
       <c r="H255" s="18" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="I255" s="18" t="s">
         <v>455</v>
@@ -14965,7 +15520,7 @@
     </row>
     <row r="256" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A256" s="18" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="B256" s="18" t="s">
         <v>51</v>
@@ -14983,13 +15538,13 @@
         <v>94</v>
       </c>
       <c r="G256" s="18" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="H256" s="18" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="I256" s="18" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="J256" s="19"/>
       <c r="K256" s="19" t="s">
@@ -15002,7 +15557,7 @@
     </row>
     <row r="257" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A257" s="18" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="B257" s="18" t="s">
         <v>51</v>
@@ -15021,10 +15576,10 @@
       </c>
       <c r="G257" s="18"/>
       <c r="H257" s="18" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="I257" s="18" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="J257" s="19"/>
       <c r="K257" s="19" t="s">
@@ -15037,7 +15592,7 @@
     </row>
     <row r="258" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A258" s="18" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="B258" s="18" t="s">
         <v>51</v>
@@ -15055,13 +15610,13 @@
         <v>94</v>
       </c>
       <c r="G258" s="18" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="H258" s="18" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="I258" s="18" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="J258" s="19"/>
       <c r="K258" s="19" t="s">
@@ -15074,13 +15629,13 @@
     </row>
     <row r="259" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A259" s="18" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="B259" s="18" t="s">
         <v>51</v>
       </c>
       <c r="C259" s="18" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="D259" s="18" t="s">
         <v>403</v>
@@ -15093,10 +15648,10 @@
       </c>
       <c r="G259" s="18"/>
       <c r="H259" s="18" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="I259" s="18" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="J259" s="19"/>
       <c r="K259" s="19" t="s">
@@ -15109,7 +15664,7 @@
     </row>
     <row r="260" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A260" s="18" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="B260" s="18" t="s">
         <v>51</v>
@@ -15124,16 +15679,16 @@
         <v>83</v>
       </c>
       <c r="F260" s="18" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="G260" s="18" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="H260" s="18" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="I260" s="18" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="J260" s="19"/>
       <c r="K260" s="19" t="s">
@@ -15146,7 +15701,7 @@
     </row>
     <row r="261" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A261" s="18" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="B261" s="18" t="s">
         <v>51</v>
@@ -15164,13 +15719,13 @@
         <v>168</v>
       </c>
       <c r="G261" s="18" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="H261" s="18" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="I261" s="18" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="J261" s="19"/>
       <c r="K261" s="19" t="s">
@@ -15183,13 +15738,13 @@
     </row>
     <row r="262" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A262" s="18" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="B262" s="18" t="s">
         <v>52</v>
       </c>
       <c r="C262" s="18" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="D262" s="18" t="s">
         <v>93</v>
@@ -15198,16 +15753,16 @@
         <v>83</v>
       </c>
       <c r="F262" s="18" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="G262" s="18" t="s">
         <v>116</v>
       </c>
       <c r="H262" s="18" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="I262" s="18" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="J262" s="19"/>
       <c r="K262" s="19" t="s">
@@ -15220,13 +15775,13 @@
     </row>
     <row r="263" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A263" s="18" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="B263" s="18" t="s">
         <v>52</v>
       </c>
       <c r="C263" s="18" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="D263" s="18" t="s">
         <v>93</v>
@@ -15235,14 +15790,14 @@
         <v>83</v>
       </c>
       <c r="F263" s="18" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="G263" s="18"/>
       <c r="H263" s="18" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="I263" s="18" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="J263" s="19"/>
       <c r="K263" s="19" t="s">
@@ -15255,13 +15810,13 @@
     </row>
     <row r="264" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A264" s="18" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="B264" s="18" t="s">
         <v>52</v>
       </c>
       <c r="C264" s="18" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="D264" s="18" t="s">
         <v>132</v>
@@ -15270,14 +15825,14 @@
         <v>83</v>
       </c>
       <c r="F264" s="18" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="G264" s="18"/>
       <c r="H264" s="18" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="I264" s="18" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="J264" s="19"/>
       <c r="K264" s="19" t="s">
@@ -15290,13 +15845,13 @@
     </row>
     <row r="265" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A265" s="18" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="B265" s="18" t="s">
         <v>52</v>
       </c>
       <c r="C265" s="18" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="D265" s="18" t="s">
         <v>106</v>
@@ -15305,14 +15860,14 @@
         <v>99</v>
       </c>
       <c r="F265" s="18" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="G265" s="18"/>
       <c r="H265" s="18" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="I265" s="18" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="J265" s="19"/>
       <c r="K265" s="19" t="s">
@@ -15325,13 +15880,13 @@
     </row>
     <row r="266" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A266" s="18" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="B266" s="18" t="s">
         <v>52</v>
       </c>
       <c r="C266" s="18" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="D266" s="18" t="s">
         <v>93</v>
@@ -15340,11 +15895,11 @@
         <v>99</v>
       </c>
       <c r="F266" s="18" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="G266" s="18"/>
       <c r="H266" s="18" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="I266" s="18" t="s">
         <v>289</v>
@@ -15360,13 +15915,13 @@
     </row>
     <row r="267" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A267" s="18" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="B267" s="18" t="s">
         <v>52</v>
       </c>
       <c r="C267" s="18" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="D267" s="18" t="s">
         <v>93</v>
@@ -15375,14 +15930,14 @@
         <v>83</v>
       </c>
       <c r="F267" s="18" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="G267" s="18"/>
       <c r="H267" s="18" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="I267" s="18" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="J267" s="19"/>
       <c r="K267" s="19" t="s">
@@ -15395,13 +15950,13 @@
     </row>
     <row r="268" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A268" s="18" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="B268" s="18" t="s">
         <v>52</v>
       </c>
       <c r="C268" s="18" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="D268" s="18" t="s">
         <v>82</v>
@@ -15410,14 +15965,14 @@
         <v>83</v>
       </c>
       <c r="F268" s="18" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="G268" s="18"/>
       <c r="H268" s="18" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="I268" s="18" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="J268" s="19"/>
       <c r="K268" s="19" t="s">
@@ -15430,13 +15985,13 @@
     </row>
     <row r="269" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A269" s="18" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="B269" s="18" t="s">
         <v>52</v>
       </c>
       <c r="C269" s="18" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="D269" s="18" t="s">
         <v>110</v>
@@ -15445,14 +16000,14 @@
         <v>111</v>
       </c>
       <c r="F269" s="18" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="G269" s="18"/>
       <c r="H269" s="18" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="I269" s="18" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="J269" s="19"/>
       <c r="K269" s="19" t="s">
@@ -15465,13 +16020,13 @@
     </row>
     <row r="270" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A270" s="18" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="B270" s="18" t="s">
         <v>52</v>
       </c>
       <c r="C270" s="18" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="D270" s="18" t="s">
         <v>93</v>
@@ -15480,16 +16035,16 @@
         <v>83</v>
       </c>
       <c r="F270" s="18" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="G270" s="18" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="H270" s="18" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="I270" s="18" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="J270" s="19"/>
       <c r="K270" s="19" t="s">
@@ -15502,7 +16057,7 @@
     </row>
     <row r="271" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A271" s="18" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="B271" s="18" t="s">
         <v>53</v>
@@ -15521,10 +16076,10 @@
       </c>
       <c r="G271" s="18"/>
       <c r="H271" s="18" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="I271" s="18" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="J271" s="19"/>
       <c r="K271" s="19" t="s">
@@ -15537,7 +16092,7 @@
     </row>
     <row r="272" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A272" s="18" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="B272" s="18" t="s">
         <v>53</v>
@@ -15556,10 +16111,10 @@
       </c>
       <c r="G272" s="18"/>
       <c r="H272" s="18" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="I272" s="18" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="J272" s="19"/>
       <c r="K272" s="19" t="s">
@@ -15572,7 +16127,7 @@
     </row>
     <row r="273" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A273" s="18" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="B273" s="18" t="s">
         <v>53</v>
@@ -15591,10 +16146,10 @@
       </c>
       <c r="G273" s="18"/>
       <c r="H273" s="18" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="I273" s="18" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="J273" s="19"/>
       <c r="K273" s="19" t="s">
@@ -15607,7 +16162,7 @@
     </row>
     <row r="274" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A274" s="18" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="B274" s="18" t="s">
         <v>53</v>
@@ -15626,10 +16181,10 @@
       </c>
       <c r="G274" s="18"/>
       <c r="H274" s="18" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="I274" s="18" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="J274" s="19"/>
       <c r="K274" s="19" t="s">
@@ -15642,7 +16197,7 @@
     </row>
     <row r="275" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A275" s="18" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="B275" s="18" t="s">
         <v>53</v>
@@ -15661,10 +16216,10 @@
       </c>
       <c r="G275" s="18"/>
       <c r="H275" s="18" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="I275" s="18" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="J275" s="19"/>
       <c r="K275" s="19" t="s">
@@ -15677,7 +16232,7 @@
     </row>
     <row r="276" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A276" s="18" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="B276" s="18" t="s">
         <v>53</v>
@@ -15696,10 +16251,10 @@
       </c>
       <c r="G276" s="18"/>
       <c r="H276" s="18" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="I276" s="18" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="J276" s="19"/>
       <c r="K276" s="19" t="s">
@@ -15712,13 +16267,13 @@
     </row>
     <row r="277" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A277" s="18" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="B277" s="18" t="s">
         <v>53</v>
       </c>
       <c r="C277" s="18" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="D277" s="18" t="s">
         <v>82</v>
@@ -15730,13 +16285,13 @@
         <v>94</v>
       </c>
       <c r="G277" s="18" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="H277" s="18" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="I277" s="18" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="J277" s="19"/>
       <c r="K277" s="19" t="s">
@@ -15749,7 +16304,7 @@
     </row>
     <row r="278" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A278" s="18" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="B278" s="18" t="s">
         <v>53</v>
@@ -15764,16 +16319,16 @@
         <v>83</v>
       </c>
       <c r="F278" s="18" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="G278" s="18" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="H278" s="18" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="I278" s="18" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="J278" s="19"/>
       <c r="K278" s="19" t="s">
@@ -15786,7 +16341,7 @@
     </row>
     <row r="279" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A279" s="18" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="B279" s="18" t="s">
         <v>53</v>
@@ -15801,14 +16356,14 @@
         <v>99</v>
       </c>
       <c r="F279" s="18" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="G279" s="18"/>
       <c r="H279" s="18" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="I279" s="18" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="J279" s="19"/>
       <c r="K279" s="19" t="s">
@@ -15821,7 +16376,7 @@
     </row>
     <row r="280" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A280" s="18" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="B280" s="18" t="s">
         <v>54</v>
@@ -15840,10 +16395,10 @@
       </c>
       <c r="G280" s="18"/>
       <c r="H280" s="18" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="I280" s="18" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="J280" s="19"/>
       <c r="K280" s="19" t="s">
@@ -15856,7 +16411,7 @@
     </row>
     <row r="281" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A281" s="18" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="B281" s="18" t="s">
         <v>55</v>
@@ -15875,10 +16430,10 @@
       </c>
       <c r="G281" s="18"/>
       <c r="H281" s="18" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="I281" s="18" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="J281" s="19"/>
       <c r="K281" s="19" t="s">
@@ -15891,7 +16446,7 @@
     </row>
     <row r="282" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A282" s="18" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="B282" s="18" t="s">
         <v>55</v>
@@ -15909,13 +16464,13 @@
         <v>168</v>
       </c>
       <c r="G282" s="18" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="H282" s="18" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="I282" s="18" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="J282" s="19"/>
       <c r="K282" s="19" t="s">
@@ -15928,13 +16483,13 @@
     </row>
     <row r="283" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A283" s="18" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="B283" s="18" t="s">
         <v>55</v>
       </c>
       <c r="C283" s="18" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="D283" s="18" t="s">
         <v>132</v>
@@ -15943,14 +16498,14 @@
         <v>99</v>
       </c>
       <c r="F283" s="18" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="G283" s="18"/>
       <c r="H283" s="18" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="I283" s="18" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="J283" s="19"/>
       <c r="K283" s="19" t="s">
@@ -15965,7 +16520,7 @@
     </row>
     <row r="284" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A284" s="18" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="B284" s="18" t="s">
         <v>55</v>
@@ -15984,10 +16539,10 @@
       </c>
       <c r="G284" s="18"/>
       <c r="H284" s="18" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="I284" s="18" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="J284" s="19"/>
       <c r="K284" s="19" t="s">
@@ -16000,7 +16555,7 @@
     </row>
     <row r="285" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A285" s="18" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="B285" s="18" t="s">
         <v>55</v>
@@ -16019,10 +16574,10 @@
       </c>
       <c r="G285" s="18"/>
       <c r="H285" s="18" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="I285" s="18" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="J285" s="19"/>
       <c r="K285" s="19" t="s">
@@ -16037,13 +16592,13 @@
     </row>
     <row r="286" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A286" s="18" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="B286" s="18" t="s">
         <v>55</v>
       </c>
       <c r="C286" s="18" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="D286" s="18" t="s">
         <v>93</v>
@@ -16055,13 +16610,13 @@
         <v>94</v>
       </c>
       <c r="G286" s="18" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="H286" s="18" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="I286" s="18" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="J286" s="19"/>
       <c r="K286" s="19" t="s">
@@ -16074,13 +16629,13 @@
     </row>
     <row r="287" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A287" s="18" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="B287" s="18" t="s">
         <v>55</v>
       </c>
       <c r="C287" s="18" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="D287" s="18" t="s">
         <v>132</v>
@@ -16092,13 +16647,13 @@
         <v>133</v>
       </c>
       <c r="G287" s="18" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="H287" s="18" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="I287" s="18" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="J287" s="19"/>
       <c r="K287" s="19" t="s">
@@ -16111,13 +16666,13 @@
     </row>
     <row r="288" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A288" s="18" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="B288" s="18" t="s">
         <v>55</v>
       </c>
       <c r="C288" s="18" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="D288" s="18" t="s">
         <v>132</v>
@@ -16130,10 +16685,10 @@
       </c>
       <c r="G288" s="18"/>
       <c r="H288" s="18" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="I288" s="18" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="J288" s="19"/>
       <c r="K288" s="19" t="s">
@@ -16146,13 +16701,13 @@
     </row>
     <row r="289" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A289" s="18" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="B289" s="18" t="s">
         <v>56</v>
       </c>
       <c r="C289" s="18" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="D289" s="18" t="s">
         <v>93</v>
@@ -16164,13 +16719,13 @@
         <v>94</v>
       </c>
       <c r="G289" s="18" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="H289" s="18" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="I289" s="18" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="J289" s="19"/>
       <c r="K289" s="19" t="s">
@@ -16183,13 +16738,13 @@
     </row>
     <row r="290" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A290" s="18" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="B290" s="18" t="s">
         <v>56</v>
       </c>
       <c r="C290" s="18" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="D290" s="18" t="s">
         <v>93</v>
@@ -16201,13 +16756,13 @@
         <v>94</v>
       </c>
       <c r="G290" s="18" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="H290" s="18" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="I290" s="18" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="J290" s="19"/>
       <c r="K290" s="19" t="s">
@@ -16220,13 +16775,13 @@
     </row>
     <row r="291" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A291" s="18" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="B291" s="18" t="s">
         <v>56</v>
       </c>
       <c r="C291" s="18" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="D291" s="18" t="s">
         <v>93</v>
@@ -16238,13 +16793,13 @@
         <v>94</v>
       </c>
       <c r="G291" s="18" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="H291" s="18" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="I291" s="18" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="J291" s="19"/>
       <c r="K291" s="19" t="s">
@@ -16257,13 +16812,13 @@
     </row>
     <row r="292" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A292" s="18" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="B292" s="18" t="s">
         <v>56</v>
       </c>
       <c r="C292" s="18" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="D292" s="18" t="s">
         <v>132</v>
@@ -16272,16 +16827,16 @@
         <v>83</v>
       </c>
       <c r="F292" s="18" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="G292" s="18" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="H292" s="18" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="I292" s="18" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="J292" s="19"/>
       <c r="K292" s="19" t="s">
@@ -16294,13 +16849,13 @@
     </row>
     <row r="293" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A293" s="18" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="B293" s="18" t="s">
         <v>56</v>
       </c>
       <c r="C293" s="18" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="D293" s="18" t="s">
         <v>93</v>
@@ -16313,10 +16868,10 @@
       </c>
       <c r="G293" s="18"/>
       <c r="H293" s="18" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="I293" s="18" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="J293" s="19"/>
       <c r="K293" s="19" t="s">
@@ -16329,13 +16884,13 @@
     </row>
     <row r="294" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A294" s="18" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="B294" s="18" t="s">
         <v>56</v>
       </c>
       <c r="C294" s="18" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="D294" s="18" t="s">
         <v>93</v>
@@ -16348,10 +16903,10 @@
       </c>
       <c r="G294" s="18"/>
       <c r="H294" s="18" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="I294" s="18" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="J294" s="19"/>
       <c r="K294" s="19" t="s">
@@ -16364,13 +16919,13 @@
     </row>
     <row r="295" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A295" s="18" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="B295" s="18" t="s">
         <v>56</v>
       </c>
       <c r="C295" s="18" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="D295" s="18" t="s">
         <v>93</v>
@@ -16383,10 +16938,10 @@
       </c>
       <c r="G295" s="18"/>
       <c r="H295" s="18" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="I295" s="18" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="J295" s="19"/>
       <c r="K295" s="19" t="s">
@@ -16399,13 +16954,13 @@
     </row>
     <row r="296" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A296" s="18" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="B296" s="18" t="s">
         <v>56</v>
       </c>
       <c r="C296" s="18" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="D296" s="18" t="s">
         <v>93</v>
@@ -16418,10 +16973,10 @@
       </c>
       <c r="G296" s="18"/>
       <c r="H296" s="18" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="I296" s="18" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="J296" s="19"/>
       <c r="K296" s="19" t="s">
@@ -16434,13 +16989,13 @@
     </row>
     <row r="297" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A297" s="18" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="B297" s="18" t="s">
         <v>56</v>
       </c>
       <c r="C297" s="18" t="s">
-        <v>1141</v>
+        <v>1142</v>
       </c>
       <c r="D297" s="18" t="s">
         <v>93</v>
@@ -16453,10 +17008,10 @@
       </c>
       <c r="G297" s="18"/>
       <c r="H297" s="18" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="I297" s="18" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="J297" s="19"/>
       <c r="K297" s="19" t="s">
@@ -16469,13 +17024,13 @@
     </row>
     <row r="298" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A298" s="18" t="s">
-        <v>1144</v>
+        <v>1145</v>
       </c>
       <c r="B298" s="18" t="s">
         <v>56</v>
       </c>
       <c r="C298" s="18" t="s">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="D298" s="18" t="s">
         <v>93</v>
@@ -16488,10 +17043,10 @@
       </c>
       <c r="G298" s="18"/>
       <c r="H298" s="18" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="I298" s="18" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
       <c r="J298" s="19"/>
       <c r="K298" s="19" t="s">
@@ -16504,7 +17059,7 @@
     </row>
     <row r="299" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A299" s="18" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="B299" s="18" t="s">
         <v>56</v>
@@ -16522,13 +17077,13 @@
         <v>94</v>
       </c>
       <c r="G299" s="18" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="H299" s="18" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="I299" s="18" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="J299" s="19"/>
       <c r="K299" s="19" t="s">
@@ -16541,13 +17096,13 @@
     </row>
     <row r="300" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A300" s="18" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="B300" s="18" t="s">
         <v>57</v>
       </c>
       <c r="C300" s="18" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="D300" s="18" t="s">
         <v>110</v>
@@ -16560,10 +17115,10 @@
       </c>
       <c r="G300" s="18"/>
       <c r="H300" s="18" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="I300" s="18" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="J300" s="19"/>
       <c r="K300" s="19" t="s">
@@ -16576,13 +17131,13 @@
     </row>
     <row r="301" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A301" s="18" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="B301" s="18" t="s">
         <v>57</v>
       </c>
       <c r="C301" s="18" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="D301" s="18" t="s">
         <v>110</v>
@@ -16595,10 +17150,10 @@
       </c>
       <c r="G301" s="18"/>
       <c r="H301" s="18" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="I301" s="18" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="J301" s="19"/>
       <c r="K301" s="19" t="s">
@@ -16611,13 +17166,13 @@
     </row>
     <row r="302" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A302" s="18" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="B302" s="18" t="s">
         <v>57</v>
       </c>
       <c r="C302" s="18" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="D302" s="18" t="s">
         <v>110</v>
@@ -16630,10 +17185,10 @@
       </c>
       <c r="G302" s="18"/>
       <c r="H302" s="18" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="I302" s="18" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="J302" s="19"/>
       <c r="K302" s="19" t="s">
@@ -16646,13 +17201,13 @@
     </row>
     <row r="303" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A303" s="18" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="B303" s="18" t="s">
         <v>57</v>
       </c>
       <c r="C303" s="18" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="D303" s="18" t="s">
         <v>93</v>
@@ -16664,13 +17219,13 @@
         <v>94</v>
       </c>
       <c r="G303" s="18" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="H303" s="18" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="I303" s="18" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="J303" s="19"/>
       <c r="K303" s="19" t="s">
@@ -16683,13 +17238,13 @@
     </row>
     <row r="304" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A304" s="18" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="B304" s="18" t="s">
         <v>57</v>
       </c>
       <c r="C304" s="18" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="D304" s="18" t="s">
         <v>82</v>
@@ -16702,10 +17257,10 @@
       </c>
       <c r="G304" s="18"/>
       <c r="H304" s="18" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="I304" s="18" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="J304" s="19"/>
       <c r="K304" s="19" t="s">
@@ -16718,13 +17273,13 @@
     </row>
     <row r="305" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A305" s="18" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="B305" s="18" t="s">
         <v>57</v>
       </c>
       <c r="C305" s="18" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="D305" s="18" t="s">
         <v>82</v>
@@ -16737,10 +17292,10 @@
       </c>
       <c r="G305" s="18"/>
       <c r="H305" s="18" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="I305" s="18" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="J305" s="19"/>
       <c r="K305" s="19" t="s">
@@ -16753,13 +17308,13 @@
     </row>
     <row r="306" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A306" s="18" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B306" s="18" t="s">
         <v>57</v>
       </c>
       <c r="C306" s="18" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="D306" s="18" t="s">
         <v>93</v>
@@ -16771,13 +17326,13 @@
         <v>133</v>
       </c>
       <c r="G306" s="18" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="H306" s="18" t="s">
-        <v>1180</v>
+        <v>1181</v>
       </c>
       <c r="I306" s="18" t="s">
-        <v>1181</v>
+        <v>1182</v>
       </c>
       <c r="J306" s="19"/>
       <c r="K306" s="19" t="s">
@@ -16790,13 +17345,13 @@
     </row>
     <row r="307" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A307" s="18" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="B307" s="18" t="s">
         <v>57</v>
       </c>
       <c r="C307" s="18" t="s">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="D307" s="18" t="s">
         <v>403</v>
@@ -16809,10 +17364,10 @@
       </c>
       <c r="G307" s="18"/>
       <c r="H307" s="18" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="I307" s="18" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="J307" s="19"/>
       <c r="K307" s="19" t="s">
@@ -16825,13 +17380,13 @@
     </row>
     <row r="308" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A308" s="18" t="s">
-        <v>1186</v>
+        <v>1187</v>
       </c>
       <c r="B308" s="18" t="s">
         <v>40</v>
       </c>
       <c r="C308" s="18" t="s">
-        <v>1187</v>
+        <v>1188</v>
       </c>
       <c r="D308" s="18" t="s">
         <v>110</v>
@@ -16846,10 +17401,10 @@
         <v>85</v>
       </c>
       <c r="H308" s="18" t="s">
-        <v>1188</v>
+        <v>1189</v>
       </c>
       <c r="I308" s="18" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="J308" s="19"/>
       <c r="K308" s="19" t="s">
@@ -16859,18 +17414,18 @@
       <c r="M308" s="20"/>
       <c r="N308" s="19"/>
       <c r="O308" s="19" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="309" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A309" s="18" t="s">
-        <v>1191</v>
+        <v>1192</v>
       </c>
       <c r="B309" s="18" t="s">
         <v>40</v>
       </c>
       <c r="C309" s="18" t="s">
-        <v>1192</v>
+        <v>1193</v>
       </c>
       <c r="D309" s="18" t="s">
         <v>110</v>
@@ -16885,10 +17440,10 @@
         <v>116</v>
       </c>
       <c r="H309" s="18" t="s">
-        <v>1193</v>
+        <v>1194</v>
       </c>
       <c r="I309" s="18" t="s">
-        <v>1194</v>
+        <v>1195</v>
       </c>
       <c r="J309" s="19"/>
       <c r="K309" s="19" t="s">
@@ -16898,18 +17453,18 @@
       <c r="M309" s="20"/>
       <c r="N309" s="19"/>
       <c r="O309" s="19" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="310" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A310" s="18" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="B310" s="18" t="s">
         <v>41</v>
       </c>
       <c r="C310" s="18" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
       <c r="D310" s="18" t="s">
         <v>93</v>
@@ -16921,13 +17476,13 @@
         <v>94</v>
       </c>
       <c r="G310" s="18" t="s">
-        <v>1197</v>
+        <v>1198</v>
       </c>
       <c r="H310" s="18" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="I310" s="18" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
       <c r="J310" s="19"/>
       <c r="K310" s="19" t="s">
@@ -16937,18 +17492,18 @@
       <c r="M310" s="20"/>
       <c r="N310" s="19"/>
       <c r="O310" s="19" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="311" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A311" s="18" t="s">
-        <v>1200</v>
+        <v>1201</v>
       </c>
       <c r="B311" s="18" t="s">
         <v>41</v>
       </c>
       <c r="C311" s="18" t="s">
-        <v>1201</v>
+        <v>1202</v>
       </c>
       <c r="D311" s="18" t="s">
         <v>110</v>
@@ -16963,10 +17518,10 @@
         <v>84</v>
       </c>
       <c r="H311" s="18" t="s">
-        <v>1202</v>
+        <v>1203</v>
       </c>
       <c r="I311" s="18" t="s">
-        <v>1203</v>
+        <v>1204</v>
       </c>
       <c r="J311" s="19"/>
       <c r="K311" s="19" t="s">
@@ -16976,12 +17531,12 @@
       <c r="M311" s="20"/>
       <c r="N311" s="19"/>
       <c r="O311" s="19" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="312" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A312" s="18" t="s">
-        <v>1204</v>
+        <v>1205</v>
       </c>
       <c r="B312" s="18" t="s">
         <v>46</v>
@@ -17002,10 +17557,10 @@
         <v>84</v>
       </c>
       <c r="H312" s="18" t="s">
-        <v>1205</v>
+        <v>1206</v>
       </c>
       <c r="I312" s="18" t="s">
-        <v>1206</v>
+        <v>1207</v>
       </c>
       <c r="J312" s="19"/>
       <c r="K312" s="19" t="s">
@@ -17015,18 +17570,18 @@
       <c r="M312" s="20"/>
       <c r="N312" s="19"/>
       <c r="O312" s="19" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="313" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A313" s="18" t="s">
-        <v>1207</v>
+        <v>1208</v>
       </c>
       <c r="B313" s="18" t="s">
         <v>46</v>
       </c>
       <c r="C313" s="18" t="s">
-        <v>1208</v>
+        <v>1209</v>
       </c>
       <c r="D313" s="18" t="s">
         <v>93</v>
@@ -17038,13 +17593,13 @@
         <v>94</v>
       </c>
       <c r="G313" s="18" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="H313" s="18" t="s">
-        <v>1210</v>
+        <v>1211</v>
       </c>
       <c r="I313" s="18" t="s">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="J313" s="19"/>
       <c r="K313" s="19" t="s">
@@ -17054,18 +17609,18 @@
       <c r="M313" s="20"/>
       <c r="N313" s="19"/>
       <c r="O313" s="19" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="314" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A314" s="18" t="s">
-        <v>1212</v>
+        <v>1213</v>
       </c>
       <c r="B314" s="18" t="s">
         <v>46</v>
       </c>
       <c r="C314" s="18" t="s">
-        <v>1213</v>
+        <v>1214</v>
       </c>
       <c r="D314" s="18" t="s">
         <v>93</v>
@@ -17077,13 +17632,13 @@
         <v>94</v>
       </c>
       <c r="G314" s="18" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
       <c r="H314" s="18" t="s">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="I314" s="18" t="s">
-        <v>1216</v>
+        <v>1217</v>
       </c>
       <c r="J314" s="19"/>
       <c r="K314" s="19" t="s">
@@ -17093,18 +17648,18 @@
       <c r="M314" s="20"/>
       <c r="N314" s="19"/>
       <c r="O314" s="19" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="315" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A315" s="18" t="s">
-        <v>1217</v>
+        <v>1218</v>
       </c>
       <c r="B315" s="18" t="s">
         <v>46</v>
       </c>
       <c r="C315" s="18" t="s">
-        <v>1218</v>
+        <v>1219</v>
       </c>
       <c r="D315" s="18" t="s">
         <v>106</v>
@@ -17119,10 +17674,10 @@
         <v>84</v>
       </c>
       <c r="H315" s="18" t="s">
-        <v>1219</v>
+        <v>1220</v>
       </c>
       <c r="I315" s="18" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
       <c r="J315" s="19"/>
       <c r="K315" s="19" t="s">
@@ -17132,18 +17687,18 @@
       <c r="M315" s="20"/>
       <c r="N315" s="19"/>
       <c r="O315" s="19" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="316" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A316" s="18" t="s">
-        <v>1221</v>
+        <v>1222</v>
       </c>
       <c r="B316" s="18" t="s">
         <v>46</v>
       </c>
       <c r="C316" s="18" t="s">
-        <v>1222</v>
+        <v>1223</v>
       </c>
       <c r="D316" s="18" t="s">
         <v>110</v>
@@ -17158,10 +17713,10 @@
         <v>84</v>
       </c>
       <c r="H316" s="18" t="s">
-        <v>1223</v>
+        <v>1224</v>
       </c>
       <c r="I316" s="18" t="s">
-        <v>1224</v>
+        <v>1225</v>
       </c>
       <c r="J316" s="19"/>
       <c r="K316" s="19" t="s">
@@ -17171,18 +17726,18 @@
       <c r="M316" s="20"/>
       <c r="N316" s="19"/>
       <c r="O316" s="19" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="317" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A317" s="18" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="B317" s="18" t="s">
         <v>47</v>
       </c>
       <c r="C317" s="18" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="D317" s="18" t="s">
         <v>93</v>
@@ -17194,13 +17749,13 @@
         <v>94</v>
       </c>
       <c r="G317" s="18" t="s">
-        <v>1227</v>
+        <v>1228</v>
       </c>
       <c r="H317" s="18" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
       <c r="I317" s="18" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="J317" s="19"/>
       <c r="K317" s="19" t="s">
@@ -17210,18 +17765,18 @@
       <c r="M317" s="20"/>
       <c r="N317" s="19"/>
       <c r="O317" s="19" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="318" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A318" s="18" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
       <c r="B318" s="18" t="s">
         <v>47</v>
       </c>
       <c r="C318" s="18" t="s">
-        <v>1231</v>
+        <v>1232</v>
       </c>
       <c r="D318" s="18" t="s">
         <v>110</v>
@@ -17236,10 +17791,10 @@
         <v>84</v>
       </c>
       <c r="H318" s="18" t="s">
-        <v>1232</v>
+        <v>1233</v>
       </c>
       <c r="I318" s="18" t="s">
-        <v>1233</v>
+        <v>1234</v>
       </c>
       <c r="J318" s="19"/>
       <c r="K318" s="19" t="s">
@@ -17249,12 +17804,12 @@
       <c r="M318" s="20"/>
       <c r="N318" s="19"/>
       <c r="O318" s="19" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="319" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A319" s="18" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="B319" s="18" t="s">
         <v>47</v>
@@ -17272,13 +17827,13 @@
         <v>94</v>
       </c>
       <c r="G319" s="18" t="s">
-        <v>1235</v>
+        <v>1236</v>
       </c>
       <c r="H319" s="18" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
       <c r="I319" s="18" t="s">
-        <v>1237</v>
+        <v>1238</v>
       </c>
       <c r="J319" s="19"/>
       <c r="K319" s="19" t="s">
@@ -17288,18 +17843,18 @@
       <c r="M319" s="20"/>
       <c r="N319" s="19"/>
       <c r="O319" s="19" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="320" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A320" s="18" t="s">
-        <v>1238</v>
+        <v>1239</v>
       </c>
       <c r="B320" s="18" t="s">
         <v>47</v>
       </c>
       <c r="C320" s="18" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="D320" s="18" t="s">
         <v>132</v>
@@ -17314,10 +17869,10 @@
         <v>84</v>
       </c>
       <c r="H320" s="18" t="s">
-        <v>1240</v>
+        <v>1241</v>
       </c>
       <c r="I320" s="18" t="s">
-        <v>1241</v>
+        <v>1242</v>
       </c>
       <c r="J320" s="19"/>
       <c r="K320" s="19" t="s">
@@ -17327,18 +17882,18 @@
       <c r="M320" s="20"/>
       <c r="N320" s="19"/>
       <c r="O320" s="19" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="321" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A321" s="18" t="s">
-        <v>1242</v>
+        <v>1243</v>
       </c>
       <c r="B321" s="18" t="s">
         <v>47</v>
       </c>
       <c r="C321" s="18" t="s">
-        <v>1243</v>
+        <v>1244</v>
       </c>
       <c r="D321" s="18" t="s">
         <v>82</v>
@@ -17350,13 +17905,13 @@
         <v>94</v>
       </c>
       <c r="G321" s="18" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="H321" s="18" t="s">
-        <v>1245</v>
+        <v>1246</v>
       </c>
       <c r="I321" s="18" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="J321" s="19"/>
       <c r="K321" s="19" t="s">
@@ -17366,18 +17921,18 @@
       <c r="M321" s="20"/>
       <c r="N321" s="19"/>
       <c r="O321" s="19" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="322" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A322" s="18" t="s">
-        <v>1247</v>
+        <v>1248</v>
       </c>
       <c r="B322" s="18" t="s">
         <v>45</v>
       </c>
       <c r="C322" s="18" t="s">
-        <v>1248</v>
+        <v>1249</v>
       </c>
       <c r="D322" s="18" t="s">
         <v>82</v>
@@ -17389,13 +17944,13 @@
         <v>94</v>
       </c>
       <c r="G322" s="18" t="s">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="H322" s="18" t="s">
         <v>400</v>
       </c>
       <c r="I322" s="18" t="s">
-        <v>1250</v>
+        <v>1251</v>
       </c>
       <c r="J322" s="19"/>
       <c r="K322" s="19" t="s">
@@ -17405,18 +17960,18 @@
       <c r="M322" s="20"/>
       <c r="N322" s="19"/>
       <c r="O322" s="19" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="323" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A323" s="18" t="s">
-        <v>1251</v>
+        <v>1252</v>
       </c>
       <c r="B323" s="18" t="s">
         <v>45</v>
       </c>
       <c r="C323" s="18" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
       <c r="D323" s="18" t="s">
         <v>93</v>
@@ -17428,13 +17983,13 @@
         <v>94</v>
       </c>
       <c r="G323" s="18" t="s">
-        <v>1253</v>
+        <v>1254</v>
       </c>
       <c r="H323" s="18" t="s">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="I323" s="18" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
       <c r="J323" s="19"/>
       <c r="K323" s="19" t="s">
@@ -17444,18 +17999,18 @@
       <c r="M323" s="20"/>
       <c r="N323" s="19"/>
       <c r="O323" s="19" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="324" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A324" s="18" t="s">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="B324" s="18" t="s">
         <v>45</v>
       </c>
       <c r="C324" s="18" t="s">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="D324" s="18" t="s">
         <v>110</v>
@@ -17470,10 +18025,10 @@
         <v>84</v>
       </c>
       <c r="H324" s="18" t="s">
-        <v>1258</v>
+        <v>1259</v>
       </c>
       <c r="I324" s="18" t="s">
-        <v>1259</v>
+        <v>1260</v>
       </c>
       <c r="J324" s="19"/>
       <c r="K324" s="19" t="s">
@@ -17483,18 +18038,18 @@
       <c r="M324" s="20"/>
       <c r="N324" s="19"/>
       <c r="O324" s="19" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="325" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A325" s="18" t="s">
-        <v>1260</v>
+        <v>1261</v>
       </c>
       <c r="B325" s="18" t="s">
         <v>48</v>
       </c>
       <c r="C325" s="18" t="s">
-        <v>1261</v>
+        <v>1262</v>
       </c>
       <c r="D325" s="18" t="s">
         <v>93</v>
@@ -17506,13 +18061,13 @@
         <v>412</v>
       </c>
       <c r="G325" s="18" t="s">
-        <v>1262</v>
+        <v>1263</v>
       </c>
       <c r="H325" s="18" t="s">
-        <v>1263</v>
+        <v>1264</v>
       </c>
       <c r="I325" s="18" t="s">
-        <v>1264</v>
+        <v>1265</v>
       </c>
       <c r="J325" s="19"/>
       <c r="K325" s="19" t="s">
@@ -17522,18 +18077,18 @@
       <c r="M325" s="20"/>
       <c r="N325" s="19"/>
       <c r="O325" s="19" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="326" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A326" s="18" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="B326" s="18" t="s">
         <v>46</v>
       </c>
       <c r="C326" s="18" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="D326" s="18" t="s">
         <v>106</v>
@@ -17548,10 +18103,10 @@
         <v>464</v>
       </c>
       <c r="H326" s="18" t="s">
-        <v>1267</v>
+        <v>1268</v>
       </c>
       <c r="I326" s="18" t="s">
-        <v>1268</v>
+        <v>1269</v>
       </c>
       <c r="J326" s="19"/>
       <c r="K326" s="19" t="s">
@@ -17561,18 +18116,18 @@
       <c r="M326" s="20"/>
       <c r="N326" s="19"/>
       <c r="O326" s="19" t="s">
-        <v>1269</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="327" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A327" s="18" t="s">
-        <v>1270</v>
+        <v>1271</v>
       </c>
       <c r="B327" s="18" t="s">
         <v>46</v>
       </c>
       <c r="C327" s="18" t="s">
-        <v>1271</v>
+        <v>1272</v>
       </c>
       <c r="D327" s="18" t="s">
         <v>93</v>
@@ -17584,13 +18139,13 @@
         <v>94</v>
       </c>
       <c r="G327" s="18" t="s">
-        <v>1272</v>
+        <v>1273</v>
       </c>
       <c r="H327" s="18" t="s">
-        <v>1273</v>
+        <v>1274</v>
       </c>
       <c r="I327" s="18" t="s">
-        <v>1274</v>
+        <v>1275</v>
       </c>
       <c r="J327" s="19"/>
       <c r="K327" s="19" t="s">
@@ -17600,18 +18155,18 @@
       <c r="M327" s="20"/>
       <c r="N327" s="19"/>
       <c r="O327" s="19" t="s">
-        <v>1269</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="328" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A328" s="18" t="s">
-        <v>1275</v>
+        <v>1276</v>
       </c>
       <c r="B328" s="18" t="s">
         <v>46</v>
       </c>
       <c r="C328" s="18" t="s">
-        <v>1276</v>
+        <v>1277</v>
       </c>
       <c r="D328" s="18" t="s">
         <v>93</v>
@@ -17623,13 +18178,13 @@
         <v>94</v>
       </c>
       <c r="G328" s="18" t="s">
-        <v>1277</v>
+        <v>1278</v>
       </c>
       <c r="H328" s="18" t="s">
-        <v>1278</v>
+        <v>1279</v>
       </c>
       <c r="I328" s="18" t="s">
-        <v>1279</v>
+        <v>1280</v>
       </c>
       <c r="J328" s="19"/>
       <c r="K328" s="19" t="s">
@@ -17639,18 +18194,18 @@
       <c r="M328" s="20"/>
       <c r="N328" s="19"/>
       <c r="O328" s="19" t="s">
-        <v>1269</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="329" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A329" s="18" t="s">
-        <v>1280</v>
+        <v>1281</v>
       </c>
       <c r="B329" s="18" t="s">
         <v>46</v>
       </c>
       <c r="C329" s="18" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="D329" s="18" t="s">
         <v>110</v>
@@ -17665,10 +18220,10 @@
         <v>84</v>
       </c>
       <c r="H329" s="18" t="s">
-        <v>1282</v>
+        <v>1283</v>
       </c>
       <c r="I329" s="18" t="s">
-        <v>1283</v>
+        <v>1284</v>
       </c>
       <c r="J329" s="19"/>
       <c r="K329" s="19" t="s">
@@ -17678,18 +18233,18 @@
       <c r="M329" s="20"/>
       <c r="N329" s="19"/>
       <c r="O329" s="19" t="s">
-        <v>1269</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="330" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A330" s="18" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="B330" s="18" t="s">
         <v>47</v>
       </c>
       <c r="C330" s="18" t="s">
-        <v>1285</v>
+        <v>1286</v>
       </c>
       <c r="D330" s="18" t="s">
         <v>110</v>
@@ -17704,10 +18259,10 @@
         <v>84</v>
       </c>
       <c r="H330" s="18" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="I330" s="18" t="s">
-        <v>1287</v>
+        <v>1288</v>
       </c>
       <c r="J330" s="19"/>
       <c r="K330" s="19" t="s">
@@ -17717,18 +18272,18 @@
       <c r="M330" s="20"/>
       <c r="N330" s="19"/>
       <c r="O330" s="19" t="s">
-        <v>1269</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="331" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A331" s="18" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="B331" s="18" t="s">
         <v>47</v>
       </c>
       <c r="C331" s="18" t="s">
-        <v>1289</v>
+        <v>1290</v>
       </c>
       <c r="D331" s="18" t="s">
         <v>93</v>
@@ -17743,10 +18298,10 @@
         <v>815</v>
       </c>
       <c r="H331" s="18" t="s">
-        <v>1290</v>
+        <v>1291</v>
       </c>
       <c r="I331" s="18" t="s">
-        <v>1291</v>
+        <v>1292</v>
       </c>
       <c r="J331" s="19"/>
       <c r="K331" s="19" t="s">
@@ -17756,18 +18311,18 @@
       <c r="M331" s="20"/>
       <c r="N331" s="19"/>
       <c r="O331" s="19" t="s">
-        <v>1269</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="332" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A332" s="18" t="s">
-        <v>1292</v>
+        <v>1293</v>
       </c>
       <c r="B332" s="18" t="s">
         <v>47</v>
       </c>
       <c r="C332" s="18" t="s">
-        <v>1293</v>
+        <v>1294</v>
       </c>
       <c r="D332" s="18" t="s">
         <v>106</v>
@@ -17782,10 +18337,10 @@
         <v>815</v>
       </c>
       <c r="H332" s="18" t="s">
-        <v>1294</v>
+        <v>1295</v>
       </c>
       <c r="I332" s="18" t="s">
-        <v>1295</v>
+        <v>1296</v>
       </c>
       <c r="J332" s="19"/>
       <c r="K332" s="19" t="s">
@@ -17795,18 +18350,18 @@
       <c r="M332" s="20"/>
       <c r="N332" s="19"/>
       <c r="O332" s="19" t="s">
-        <v>1269</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="333" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A333" s="18" t="s">
-        <v>1296</v>
+        <v>1297</v>
       </c>
       <c r="B333" s="18" t="s">
         <v>47</v>
       </c>
       <c r="C333" s="18" t="s">
-        <v>1297</v>
+        <v>1298</v>
       </c>
       <c r="D333" s="18" t="s">
         <v>93</v>
@@ -17818,13 +18373,13 @@
         <v>94</v>
       </c>
       <c r="G333" s="18" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="H333" s="18" t="s">
-        <v>1299</v>
+        <v>1300</v>
       </c>
       <c r="I333" s="18" t="s">
-        <v>1300</v>
+        <v>1301</v>
       </c>
       <c r="J333" s="19"/>
       <c r="K333" s="19" t="s">
@@ -17834,18 +18389,18 @@
       <c r="M333" s="20"/>
       <c r="N333" s="19"/>
       <c r="O333" s="19" t="s">
-        <v>1269</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="334" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A334" s="18" t="s">
-        <v>1301</v>
+        <v>1302</v>
       </c>
       <c r="B334" s="18" t="s">
         <v>50</v>
       </c>
       <c r="C334" s="18" t="s">
-        <v>1302</v>
+        <v>1303</v>
       </c>
       <c r="D334" s="18" t="s">
         <v>93</v>
@@ -17860,10 +18415,10 @@
         <v>84</v>
       </c>
       <c r="H334" s="18" t="s">
-        <v>1303</v>
+        <v>1304</v>
       </c>
       <c r="I334" s="18" t="s">
-        <v>1304</v>
+        <v>1305</v>
       </c>
       <c r="J334" s="19"/>
       <c r="K334" s="19" t="s">
@@ -17873,18 +18428,18 @@
       <c r="M334" s="20"/>
       <c r="N334" s="19"/>
       <c r="O334" s="19" t="s">
-        <v>1269</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="335" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A335" s="18" t="s">
-        <v>1305</v>
+        <v>1306</v>
       </c>
       <c r="B335" s="18" t="s">
         <v>40</v>
       </c>
       <c r="C335" s="18" t="s">
-        <v>1306</v>
+        <v>1307</v>
       </c>
       <c r="D335" s="18" t="s">
         <v>110</v>
@@ -17896,13 +18451,13 @@
         <v>94</v>
       </c>
       <c r="G335" s="18" t="s">
-        <v>1307</v>
+        <v>1308</v>
       </c>
       <c r="H335" s="18" t="s">
-        <v>1308</v>
+        <v>1309</v>
       </c>
       <c r="I335" s="18" t="s">
-        <v>1309</v>
+        <v>1310</v>
       </c>
       <c r="J335" s="19"/>
       <c r="K335" s="19" t="s">
@@ -17912,18 +18467,18 @@
       <c r="M335" s="20"/>
       <c r="N335" s="19"/>
       <c r="O335" s="19" t="s">
-        <v>1269</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="336" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A336" s="18" t="s">
-        <v>1310</v>
+        <v>1311</v>
       </c>
       <c r="B336" s="18" t="s">
         <v>42</v>
       </c>
       <c r="C336" s="18" t="s">
-        <v>1311</v>
+        <v>1312</v>
       </c>
       <c r="D336" s="18" t="s">
         <v>93</v>
@@ -17935,13 +18490,13 @@
         <v>94</v>
       </c>
       <c r="G336" s="18" t="s">
-        <v>1312</v>
+        <v>1313</v>
       </c>
       <c r="H336" s="18" t="s">
-        <v>1313</v>
+        <v>1314</v>
       </c>
       <c r="I336" s="18" t="s">
-        <v>1314</v>
+        <v>1315</v>
       </c>
       <c r="J336" s="19"/>
       <c r="K336" s="19" t="s">
@@ -17951,12 +18506,1307 @@
       <c r="M336" s="20"/>
       <c r="N336" s="19"/>
       <c r="O336" s="19" t="s">
-        <v>1269</v>
-      </c>
+        <v>1270</v>
+      </c>
+    </row>
+    <row r="337" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A337" s="18" t="s">
+        <v>1316</v>
+      </c>
+      <c r="B337" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="C337" s="18" t="s">
+        <v>1317</v>
+      </c>
+      <c r="D337" s="18" t="s">
+        <v>93</v>
+      </c>
+      <c r="E337" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="F337" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="G337" s="18" t="s">
+        <v>1318</v>
+      </c>
+      <c r="H337" s="18" t="s">
+        <v>1319</v>
+      </c>
+      <c r="I337" s="18" t="s">
+        <v>1320</v>
+      </c>
+      <c r="J337" s="19"/>
+      <c r="K337" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="L337" s="19"/>
+      <c r="M337" s="20"/>
+      <c r="N337" s="19"/>
+      <c r="O337" s="19"/>
+    </row>
+    <row r="338" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A338" s="18" t="s">
+        <v>1321</v>
+      </c>
+      <c r="B338" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="C338" s="18" t="s">
+        <v>1322</v>
+      </c>
+      <c r="D338" s="18" t="s">
+        <v>93</v>
+      </c>
+      <c r="E338" s="18" t="s">
+        <v>99</v>
+      </c>
+      <c r="F338" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="G338" s="18" t="s">
+        <v>1323</v>
+      </c>
+      <c r="H338" s="18" t="s">
+        <v>1319</v>
+      </c>
+      <c r="I338" s="18" t="s">
+        <v>1324</v>
+      </c>
+      <c r="J338" s="19"/>
+      <c r="K338" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="L338" s="19"/>
+      <c r="M338" s="20"/>
+      <c r="N338" s="19"/>
+      <c r="O338" s="19"/>
+    </row>
+    <row r="339" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A339" s="18" t="s">
+        <v>1325</v>
+      </c>
+      <c r="B339" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="C339" s="18" t="s">
+        <v>1326</v>
+      </c>
+      <c r="D339" s="18" t="s">
+        <v>93</v>
+      </c>
+      <c r="E339" s="18" t="s">
+        <v>99</v>
+      </c>
+      <c r="F339" s="18" t="s">
+        <v>168</v>
+      </c>
+      <c r="G339" s="18" t="s">
+        <v>1327</v>
+      </c>
+      <c r="H339" s="18" t="s">
+        <v>1328</v>
+      </c>
+      <c r="I339" s="18" t="s">
+        <v>1329</v>
+      </c>
+      <c r="J339" s="19"/>
+      <c r="K339" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="L339" s="19"/>
+      <c r="M339" s="20"/>
+      <c r="N339" s="19"/>
+      <c r="O339" s="19"/>
+    </row>
+    <row r="340" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A340" s="18" t="s">
+        <v>1330</v>
+      </c>
+      <c r="B340" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="C340" s="18" t="s">
+        <v>1331</v>
+      </c>
+      <c r="D340" s="18" t="s">
+        <v>93</v>
+      </c>
+      <c r="E340" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="F340" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="G340" s="18" t="s">
+        <v>1332</v>
+      </c>
+      <c r="H340" s="18" t="s">
+        <v>1333</v>
+      </c>
+      <c r="I340" s="18" t="s">
+        <v>1334</v>
+      </c>
+      <c r="J340" s="19"/>
+      <c r="K340" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="L340" s="19"/>
+      <c r="M340" s="20"/>
+      <c r="N340" s="19"/>
+      <c r="O340" s="19"/>
+    </row>
+    <row r="341" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A341" s="18" t="s">
+        <v>1335</v>
+      </c>
+      <c r="B341" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="C341" s="18" t="s">
+        <v>1336</v>
+      </c>
+      <c r="D341" s="18" t="s">
+        <v>132</v>
+      </c>
+      <c r="E341" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="F341" s="18" t="s">
+        <v>1337</v>
+      </c>
+      <c r="G341" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="H341" s="18" t="s">
+        <v>418</v>
+      </c>
+      <c r="I341" s="18" t="s">
+        <v>1338</v>
+      </c>
+      <c r="J341" s="19"/>
+      <c r="K341" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="L341" s="19"/>
+      <c r="M341" s="20"/>
+      <c r="N341" s="19"/>
+      <c r="O341" s="19"/>
+    </row>
+    <row r="342" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A342" s="18" t="s">
+        <v>1339</v>
+      </c>
+      <c r="B342" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="C342" s="18" t="s">
+        <v>1340</v>
+      </c>
+      <c r="D342" s="18" t="s">
+        <v>93</v>
+      </c>
+      <c r="E342" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="F342" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="G342" s="18" t="s">
+        <v>1341</v>
+      </c>
+      <c r="H342" s="18" t="s">
+        <v>1342</v>
+      </c>
+      <c r="I342" s="18" t="s">
+        <v>1343</v>
+      </c>
+      <c r="J342" s="19"/>
+      <c r="K342" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="L342" s="19"/>
+      <c r="M342" s="20"/>
+      <c r="N342" s="19"/>
+      <c r="O342" s="19"/>
+    </row>
+    <row r="343" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A343" s="18" t="s">
+        <v>1344</v>
+      </c>
+      <c r="B343" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="C343" s="18" t="s">
+        <v>1345</v>
+      </c>
+      <c r="D343" s="18" t="s">
+        <v>132</v>
+      </c>
+      <c r="E343" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="F343" s="18" t="s">
+        <v>1346</v>
+      </c>
+      <c r="G343" s="18" t="s">
+        <v>1347</v>
+      </c>
+      <c r="H343" s="18" t="s">
+        <v>1348</v>
+      </c>
+      <c r="I343" s="18" t="s">
+        <v>1349</v>
+      </c>
+      <c r="J343" s="19"/>
+      <c r="K343" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="L343" s="19"/>
+      <c r="M343" s="20"/>
+      <c r="N343" s="19"/>
+      <c r="O343" s="19"/>
+    </row>
+    <row r="344" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A344" s="18" t="s">
+        <v>1350</v>
+      </c>
+      <c r="B344" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="C344" s="18" t="s">
+        <v>1351</v>
+      </c>
+      <c r="D344" s="18" t="s">
+        <v>82</v>
+      </c>
+      <c r="E344" s="18" t="s">
+        <v>99</v>
+      </c>
+      <c r="F344" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="G344" s="18" t="s">
+        <v>1352</v>
+      </c>
+      <c r="H344" s="18" t="s">
+        <v>1353</v>
+      </c>
+      <c r="I344" s="18" t="s">
+        <v>1354</v>
+      </c>
+      <c r="J344" s="19"/>
+      <c r="K344" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="L344" s="19"/>
+      <c r="M344" s="20"/>
+      <c r="N344" s="19"/>
+      <c r="O344" s="19"/>
+    </row>
+    <row r="345" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A345" s="18" t="s">
+        <v>1355</v>
+      </c>
+      <c r="B345" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="C345" s="18" t="s">
+        <v>1356</v>
+      </c>
+      <c r="D345" s="18" t="s">
+        <v>93</v>
+      </c>
+      <c r="E345" s="18" t="s">
+        <v>99</v>
+      </c>
+      <c r="F345" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="G345" s="18" t="s">
+        <v>1357</v>
+      </c>
+      <c r="H345" s="18" t="s">
+        <v>1358</v>
+      </c>
+      <c r="I345" s="18" t="s">
+        <v>1359</v>
+      </c>
+      <c r="J345" s="19"/>
+      <c r="K345" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="L345" s="19"/>
+      <c r="M345" s="20"/>
+      <c r="N345" s="19"/>
+      <c r="O345" s="19"/>
+    </row>
+    <row r="346" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A346" s="18" t="s">
+        <v>1360</v>
+      </c>
+      <c r="B346" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="C346" s="18" t="s">
+        <v>1361</v>
+      </c>
+      <c r="D346" s="18" t="s">
+        <v>93</v>
+      </c>
+      <c r="E346" s="18" t="s">
+        <v>99</v>
+      </c>
+      <c r="F346" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="G346" s="18" t="s">
+        <v>1362</v>
+      </c>
+      <c r="H346" s="18" t="s">
+        <v>1363</v>
+      </c>
+      <c r="I346" s="18" t="s">
+        <v>1364</v>
+      </c>
+      <c r="J346" s="19"/>
+      <c r="K346" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="L346" s="19"/>
+      <c r="M346" s="20"/>
+      <c r="N346" s="19"/>
+      <c r="O346" s="19"/>
+    </row>
+    <row r="347" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A347" s="18" t="s">
+        <v>1365</v>
+      </c>
+      <c r="B347" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="C347" s="18" t="s">
+        <v>1366</v>
+      </c>
+      <c r="D347" s="18" t="s">
+        <v>403</v>
+      </c>
+      <c r="E347" s="18" t="s">
+        <v>111</v>
+      </c>
+      <c r="F347" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="G347" s="18" t="s">
+        <v>1367</v>
+      </c>
+      <c r="H347" s="18" t="s">
+        <v>1368</v>
+      </c>
+      <c r="I347" s="18" t="s">
+        <v>1369</v>
+      </c>
+      <c r="J347" s="19"/>
+      <c r="K347" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="L347" s="19"/>
+      <c r="M347" s="20"/>
+      <c r="N347" s="19"/>
+      <c r="O347" s="19"/>
+    </row>
+    <row r="348" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A348" s="18" t="s">
+        <v>1370</v>
+      </c>
+      <c r="B348" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="C348" s="18" t="s">
+        <v>1371</v>
+      </c>
+      <c r="D348" s="18" t="s">
+        <v>93</v>
+      </c>
+      <c r="E348" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="F348" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="G348" s="18" t="s">
+        <v>1372</v>
+      </c>
+      <c r="H348" s="18" t="s">
+        <v>1373</v>
+      </c>
+      <c r="I348" s="18" t="s">
+        <v>1374</v>
+      </c>
+      <c r="J348" s="19"/>
+      <c r="K348" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="L348" s="19"/>
+      <c r="M348" s="20"/>
+      <c r="N348" s="19"/>
+      <c r="O348" s="19"/>
+    </row>
+    <row r="349" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A349" s="18" t="s">
+        <v>1375</v>
+      </c>
+      <c r="B349" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="C349" s="18" t="s">
+        <v>1376</v>
+      </c>
+      <c r="D349" s="18" t="s">
+        <v>106</v>
+      </c>
+      <c r="E349" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="F349" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="G349" s="18" t="s">
+        <v>1377</v>
+      </c>
+      <c r="H349" s="18" t="s">
+        <v>1378</v>
+      </c>
+      <c r="I349" s="18" t="s">
+        <v>1379</v>
+      </c>
+      <c r="J349" s="19"/>
+      <c r="K349" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="L349" s="19"/>
+      <c r="M349" s="20"/>
+      <c r="N349" s="19"/>
+      <c r="O349" s="19"/>
+    </row>
+    <row r="350" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A350" s="18" t="s">
+        <v>1380</v>
+      </c>
+      <c r="B350" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="C350" s="18" t="s">
+        <v>1381</v>
+      </c>
+      <c r="D350" s="18" t="s">
+        <v>106</v>
+      </c>
+      <c r="E350" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="F350" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="G350" s="18" t="s">
+        <v>1377</v>
+      </c>
+      <c r="H350" s="18" t="s">
+        <v>1382</v>
+      </c>
+      <c r="I350" s="18" t="s">
+        <v>1383</v>
+      </c>
+      <c r="J350" s="19"/>
+      <c r="K350" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="L350" s="19"/>
+      <c r="M350" s="20"/>
+      <c r="N350" s="19"/>
+      <c r="O350" s="19"/>
+    </row>
+    <row r="351" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A351" s="18" t="s">
+        <v>1384</v>
+      </c>
+      <c r="B351" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="C351" s="18" t="s">
+        <v>1385</v>
+      </c>
+      <c r="D351" s="18" t="s">
+        <v>82</v>
+      </c>
+      <c r="E351" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="F351" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="G351" s="18" t="s">
+        <v>1386</v>
+      </c>
+      <c r="H351" s="18" t="s">
+        <v>1387</v>
+      </c>
+      <c r="I351" s="18" t="s">
+        <v>1388</v>
+      </c>
+      <c r="J351" s="19"/>
+      <c r="K351" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="L351" s="19"/>
+      <c r="M351" s="20"/>
+      <c r="N351" s="19"/>
+      <c r="O351" s="19"/>
+    </row>
+    <row r="352" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A352" s="18" t="s">
+        <v>1389</v>
+      </c>
+      <c r="B352" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="C352" s="18" t="s">
+        <v>1390</v>
+      </c>
+      <c r="D352" s="18" t="s">
+        <v>93</v>
+      </c>
+      <c r="E352" s="18" t="s">
+        <v>99</v>
+      </c>
+      <c r="F352" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="G352" s="18" t="s">
+        <v>1391</v>
+      </c>
+      <c r="H352" s="18" t="s">
+        <v>1373</v>
+      </c>
+      <c r="I352" s="18" t="s">
+        <v>1392</v>
+      </c>
+      <c r="J352" s="19"/>
+      <c r="K352" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="L352" s="19"/>
+      <c r="M352" s="20"/>
+      <c r="N352" s="19"/>
+      <c r="O352" s="19"/>
+    </row>
+    <row r="353" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A353" s="18" t="s">
+        <v>1393</v>
+      </c>
+      <c r="B353" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="C353" s="18" t="s">
+        <v>1394</v>
+      </c>
+      <c r="D353" s="18" t="s">
+        <v>82</v>
+      </c>
+      <c r="E353" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="F353" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="G353" s="18" t="s">
+        <v>1395</v>
+      </c>
+      <c r="H353" s="18" t="s">
+        <v>1396</v>
+      </c>
+      <c r="I353" s="18" t="s">
+        <v>1397</v>
+      </c>
+      <c r="J353" s="19"/>
+      <c r="K353" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="L353" s="19"/>
+      <c r="M353" s="20"/>
+      <c r="N353" s="19"/>
+      <c r="O353" s="19"/>
+    </row>
+    <row r="354" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A354" s="18" t="s">
+        <v>1398</v>
+      </c>
+      <c r="B354" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="C354" s="18" t="s">
+        <v>1399</v>
+      </c>
+      <c r="D354" s="18" t="s">
+        <v>82</v>
+      </c>
+      <c r="E354" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="F354" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="G354" s="18" t="s">
+        <v>1400</v>
+      </c>
+      <c r="H354" s="18" t="s">
+        <v>1401</v>
+      </c>
+      <c r="I354" s="18" t="s">
+        <v>1402</v>
+      </c>
+      <c r="J354" s="19"/>
+      <c r="K354" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="L354" s="19"/>
+      <c r="M354" s="20"/>
+      <c r="N354" s="19"/>
+      <c r="O354" s="19"/>
+    </row>
+    <row r="355" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A355" s="18" t="s">
+        <v>1403</v>
+      </c>
+      <c r="B355" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="C355" s="18" t="s">
+        <v>1404</v>
+      </c>
+      <c r="D355" s="18" t="s">
+        <v>93</v>
+      </c>
+      <c r="E355" s="18" t="s">
+        <v>99</v>
+      </c>
+      <c r="F355" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="G355" s="18" t="s">
+        <v>1405</v>
+      </c>
+      <c r="H355" s="18" t="s">
+        <v>1406</v>
+      </c>
+      <c r="I355" s="18" t="s">
+        <v>1407</v>
+      </c>
+      <c r="J355" s="19"/>
+      <c r="K355" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="L355" s="19"/>
+      <c r="M355" s="20"/>
+      <c r="N355" s="19"/>
+      <c r="O355" s="19"/>
+    </row>
+    <row r="356" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A356" s="18" t="s">
+        <v>1408</v>
+      </c>
+      <c r="B356" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="C356" s="18" t="s">
+        <v>1409</v>
+      </c>
+      <c r="D356" s="18" t="s">
+        <v>93</v>
+      </c>
+      <c r="E356" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="F356" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="G356" s="18" t="s">
+        <v>1410</v>
+      </c>
+      <c r="H356" s="18" t="s">
+        <v>1411</v>
+      </c>
+      <c r="I356" s="18" t="s">
+        <v>1412</v>
+      </c>
+      <c r="J356" s="19"/>
+      <c r="K356" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="L356" s="19"/>
+      <c r="M356" s="20"/>
+      <c r="N356" s="19"/>
+      <c r="O356" s="19"/>
+    </row>
+    <row r="357" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A357" s="18" t="s">
+        <v>1413</v>
+      </c>
+      <c r="B357" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="C357" s="18" t="s">
+        <v>1414</v>
+      </c>
+      <c r="D357" s="18" t="s">
+        <v>82</v>
+      </c>
+      <c r="E357" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="F357" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="G357" s="18" t="s">
+        <v>1415</v>
+      </c>
+      <c r="H357" s="18" t="s">
+        <v>1416</v>
+      </c>
+      <c r="I357" s="18" t="s">
+        <v>1417</v>
+      </c>
+      <c r="J357" s="19"/>
+      <c r="K357" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="L357" s="19"/>
+      <c r="M357" s="20"/>
+      <c r="N357" s="19"/>
+      <c r="O357" s="19"/>
+    </row>
+    <row r="358" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A358" s="18" t="s">
+        <v>1418</v>
+      </c>
+      <c r="B358" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="C358" s="18" t="s">
+        <v>1419</v>
+      </c>
+      <c r="D358" s="18" t="s">
+        <v>106</v>
+      </c>
+      <c r="E358" s="18" t="s">
+        <v>99</v>
+      </c>
+      <c r="F358" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="G358" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="H358" s="18" t="s">
+        <v>1420</v>
+      </c>
+      <c r="I358" s="18" t="s">
+        <v>1421</v>
+      </c>
+      <c r="J358" s="19"/>
+      <c r="K358" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="L358" s="19"/>
+      <c r="M358" s="20"/>
+      <c r="N358" s="19"/>
+      <c r="O358" s="19"/>
+    </row>
+    <row r="359" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A359" s="18" t="s">
+        <v>1422</v>
+      </c>
+      <c r="B359" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="C359" s="18" t="s">
+        <v>1423</v>
+      </c>
+      <c r="D359" s="18" t="s">
+        <v>106</v>
+      </c>
+      <c r="E359" s="18" t="s">
+        <v>99</v>
+      </c>
+      <c r="F359" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="G359" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="H359" s="18" t="s">
+        <v>1424</v>
+      </c>
+      <c r="I359" s="18" t="s">
+        <v>1425</v>
+      </c>
+      <c r="J359" s="19"/>
+      <c r="K359" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="L359" s="19"/>
+      <c r="M359" s="20"/>
+      <c r="N359" s="19"/>
+      <c r="O359" s="19"/>
+    </row>
+    <row r="360" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A360" s="18" t="s">
+        <v>1426</v>
+      </c>
+      <c r="B360" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="C360" s="18" t="s">
+        <v>1427</v>
+      </c>
+      <c r="D360" s="18" t="s">
+        <v>403</v>
+      </c>
+      <c r="E360" s="18" t="s">
+        <v>111</v>
+      </c>
+      <c r="F360" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="G360" s="18" t="s">
+        <v>1428</v>
+      </c>
+      <c r="H360" s="18" t="s">
+        <v>1429</v>
+      </c>
+      <c r="I360" s="18" t="s">
+        <v>1430</v>
+      </c>
+      <c r="J360" s="19"/>
+      <c r="K360" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="L360" s="19"/>
+      <c r="M360" s="20"/>
+      <c r="N360" s="19"/>
+      <c r="O360" s="19"/>
+    </row>
+    <row r="361" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A361" s="18" t="s">
+        <v>1431</v>
+      </c>
+      <c r="B361" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="C361" s="18" t="s">
+        <v>1432</v>
+      </c>
+      <c r="D361" s="18" t="s">
+        <v>82</v>
+      </c>
+      <c r="E361" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="F361" s="18" t="s">
+        <v>168</v>
+      </c>
+      <c r="G361" s="18" t="s">
+        <v>1433</v>
+      </c>
+      <c r="H361" s="18" t="s">
+        <v>1434</v>
+      </c>
+      <c r="I361" s="18" t="s">
+        <v>1435</v>
+      </c>
+      <c r="J361" s="19"/>
+      <c r="K361" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="L361" s="19"/>
+      <c r="M361" s="20"/>
+      <c r="N361" s="19"/>
+      <c r="O361" s="19"/>
+    </row>
+    <row r="362" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A362" s="18" t="s">
+        <v>1436</v>
+      </c>
+      <c r="B362" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="C362" s="18" t="s">
+        <v>1437</v>
+      </c>
+      <c r="D362" s="18" t="s">
+        <v>93</v>
+      </c>
+      <c r="E362" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="F362" s="18" t="s">
+        <v>412</v>
+      </c>
+      <c r="G362" s="18" t="s">
+        <v>1438</v>
+      </c>
+      <c r="H362" s="18" t="s">
+        <v>1439</v>
+      </c>
+      <c r="I362" s="18" t="s">
+        <v>1440</v>
+      </c>
+      <c r="J362" s="19"/>
+      <c r="K362" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="L362" s="19"/>
+      <c r="M362" s="20"/>
+      <c r="N362" s="19"/>
+      <c r="O362" s="19"/>
+    </row>
+    <row r="363" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A363" s="18" t="s">
+        <v>1441</v>
+      </c>
+      <c r="B363" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="C363" s="18" t="s">
+        <v>1442</v>
+      </c>
+      <c r="D363" s="18" t="s">
+        <v>93</v>
+      </c>
+      <c r="E363" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="F363" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="G363" s="18" t="s">
+        <v>1443</v>
+      </c>
+      <c r="H363" s="18" t="s">
+        <v>1444</v>
+      </c>
+      <c r="I363" s="18" t="s">
+        <v>1445</v>
+      </c>
+      <c r="J363" s="19"/>
+      <c r="K363" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="L363" s="19"/>
+      <c r="M363" s="20"/>
+      <c r="N363" s="19"/>
+      <c r="O363" s="19"/>
+    </row>
+    <row r="364" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A364" s="18" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B364" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="C364" s="18" t="s">
+        <v>1447</v>
+      </c>
+      <c r="D364" s="18" t="s">
+        <v>93</v>
+      </c>
+      <c r="E364" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="F364" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="G364" s="18" t="s">
+        <v>1448</v>
+      </c>
+      <c r="H364" s="18" t="s">
+        <v>1449</v>
+      </c>
+      <c r="I364" s="18" t="s">
+        <v>1450</v>
+      </c>
+      <c r="J364" s="19"/>
+      <c r="K364" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="L364" s="19"/>
+      <c r="M364" s="20"/>
+      <c r="N364" s="19"/>
+      <c r="O364" s="19"/>
+    </row>
+    <row r="365" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A365" s="18" t="s">
+        <v>1451</v>
+      </c>
+      <c r="B365" s="18" t="s">
+        <v>50</v>
+      </c>
+      <c r="C365" s="18" t="s">
+        <v>1452</v>
+      </c>
+      <c r="D365" s="18" t="s">
+        <v>93</v>
+      </c>
+      <c r="E365" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="F365" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="G365" s="18" t="s">
+        <v>1453</v>
+      </c>
+      <c r="H365" s="18" t="s">
+        <v>1454</v>
+      </c>
+      <c r="I365" s="18" t="s">
+        <v>1455</v>
+      </c>
+      <c r="J365" s="19"/>
+      <c r="K365" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="L365" s="19"/>
+      <c r="M365" s="20"/>
+      <c r="N365" s="19"/>
+      <c r="O365" s="19"/>
+    </row>
+    <row r="366" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A366" s="18" t="s">
+        <v>1456</v>
+      </c>
+      <c r="B366" s="18" t="s">
+        <v>50</v>
+      </c>
+      <c r="C366" s="18" t="s">
+        <v>1457</v>
+      </c>
+      <c r="D366" s="18" t="s">
+        <v>403</v>
+      </c>
+      <c r="E366" s="18" t="s">
+        <v>99</v>
+      </c>
+      <c r="F366" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="G366" s="18" t="s">
+        <v>1458</v>
+      </c>
+      <c r="H366" s="18" t="s">
+        <v>1459</v>
+      </c>
+      <c r="I366" s="18" t="s">
+        <v>1460</v>
+      </c>
+      <c r="J366" s="19"/>
+      <c r="K366" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="L366" s="19"/>
+      <c r="M366" s="20"/>
+      <c r="N366" s="19"/>
+      <c r="O366" s="19"/>
+    </row>
+    <row r="367" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A367" s="18" t="s">
+        <v>1461</v>
+      </c>
+      <c r="B367" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="C367" s="18" t="s">
+        <v>1462</v>
+      </c>
+      <c r="D367" s="18" t="s">
+        <v>93</v>
+      </c>
+      <c r="E367" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="F367" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="G367" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="H367" s="18" t="s">
+        <v>1463</v>
+      </c>
+      <c r="I367" s="18" t="s">
+        <v>1464</v>
+      </c>
+      <c r="J367" s="19"/>
+      <c r="K367" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="L367" s="19"/>
+      <c r="M367" s="20"/>
+      <c r="N367" s="19"/>
+      <c r="O367" s="19"/>
+    </row>
+    <row r="368" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A368" s="18" t="s">
+        <v>1465</v>
+      </c>
+      <c r="B368" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="C368" s="18" t="s">
+        <v>1466</v>
+      </c>
+      <c r="D368" s="18" t="s">
+        <v>93</v>
+      </c>
+      <c r="E368" s="18" t="s">
+        <v>99</v>
+      </c>
+      <c r="F368" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="G368" s="18" t="s">
+        <v>1467</v>
+      </c>
+      <c r="H368" s="18" t="s">
+        <v>1468</v>
+      </c>
+      <c r="I368" s="18" t="s">
+        <v>1469</v>
+      </c>
+      <c r="J368" s="19"/>
+      <c r="K368" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="L368" s="19"/>
+      <c r="M368" s="20"/>
+      <c r="N368" s="19"/>
+      <c r="O368" s="19"/>
+    </row>
+    <row r="369" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A369" s="18" t="s">
+        <v>1470</v>
+      </c>
+      <c r="B369" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="C369" s="18" t="s">
+        <v>1471</v>
+      </c>
+      <c r="D369" s="18" t="s">
+        <v>106</v>
+      </c>
+      <c r="E369" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="F369" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="G369" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="H369" s="18" t="s">
+        <v>1472</v>
+      </c>
+      <c r="I369" s="18" t="s">
+        <v>1473</v>
+      </c>
+      <c r="J369" s="19"/>
+      <c r="K369" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="L369" s="19"/>
+      <c r="M369" s="20"/>
+      <c r="N369" s="19"/>
+      <c r="O369" s="19"/>
+    </row>
+    <row r="370" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A370" s="18" t="s">
+        <v>1474</v>
+      </c>
+      <c r="B370" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="C370" s="18" t="s">
+        <v>1475</v>
+      </c>
+      <c r="D370" s="18" t="s">
+        <v>93</v>
+      </c>
+      <c r="E370" s="18" t="s">
+        <v>99</v>
+      </c>
+      <c r="F370" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="G370" s="18" t="s">
+        <v>1476</v>
+      </c>
+      <c r="H370" s="18" t="s">
+        <v>1477</v>
+      </c>
+      <c r="I370" s="18" t="s">
+        <v>1478</v>
+      </c>
+      <c r="J370" s="19"/>
+      <c r="K370" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="L370" s="19"/>
+      <c r="M370" s="20"/>
+      <c r="N370" s="19"/>
+      <c r="O370" s="19"/>
+    </row>
+    <row r="371" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A371" s="18" t="s">
+        <v>1479</v>
+      </c>
+      <c r="B371" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="C371" s="18" t="s">
+        <v>1480</v>
+      </c>
+      <c r="D371" s="18" t="s">
+        <v>132</v>
+      </c>
+      <c r="E371" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="F371" s="18" t="s">
+        <v>1481</v>
+      </c>
+      <c r="G371" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="H371" s="18" t="s">
+        <v>1482</v>
+      </c>
+      <c r="I371" s="18" t="s">
+        <v>1483</v>
+      </c>
+      <c r="J371" s="19"/>
+      <c r="K371" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="L371" s="19"/>
+      <c r="M371" s="20"/>
+      <c r="N371" s="19"/>
+      <c r="O371" s="19"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O336"/>
-  <conditionalFormatting sqref="K2:K336">
+  <autoFilter ref="A1:O371"/>
+  <conditionalFormatting sqref="K2:K371">
     <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
       <formula>"Pass"</formula>
     </cfRule>
@@ -17970,17 +19820,17 @@
       <formula>"Not Run"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2:E336">
+  <conditionalFormatting sqref="A2:E371">
     <cfRule type="expression" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
       <formula>$E2="High"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="K2:K336" type="list">
+    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="K2:K371" type="list">
       <formula1>"Not Run,Pass,Fail,Blocked,N/A"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Enter a date" errorStyle="stop" operator="greaterThan" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="M2:M336" type="date">
+    <dataValidation allowBlank="true" error="Enter a date" errorStyle="stop" operator="greaterThan" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="M2:M371" type="date">
       <formula1>36526</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -18001,7 +19851,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="22"/>
@@ -18012,223 +19862,280 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>1315</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="10" t="s">
-        <v>1316</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="21" t="s">
-        <v>1317</v>
+        <v>1486</v>
       </c>
       <c r="B4" s="21" t="s">
-        <v>1318</v>
+        <v>1487</v>
       </c>
       <c r="C4" s="21" t="s">
-        <v>1319</v>
+        <v>1488</v>
       </c>
       <c r="D4" s="21" t="s">
-        <v>1320</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="18" t="s">
-        <v>1321</v>
+        <v>1490</v>
       </c>
       <c r="B5" s="18" t="s">
         <v>94</v>
       </c>
       <c r="C5" s="18" t="s">
-        <v>1322</v>
+        <v>1491</v>
       </c>
       <c r="D5" s="18" t="s">
-        <v>1323</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="18" t="s">
-        <v>1324</v>
+        <v>1493</v>
       </c>
       <c r="B6" s="18" t="s">
         <v>94</v>
       </c>
       <c r="C6" s="18" t="s">
-        <v>1325</v>
+        <v>1494</v>
       </c>
       <c r="D6" s="18" t="s">
-        <v>1326</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="18" t="s">
-        <v>1327</v>
+        <v>1496</v>
       </c>
       <c r="B7" s="18" t="s">
         <v>168</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>1328</v>
+        <v>1497</v>
       </c>
       <c r="D7" s="18" t="s">
-        <v>1329</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="18" t="s">
-        <v>1330</v>
+        <v>1499</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="C8" s="18" t="s">
-        <v>1331</v>
+        <v>1500</v>
       </c>
       <c r="D8" s="18" t="s">
-        <v>1332</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="18" t="s">
-        <v>1333</v>
+        <v>1502</v>
       </c>
       <c r="B9" s="18" t="s">
         <v>412</v>
       </c>
       <c r="C9" s="18" t="s">
-        <v>1334</v>
+        <v>1503</v>
       </c>
       <c r="D9" s="18" t="s">
-        <v>1335</v>
+        <v>1504</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="18" t="s">
-        <v>1336</v>
+        <v>1505</v>
       </c>
       <c r="B10" s="18" t="s">
-        <v>1337</v>
+        <v>1506</v>
       </c>
       <c r="C10" s="18" t="s">
-        <v>1338</v>
+        <v>1507</v>
       </c>
       <c r="D10" s="18" t="s">
-        <v>1339</v>
+        <v>1508</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="18" t="s">
+        <v>1509</v>
+      </c>
+      <c r="B11" s="18" t="s">
+        <v>1510</v>
+      </c>
+      <c r="C11" s="18" t="s">
+        <v>1511</v>
+      </c>
+      <c r="D11" s="18" t="s">
+        <v>1512</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="6" t="s">
-        <v>1340</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="21" t="s">
-        <v>1341</v>
-      </c>
-      <c r="B13" s="21" t="s">
-        <v>1342</v>
-      </c>
-      <c r="C13" s="21" t="s">
-        <v>1343</v>
-      </c>
-      <c r="D13" s="21" t="s">
-        <v>1320</v>
-      </c>
-    </row>
+      <c r="A12" s="18" t="s">
+        <v>1513</v>
+      </c>
+      <c r="B12" s="18" t="s">
+        <v>1514</v>
+      </c>
+      <c r="C12" s="18" t="s">
+        <v>1515</v>
+      </c>
+      <c r="D12" s="18" t="s">
+        <v>1516</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="14" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="18" t="s">
-        <v>1344</v>
-      </c>
-      <c r="B14" s="18" t="s">
-        <v>269</v>
-      </c>
-      <c r="C14" s="18" t="s">
-        <v>1345</v>
-      </c>
-      <c r="D14" s="18" t="s">
-        <v>1346</v>
+      <c r="A14" s="6" t="s">
+        <v>1517</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="18" t="s">
-        <v>1347</v>
-      </c>
-      <c r="B15" s="18" t="s">
-        <v>1348</v>
-      </c>
-      <c r="C15" s="18" t="s">
-        <v>1349</v>
-      </c>
-      <c r="D15" s="18"/>
+      <c r="A15" s="21" t="s">
+        <v>1518</v>
+      </c>
+      <c r="B15" s="21" t="s">
+        <v>1519</v>
+      </c>
+      <c r="C15" s="21" t="s">
+        <v>1520</v>
+      </c>
+      <c r="D15" s="21" t="s">
+        <v>1489</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="18" t="s">
-        <v>1350</v>
+        <v>1521</v>
       </c>
       <c r="B16" s="18" t="s">
-        <v>1351</v>
+        <v>269</v>
       </c>
       <c r="C16" s="18" t="s">
-        <v>1352</v>
+        <v>1522</v>
       </c>
       <c r="D16" s="18" t="s">
-        <v>1353</v>
+        <v>1523</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="18" t="s">
-        <v>1350</v>
+        <v>1524</v>
       </c>
       <c r="B17" s="18" t="s">
-        <v>1354</v>
+        <v>1525</v>
       </c>
       <c r="C17" s="18" t="s">
-        <v>1355</v>
+        <v>1526</v>
       </c>
       <c r="D17" s="18"/>
     </row>
     <row r="18" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="18" t="s">
-        <v>1356</v>
+        <v>1527</v>
       </c>
       <c r="B18" s="18" t="s">
-        <v>1357</v>
+        <v>1528</v>
       </c>
       <c r="C18" s="18" t="s">
-        <v>1358</v>
+        <v>1529</v>
       </c>
       <c r="D18" s="18" t="s">
-        <v>1359</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="18" t="s">
-        <v>49</v>
+        <v>1527</v>
       </c>
       <c r="B19" s="18" t="s">
-        <v>1360</v>
+        <v>1531</v>
       </c>
       <c r="C19" s="18" t="s">
-        <v>1361</v>
-      </c>
-      <c r="D19" s="18" t="s">
-        <v>1362</v>
-      </c>
+        <v>1532</v>
+      </c>
+      <c r="D19" s="18"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="18" t="s">
-        <v>1363</v>
+        <v>1533</v>
       </c>
       <c r="B20" s="18" t="s">
-        <v>1364</v>
+        <v>1534</v>
       </c>
       <c r="C20" s="18" t="s">
-        <v>1365</v>
+        <v>1535</v>
       </c>
       <c r="D20" s="18" t="s">
-        <v>1366</v>
+        <v>1536</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="B21" s="18" t="s">
+        <v>1537</v>
+      </c>
+      <c r="C21" s="18" t="s">
+        <v>1538</v>
+      </c>
+      <c r="D21" s="18" t="s">
+        <v>1539</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="18" t="s">
+        <v>1540</v>
+      </c>
+      <c r="B22" s="18" t="s">
+        <v>1541</v>
+      </c>
+      <c r="C22" s="18" t="s">
+        <v>1542</v>
+      </c>
+      <c r="D22" s="18" t="s">
+        <v>1543</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="18" t="s">
+        <v>1544</v>
+      </c>
+      <c r="B23" s="18" t="s">
+        <v>1545</v>
+      </c>
+      <c r="C23" s="18" t="s">
+        <v>1546</v>
+      </c>
+      <c r="D23" s="18" t="s">
+        <v>1547</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="18" t="s">
+        <v>1548</v>
+      </c>
+      <c r="B24" s="18" t="s">
+        <v>1549</v>
+      </c>
+      <c r="C24" s="18" t="s">
+        <v>1550</v>
+      </c>
+      <c r="D24" s="18" t="s">
+        <v>1551</v>
       </c>
     </row>
   </sheetData>
@@ -18265,15 +20172,15 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>1367</v>
+        <v>1552</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="10" t="s">
-        <v>1368</v>
+        <v>1553</v>
       </c>
       <c r="L2" s="10" t="s">
-        <v>1369</v>
+        <v>1554</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -18281,7 +20188,7 @@
         <v>78</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>1370</v>
+        <v>1555</v>
       </c>
       <c r="C4" s="11" t="s">
         <v>31</v>
@@ -18290,36 +20197,36 @@
         <v>66</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>1371</v>
+        <v>1556</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>1372</v>
+        <v>1557</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>1373</v>
+        <v>1558</v>
       </c>
       <c r="H4" s="11" t="s">
-        <v>1374</v>
+        <v>1559</v>
       </c>
       <c r="I4" s="11" t="s">
         <v>75</v>
       </c>
       <c r="J4" s="11" t="s">
-        <v>1375</v>
+        <v>1560</v>
       </c>
       <c r="K4" s="11" t="s">
-        <v>1376</v>
+        <v>1561</v>
       </c>
       <c r="L4" s="11" t="s">
-        <v>1377</v>
+        <v>1562</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="22" t="s">
-        <v>1378</v>
+        <v>1563</v>
       </c>
       <c r="B5" s="22" t="s">
-        <v>1379</v>
+        <v>1564</v>
       </c>
       <c r="C5" s="22" t="s">
         <v>47</v>
@@ -18328,25 +20235,25 @@
         <v>664</v>
       </c>
       <c r="E5" s="22" t="s">
-        <v>1380</v>
+        <v>1565</v>
       </c>
       <c r="F5" s="22" t="s">
-        <v>1381</v>
+        <v>1566</v>
       </c>
       <c r="G5" s="22" t="s">
-        <v>1382</v>
+        <v>1567</v>
       </c>
       <c r="H5" s="22" t="s">
         <v>83</v>
       </c>
       <c r="I5" s="22" t="s">
-        <v>1383</v>
+        <v>1568</v>
       </c>
       <c r="J5" s="22" t="s">
-        <v>1384</v>
+        <v>1569</v>
       </c>
       <c r="K5" s="22" t="s">
-        <v>1385</v>
+        <v>1570</v>
       </c>
       <c r="L5" s="22"/>
     </row>

--- a/docs/Eschool_Functional_Test_Plan.xlsx
+++ b/docs/Eschool_Functional_Test_Plan.xlsx
@@ -14,7 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Defect Log" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Test Cases'!$A$1:$O$413</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Test Cases'!$A$1:$O$441</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Defect Log'!$A$4:$L$204</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
@@ -675,7 +675,7 @@
     <row r="2" ht="15" customHeight="1" s="24">
       <c r="B2" s="26" t="inlineStr">
         <is>
-          <t>Scope: everything built so far (Oct 2026 build, includes Admissions 'pick an existing parent', Timetable)</t>
+          <t>Scope: everything built so far (Oct 2026 build, includes Admissions 'pick an existing parent', Timetable, Academic Years)</t>
         </is>
       </c>
     </row>
@@ -700,7 +700,7 @@
       </c>
       <c r="C5" s="28" t="inlineStr">
         <is>
-          <t>Login &amp; Layout, Reusable Components, Class Sections, Subjects, Teachers, Parents, Admissions (incl. existing-parent picker), Students, Attendance, Documents, Users &amp; Staff, Roles &amp; Permissions, My Account, School Settings (incl. Masters &gt; Admission fees), Dashboard, role-based access, end-to-end flows, non-functional checks, Timetable (periods, class grid, Copy From, teacher view, clash rules).</t>
+          <t>Login &amp; Layout, Reusable Components, Class Sections, Subjects, Teachers, Parents, Admissions (incl. existing-parent picker), Students, Attendance, Documents, Users &amp; Staff, Roles &amp; Permissions, My Account, School Settings (incl. Masters &gt; Admission fees), Dashboard, role-based access, end-to-end flows, non-functional checks, Timetable (periods, class grid, Copy From, teacher view, clash rules), Academic Years (lifecycle, Set current, Close, Copy periods).</t>
         </is>
       </c>
     </row>
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:I34"/>
+  <dimension ref="A1:I36"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="30" customWidth="1" style="23" min="1" max="1"/>
@@ -934,27 +934,27 @@
         </is>
       </c>
       <c r="B5" s="36">
-        <f>COUNTIF('Test Cases'!$B$2:$B$413,$A5)</f>
+        <f>COUNTIF('Test Cases'!$B$2:$B$441,$A5)</f>
         <v/>
       </c>
       <c r="C5" s="36">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$413,$A5,'Test Cases'!$K$2:$K$413,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$441,$A5,'Test Cases'!$K$2:$K$441,"Pass")</f>
         <v/>
       </c>
       <c r="D5" s="36">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$413,$A5,'Test Cases'!$K$2:$K$413,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$441,$A5,'Test Cases'!$K$2:$K$441,"Fail")</f>
         <v/>
       </c>
       <c r="E5" s="36">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$413,$A5,'Test Cases'!$K$2:$K$413,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$441,$A5,'Test Cases'!$K$2:$K$441,"Blocked")</f>
         <v/>
       </c>
       <c r="F5" s="36">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$413,$A5,'Test Cases'!$K$2:$K$413,"N/A")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$441,$A5,'Test Cases'!$K$2:$K$441,"N/A")</f>
         <v/>
       </c>
       <c r="G5" s="36">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$413,$A5,'Test Cases'!$K$2:$K$413,"Not Run")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$441,$A5,'Test Cases'!$K$2:$K$441,"Not Run")</f>
         <v/>
       </c>
       <c r="H5" s="37">
@@ -973,27 +973,27 @@
         </is>
       </c>
       <c r="B6" s="36">
-        <f>COUNTIF('Test Cases'!$B$2:$B$413,$A6)</f>
+        <f>COUNTIF('Test Cases'!$B$2:$B$441,$A6)</f>
         <v/>
       </c>
       <c r="C6" s="36">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$413,$A6,'Test Cases'!$K$2:$K$413,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$441,$A6,'Test Cases'!$K$2:$K$441,"Pass")</f>
         <v/>
       </c>
       <c r="D6" s="36">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$413,$A6,'Test Cases'!$K$2:$K$413,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$441,$A6,'Test Cases'!$K$2:$K$441,"Fail")</f>
         <v/>
       </c>
       <c r="E6" s="36">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$413,$A6,'Test Cases'!$K$2:$K$413,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$441,$A6,'Test Cases'!$K$2:$K$441,"Blocked")</f>
         <v/>
       </c>
       <c r="F6" s="36">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$413,$A6,'Test Cases'!$K$2:$K$413,"N/A")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$441,$A6,'Test Cases'!$K$2:$K$441,"N/A")</f>
         <v/>
       </c>
       <c r="G6" s="36">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$413,$A6,'Test Cases'!$K$2:$K$413,"Not Run")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$441,$A6,'Test Cases'!$K$2:$K$441,"Not Run")</f>
         <v/>
       </c>
       <c r="H6" s="37">
@@ -1012,27 +1012,27 @@
         </is>
       </c>
       <c r="B7" s="36">
-        <f>COUNTIF('Test Cases'!$B$2:$B$413,$A7)</f>
+        <f>COUNTIF('Test Cases'!$B$2:$B$441,$A7)</f>
         <v/>
       </c>
       <c r="C7" s="36">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$413,$A7,'Test Cases'!$K$2:$K$413,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$441,$A7,'Test Cases'!$K$2:$K$441,"Pass")</f>
         <v/>
       </c>
       <c r="D7" s="36">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$413,$A7,'Test Cases'!$K$2:$K$413,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$441,$A7,'Test Cases'!$K$2:$K$441,"Fail")</f>
         <v/>
       </c>
       <c r="E7" s="36">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$413,$A7,'Test Cases'!$K$2:$K$413,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$441,$A7,'Test Cases'!$K$2:$K$441,"Blocked")</f>
         <v/>
       </c>
       <c r="F7" s="36">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$413,$A7,'Test Cases'!$K$2:$K$413,"N/A")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$441,$A7,'Test Cases'!$K$2:$K$441,"N/A")</f>
         <v/>
       </c>
       <c r="G7" s="36">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$413,$A7,'Test Cases'!$K$2:$K$413,"Not Run")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$441,$A7,'Test Cases'!$K$2:$K$441,"Not Run")</f>
         <v/>
       </c>
       <c r="H7" s="37">
@@ -1051,27 +1051,27 @@
         </is>
       </c>
       <c r="B8" s="36">
-        <f>COUNTIF('Test Cases'!$B$2:$B$413,$A8)</f>
+        <f>COUNTIF('Test Cases'!$B$2:$B$441,$A8)</f>
         <v/>
       </c>
       <c r="C8" s="36">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$413,$A8,'Test Cases'!$K$2:$K$413,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$441,$A8,'Test Cases'!$K$2:$K$441,"Pass")</f>
         <v/>
       </c>
       <c r="D8" s="36">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$413,$A8,'Test Cases'!$K$2:$K$413,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$441,$A8,'Test Cases'!$K$2:$K$441,"Fail")</f>
         <v/>
       </c>
       <c r="E8" s="36">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$413,$A8,'Test Cases'!$K$2:$K$413,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$441,$A8,'Test Cases'!$K$2:$K$441,"Blocked")</f>
         <v/>
       </c>
       <c r="F8" s="36">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$413,$A8,'Test Cases'!$K$2:$K$413,"N/A")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$441,$A8,'Test Cases'!$K$2:$K$441,"N/A")</f>
         <v/>
       </c>
       <c r="G8" s="36">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$413,$A8,'Test Cases'!$K$2:$K$413,"Not Run")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$441,$A8,'Test Cases'!$K$2:$K$441,"Not Run")</f>
         <v/>
       </c>
       <c r="H8" s="37">
@@ -1090,27 +1090,27 @@
         </is>
       </c>
       <c r="B9" s="36">
-        <f>COUNTIF('Test Cases'!$B$2:$B$413,$A9)</f>
+        <f>COUNTIF('Test Cases'!$B$2:$B$441,$A9)</f>
         <v/>
       </c>
       <c r="C9" s="36">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$413,$A9,'Test Cases'!$K$2:$K$413,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$441,$A9,'Test Cases'!$K$2:$K$441,"Pass")</f>
         <v/>
       </c>
       <c r="D9" s="36">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$413,$A9,'Test Cases'!$K$2:$K$413,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$441,$A9,'Test Cases'!$K$2:$K$441,"Fail")</f>
         <v/>
       </c>
       <c r="E9" s="36">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$413,$A9,'Test Cases'!$K$2:$K$413,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$441,$A9,'Test Cases'!$K$2:$K$441,"Blocked")</f>
         <v/>
       </c>
       <c r="F9" s="36">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$413,$A9,'Test Cases'!$K$2:$K$413,"N/A")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$441,$A9,'Test Cases'!$K$2:$K$441,"N/A")</f>
         <v/>
       </c>
       <c r="G9" s="36">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$413,$A9,'Test Cases'!$K$2:$K$413,"Not Run")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$441,$A9,'Test Cases'!$K$2:$K$441,"Not Run")</f>
         <v/>
       </c>
       <c r="H9" s="37">
@@ -1129,27 +1129,27 @@
         </is>
       </c>
       <c r="B10" s="36">
-        <f>COUNTIF('Test Cases'!$B$2:$B$413,$A10)</f>
+        <f>COUNTIF('Test Cases'!$B$2:$B$441,$A10)</f>
         <v/>
       </c>
       <c r="C10" s="36">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$413,$A10,'Test Cases'!$K$2:$K$413,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$441,$A10,'Test Cases'!$K$2:$K$441,"Pass")</f>
         <v/>
       </c>
       <c r="D10" s="36">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$413,$A10,'Test Cases'!$K$2:$K$413,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$441,$A10,'Test Cases'!$K$2:$K$441,"Fail")</f>
         <v/>
       </c>
       <c r="E10" s="36">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$413,$A10,'Test Cases'!$K$2:$K$413,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$441,$A10,'Test Cases'!$K$2:$K$441,"Blocked")</f>
         <v/>
       </c>
       <c r="F10" s="36">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$413,$A10,'Test Cases'!$K$2:$K$413,"N/A")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$441,$A10,'Test Cases'!$K$2:$K$441,"N/A")</f>
         <v/>
       </c>
       <c r="G10" s="36">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$413,$A10,'Test Cases'!$K$2:$K$413,"Not Run")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$441,$A10,'Test Cases'!$K$2:$K$441,"Not Run")</f>
         <v/>
       </c>
       <c r="H10" s="37">
@@ -1164,31 +1164,31 @@
     <row r="11" ht="15" customHeight="1" s="24">
       <c r="A11" s="35" t="inlineStr">
         <is>
-          <t>Parents</t>
+          <t>Academic Years</t>
         </is>
       </c>
       <c r="B11" s="36">
-        <f>COUNTIF('Test Cases'!$B$2:$B$413,$A11)</f>
+        <f>COUNTIF('Test Cases'!$B$2:$B$441,$A11)</f>
         <v/>
       </c>
       <c r="C11" s="36">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$413,$A11,'Test Cases'!$K$2:$K$413,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$441,$A11,'Test Cases'!$K$2:$K$441,"Pass")</f>
         <v/>
       </c>
       <c r="D11" s="36">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$413,$A11,'Test Cases'!$K$2:$K$413,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$441,$A11,'Test Cases'!$K$2:$K$441,"Fail")</f>
         <v/>
       </c>
       <c r="E11" s="36">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$413,$A11,'Test Cases'!$K$2:$K$413,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$441,$A11,'Test Cases'!$K$2:$K$441,"Blocked")</f>
         <v/>
       </c>
       <c r="F11" s="36">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$413,$A11,'Test Cases'!$K$2:$K$413,"N/A")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$441,$A11,'Test Cases'!$K$2:$K$441,"N/A")</f>
         <v/>
       </c>
       <c r="G11" s="36">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$413,$A11,'Test Cases'!$K$2:$K$413,"Not Run")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$441,$A11,'Test Cases'!$K$2:$K$441,"Not Run")</f>
         <v/>
       </c>
       <c r="H11" s="37">
@@ -1203,31 +1203,31 @@
     <row r="12" ht="15" customHeight="1" s="24">
       <c r="A12" s="35" t="inlineStr">
         <is>
-          <t>Admissions</t>
+          <t>Parents</t>
         </is>
       </c>
       <c r="B12" s="36">
-        <f>COUNTIF('Test Cases'!$B$2:$B$413,$A12)</f>
+        <f>COUNTIF('Test Cases'!$B$2:$B$441,$A12)</f>
         <v/>
       </c>
       <c r="C12" s="36">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$413,$A12,'Test Cases'!$K$2:$K$413,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$441,$A12,'Test Cases'!$K$2:$K$441,"Pass")</f>
         <v/>
       </c>
       <c r="D12" s="36">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$413,$A12,'Test Cases'!$K$2:$K$413,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$441,$A12,'Test Cases'!$K$2:$K$441,"Fail")</f>
         <v/>
       </c>
       <c r="E12" s="36">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$413,$A12,'Test Cases'!$K$2:$K$413,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$441,$A12,'Test Cases'!$K$2:$K$441,"Blocked")</f>
         <v/>
       </c>
       <c r="F12" s="36">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$413,$A12,'Test Cases'!$K$2:$K$413,"N/A")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$441,$A12,'Test Cases'!$K$2:$K$441,"N/A")</f>
         <v/>
       </c>
       <c r="G12" s="36">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$413,$A12,'Test Cases'!$K$2:$K$413,"Not Run")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$441,$A12,'Test Cases'!$K$2:$K$441,"Not Run")</f>
         <v/>
       </c>
       <c r="H12" s="37">
@@ -1242,31 +1242,31 @@
     <row r="13" ht="15" customHeight="1" s="24">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Admissions</t>
         </is>
       </c>
       <c r="B13" s="36">
-        <f>COUNTIF('Test Cases'!$B$2:$B$413,$A13)</f>
+        <f>COUNTIF('Test Cases'!$B$2:$B$441,$A13)</f>
         <v/>
       </c>
       <c r="C13" s="36">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$413,$A13,'Test Cases'!$K$2:$K$413,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$441,$A13,'Test Cases'!$K$2:$K$441,"Pass")</f>
         <v/>
       </c>
       <c r="D13" s="36">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$413,$A13,'Test Cases'!$K$2:$K$413,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$441,$A13,'Test Cases'!$K$2:$K$441,"Fail")</f>
         <v/>
       </c>
       <c r="E13" s="36">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$413,$A13,'Test Cases'!$K$2:$K$413,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$441,$A13,'Test Cases'!$K$2:$K$441,"Blocked")</f>
         <v/>
       </c>
       <c r="F13" s="36">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$413,$A13,'Test Cases'!$K$2:$K$413,"N/A")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$441,$A13,'Test Cases'!$K$2:$K$441,"N/A")</f>
         <v/>
       </c>
       <c r="G13" s="36">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$413,$A13,'Test Cases'!$K$2:$K$413,"Not Run")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$441,$A13,'Test Cases'!$K$2:$K$441,"Not Run")</f>
         <v/>
       </c>
       <c r="H13" s="37">
@@ -1281,31 +1281,31 @@
     <row r="14" ht="15" customHeight="1" s="24">
       <c r="A14" s="35" t="inlineStr">
         <is>
-          <t>Attendance</t>
+          <t>Students</t>
         </is>
       </c>
       <c r="B14" s="36">
-        <f>COUNTIF('Test Cases'!$B$2:$B$413,$A14)</f>
+        <f>COUNTIF('Test Cases'!$B$2:$B$441,$A14)</f>
         <v/>
       </c>
       <c r="C14" s="36">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$413,$A14,'Test Cases'!$K$2:$K$413,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$441,$A14,'Test Cases'!$K$2:$K$441,"Pass")</f>
         <v/>
       </c>
       <c r="D14" s="36">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$413,$A14,'Test Cases'!$K$2:$K$413,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$441,$A14,'Test Cases'!$K$2:$K$441,"Fail")</f>
         <v/>
       </c>
       <c r="E14" s="36">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$413,$A14,'Test Cases'!$K$2:$K$413,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$441,$A14,'Test Cases'!$K$2:$K$441,"Blocked")</f>
         <v/>
       </c>
       <c r="F14" s="36">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$413,$A14,'Test Cases'!$K$2:$K$413,"N/A")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$441,$A14,'Test Cases'!$K$2:$K$441,"N/A")</f>
         <v/>
       </c>
       <c r="G14" s="36">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$413,$A14,'Test Cases'!$K$2:$K$413,"Not Run")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$441,$A14,'Test Cases'!$K$2:$K$441,"Not Run")</f>
         <v/>
       </c>
       <c r="H14" s="37">
@@ -1320,31 +1320,31 @@
     <row r="15" ht="15" customHeight="1" s="24">
       <c r="A15" s="35" t="inlineStr">
         <is>
-          <t>Documents</t>
+          <t>Attendance</t>
         </is>
       </c>
       <c r="B15" s="36">
-        <f>COUNTIF('Test Cases'!$B$2:$B$413,$A15)</f>
+        <f>COUNTIF('Test Cases'!$B$2:$B$441,$A15)</f>
         <v/>
       </c>
       <c r="C15" s="36">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$413,$A15,'Test Cases'!$K$2:$K$413,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$441,$A15,'Test Cases'!$K$2:$K$441,"Pass")</f>
         <v/>
       </c>
       <c r="D15" s="36">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$413,$A15,'Test Cases'!$K$2:$K$413,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$441,$A15,'Test Cases'!$K$2:$K$441,"Fail")</f>
         <v/>
       </c>
       <c r="E15" s="36">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$413,$A15,'Test Cases'!$K$2:$K$413,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$441,$A15,'Test Cases'!$K$2:$K$441,"Blocked")</f>
         <v/>
       </c>
       <c r="F15" s="36">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$413,$A15,'Test Cases'!$K$2:$K$413,"N/A")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$441,$A15,'Test Cases'!$K$2:$K$441,"N/A")</f>
         <v/>
       </c>
       <c r="G15" s="36">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$413,$A15,'Test Cases'!$K$2:$K$413,"Not Run")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$441,$A15,'Test Cases'!$K$2:$K$441,"Not Run")</f>
         <v/>
       </c>
       <c r="H15" s="37">
@@ -1359,31 +1359,31 @@
     <row r="16" ht="15" customHeight="1" s="24">
       <c r="A16" s="35" t="inlineStr">
         <is>
-          <t>Users &amp; Staff</t>
+          <t>Documents</t>
         </is>
       </c>
       <c r="B16" s="36">
-        <f>COUNTIF('Test Cases'!$B$2:$B$413,$A16)</f>
+        <f>COUNTIF('Test Cases'!$B$2:$B$441,$A16)</f>
         <v/>
       </c>
       <c r="C16" s="36">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$413,$A16,'Test Cases'!$K$2:$K$413,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$441,$A16,'Test Cases'!$K$2:$K$441,"Pass")</f>
         <v/>
       </c>
       <c r="D16" s="36">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$413,$A16,'Test Cases'!$K$2:$K$413,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$441,$A16,'Test Cases'!$K$2:$K$441,"Fail")</f>
         <v/>
       </c>
       <c r="E16" s="36">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$413,$A16,'Test Cases'!$K$2:$K$413,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$441,$A16,'Test Cases'!$K$2:$K$441,"Blocked")</f>
         <v/>
       </c>
       <c r="F16" s="36">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$413,$A16,'Test Cases'!$K$2:$K$413,"N/A")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$441,$A16,'Test Cases'!$K$2:$K$441,"N/A")</f>
         <v/>
       </c>
       <c r="G16" s="36">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$413,$A16,'Test Cases'!$K$2:$K$413,"Not Run")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$441,$A16,'Test Cases'!$K$2:$K$441,"Not Run")</f>
         <v/>
       </c>
       <c r="H16" s="37">
@@ -1398,31 +1398,31 @@
     <row r="17" ht="15" customHeight="1" s="24">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>Roles &amp; Permissions</t>
+          <t>Users &amp; Staff</t>
         </is>
       </c>
       <c r="B17" s="36">
-        <f>COUNTIF('Test Cases'!$B$2:$B$413,$A17)</f>
+        <f>COUNTIF('Test Cases'!$B$2:$B$441,$A17)</f>
         <v/>
       </c>
       <c r="C17" s="36">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$413,$A17,'Test Cases'!$K$2:$K$413,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$441,$A17,'Test Cases'!$K$2:$K$441,"Pass")</f>
         <v/>
       </c>
       <c r="D17" s="36">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$413,$A17,'Test Cases'!$K$2:$K$413,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$441,$A17,'Test Cases'!$K$2:$K$441,"Fail")</f>
         <v/>
       </c>
       <c r="E17" s="36">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$413,$A17,'Test Cases'!$K$2:$K$413,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$441,$A17,'Test Cases'!$K$2:$K$441,"Blocked")</f>
         <v/>
       </c>
       <c r="F17" s="36">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$413,$A17,'Test Cases'!$K$2:$K$413,"N/A")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$441,$A17,'Test Cases'!$K$2:$K$441,"N/A")</f>
         <v/>
       </c>
       <c r="G17" s="36">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$413,$A17,'Test Cases'!$K$2:$K$413,"Not Run")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$441,$A17,'Test Cases'!$K$2:$K$441,"Not Run")</f>
         <v/>
       </c>
       <c r="H17" s="37">
@@ -1437,31 +1437,31 @@
     <row r="18" ht="15" customHeight="1" s="24">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>My Account</t>
+          <t>Roles &amp; Permissions</t>
         </is>
       </c>
       <c r="B18" s="36">
-        <f>COUNTIF('Test Cases'!$B$2:$B$413,$A18)</f>
+        <f>COUNTIF('Test Cases'!$B$2:$B$441,$A18)</f>
         <v/>
       </c>
       <c r="C18" s="36">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$413,$A18,'Test Cases'!$K$2:$K$413,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$441,$A18,'Test Cases'!$K$2:$K$441,"Pass")</f>
         <v/>
       </c>
       <c r="D18" s="36">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$413,$A18,'Test Cases'!$K$2:$K$413,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$441,$A18,'Test Cases'!$K$2:$K$441,"Fail")</f>
         <v/>
       </c>
       <c r="E18" s="36">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$413,$A18,'Test Cases'!$K$2:$K$413,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$441,$A18,'Test Cases'!$K$2:$K$441,"Blocked")</f>
         <v/>
       </c>
       <c r="F18" s="36">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$413,$A18,'Test Cases'!$K$2:$K$413,"N/A")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$441,$A18,'Test Cases'!$K$2:$K$441,"N/A")</f>
         <v/>
       </c>
       <c r="G18" s="36">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$413,$A18,'Test Cases'!$K$2:$K$413,"Not Run")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$441,$A18,'Test Cases'!$K$2:$K$441,"Not Run")</f>
         <v/>
       </c>
       <c r="H18" s="37">
@@ -1476,31 +1476,31 @@
     <row r="19" ht="15" customHeight="1" s="24">
       <c r="A19" s="35" t="inlineStr">
         <is>
-          <t>School Settings</t>
+          <t>My Account</t>
         </is>
       </c>
       <c r="B19" s="36">
-        <f>COUNTIF('Test Cases'!$B$2:$B$413,$A19)</f>
+        <f>COUNTIF('Test Cases'!$B$2:$B$441,$A19)</f>
         <v/>
       </c>
       <c r="C19" s="36">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$413,$A19,'Test Cases'!$K$2:$K$413,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$441,$A19,'Test Cases'!$K$2:$K$441,"Pass")</f>
         <v/>
       </c>
       <c r="D19" s="36">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$413,$A19,'Test Cases'!$K$2:$K$413,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$441,$A19,'Test Cases'!$K$2:$K$441,"Fail")</f>
         <v/>
       </c>
       <c r="E19" s="36">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$413,$A19,'Test Cases'!$K$2:$K$413,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$441,$A19,'Test Cases'!$K$2:$K$441,"Blocked")</f>
         <v/>
       </c>
       <c r="F19" s="36">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$413,$A19,'Test Cases'!$K$2:$K$413,"N/A")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$441,$A19,'Test Cases'!$K$2:$K$441,"N/A")</f>
         <v/>
       </c>
       <c r="G19" s="36">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$413,$A19,'Test Cases'!$K$2:$K$413,"Not Run")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$441,$A19,'Test Cases'!$K$2:$K$441,"Not Run")</f>
         <v/>
       </c>
       <c r="H19" s="37">
@@ -1515,31 +1515,31 @@
     <row r="20" ht="15" customHeight="1" s="24">
       <c r="A20" s="35" t="inlineStr">
         <is>
-          <t>Dashboard</t>
+          <t>School Settings</t>
         </is>
       </c>
       <c r="B20" s="36">
-        <f>COUNTIF('Test Cases'!$B$2:$B$413,$A20)</f>
+        <f>COUNTIF('Test Cases'!$B$2:$B$441,$A20)</f>
         <v/>
       </c>
       <c r="C20" s="36">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$413,$A20,'Test Cases'!$K$2:$K$413,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$441,$A20,'Test Cases'!$K$2:$K$441,"Pass")</f>
         <v/>
       </c>
       <c r="D20" s="36">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$413,$A20,'Test Cases'!$K$2:$K$413,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$441,$A20,'Test Cases'!$K$2:$K$441,"Fail")</f>
         <v/>
       </c>
       <c r="E20" s="36">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$413,$A20,'Test Cases'!$K$2:$K$413,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$441,$A20,'Test Cases'!$K$2:$K$441,"Blocked")</f>
         <v/>
       </c>
       <c r="F20" s="36">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$413,$A20,'Test Cases'!$K$2:$K$413,"N/A")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$441,$A20,'Test Cases'!$K$2:$K$441,"N/A")</f>
         <v/>
       </c>
       <c r="G20" s="36">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$413,$A20,'Test Cases'!$K$2:$K$413,"Not Run")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$441,$A20,'Test Cases'!$K$2:$K$441,"Not Run")</f>
         <v/>
       </c>
       <c r="H20" s="37">
@@ -1554,31 +1554,31 @@
     <row r="21" ht="15" customHeight="1" s="24">
       <c r="A21" s="35" t="inlineStr">
         <is>
-          <t>Roles &amp; Access (RBAC)</t>
+          <t>Dashboard</t>
         </is>
       </c>
       <c r="B21" s="36">
-        <f>COUNTIF('Test Cases'!$B$2:$B$413,$A21)</f>
+        <f>COUNTIF('Test Cases'!$B$2:$B$441,$A21)</f>
         <v/>
       </c>
       <c r="C21" s="36">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$413,$A21,'Test Cases'!$K$2:$K$413,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$441,$A21,'Test Cases'!$K$2:$K$441,"Pass")</f>
         <v/>
       </c>
       <c r="D21" s="36">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$413,$A21,'Test Cases'!$K$2:$K$413,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$441,$A21,'Test Cases'!$K$2:$K$441,"Fail")</f>
         <v/>
       </c>
       <c r="E21" s="36">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$413,$A21,'Test Cases'!$K$2:$K$413,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$441,$A21,'Test Cases'!$K$2:$K$441,"Blocked")</f>
         <v/>
       </c>
       <c r="F21" s="36">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$413,$A21,'Test Cases'!$K$2:$K$413,"N/A")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$441,$A21,'Test Cases'!$K$2:$K$441,"N/A")</f>
         <v/>
       </c>
       <c r="G21" s="36">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$413,$A21,'Test Cases'!$K$2:$K$413,"Not Run")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$441,$A21,'Test Cases'!$K$2:$K$441,"Not Run")</f>
         <v/>
       </c>
       <c r="H21" s="37">
@@ -1593,31 +1593,31 @@
     <row r="22" ht="15" customHeight="1" s="24">
       <c r="A22" s="35" t="inlineStr">
         <is>
-          <t>End-to-End</t>
+          <t>Roles &amp; Access (RBAC)</t>
         </is>
       </c>
       <c r="B22" s="36">
-        <f>COUNTIF('Test Cases'!$B$2:$B$413,$A22)</f>
+        <f>COUNTIF('Test Cases'!$B$2:$B$441,$A22)</f>
         <v/>
       </c>
       <c r="C22" s="36">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$413,$A22,'Test Cases'!$K$2:$K$413,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$441,$A22,'Test Cases'!$K$2:$K$441,"Pass")</f>
         <v/>
       </c>
       <c r="D22" s="36">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$413,$A22,'Test Cases'!$K$2:$K$413,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$441,$A22,'Test Cases'!$K$2:$K$441,"Fail")</f>
         <v/>
       </c>
       <c r="E22" s="36">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$413,$A22,'Test Cases'!$K$2:$K$413,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$441,$A22,'Test Cases'!$K$2:$K$441,"Blocked")</f>
         <v/>
       </c>
       <c r="F22" s="36">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$413,$A22,'Test Cases'!$K$2:$K$413,"N/A")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$441,$A22,'Test Cases'!$K$2:$K$441,"N/A")</f>
         <v/>
       </c>
       <c r="G22" s="36">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$413,$A22,'Test Cases'!$K$2:$K$413,"Not Run")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$441,$A22,'Test Cases'!$K$2:$K$441,"Not Run")</f>
         <v/>
       </c>
       <c r="H22" s="37">
@@ -1632,31 +1632,31 @@
     <row r="23" ht="15" customHeight="1" s="24">
       <c r="A23" s="35" t="inlineStr">
         <is>
-          <t>Non-functional</t>
+          <t>End-to-End</t>
         </is>
       </c>
       <c r="B23" s="36">
-        <f>COUNTIF('Test Cases'!$B$2:$B$413,$A23)</f>
+        <f>COUNTIF('Test Cases'!$B$2:$B$441,$A23)</f>
         <v/>
       </c>
       <c r="C23" s="36">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$413,$A23,'Test Cases'!$K$2:$K$413,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$441,$A23,'Test Cases'!$K$2:$K$441,"Pass")</f>
         <v/>
       </c>
       <c r="D23" s="36">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$413,$A23,'Test Cases'!$K$2:$K$413,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$441,$A23,'Test Cases'!$K$2:$K$441,"Fail")</f>
         <v/>
       </c>
       <c r="E23" s="36">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$413,$A23,'Test Cases'!$K$2:$K$413,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$441,$A23,'Test Cases'!$K$2:$K$441,"Blocked")</f>
         <v/>
       </c>
       <c r="F23" s="36">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$413,$A23,'Test Cases'!$K$2:$K$413,"N/A")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$441,$A23,'Test Cases'!$K$2:$K$441,"N/A")</f>
         <v/>
       </c>
       <c r="G23" s="36">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$413,$A23,'Test Cases'!$K$2:$K$413,"Not Run")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$441,$A23,'Test Cases'!$K$2:$K$441,"Not Run")</f>
         <v/>
       </c>
       <c r="H23" s="37">
@@ -1669,116 +1669,156 @@
       </c>
     </row>
     <row r="24" ht="15" customHeight="1" s="24">
-      <c r="A24" s="38" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B24" s="39">
-        <f>SUM(B5:B23)</f>
+      <c r="A24" s="35" t="inlineStr">
+        <is>
+          <t>Non-functional</t>
+        </is>
+      </c>
+      <c r="B24" s="36">
+        <f>COUNTIF('Test Cases'!$B$2:$B$441,$A24)</f>
         <v/>
       </c>
-      <c r="C24" s="39">
-        <f>SUM(C5:C23)</f>
+      <c r="C24" s="36">
+        <f>COUNTIFS('Test Cases'!$B$2:$B$441,$A24,'Test Cases'!$K$2:$K$441,"Pass")</f>
         <v/>
       </c>
-      <c r="D24" s="39">
-        <f>SUM(D5:D23)</f>
+      <c r="D24" s="36">
+        <f>COUNTIFS('Test Cases'!$B$2:$B$441,$A24,'Test Cases'!$K$2:$K$441,"Fail")</f>
         <v/>
       </c>
-      <c r="E24" s="39">
-        <f>SUM(E5:E23)</f>
+      <c r="E24" s="36">
+        <f>COUNTIFS('Test Cases'!$B$2:$B$441,$A24,'Test Cases'!$K$2:$K$441,"Blocked")</f>
         <v/>
       </c>
-      <c r="F24" s="39">
-        <f>SUM(F5:F23)</f>
+      <c r="F24" s="36">
+        <f>COUNTIFS('Test Cases'!$B$2:$B$441,$A24,'Test Cases'!$K$2:$K$441,"N/A")</f>
         <v/>
       </c>
-      <c r="G24" s="39">
-        <f>SUM(G5:G23)</f>
+      <c r="G24" s="36">
+        <f>COUNTIFS('Test Cases'!$B$2:$B$441,$A24,'Test Cases'!$K$2:$K$441,"Not Run")</f>
         <v/>
       </c>
-      <c r="H24" s="40">
+      <c r="H24" s="37">
         <f>IFERROR((B24-G24-F24)/(B24-F24),0)</f>
         <v/>
       </c>
-      <c r="I24" s="40">
+      <c r="I24" s="37">
         <f>IFERROR(C24/(C24+D24),0)</f>
         <v/>
       </c>
     </row>
-    <row r="25" s="24"/>
+    <row r="25" ht="15" customHeight="1" s="24">
+      <c r="A25" s="38" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B25" s="39">
+        <f>SUM(B5:B24)</f>
+        <v/>
+      </c>
+      <c r="C25" s="39">
+        <f>SUM(C5:C24)</f>
+        <v/>
+      </c>
+      <c r="D25" s="39">
+        <f>SUM(D5:D24)</f>
+        <v/>
+      </c>
+      <c r="E25" s="39">
+        <f>SUM(E5:E24)</f>
+        <v/>
+      </c>
+      <c r="F25" s="39">
+        <f>SUM(F5:F24)</f>
+        <v/>
+      </c>
+      <c r="G25" s="39">
+        <f>SUM(G5:G24)</f>
+        <v/>
+      </c>
+      <c r="H25" s="40">
+        <f>IFERROR((B25-G25-F25)/(B25-F25),0)</f>
+        <v/>
+      </c>
+      <c r="I25" s="40">
+        <f>IFERROR(C25/(C25+D25),0)</f>
+        <v/>
+      </c>
+    </row>
     <row r="26" s="24"/>
-    <row r="27" ht="15" customHeight="1" s="24">
-      <c r="A27" s="29" t="inlineStr">
+    <row r="27" s="24"/>
+    <row r="28" ht="15" customHeight="1" s="24">
+      <c r="A28" s="29" t="inlineStr">
         <is>
           <t>High-priority cases</t>
         </is>
-      </c>
-    </row>
-    <row r="28" ht="15" customHeight="1" s="24">
-      <c r="A28" s="31" t="inlineStr">
-        <is>
-          <t>High priority total</t>
-        </is>
-      </c>
-      <c r="B28" s="31">
-        <f>COUNTIF('Test Cases'!$E$2:$E$413,"High")</f>
-        <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1" s="24">
       <c r="A29" s="31" t="inlineStr">
         <is>
-          <t>High priority failed</t>
+          <t>High priority total</t>
         </is>
       </c>
       <c r="B29" s="31">
-        <f>COUNTIFS('Test Cases'!$E$2:$E$413,"High",'Test Cases'!$K$2:$K$413,"Fail")</f>
+        <f>COUNTIF('Test Cases'!$E$2:$E$441,"High")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1" s="24">
       <c r="A30" s="31" t="inlineStr">
         <is>
+          <t>High priority failed</t>
+        </is>
+      </c>
+      <c r="B30" s="31">
+        <f>COUNTIFS('Test Cases'!$E$2:$E$441,"High",'Test Cases'!$K$2:$K$441,"Fail")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" ht="15" customHeight="1" s="24">
+      <c r="A31" s="31" t="inlineStr">
+        <is>
           <t>High priority not yet run</t>
         </is>
       </c>
-      <c r="B30" s="31">
-        <f>COUNTIFS('Test Cases'!$E$2:$E$413,"High",'Test Cases'!$K$2:$K$413,"Not Run")</f>
+      <c r="B31" s="31">
+        <f>COUNTIFS('Test Cases'!$E$2:$E$441,"High",'Test Cases'!$K$2:$K$441,"Not Run")</f>
         <v/>
       </c>
     </row>
-    <row r="31" s="24"/>
-    <row r="32" ht="15" customHeight="1" s="24">
-      <c r="A32" s="29" t="inlineStr">
+    <row r="32" s="24"/>
+    <row r="33" ht="15" customHeight="1" s="24">
+      <c r="A33" s="29" t="inlineStr">
         <is>
           <t>Open defects (Defect Log)</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="15" customHeight="1" s="24">
-      <c r="A33" s="31" t="inlineStr">
+    <row r="34" ht="15" customHeight="1" s="24">
+      <c r="A34" s="31" t="inlineStr">
         <is>
           <t>Open (New, In Progress, Reopened, Retest Failed)</t>
         </is>
       </c>
-      <c r="B33" s="31">
+      <c r="B34" s="31">
         <f>COUNTIF('Defect Log'!$I$6:$I$500,"New")+COUNTIF('Defect Log'!$I$6:$I$500,"In Progress")+COUNTIF('Defect Log'!$I$6:$I$500,"Reopened")+COUNTIF('Defect Log'!$I$6:$I$500,"Retest Failed")</f>
         <v/>
       </c>
     </row>
-    <row r="34" ht="15" customHeight="1" s="24">
-      <c r="A34" s="31" t="inlineStr">
+    <row r="35" ht="15" customHeight="1" s="24">
+      <c r="A35" s="31" t="inlineStr">
         <is>
           <t>Critical / High severity still open</t>
         </is>
       </c>
-      <c r="B34" s="31">
+      <c r="B35" s="31">
         <f>COUNTIFS('Defect Log'!$H$6:$H$500,"Critical",'Defect Log'!$I$6:$I$500,"&lt;&gt;Closed",'Defect Log'!$I$6:$I$500,"&lt;&gt;Fixed",'Defect Log'!$I$6:$I$500,"&lt;&gt;")+COUNTIFS('Defect Log'!$H$6:$H$500,"High",'Defect Log'!$I$6:$I$500,"&lt;&gt;Closed",'Defect Log'!$I$6:$I$500,"&lt;&gt;Fixed",'Defect Log'!$I$6:$I$500,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
+    <row r="36" s="24"/>
   </sheetData>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -1792,7 +1832,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:O413"/>
+  <dimension ref="A1:O441"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="10" customWidth="1" style="23" min="1" max="1"/>
@@ -24808,9 +24848,1597 @@
       <c r="N413" s="42" t="n"/>
       <c r="O413" s="42" t="n"/>
     </row>
+    <row r="414" ht="15" customHeight="1" s="24">
+      <c r="A414" s="41" t="inlineStr">
+        <is>
+          <t>AYR-01</t>
+        </is>
+      </c>
+      <c r="B414" s="41" t="inlineStr">
+        <is>
+          <t>Academic Years</t>
+        </is>
+      </c>
+      <c r="C414" s="41" t="inlineStr">
+        <is>
+          <t>Page access</t>
+        </is>
+      </c>
+      <c r="D414" s="41" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E414" s="41" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F414" s="41" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="G414" s="41" t="inlineStr">
+        <is>
+          <t>Seeded year 2026-2027 is current</t>
+        </is>
+      </c>
+      <c r="H414" s="41" t="inlineStr">
+        <is>
+          <t>Open Academic Years in the sidebar (Administration)</t>
+        </is>
+      </c>
+      <c r="I414" s="41" t="inlineStr">
+        <is>
+          <t>Page opens: table of years with Status, Classes, Active students, Periods. 2026-2027 shows Current</t>
+        </is>
+      </c>
+      <c r="J414" s="42" t="n"/>
+      <c r="K414" s="42" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L414" s="42" t="n"/>
+      <c r="M414" s="43" t="n"/>
+      <c r="N414" s="42" t="n"/>
+      <c r="O414" s="42" t="n"/>
+    </row>
+    <row r="415" ht="15" customHeight="1" s="24">
+      <c r="A415" s="41" t="inlineStr">
+        <is>
+          <t>AYR-02</t>
+        </is>
+      </c>
+      <c r="B415" s="41" t="inlineStr">
+        <is>
+          <t>Academic Years</t>
+        </is>
+      </c>
+      <c r="C415" s="41" t="inlineStr">
+        <is>
+          <t>Page access</t>
+        </is>
+      </c>
+      <c r="D415" s="41" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="E415" s="41" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F415" s="41" t="inlineStr">
+        <is>
+          <t>Supervisor</t>
+        </is>
+      </c>
+      <c r="G415" s="41" t="inlineStr">
+        <is>
+          <t>Seeded Supervisor role</t>
+        </is>
+      </c>
+      <c r="H415" s="41" t="inlineStr">
+        <is>
+          <t>Look for Academic Years in the sidebar; open /academic-years directly</t>
+        </is>
+      </c>
+      <c r="I415" s="41" t="inlineStr">
+        <is>
+          <t>Not in the sidebar; URL refused. The Timetable year drop-down still lists the years</t>
+        </is>
+      </c>
+      <c r="J415" s="42" t="n"/>
+      <c r="K415" s="42" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L415" s="42" t="n"/>
+      <c r="M415" s="43" t="n"/>
+      <c r="N415" s="42" t="n"/>
+      <c r="O415" s="42" t="n"/>
+    </row>
+    <row r="416" ht="15" customHeight="1" s="24">
+      <c r="A416" s="41" t="inlineStr">
+        <is>
+          <t>AYR-03</t>
+        </is>
+      </c>
+      <c r="B416" s="41" t="inlineStr">
+        <is>
+          <t>Academic Years</t>
+        </is>
+      </c>
+      <c r="C416" s="41" t="inlineStr">
+        <is>
+          <t>Page access</t>
+        </is>
+      </c>
+      <c r="D416" s="41" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="E416" s="41" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F416" s="41" t="inlineStr">
+        <is>
+          <t>Clerk</t>
+        </is>
+      </c>
+      <c r="G416" s="41" t="inlineStr">
+        <is>
+          <t>Seeded Clerk role</t>
+        </is>
+      </c>
+      <c r="H416" s="41" t="inlineStr">
+        <is>
+          <t>Open Timetable and look at the year drop-down</t>
+        </is>
+      </c>
+      <c r="I416" s="41" t="inlineStr">
+        <is>
+          <t>Years load (the list is open to every signed-in user) but there is no Academic Years page</t>
+        </is>
+      </c>
+      <c r="J416" s="42" t="n"/>
+      <c r="K416" s="42" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L416" s="42" t="n"/>
+      <c r="M416" s="43" t="n"/>
+      <c r="N416" s="42" t="n"/>
+      <c r="O416" s="42" t="n"/>
+    </row>
+    <row r="417" ht="15" customHeight="1" s="24">
+      <c r="A417" s="41" t="inlineStr">
+        <is>
+          <t>AYR-04</t>
+        </is>
+      </c>
+      <c r="B417" s="41" t="inlineStr">
+        <is>
+          <t>Academic Years</t>
+        </is>
+      </c>
+      <c r="C417" s="41" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="D417" s="41" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E417" s="41" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F417" s="41" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="G417" s="41" t="n"/>
+      <c r="H417" s="41" t="inlineStr">
+        <is>
+          <t>Add year: name 2027-2028, 2027-06-01 to 2028-03-31</t>
+        </is>
+      </c>
+      <c r="I417" s="41" t="inlineStr">
+        <is>
+          <t>Saved as Upcoming with 0 classes and 0 periods; no Current badge</t>
+        </is>
+      </c>
+      <c r="J417" s="42" t="n"/>
+      <c r="K417" s="42" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L417" s="42" t="n"/>
+      <c r="M417" s="43" t="n"/>
+      <c r="N417" s="42" t="n"/>
+      <c r="O417" s="42" t="n"/>
+    </row>
+    <row r="418" ht="15" customHeight="1" s="24">
+      <c r="A418" s="41" t="inlineStr">
+        <is>
+          <t>AYR-05</t>
+        </is>
+      </c>
+      <c r="B418" s="41" t="inlineStr">
+        <is>
+          <t>Academic Years</t>
+        </is>
+      </c>
+      <c r="C418" s="41" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="D418" s="41" t="inlineStr">
+        <is>
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="E418" s="41" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F418" s="41" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="G418" s="41" t="n"/>
+      <c r="H418" s="41" t="inlineStr">
+        <is>
+          <t>Try: empty name; name over 20 characters; end before start; end equal to start; missing dates</t>
+        </is>
+      </c>
+      <c r="I418" s="41" t="inlineStr">
+        <is>
+          <t>Each refused with a message; nothing saved</t>
+        </is>
+      </c>
+      <c r="J418" s="42" t="n"/>
+      <c r="K418" s="42" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L418" s="42" t="n"/>
+      <c r="M418" s="43" t="n"/>
+      <c r="N418" s="42" t="n"/>
+      <c r="O418" s="42" t="n"/>
+    </row>
+    <row r="419" ht="15" customHeight="1" s="24">
+      <c r="A419" s="41" t="inlineStr">
+        <is>
+          <t>AYR-06</t>
+        </is>
+      </c>
+      <c r="B419" s="41" t="inlineStr">
+        <is>
+          <t>Academic Years</t>
+        </is>
+      </c>
+      <c r="C419" s="41" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="D419" s="41" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E419" s="41" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F419" s="41" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="G419" s="41" t="inlineStr">
+        <is>
+          <t>2026-2027 is 2026-06-01 to 2027-03-31</t>
+        </is>
+      </c>
+      <c r="H419" s="41" t="inlineStr">
+        <is>
+          <t>Add a year starting 2027-03-31</t>
+        </is>
+      </c>
+      <c r="I419" s="41" t="inlineStr">
+        <is>
+          <t>Refused: dates overlap 2026-2027 (a shared date overlaps)</t>
+        </is>
+      </c>
+      <c r="J419" s="42" t="n"/>
+      <c r="K419" s="42" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L419" s="42" t="n"/>
+      <c r="M419" s="43" t="n"/>
+      <c r="N419" s="42" t="n"/>
+      <c r="O419" s="42" t="n"/>
+    </row>
+    <row r="420" ht="15" customHeight="1" s="24">
+      <c r="A420" s="41" t="inlineStr">
+        <is>
+          <t>AYR-07</t>
+        </is>
+      </c>
+      <c r="B420" s="41" t="inlineStr">
+        <is>
+          <t>Academic Years</t>
+        </is>
+      </c>
+      <c r="C420" s="41" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="D420" s="41" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E420" s="41" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F420" s="41" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="G420" s="41" t="inlineStr">
+        <is>
+          <t>2027-2028 exists</t>
+        </is>
+      </c>
+      <c r="H420" s="41" t="inlineStr">
+        <is>
+          <t>Add another year named 2027-2028 (also try lower case) with free dates</t>
+        </is>
+      </c>
+      <c r="I420" s="41" t="inlineStr">
+        <is>
+          <t>Refused: a year with that name already exists</t>
+        </is>
+      </c>
+      <c r="J420" s="42" t="n"/>
+      <c r="K420" s="42" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L420" s="42" t="n"/>
+      <c r="M420" s="43" t="n"/>
+      <c r="N420" s="42" t="n"/>
+      <c r="O420" s="42" t="n"/>
+    </row>
+    <row r="421" ht="15" customHeight="1" s="24">
+      <c r="A421" s="41" t="inlineStr">
+        <is>
+          <t>AYR-08</t>
+        </is>
+      </c>
+      <c r="B421" s="41" t="inlineStr">
+        <is>
+          <t>Academic Years</t>
+        </is>
+      </c>
+      <c r="C421" s="41" t="inlineStr">
+        <is>
+          <t>Edit</t>
+        </is>
+      </c>
+      <c r="D421" s="41" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E421" s="41" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F421" s="41" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="G421" s="41" t="inlineStr">
+        <is>
+          <t>An Upcoming year</t>
+        </is>
+      </c>
+      <c r="H421" s="41" t="inlineStr">
+        <is>
+          <t>Edit name and both dates; save</t>
+        </is>
+      </c>
+      <c r="I421" s="41" t="inlineStr">
+        <is>
+          <t>Saved; table shows the new values</t>
+        </is>
+      </c>
+      <c r="J421" s="42" t="n"/>
+      <c r="K421" s="42" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L421" s="42" t="n"/>
+      <c r="M421" s="43" t="n"/>
+      <c r="N421" s="42" t="n"/>
+      <c r="O421" s="42" t="n"/>
+    </row>
+    <row r="422" ht="15" customHeight="1" s="24">
+      <c r="A422" s="41" t="inlineStr">
+        <is>
+          <t>AYR-09</t>
+        </is>
+      </c>
+      <c r="B422" s="41" t="inlineStr">
+        <is>
+          <t>Academic Years</t>
+        </is>
+      </c>
+      <c r="C422" s="41" t="inlineStr">
+        <is>
+          <t>Edit</t>
+        </is>
+      </c>
+      <c r="D422" s="41" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E422" s="41" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F422" s="41" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="G422" s="41" t="inlineStr">
+        <is>
+          <t>Current year with attendance taken</t>
+        </is>
+      </c>
+      <c r="H422" s="41" t="inlineStr">
+        <is>
+          <t>Edit the current year: try an end date before the last attendance day</t>
+        </is>
+      </c>
+      <c r="I422" s="41" t="inlineStr">
+        <is>
+          <t>Refused: dates must cover every record already saved. Start date field is disabled for a Current year</t>
+        </is>
+      </c>
+      <c r="J422" s="42" t="n"/>
+      <c r="K422" s="42" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L422" s="42" t="n"/>
+      <c r="M422" s="43" t="n"/>
+      <c r="N422" s="42" t="n"/>
+      <c r="O422" s="42" t="n"/>
+    </row>
+    <row r="423" ht="15" customHeight="1" s="24">
+      <c r="A423" s="41" t="inlineStr">
+        <is>
+          <t>AYR-10</t>
+        </is>
+      </c>
+      <c r="B423" s="41" t="inlineStr">
+        <is>
+          <t>Academic Years</t>
+        </is>
+      </c>
+      <c r="C423" s="41" t="inlineStr">
+        <is>
+          <t>Edit</t>
+        </is>
+      </c>
+      <c r="D423" s="41" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E423" s="41" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F423" s="41" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="G423" s="41" t="inlineStr">
+        <is>
+          <t>Same year open in two browser tabs</t>
+        </is>
+      </c>
+      <c r="H423" s="41" t="inlineStr">
+        <is>
+          <t>Save in tab 1, then save in tab 2 without reloading</t>
+        </is>
+      </c>
+      <c r="I423" s="41" t="inlineStr">
+        <is>
+          <t>Tab 2 refused with a conflict message; reload shows tab 1's values</t>
+        </is>
+      </c>
+      <c r="J423" s="42" t="n"/>
+      <c r="K423" s="42" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L423" s="42" t="n"/>
+      <c r="M423" s="43" t="n"/>
+      <c r="N423" s="42" t="n"/>
+      <c r="O423" s="42" t="n"/>
+    </row>
+    <row r="424" ht="15" customHeight="1" s="24">
+      <c r="A424" s="41" t="inlineStr">
+        <is>
+          <t>AYR-11</t>
+        </is>
+      </c>
+      <c r="B424" s="41" t="inlineStr">
+        <is>
+          <t>Academic Years</t>
+        </is>
+      </c>
+      <c r="C424" s="41" t="inlineStr">
+        <is>
+          <t>Set current</t>
+        </is>
+      </c>
+      <c r="D424" s="41" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E424" s="41" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F424" s="41" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="G424" s="41" t="inlineStr">
+        <is>
+          <t>2026-2027 Current, 2027-2028 Upcoming</t>
+        </is>
+      </c>
+      <c r="H424" s="41" t="inlineStr">
+        <is>
+          <t>Click Make current on 2027-2028</t>
+        </is>
+      </c>
+      <c r="I424" s="41" t="inlineStr">
+        <is>
+          <t>Dialog names both years and warns teachers will see the new year. After confirming: 2027-2028 Current, 2026-2027 Ended, exactly one Current</t>
+        </is>
+      </c>
+      <c r="J424" s="42" t="n"/>
+      <c r="K424" s="42" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L424" s="42" t="n"/>
+      <c r="M424" s="43" t="n"/>
+      <c r="N424" s="42" t="n"/>
+      <c r="O424" s="42" t="n"/>
+    </row>
+    <row r="425" ht="15" customHeight="1" s="24">
+      <c r="A425" s="41" t="inlineStr">
+        <is>
+          <t>AYR-12</t>
+        </is>
+      </c>
+      <c r="B425" s="41" t="inlineStr">
+        <is>
+          <t>Academic Years</t>
+        </is>
+      </c>
+      <c r="C425" s="41" t="inlineStr">
+        <is>
+          <t>Set current</t>
+        </is>
+      </c>
+      <c r="D425" s="41" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="E425" s="41" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F425" s="41" t="inlineStr">
+        <is>
+          <t>Teacher</t>
+        </is>
+      </c>
+      <c r="G425" s="41" t="inlineStr">
+        <is>
+          <t>zt.teacher1 is class teacher of a class in 2026-2027</t>
+        </is>
+      </c>
+      <c r="H425" s="41" t="inlineStr">
+        <is>
+          <t>After the switch, log in as zt.teacher1 and open Students and Attendance</t>
+        </is>
+      </c>
+      <c r="I425" s="41" t="inlineStr">
+        <is>
+          <t>Teacher sees nothing from 2026-2027 (new year is empty) until classes exist in 2027-2028. Switching back restores the view</t>
+        </is>
+      </c>
+      <c r="J425" s="42" t="n"/>
+      <c r="K425" s="42" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L425" s="42" t="n"/>
+      <c r="M425" s="43" t="n"/>
+      <c r="N425" s="42" t="n"/>
+      <c r="O425" s="42" t="n"/>
+    </row>
+    <row r="426" ht="15" customHeight="1" s="24">
+      <c r="A426" s="41" t="inlineStr">
+        <is>
+          <t>AYR-13</t>
+        </is>
+      </c>
+      <c r="B426" s="41" t="inlineStr">
+        <is>
+          <t>Academic Years</t>
+        </is>
+      </c>
+      <c r="C426" s="41" t="inlineStr">
+        <is>
+          <t>Set current</t>
+        </is>
+      </c>
+      <c r="D426" s="41" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E426" s="41" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F426" s="41" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="G426" s="41" t="inlineStr">
+        <is>
+          <t>An Ended year and a Closed year</t>
+        </is>
+      </c>
+      <c r="H426" s="41" t="inlineStr">
+        <is>
+          <t>Look for Make current on them; call POST set-current in Swagger</t>
+        </is>
+      </c>
+      <c r="I426" s="41" t="inlineStr">
+        <is>
+          <t>No button; API answers 409 (only an Upcoming year can be made current)</t>
+        </is>
+      </c>
+      <c r="J426" s="42" t="n"/>
+      <c r="K426" s="42" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L426" s="42" t="n"/>
+      <c r="M426" s="43" t="n"/>
+      <c r="N426" s="42" t="n"/>
+      <c r="O426" s="42" t="n"/>
+    </row>
+    <row r="427" ht="15" customHeight="1" s="24">
+      <c r="A427" s="41" t="inlineStr">
+        <is>
+          <t>AYR-14</t>
+        </is>
+      </c>
+      <c r="B427" s="41" t="inlineStr">
+        <is>
+          <t>Academic Years</t>
+        </is>
+      </c>
+      <c r="C427" s="41" t="inlineStr">
+        <is>
+          <t>Set current</t>
+        </is>
+      </c>
+      <c r="D427" s="41" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E427" s="41" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F427" s="41" t="inlineStr">
+        <is>
+          <t>Two Admins</t>
+        </is>
+      </c>
+      <c r="G427" s="41" t="inlineStr">
+        <is>
+          <t>Two browsers, two Upcoming years</t>
+        </is>
+      </c>
+      <c r="H427" s="41" t="inlineStr">
+        <is>
+          <t>Both click Make current on different years at the same moment</t>
+        </is>
+      </c>
+      <c r="I427" s="41" t="inlineStr">
+        <is>
+          <t>Exactly one succeeds; the other gets a message that the current year changed. One Current year only</t>
+        </is>
+      </c>
+      <c r="J427" s="42" t="n"/>
+      <c r="K427" s="42" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L427" s="42" t="n"/>
+      <c r="M427" s="43" t="n"/>
+      <c r="N427" s="42" t="n"/>
+      <c r="O427" s="42" t="n"/>
+    </row>
+    <row r="428" ht="15" customHeight="1" s="24">
+      <c r="A428" s="41" t="inlineStr">
+        <is>
+          <t>AYR-15</t>
+        </is>
+      </c>
+      <c r="B428" s="41" t="inlineStr">
+        <is>
+          <t>Academic Years</t>
+        </is>
+      </c>
+      <c r="C428" s="41" t="inlineStr">
+        <is>
+          <t>Set current</t>
+        </is>
+      </c>
+      <c r="D428" s="41" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E428" s="41" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F428" s="41" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="G428" s="41" t="inlineStr">
+        <is>
+          <t>New classes</t>
+        </is>
+      </c>
+      <c r="H428" s="41" t="inlineStr">
+        <is>
+          <t>After a switch, create a class without choosing a year; open the Timetable</t>
+        </is>
+      </c>
+      <c r="I428" s="41" t="inlineStr">
+        <is>
+          <t>The class and the Timetable default to the new current year</t>
+        </is>
+      </c>
+      <c r="J428" s="42" t="n"/>
+      <c r="K428" s="42" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L428" s="42" t="n"/>
+      <c r="M428" s="43" t="n"/>
+      <c r="N428" s="42" t="n"/>
+      <c r="O428" s="42" t="n"/>
+    </row>
+    <row r="429" ht="15" customHeight="1" s="24">
+      <c r="A429" s="41" t="inlineStr">
+        <is>
+          <t>AYR-16</t>
+        </is>
+      </c>
+      <c r="B429" s="41" t="inlineStr">
+        <is>
+          <t>Academic Years</t>
+        </is>
+      </c>
+      <c r="C429" s="41" t="inlineStr">
+        <is>
+          <t>Close</t>
+        </is>
+      </c>
+      <c r="D429" s="41" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E429" s="41" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F429" s="41" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="G429" s="41" t="inlineStr">
+        <is>
+          <t>The current year</t>
+        </is>
+      </c>
+      <c r="H429" s="41" t="inlineStr">
+        <is>
+          <t>Look for Close on the Current year</t>
+        </is>
+      </c>
+      <c r="I429" s="41" t="inlineStr">
+        <is>
+          <t>No Close button; API answers 409 (make another year current first)</t>
+        </is>
+      </c>
+      <c r="J429" s="42" t="n"/>
+      <c r="K429" s="42" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L429" s="42" t="n"/>
+      <c r="M429" s="43" t="n"/>
+      <c r="N429" s="42" t="n"/>
+      <c r="O429" s="42" t="n"/>
+    </row>
+    <row r="430" ht="15" customHeight="1" s="24">
+      <c r="A430" s="41" t="inlineStr">
+        <is>
+          <t>AYR-17</t>
+        </is>
+      </c>
+      <c r="B430" s="41" t="inlineStr">
+        <is>
+          <t>Academic Years</t>
+        </is>
+      </c>
+      <c r="C430" s="41" t="inlineStr">
+        <is>
+          <t>Close</t>
+        </is>
+      </c>
+      <c r="D430" s="41" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E430" s="41" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F430" s="41" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="G430" s="41" t="inlineStr">
+        <is>
+          <t>An Ended year with no Active students</t>
+        </is>
+      </c>
+      <c r="H430" s="41" t="inlineStr">
+        <is>
+          <t>Click Close, type the wrong name, then the exact name</t>
+        </is>
+      </c>
+      <c r="I430" s="41" t="inlineStr">
+        <is>
+          <t>Button stays disabled until the name matches exactly; then the year is Closed and read-only</t>
+        </is>
+      </c>
+      <c r="J430" s="42" t="n"/>
+      <c r="K430" s="42" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L430" s="42" t="n"/>
+      <c r="M430" s="43" t="n"/>
+      <c r="N430" s="42" t="n"/>
+      <c r="O430" s="42" t="n"/>
+    </row>
+    <row r="431" ht="15" customHeight="1" s="24">
+      <c r="A431" s="41" t="inlineStr">
+        <is>
+          <t>AYR-18</t>
+        </is>
+      </c>
+      <c r="B431" s="41" t="inlineStr">
+        <is>
+          <t>Academic Years</t>
+        </is>
+      </c>
+      <c r="C431" s="41" t="inlineStr">
+        <is>
+          <t>Close</t>
+        </is>
+      </c>
+      <c r="D431" s="41" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E431" s="41" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F431" s="41" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="G431" s="41" t="inlineStr">
+        <is>
+          <t>An Ended year with an Active student</t>
+        </is>
+      </c>
+      <c r="H431" s="41" t="inlineStr">
+        <is>
+          <t>Click Close</t>
+        </is>
+      </c>
+      <c r="I431" s="41" t="inlineStr">
+        <is>
+          <t>Dialog says N students are still Active; Close is not possible until they are promoted, repeated or transferred</t>
+        </is>
+      </c>
+      <c r="J431" s="42" t="n"/>
+      <c r="K431" s="42" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L431" s="42" t="n"/>
+      <c r="M431" s="43" t="n"/>
+      <c r="N431" s="42" t="n"/>
+      <c r="O431" s="42" t="n"/>
+    </row>
+    <row r="432" ht="15" customHeight="1" s="24">
+      <c r="A432" s="41" t="inlineStr">
+        <is>
+          <t>AYR-19</t>
+        </is>
+      </c>
+      <c r="B432" s="41" t="inlineStr">
+        <is>
+          <t>Academic Years</t>
+        </is>
+      </c>
+      <c r="C432" s="41" t="inlineStr">
+        <is>
+          <t>Close</t>
+        </is>
+      </c>
+      <c r="D432" s="41" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E432" s="41" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F432" s="41" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="G432" s="41" t="inlineStr">
+        <is>
+          <t>A Closed year</t>
+        </is>
+      </c>
+      <c r="H432" s="41" t="inlineStr">
+        <is>
+          <t>Try to edit it, add a class to it, add a period or lesson to it</t>
+        </is>
+      </c>
+      <c r="I432" s="41" t="inlineStr">
+        <is>
+          <t>All refused (409: closed and read-only). No Edit button on the row</t>
+        </is>
+      </c>
+      <c r="J432" s="42" t="n"/>
+      <c r="K432" s="42" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L432" s="42" t="n"/>
+      <c r="M432" s="43" t="n"/>
+      <c r="N432" s="42" t="n"/>
+      <c r="O432" s="42" t="n"/>
+    </row>
+    <row r="433" ht="15" customHeight="1" s="24">
+      <c r="A433" s="41" t="inlineStr">
+        <is>
+          <t>AYR-20</t>
+        </is>
+      </c>
+      <c r="B433" s="41" t="inlineStr">
+        <is>
+          <t>Academic Years</t>
+        </is>
+      </c>
+      <c r="C433" s="41" t="inlineStr">
+        <is>
+          <t>Delete</t>
+        </is>
+      </c>
+      <c r="D433" s="41" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E433" s="41" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F433" s="41" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="G433" s="41" t="inlineStr">
+        <is>
+          <t>An Upcoming year with no classes or periods</t>
+        </is>
+      </c>
+      <c r="H433" s="41" t="inlineStr">
+        <is>
+          <t>Delete it and confirm</t>
+        </is>
+      </c>
+      <c r="I433" s="41" t="inlineStr">
+        <is>
+          <t>Removed; its name can be used again</t>
+        </is>
+      </c>
+      <c r="J433" s="42" t="n"/>
+      <c r="K433" s="42" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L433" s="42" t="n"/>
+      <c r="M433" s="43" t="n"/>
+      <c r="N433" s="42" t="n"/>
+      <c r="O433" s="42" t="n"/>
+    </row>
+    <row r="434" ht="15" customHeight="1" s="24">
+      <c r="A434" s="41" t="inlineStr">
+        <is>
+          <t>AYR-21</t>
+        </is>
+      </c>
+      <c r="B434" s="41" t="inlineStr">
+        <is>
+          <t>Academic Years</t>
+        </is>
+      </c>
+      <c r="C434" s="41" t="inlineStr">
+        <is>
+          <t>Delete</t>
+        </is>
+      </c>
+      <c r="D434" s="41" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E434" s="41" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F434" s="41" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="G434" s="41" t="inlineStr">
+        <is>
+          <t>Upcoming year with a class or a period; an Ended year</t>
+        </is>
+      </c>
+      <c r="H434" s="41" t="inlineStr">
+        <is>
+          <t>Look for Delete on those rows; call DELETE in Swagger</t>
+        </is>
+      </c>
+      <c r="I434" s="41" t="inlineStr">
+        <is>
+          <t>No Delete button; API answers 409</t>
+        </is>
+      </c>
+      <c r="J434" s="42" t="n"/>
+      <c r="K434" s="42" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L434" s="42" t="n"/>
+      <c r="M434" s="43" t="n"/>
+      <c r="N434" s="42" t="n"/>
+      <c r="O434" s="42" t="n"/>
+    </row>
+    <row r="435" ht="15" customHeight="1" s="24">
+      <c r="A435" s="41" t="inlineStr">
+        <is>
+          <t>AYR-22</t>
+        </is>
+      </c>
+      <c r="B435" s="41" t="inlineStr">
+        <is>
+          <t>Academic Years</t>
+        </is>
+      </c>
+      <c r="C435" s="41" t="inlineStr">
+        <is>
+          <t>Copy periods</t>
+        </is>
+      </c>
+      <c r="D435" s="41" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E435" s="41" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F435" s="41" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="G435" s="41" t="inlineStr">
+        <is>
+          <t>2026-2027 has periods; 2027-2028 Upcoming with none</t>
+        </is>
+      </c>
+      <c r="H435" s="41" t="inlineStr">
+        <is>
+          <t>Click Copy periods on 2027-2028; choose 2026-2027</t>
+        </is>
+      </c>
+      <c r="I435" s="41" t="inlineStr">
+        <is>
+          <t>Periods (names, times, breaks, order) copied; Periods column shows the same count; lessons are not copied</t>
+        </is>
+      </c>
+      <c r="J435" s="42" t="n"/>
+      <c r="K435" s="42" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L435" s="42" t="n"/>
+      <c r="M435" s="43" t="n"/>
+      <c r="N435" s="42" t="n"/>
+      <c r="O435" s="42" t="n"/>
+    </row>
+    <row r="436" ht="15" customHeight="1" s="24">
+      <c r="A436" s="41" t="inlineStr">
+        <is>
+          <t>AYR-23</t>
+        </is>
+      </c>
+      <c r="B436" s="41" t="inlineStr">
+        <is>
+          <t>Academic Years</t>
+        </is>
+      </c>
+      <c r="C436" s="41" t="inlineStr">
+        <is>
+          <t>Copy periods</t>
+        </is>
+      </c>
+      <c r="D436" s="41" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E436" s="41" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F436" s="41" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="G436" s="41" t="inlineStr">
+        <is>
+          <t>Target year already has periods</t>
+        </is>
+      </c>
+      <c r="H436" s="41" t="inlineStr">
+        <is>
+          <t>Open Copy periods on it</t>
+        </is>
+      </c>
+      <c r="I436" s="41" t="inlineStr">
+        <is>
+          <t>Notice says it already has periods; copying never merges; button disabled</t>
+        </is>
+      </c>
+      <c r="J436" s="42" t="n"/>
+      <c r="K436" s="42" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L436" s="42" t="n"/>
+      <c r="M436" s="43" t="n"/>
+      <c r="N436" s="42" t="n"/>
+      <c r="O436" s="42" t="n"/>
+    </row>
+    <row r="437" ht="15" customHeight="1" s="24">
+      <c r="A437" s="41" t="inlineStr">
+        <is>
+          <t>AYR-24</t>
+        </is>
+      </c>
+      <c r="B437" s="41" t="inlineStr">
+        <is>
+          <t>Academic Years</t>
+        </is>
+      </c>
+      <c r="C437" s="41" t="inlineStr">
+        <is>
+          <t>Copy periods</t>
+        </is>
+      </c>
+      <c r="D437" s="41" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E437" s="41" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F437" s="41" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="G437" s="41" t="inlineStr">
+        <is>
+          <t>Swagger</t>
+        </is>
+      </c>
+      <c r="H437" s="41" t="inlineStr">
+        <is>
+          <t>Copy a year into itself; copy from a year with no periods; copy into a Closed year</t>
+        </is>
+      </c>
+      <c r="I437" s="41" t="inlineStr">
+        <is>
+          <t>422, 422 and 409</t>
+        </is>
+      </c>
+      <c r="J437" s="42" t="n"/>
+      <c r="K437" s="42" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L437" s="42" t="n"/>
+      <c r="M437" s="43" t="n"/>
+      <c r="N437" s="42" t="n"/>
+      <c r="O437" s="42" t="n"/>
+    </row>
+    <row r="438" ht="15" customHeight="1" s="24">
+      <c r="A438" s="41" t="inlineStr">
+        <is>
+          <t>AYR-25</t>
+        </is>
+      </c>
+      <c r="B438" s="41" t="inlineStr">
+        <is>
+          <t>Academic Years</t>
+        </is>
+      </c>
+      <c r="C438" s="41" t="inlineStr">
+        <is>
+          <t>Permissions</t>
+        </is>
+      </c>
+      <c r="D438" s="41" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="E438" s="41" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F438" s="41" t="inlineStr">
+        <is>
+          <t>Role with AcademicYears.View only</t>
+        </is>
+      </c>
+      <c r="G438" s="41" t="inlineStr">
+        <is>
+          <t>Custom role 'ZT YearsView'</t>
+        </is>
+      </c>
+      <c r="H438" s="41" t="inlineStr">
+        <is>
+          <t>Open Academic Years</t>
+        </is>
+      </c>
+      <c r="I438" s="41" t="inlineStr">
+        <is>
+          <t>Page lists years but shows no Add, Edit, Make current, Copy, Close or Delete</t>
+        </is>
+      </c>
+      <c r="J438" s="42" t="n"/>
+      <c r="K438" s="42" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L438" s="42" t="n"/>
+      <c r="M438" s="43" t="n"/>
+      <c r="N438" s="42" t="n"/>
+      <c r="O438" s="42" t="n"/>
+    </row>
+    <row r="439" ht="15" customHeight="1" s="24">
+      <c r="A439" s="41" t="inlineStr">
+        <is>
+          <t>AYR-26</t>
+        </is>
+      </c>
+      <c r="B439" s="41" t="inlineStr">
+        <is>
+          <t>Academic Years</t>
+        </is>
+      </c>
+      <c r="C439" s="41" t="inlineStr">
+        <is>
+          <t>Permissions</t>
+        </is>
+      </c>
+      <c r="D439" s="41" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="E439" s="41" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F439" s="41" t="inlineStr">
+        <is>
+          <t>Role with AcademicYears.Edit but not View</t>
+        </is>
+      </c>
+      <c r="G439" s="41" t="inlineStr">
+        <is>
+          <t>Roles page</t>
+        </is>
+      </c>
+      <c r="H439" s="41" t="inlineStr">
+        <is>
+          <t>Try to save the role</t>
+        </is>
+      </c>
+      <c r="I439" s="41" t="inlineStr">
+        <is>
+          <t>Refused: AcademicYears.Edit needs AcademicYears.View</t>
+        </is>
+      </c>
+      <c r="J439" s="42" t="n"/>
+      <c r="K439" s="42" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L439" s="42" t="n"/>
+      <c r="M439" s="43" t="n"/>
+      <c r="N439" s="42" t="n"/>
+      <c r="O439" s="42" t="n"/>
+    </row>
+    <row r="440" ht="15" customHeight="1" s="24">
+      <c r="A440" s="41" t="inlineStr">
+        <is>
+          <t>AYR-27</t>
+        </is>
+      </c>
+      <c r="B440" s="41" t="inlineStr">
+        <is>
+          <t>Academic Years</t>
+        </is>
+      </c>
+      <c r="C440" s="41" t="inlineStr">
+        <is>
+          <t>Permissions</t>
+        </is>
+      </c>
+      <c r="D440" s="41" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="E440" s="41" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F440" s="41" t="inlineStr">
+        <is>
+          <t>Role without AcademicYears.SetCurrent</t>
+        </is>
+      </c>
+      <c r="G440" s="41" t="inlineStr">
+        <is>
+          <t>Custom role with View + Edit</t>
+        </is>
+      </c>
+      <c r="H440" s="41" t="inlineStr">
+        <is>
+          <t>Call POST /academic-years/{id}/set-current</t>
+        </is>
+      </c>
+      <c r="I440" s="41" t="inlineStr">
+        <is>
+          <t>403</t>
+        </is>
+      </c>
+      <c r="J440" s="42" t="n"/>
+      <c r="K440" s="42" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L440" s="42" t="n"/>
+      <c r="M440" s="43" t="n"/>
+      <c r="N440" s="42" t="n"/>
+      <c r="O440" s="42" t="n"/>
+    </row>
+    <row r="441" ht="15" customHeight="1" s="24">
+      <c r="A441" s="41" t="inlineStr">
+        <is>
+          <t>AYR-28</t>
+        </is>
+      </c>
+      <c r="B441" s="41" t="inlineStr">
+        <is>
+          <t>Academic Years</t>
+        </is>
+      </c>
+      <c r="C441" s="41" t="inlineStr">
+        <is>
+          <t>Audit</t>
+        </is>
+      </c>
+      <c r="D441" s="41" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E441" s="41" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F441" s="41" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="G441" s="41" t="inlineStr">
+        <is>
+          <t>A Set current was done</t>
+        </is>
+      </c>
+      <c r="H441" s="41" t="inlineStr">
+        <is>
+          <t>Check the AuditLogs table (or the audit view) for both years</t>
+        </is>
+      </c>
+      <c r="I441" s="41" t="inlineStr">
+        <is>
+          <t>One Update row for the old year (status to Ended) and one for the new year (status to Current)</t>
+        </is>
+      </c>
+      <c r="J441" s="42" t="n"/>
+      <c r="K441" s="42" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L441" s="42" t="n"/>
+      <c r="M441" s="43" t="n"/>
+      <c r="N441" s="42" t="n"/>
+      <c r="O441" s="42" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O413"/>
-  <conditionalFormatting sqref="K2:K413">
+  <autoFilter ref="A1:O441"/>
+  <conditionalFormatting sqref="K2:K441">
     <cfRule type="cellIs" rank="0" priority="2" equalAverage="0" operator="equal" aboveAverage="0" dxfId="6" text="" percent="0" bottom="0">
       <formula>"Pass"</formula>
     </cfRule>
@@ -24824,17 +26452,17 @@
       <formula>"Not Run"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2:E413">
+  <conditionalFormatting sqref="A2:E441">
     <cfRule type="expression" rank="0" priority="6" equalAverage="0" aboveAverage="0" dxfId="10" text="" percent="0" bottom="0">
       <formula>$E2="High"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="K2:K413" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list" errorStyle="stop" operator="between">
+    <dataValidation sqref="K2:K441" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list" errorStyle="stop" operator="between">
       <formula1>"Not Run,Pass,Fail,Blocked,N/A"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation sqref="M2:M413" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Enter a date" type="date" errorStyle="stop" operator="greaterThan">
+    <dataValidation sqref="M2:M441" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Enter a date" type="date" errorStyle="stop" operator="greaterThan">
       <formula1>36526</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -24851,7 +26479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:D28"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="22" customWidth="1" style="23" min="1" max="1"/>
@@ -25333,6 +26961,50 @@
       <c r="D26" s="41" t="inlineStr">
         <is>
           <t>TIM-21 to TIM-23 and Copy From cases need the same teacher in both classes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="41" t="inlineStr">
+        <is>
+          <t>Academic years</t>
+        </is>
+      </c>
+      <c r="B27" s="41" t="inlineStr">
+        <is>
+          <t>2027-2028: 2027-06-01 to 2028-03-31 (Upcoming); a second Upcoming year with free dates</t>
+        </is>
+      </c>
+      <c r="C27" s="41" t="inlineStr">
+        <is>
+          <t>Academic Years page</t>
+        </is>
+      </c>
+      <c r="D27" s="41" t="inlineStr">
+        <is>
+          <t>For all AYR cases. Do not edit the seeded 2026-2027 dates. Put the current year back to 2026-2027 after the Set current cases.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="41" t="inlineStr">
+        <is>
+          <t>Role</t>
+        </is>
+      </c>
+      <c r="B28" s="41" t="inlineStr">
+        <is>
+          <t>Custom role 'ZT YearsView'</t>
+        </is>
+      </c>
+      <c r="C28" s="41" t="inlineStr">
+        <is>
+          <t>AcademicYears.View only</t>
+        </is>
+      </c>
+      <c r="D28" s="41" t="inlineStr">
+        <is>
+          <t>Used by the Permissions cases.</t>
         </is>
       </c>
     </row>
